--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
@@ -54554,22 +54554,22 @@
         <v>2.94</v>
       </c>
       <c r="AU248" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AV248" t="n">
         <v>3</v>
       </c>
       <c r="AW248" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AX248" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY248" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AZ248" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA248" t="n">
         <v>5</v>
@@ -54993,19 +54993,19 @@
         <v>4</v>
       </c>
       <c r="AV250" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AW250" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AX250" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY250" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ250" t="n">
         <v>13</v>
-      </c>
-      <c r="AZ250" t="n">
-        <v>15</v>
       </c>
       <c r="BA250" t="n">
         <v>9</v>
@@ -55208,31 +55208,31 @@
         <v>2.41</v>
       </c>
       <c r="AU251" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AV251" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AW251" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AX251" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AY251" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="AZ251" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="BA251" t="n">
         <v>7</v>
       </c>
       <c r="BB251" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BC251" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD251" t="n">
         <v>1.65</v>
@@ -55426,22 +55426,22 @@
         <v>3.52</v>
       </c>
       <c r="AU252" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV252" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AW252" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AX252" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AY252" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AZ252" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="BA252" t="n">
         <v>3</v>
@@ -55644,19 +55644,19 @@
         <v>3.11</v>
       </c>
       <c r="AU253" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AV253" t="n">
         <v>3</v>
       </c>
       <c r="AW253" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="AX253" t="n">
         <v>3</v>
       </c>
       <c r="AY253" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AZ253" t="n">
         <v>6</v>
@@ -55865,16 +55865,16 @@
         <v>7</v>
       </c>
       <c r="AV254" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW254" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AX254" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY254" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AZ254" t="n">
         <v>8</v>
@@ -56080,22 +56080,22 @@
         <v>3</v>
       </c>
       <c r="AU255" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AV255" t="n">
         <v>7</v>
       </c>
       <c r="AW255" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AX255" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AY255" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AZ255" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BA255" t="n">
         <v>8</v>
@@ -56304,16 +56304,16 @@
         <v>7</v>
       </c>
       <c r="AW256" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AX256" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AY256" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AZ256" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="BA256" t="n">
         <v>4</v>
@@ -56516,22 +56516,22 @@
         <v>3.5</v>
       </c>
       <c r="AU257" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AV257" t="n">
         <v>4</v>
       </c>
       <c r="AW257" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AX257" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AY257" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AZ257" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BA257" t="n">
         <v>4</v>
@@ -56734,22 +56734,22 @@
         <v>2.98</v>
       </c>
       <c r="AU258" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV258" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AW258" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AX258" t="n">
         <v>2</v>
       </c>
       <c r="AY258" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AZ258" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="BA258" t="n">
         <v>8</v>
@@ -56955,16 +56955,16 @@
         <v>10</v>
       </c>
       <c r="AV259" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW259" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX259" t="n">
         <v>3</v>
       </c>
-      <c r="AW259" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX259" t="n">
-        <v>4</v>
-      </c>
       <c r="AY259" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AZ259" t="n">
         <v>7</v>
@@ -57173,19 +57173,19 @@
         <v>7</v>
       </c>
       <c r="AV260" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AW260" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AX260" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AY260" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AZ260" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="BA260" t="n">
         <v>3</v>
@@ -57391,19 +57391,19 @@
         <v>6</v>
       </c>
       <c r="AV261" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AW261" t="n">
         <v>4</v>
       </c>
       <c r="AX261" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AY261" t="n">
         <v>10</v>
       </c>
       <c r="AZ261" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA261" t="n">
         <v>6</v>
@@ -57606,22 +57606,22 @@
         <v>3.08</v>
       </c>
       <c r="AU262" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV262" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AW262" t="n">
         <v>8</v>
       </c>
       <c r="AX262" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AY262" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ262" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="BA262" t="n">
         <v>7</v>
@@ -58042,22 +58042,22 @@
         <v>2.84</v>
       </c>
       <c r="AU264" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AV264" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AW264" t="n">
         <v>0</v>
       </c>
       <c r="AX264" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AY264" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AZ264" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="BA264" t="n">
         <v>2</v>
@@ -58263,16 +58263,16 @@
         <v>3</v>
       </c>
       <c r="AV265" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW265" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AX265" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY265" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AZ265" t="n">
         <v>8</v>
@@ -58478,22 +58478,22 @@
         <v>3.1</v>
       </c>
       <c r="AU266" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AV266" t="n">
         <v>2</v>
       </c>
       <c r="AW266" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX266" t="n">
         <v>6</v>
       </c>
-      <c r="AX266" t="n">
-        <v>3</v>
-      </c>
       <c r="AY266" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="AZ266" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BA266" t="n">
         <v>10</v>
@@ -58687,31 +58687,31 @@
         <v>0.36</v>
       </c>
       <c r="AR267" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AS267" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="AT267" t="n">
-        <v>3.24</v>
+        <v>3.19</v>
       </c>
       <c r="AU267" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV267" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW267" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX267" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AY267" t="n">
         <v>16</v>
       </c>
       <c r="AZ267" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BA267" t="n">
         <v>7</v>
@@ -58908,28 +58908,28 @@
         <v>1.55</v>
       </c>
       <c r="AS268" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AT268" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="AU268" t="n">
         <v>5</v>
       </c>
       <c r="AV268" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW268" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX268" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY268" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ268" t="n">
         <v>12</v>
-      </c>
-      <c r="AW268" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX268" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY268" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ268" t="n">
-        <v>14</v>
       </c>
       <c r="BA268" t="n">
         <v>3</v>
@@ -59123,13 +59123,13 @@
         <v>1.58</v>
       </c>
       <c r="AR269" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AS269" t="n">
         <v>1.6</v>
       </c>
       <c r="AT269" t="n">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="AU269" t="n">
         <v>5</v>
@@ -59344,28 +59344,28 @@
         <v>1.42</v>
       </c>
       <c r="AS270" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AT270" t="n">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="AU270" t="n">
         <v>3</v>
       </c>
       <c r="AV270" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AW270" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AX270" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY270" t="n">
         <v>3</v>
       </c>
-      <c r="AY270" t="n">
-        <v>11</v>
-      </c>
       <c r="AZ270" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="BA270" t="n">
         <v>4</v>
@@ -59559,31 +59559,31 @@
         <v>1.18</v>
       </c>
       <c r="AR271" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AS271" t="n">
         <v>1.14</v>
       </c>
       <c r="AT271" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="AU271" t="n">
         <v>5</v>
       </c>
       <c r="AV271" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW271" t="n">
         <v>3</v>
       </c>
-      <c r="AW271" t="n">
-        <v>4</v>
-      </c>
       <c r="AX271" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AY271" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ271" t="n">
         <v>9</v>
-      </c>
-      <c r="AZ271" t="n">
-        <v>8</v>
       </c>
       <c r="BA271" t="n">
         <v>6</v>
@@ -59777,31 +59777,31 @@
         <v>1.77</v>
       </c>
       <c r="AR272" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AS272" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AT272" t="n">
-        <v>3.1</v>
+        <v>3.03</v>
       </c>
       <c r="AU272" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AV272" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AW272" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AX272" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY272" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AZ272" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="BA272" t="n">
         <v>5</v>
@@ -59995,16 +59995,16 @@
         <v>0.77</v>
       </c>
       <c r="AR273" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AS273" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AT273" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="AU273" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AV273" t="n">
         <v>6</v>
@@ -60013,13 +60013,13 @@
         <v>10</v>
       </c>
       <c r="AX273" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY273" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AZ273" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA273" t="n">
         <v>5</v>
@@ -60225,19 +60225,19 @@
         <v>3</v>
       </c>
       <c r="AV274" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AW274" t="n">
         <v>7</v>
       </c>
       <c r="AX274" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY274" t="n">
         <v>10</v>
       </c>
       <c r="AZ274" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BA274" t="n">
         <v>1</v>
@@ -60443,19 +60443,19 @@
         <v>9</v>
       </c>
       <c r="AV275" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AW275" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AX275" t="n">
         <v>6</v>
       </c>
       <c r="AY275" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AZ275" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="BA275" t="n">
         <v>0</v>
@@ -60649,16 +60649,16 @@
         <v>1.91</v>
       </c>
       <c r="AR276" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AS276" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AT276" t="n">
-        <v>3.68</v>
+        <v>3.72</v>
       </c>
       <c r="AU276" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV276" t="n">
         <v>9</v>
@@ -60670,7 +60670,7 @@
         <v>1</v>
       </c>
       <c r="AY276" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ276" t="n">
         <v>10</v>
@@ -60867,31 +60867,31 @@
         <v>0.38</v>
       </c>
       <c r="AR277" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AS277" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AT277" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="AU277" t="n">
         <v>5</v>
       </c>
       <c r="AV277" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AW277" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX277" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY277" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ277" t="n">
         <v>3</v>
-      </c>
-      <c r="AX277" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY277" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ277" t="n">
-        <v>9</v>
       </c>
       <c r="BA277" t="n">
         <v>0</v>
@@ -61088,10 +61088,10 @@
         <v>1.92</v>
       </c>
       <c r="AS278" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AT278" t="n">
-        <v>3.57</v>
+        <v>3.58</v>
       </c>
       <c r="AU278" t="n">
         <v>4</v>
@@ -61100,25 +61100,25 @@
         <v>5</v>
       </c>
       <c r="AW278" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AX278" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY278" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ278" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA278" t="n">
         <v>3</v>
-      </c>
-      <c r="AY278" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ278" t="n">
-        <v>8</v>
-      </c>
-      <c r="BA278" t="n">
-        <v>4</v>
       </c>
       <c r="BB278" t="n">
         <v>2</v>
       </c>
       <c r="BC278" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD278" t="n">
         <v>1.68</v>
@@ -61303,31 +61303,31 @@
         <v>1.27</v>
       </c>
       <c r="AR279" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AS279" t="n">
         <v>1.51</v>
       </c>
       <c r="AT279" t="n">
-        <v>2.93</v>
+        <v>2.81</v>
       </c>
       <c r="AU279" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV279" t="n">
         <v>0</v>
       </c>
       <c r="AW279" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AX279" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AY279" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ279" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="BA279" t="n">
         <v>9</v>
@@ -61536,16 +61536,16 @@
         <v>3</v>
       </c>
       <c r="AW280" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AX280" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AY280" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AZ280" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BA280" t="n">
         <v>6</v>
@@ -61739,13 +61739,13 @@
         <v>1.08</v>
       </c>
       <c r="AR281" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AS281" t="n">
         <v>1.26</v>
       </c>
       <c r="AT281" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="AU281" t="n">
         <v>7</v>
@@ -61754,16 +61754,16 @@
         <v>3</v>
       </c>
       <c r="AW281" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AX281" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AY281" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ281" t="n">
         <v>10</v>
-      </c>
-      <c r="AZ281" t="n">
-        <v>7</v>
       </c>
       <c r="BA281" t="n">
         <v>5</v>
@@ -62175,13 +62175,13 @@
         <v>0.77</v>
       </c>
       <c r="AR283" t="n">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="AS283" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AT283" t="n">
-        <v>2.82</v>
+        <v>2.79</v>
       </c>
       <c r="AU283" t="n">
         <v>6</v>
@@ -62190,16 +62190,16 @@
         <v>3</v>
       </c>
       <c r="AW283" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AX283" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY283" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AZ283" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA283" t="n">
         <v>3</v>
@@ -62393,31 +62393,31 @@
         <v>1.91</v>
       </c>
       <c r="AR284" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AS284" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AT284" t="n">
-        <v>2.89</v>
+        <v>2.99</v>
       </c>
       <c r="AU284" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV284" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW284" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AX284" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AY284" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AZ284" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="BA284" t="n">
         <v>5</v>
@@ -62611,13 +62611,13 @@
         <v>0.42</v>
       </c>
       <c r="AR285" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AS285" t="n">
         <v>1.17</v>
       </c>
       <c r="AT285" t="n">
-        <v>2.89</v>
+        <v>2.84</v>
       </c>
       <c r="AU285" t="n">
         <v>7</v>
@@ -62629,13 +62629,13 @@
         <v>9</v>
       </c>
       <c r="AX285" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AY285" t="n">
         <v>16</v>
       </c>
       <c r="AZ285" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="BA285" t="n">
         <v>7</v>
@@ -62829,31 +62829,31 @@
         <v>1</v>
       </c>
       <c r="AR286" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AS286" t="n">
         <v>1.57</v>
       </c>
       <c r="AT286" t="n">
-        <v>3.18</v>
+        <v>3.21</v>
       </c>
       <c r="AU286" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV286" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW286" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AX286" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AY286" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AZ286" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BA286" t="n">
         <v>6</v>
@@ -63050,28 +63050,28 @@
         <v>2.04</v>
       </c>
       <c r="AS287" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AT287" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="AU287" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV287" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW287" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AX287" t="n">
         <v>6</v>
       </c>
       <c r="AY287" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ287" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA287" t="n">
         <v>3</v>
@@ -63268,10 +63268,10 @@
         <v>1.85</v>
       </c>
       <c r="AS288" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AT288" t="n">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="AU288" t="n">
         <v>7</v>
@@ -63280,16 +63280,16 @@
         <v>2</v>
       </c>
       <c r="AW288" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AX288" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AY288" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AZ288" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="BA288" t="n">
         <v>3</v>
@@ -63483,31 +63483,31 @@
         <v>1.67</v>
       </c>
       <c r="AR289" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AS289" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AT289" t="n">
-        <v>3.6</v>
+        <v>3.49</v>
       </c>
       <c r="AU289" t="n">
         <v>4</v>
       </c>
       <c r="AV289" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW289" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AX289" t="n">
         <v>6</v>
       </c>
       <c r="AY289" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AZ289" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BA289" t="n">
         <v>2</v>
@@ -63701,31 +63701,31 @@
         <v>1.69</v>
       </c>
       <c r="AR290" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="AS290" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AT290" t="n">
-        <v>3.42</v>
+        <v>3.41</v>
       </c>
       <c r="AU290" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV290" t="n">
         <v>2</v>
       </c>
       <c r="AW290" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX290" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY290" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ290" t="n">
         <v>7</v>
-      </c>
-      <c r="AX290" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY290" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ290" t="n">
-        <v>4</v>
       </c>
       <c r="BA290" t="n">
         <v>4</v>
@@ -63919,31 +63919,31 @@
         <v>1</v>
       </c>
       <c r="AR291" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AS291" t="n">
         <v>1.17</v>
       </c>
       <c r="AT291" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="AU291" t="n">
         <v>7</v>
       </c>
       <c r="AV291" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AW291" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AX291" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AY291" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AZ291" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="BA291" t="n">
         <v>5</v>
@@ -64137,31 +64137,31 @@
         <v>1.77</v>
       </c>
       <c r="AR292" t="n">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="AS292" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AT292" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="AU292" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AV292" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AW292" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX292" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY292" t="n">
         <v>8</v>
       </c>
-      <c r="AX292" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY292" t="n">
-        <v>15</v>
-      </c>
       <c r="AZ292" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BA292" t="n">
         <v>4</v>
@@ -64355,28 +64355,28 @@
         <v>1</v>
       </c>
       <c r="AR293" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AS293" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AT293" t="n">
-        <v>3.01</v>
+        <v>2.86</v>
       </c>
       <c r="AU293" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AV293" t="n">
         <v>3</v>
       </c>
       <c r="AW293" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="AX293" t="n">
         <v>3</v>
       </c>
       <c r="AY293" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="AZ293" t="n">
         <v>6</v>
@@ -64576,25 +64576,25 @@
         <v>1.45</v>
       </c>
       <c r="AS294" t="n">
-        <v>1.65</v>
+        <v>1.49</v>
       </c>
       <c r="AT294" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="AU294" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AV294" t="n">
         <v>2</v>
       </c>
       <c r="AW294" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX294" t="n">
         <v>2</v>
       </c>
       <c r="AY294" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ294" t="n">
         <v>4</v>
@@ -64794,28 +64794,28 @@
         <v>1.73</v>
       </c>
       <c r="AS295" t="n">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="AT295" t="n">
-        <v>3.15</v>
+        <v>3.29</v>
       </c>
       <c r="AU295" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AV295" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AW295" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AX295" t="n">
         <v>5</v>
       </c>
       <c r="AY295" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AZ295" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA295" t="n">
         <v>2</v>
@@ -65012,28 +65012,28 @@
         <v>1.88</v>
       </c>
       <c r="AS296" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AT296" t="n">
-        <v>3.47</v>
+        <v>3.49</v>
       </c>
       <c r="AU296" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV296" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AW296" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX296" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AY296" t="n">
         <v>11</v>
       </c>
       <c r="AZ296" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BA296" t="n">
         <v>1</v>
@@ -65230,28 +65230,28 @@
         <v>1.23</v>
       </c>
       <c r="AS297" t="n">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="AT297" t="n">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="AU297" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV297" t="n">
         <v>2</v>
       </c>
       <c r="AW297" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX297" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY297" t="n">
         <v>9</v>
       </c>
       <c r="AZ297" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA297" t="n">
         <v>3</v>
@@ -65454,13 +65454,13 @@
         <v>2.87</v>
       </c>
       <c r="AU298" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV298" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AW298" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AX298" t="n">
         <v>3</v>
@@ -65469,16 +65469,16 @@
         <v>13</v>
       </c>
       <c r="AZ298" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BA298" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB298" t="n">
         <v>2</v>
       </c>
       <c r="BC298" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD298" t="n">
         <v>1.9</v>
@@ -65666,10 +65666,10 @@
         <v>1.87</v>
       </c>
       <c r="AS299" t="n">
-        <v>1.75</v>
+        <v>1.52</v>
       </c>
       <c r="AT299" t="n">
-        <v>3.62</v>
+        <v>3.39</v>
       </c>
       <c r="AU299" t="n">
         <v>5</v>
@@ -65881,28 +65881,28 @@
         <v>0.42</v>
       </c>
       <c r="AR300" t="n">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="AS300" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AT300" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="AU300" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV300" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW300" t="n">
         <v>7</v>
       </c>
-      <c r="AV300" t="n">
-        <v>7</v>
-      </c>
-      <c r="AW300" t="n">
-        <v>2</v>
-      </c>
       <c r="AX300" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY300" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AZ300" t="n">
         <v>15</v>
@@ -66099,13 +66099,13 @@
         <v>1.33</v>
       </c>
       <c r="AR301" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AS301" t="n">
         <v>1.44</v>
       </c>
       <c r="AT301" t="n">
-        <v>2.68</v>
+        <v>2.77</v>
       </c>
       <c r="AU301" t="n">
         <v>6</v>
@@ -66114,16 +66114,16 @@
         <v>5</v>
       </c>
       <c r="AW301" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AX301" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AY301" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AZ301" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BA301" t="n">
         <v>5</v>
@@ -66326,22 +66326,22 @@
         <v>2.91</v>
       </c>
       <c r="AU302" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV302" t="n">
         <v>6</v>
       </c>
       <c r="AW302" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX302" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AY302" t="n">
         <v>12</v>
       </c>
       <c r="AZ302" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BA302" t="n">
         <v>5</v>
@@ -66535,31 +66535,31 @@
         <v>0.54</v>
       </c>
       <c r="AR303" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="AS303" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AT303" t="n">
-        <v>3.21</v>
+        <v>3.11</v>
       </c>
       <c r="AU303" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV303" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW303" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AX303" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AY303" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ303" t="n">
         <v>13</v>
-      </c>
-      <c r="AZ303" t="n">
-        <v>7</v>
       </c>
       <c r="BA303" t="n">
         <v>9</v>
@@ -66753,13 +66753,13 @@
         <v>1.45</v>
       </c>
       <c r="AR304" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AS304" t="n">
         <v>1.44</v>
       </c>
       <c r="AT304" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="AU304" t="n">
         <v>3</v>
@@ -66768,25 +66768,25 @@
         <v>4</v>
       </c>
       <c r="AW304" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AX304" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AY304" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AZ304" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BA304" t="n">
         <v>2</v>
       </c>
       <c r="BB304" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BC304" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BD304" t="n">
         <v>1.67</v>
@@ -66971,31 +66971,31 @@
         <v>1.91</v>
       </c>
       <c r="AR305" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AS305" t="n">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="AT305" t="n">
-        <v>2.65</v>
+        <v>2.81</v>
       </c>
       <c r="AU305" t="n">
         <v>7</v>
       </c>
       <c r="AV305" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW305" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX305" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AY305" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ305" t="n">
         <v>14</v>
-      </c>
-      <c r="AZ305" t="n">
-        <v>8</v>
       </c>
       <c r="BA305" t="n">
         <v>5</v>
@@ -67189,13 +67189,13 @@
         <v>0.82</v>
       </c>
       <c r="AR306" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AS306" t="n">
         <v>0.97</v>
       </c>
       <c r="AT306" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="AU306" t="n">
         <v>6</v>
@@ -67204,16 +67204,16 @@
         <v>3</v>
       </c>
       <c r="AW306" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AX306" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY306" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AZ306" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA306" t="n">
         <v>2</v>
@@ -67407,31 +67407,31 @@
         <v>0.54</v>
       </c>
       <c r="AR307" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AS307" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AT307" t="n">
-        <v>3.04</v>
+        <v>3.09</v>
       </c>
       <c r="AU307" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV307" t="n">
         <v>2</v>
       </c>
       <c r="AW307" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX307" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY307" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ307" t="n">
         <v>9</v>
-      </c>
-      <c r="AX307" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY307" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ307" t="n">
-        <v>7</v>
       </c>
       <c r="BA307" t="n">
         <v>8</v>
@@ -67625,31 +67625,31 @@
         <v>0.36</v>
       </c>
       <c r="AR308" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="AS308" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="AT308" t="n">
-        <v>2.81</v>
+        <v>2.59</v>
       </c>
       <c r="AU308" t="n">
         <v>6</v>
       </c>
       <c r="AV308" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW308" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AX308" t="n">
         <v>6</v>
       </c>
       <c r="AY308" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AZ308" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA308" t="n">
         <v>3</v>
@@ -67843,31 +67843,31 @@
         <v>0.92</v>
       </c>
       <c r="AR309" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AS309" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AT309" t="n">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="AU309" t="n">
         <v>5</v>
       </c>
       <c r="AV309" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW309" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AX309" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY309" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AZ309" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BA309" t="n">
         <v>3</v>
@@ -68279,13 +68279,13 @@
         <v>1.08</v>
       </c>
       <c r="AR311" t="n">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AS311" t="n">
-        <v>1.76</v>
+        <v>1.92</v>
       </c>
       <c r="AT311" t="n">
-        <v>3.58</v>
+        <v>3.65</v>
       </c>
       <c r="AU311" t="n">
         <v>7</v>
@@ -68294,16 +68294,16 @@
         <v>5</v>
       </c>
       <c r="AW311" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX311" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AY311" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ311" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BA311" t="n">
         <v>5</v>
@@ -68497,10 +68497,10 @@
         <v>1.08</v>
       </c>
       <c r="AR312" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AS312" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="AT312" t="n">
         <v>3.17</v>
@@ -68509,16 +68509,16 @@
         <v>10</v>
       </c>
       <c r="AV312" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW312" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX312" t="n">
         <v>6</v>
       </c>
-      <c r="AX312" t="n">
-        <v>5</v>
-      </c>
       <c r="AY312" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AZ312" t="n">
         <v>13</v>
@@ -68715,13 +68715,13 @@
         <v>1.91</v>
       </c>
       <c r="AR313" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="AS313" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AT313" t="n">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="AU313" t="n">
         <v>5</v>
@@ -68730,13 +68730,13 @@
         <v>5</v>
       </c>
       <c r="AW313" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AX313" t="n">
         <v>2</v>
       </c>
       <c r="AY313" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AZ313" t="n">
         <v>7</v>
@@ -68933,31 +68933,31 @@
         <v>1.45</v>
       </c>
       <c r="AR314" t="n">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="AS314" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AT314" t="n">
-        <v>3.32</v>
+        <v>3.19</v>
       </c>
       <c r="AU314" t="n">
         <v>5</v>
       </c>
       <c r="AV314" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW314" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AX314" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY314" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AZ314" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BA314" t="n">
         <v>5</v>
@@ -69151,31 +69151,31 @@
         <v>1.08</v>
       </c>
       <c r="AR315" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="AS315" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AT315" t="n">
-        <v>2.99</v>
+        <v>2.89</v>
       </c>
       <c r="AU315" t="n">
         <v>4</v>
       </c>
       <c r="AV315" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AW315" t="n">
         <v>4</v>
       </c>
       <c r="AX315" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="AY315" t="n">
         <v>8</v>
       </c>
       <c r="AZ315" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="BA315" t="n">
         <v>3</v>
@@ -69369,31 +69369,31 @@
         <v>1.69</v>
       </c>
       <c r="AR316" t="n">
-        <v>1.67</v>
+        <v>1.51</v>
       </c>
       <c r="AS316" t="n">
-        <v>1.65</v>
+        <v>1.41</v>
       </c>
       <c r="AT316" t="n">
-        <v>3.32</v>
+        <v>2.92</v>
       </c>
       <c r="AU316" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AV316" t="n">
         <v>3</v>
       </c>
       <c r="AW316" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AX316" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AY316" t="n">
         <v>15</v>
       </c>
       <c r="AZ316" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="BA316" t="n">
         <v>7</v>
@@ -69587,28 +69587,28 @@
         <v>1.18</v>
       </c>
       <c r="AR317" t="n">
-        <v>1.45</v>
+        <v>1.61</v>
       </c>
       <c r="AS317" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AT317" t="n">
-        <v>2.59</v>
+        <v>2.76</v>
       </c>
       <c r="AU317" t="n">
         <v>6</v>
       </c>
       <c r="AV317" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW317" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AX317" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY317" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AZ317" t="n">
         <v>16</v>
@@ -69805,13 +69805,13 @@
         <v>0.67</v>
       </c>
       <c r="AR318" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AS318" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AT318" t="n">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="AU318" t="n">
         <v>6</v>
@@ -69820,16 +69820,16 @@
         <v>4</v>
       </c>
       <c r="AW318" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AX318" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AY318" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AZ318" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BA318" t="n">
         <v>2</v>
@@ -70023,31 +70023,31 @@
         <v>1.42</v>
       </c>
       <c r="AR319" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AS319" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AT319" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AU319" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV319" t="n">
         <v>2</v>
       </c>
       <c r="AW319" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AX319" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AY319" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ319" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BA319" t="n">
         <v>8</v>
@@ -70241,31 +70241,31 @@
         <v>1.27</v>
       </c>
       <c r="AR320" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AS320" t="n">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="AT320" t="n">
-        <v>3.19</v>
+        <v>3.15</v>
       </c>
       <c r="AU320" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AV320" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW320" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AX320" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AY320" t="n">
         <v>19</v>
       </c>
       <c r="AZ320" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="BA320" t="n">
         <v>4</v>
@@ -70459,31 +70459,31 @@
         <v>1.33</v>
       </c>
       <c r="AR321" t="n">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="AS321" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AT321" t="n">
-        <v>3.07</v>
+        <v>3.23</v>
       </c>
       <c r="AU321" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV321" t="n">
         <v>9</v>
       </c>
-      <c r="AV321" t="n">
-        <v>7</v>
-      </c>
       <c r="AW321" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AX321" t="n">
         <v>7</v>
       </c>
       <c r="AY321" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ321" t="n">
         <v>16</v>
-      </c>
-      <c r="AZ321" t="n">
-        <v>14</v>
       </c>
       <c r="BA321" t="n">
         <v>3</v>
@@ -70677,31 +70677,31 @@
         <v>1.91</v>
       </c>
       <c r="AR322" t="n">
-        <v>1.88</v>
+        <v>1.74</v>
       </c>
       <c r="AS322" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AT322" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="AU322" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV322" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW322" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX322" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AY322" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ322" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BA322" t="n">
         <v>1</v>
@@ -70895,31 +70895,31 @@
         <v>0.67</v>
       </c>
       <c r="AR323" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AS323" t="n">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="AT323" t="n">
-        <v>3.38</v>
+        <v>3.08</v>
       </c>
       <c r="AU323" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV323" t="n">
         <v>2</v>
       </c>
       <c r="AW323" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AX323" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AY323" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AZ323" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BA323" t="n">
         <v>9</v>
@@ -71116,28 +71116,28 @@
         <v>1.56</v>
       </c>
       <c r="AS324" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AT324" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="AU324" t="n">
         <v>5</v>
       </c>
       <c r="AV324" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AW324" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AX324" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY324" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AZ324" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BA324" t="n">
         <v>3</v>
@@ -71331,31 +71331,31 @@
         <v>1.08</v>
       </c>
       <c r="AR325" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AS325" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AT325" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="AU325" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV325" t="n">
         <v>5</v>
       </c>
       <c r="AW325" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AX325" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AY325" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="AZ325" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BA325" t="n">
         <v>9</v>
@@ -71552,10 +71552,10 @@
         <v>1.87</v>
       </c>
       <c r="AS326" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AT326" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="AU326" t="n">
         <v>5</v>
@@ -71767,28 +71767,28 @@
         <v>1.69</v>
       </c>
       <c r="AR327" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AS327" t="n">
-        <v>1.65</v>
+        <v>1.42</v>
       </c>
       <c r="AT327" t="n">
-        <v>3.37</v>
+        <v>3.11</v>
       </c>
       <c r="AU327" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV327" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW327" t="n">
         <v>8</v>
       </c>
-      <c r="AW327" t="n">
-        <v>6</v>
-      </c>
       <c r="AX327" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY327" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AZ327" t="n">
         <v>12</v>
@@ -71985,31 +71985,31 @@
         <v>1.11</v>
       </c>
       <c r="AR328" t="n">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="AS328" t="n">
         <v>1.55</v>
       </c>
       <c r="AT328" t="n">
-        <v>3.37</v>
+        <v>3.25</v>
       </c>
       <c r="AU328" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV328" t="n">
         <v>7</v>
       </c>
       <c r="AW328" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AX328" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY328" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AZ328" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA328" t="n">
         <v>10</v>
@@ -72203,31 +72203,31 @@
         <v>0.82</v>
       </c>
       <c r="AR329" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AS329" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="AT329" t="n">
-        <v>2.82</v>
+        <v>2.68</v>
       </c>
       <c r="AU329" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AV329" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AW329" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AX329" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY329" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="AZ329" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="BA329" t="n">
         <v>3</v>
@@ -72421,31 +72421,31 @@
         <v>1.42</v>
       </c>
       <c r="AR330" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="AS330" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AT330" t="n">
-        <v>3.42</v>
+        <v>3.31</v>
       </c>
       <c r="AU330" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV330" t="n">
         <v>4</v>
       </c>
-      <c r="AV330" t="n">
+      <c r="AW330" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX330" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY330" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ330" t="n">
         <v>6</v>
-      </c>
-      <c r="AW330" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX330" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY330" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ330" t="n">
-        <v>12</v>
       </c>
       <c r="BA330" t="n">
         <v>4</v>
@@ -72642,28 +72642,28 @@
         <v>1.77</v>
       </c>
       <c r="AS331" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AT331" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="AU331" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV331" t="n">
         <v>2</v>
       </c>
-      <c r="AV331" t="n">
-        <v>3</v>
-      </c>
       <c r="AW331" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX331" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY331" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AZ331" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BA331" t="n">
         <v>4</v>
@@ -72857,31 +72857,31 @@
         <v>1.18</v>
       </c>
       <c r="AR332" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AS332" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AT332" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="AU332" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV332" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW332" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX332" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY332" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ332" t="n">
         <v>5</v>
-      </c>
-      <c r="AV332" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW332" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX332" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY332" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ332" t="n">
-        <v>7</v>
       </c>
       <c r="BA332" t="n">
         <v>8</v>
@@ -73075,31 +73075,31 @@
         <v>1</v>
       </c>
       <c r="AR333" t="n">
-        <v>1.24</v>
+        <v>1.39</v>
       </c>
       <c r="AS333" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AT333" t="n">
-        <v>2.81</v>
+        <v>3.04</v>
       </c>
       <c r="AU333" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV333" t="n">
         <v>2</v>
       </c>
-      <c r="AV333" t="n">
+      <c r="AW333" t="n">
         <v>5</v>
       </c>
-      <c r="AW333" t="n">
-        <v>7</v>
-      </c>
       <c r="AX333" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AY333" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AZ333" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="BA333" t="n">
         <v>9</v>
@@ -73293,31 +73293,31 @@
         <v>1.91</v>
       </c>
       <c r="AR334" t="n">
-        <v>1.63</v>
+        <v>1.77</v>
       </c>
       <c r="AS334" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AT334" t="n">
-        <v>2.95</v>
+        <v>3.17</v>
       </c>
       <c r="AU334" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV334" t="n">
         <v>9</v>
       </c>
       <c r="AW334" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX334" t="n">
         <v>5</v>
       </c>
-      <c r="AX334" t="n">
-        <v>1</v>
-      </c>
       <c r="AY334" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AZ334" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BA334" t="n">
         <v>2</v>
@@ -73511,31 +73511,31 @@
         <v>0.77</v>
       </c>
       <c r="AR335" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AS335" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AT335" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="AU335" t="n">
         <v>7</v>
       </c>
       <c r="AV335" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW335" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AX335" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AY335" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AZ335" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BA335" t="n">
         <v>7</v>
@@ -73729,13 +73729,13 @@
         <v>1.69</v>
       </c>
       <c r="AR336" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AS336" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="AT336" t="n">
-        <v>3.14</v>
+        <v>3.21</v>
       </c>
       <c r="AU336" t="n">
         <v>5</v>
@@ -73744,16 +73744,16 @@
         <v>5</v>
       </c>
       <c r="AW336" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AX336" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AY336" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AZ336" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BA336" t="n">
         <v>5</v>
@@ -73947,13 +73947,13 @@
         <v>1.77</v>
       </c>
       <c r="AR337" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AS337" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AT337" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="AU337" t="n">
         <v>4</v>
@@ -73962,16 +73962,16 @@
         <v>6</v>
       </c>
       <c r="AW337" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AX337" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY337" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AZ337" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA337" t="n">
         <v>9</v>
@@ -74165,31 +74165,31 @@
         <v>0.67</v>
       </c>
       <c r="AR338" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AS338" t="n">
-        <v>1.65</v>
+        <v>1.46</v>
       </c>
       <c r="AT338" t="n">
-        <v>3.5</v>
+        <v>3.27</v>
       </c>
       <c r="AU338" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV338" t="n">
         <v>2</v>
       </c>
       <c r="AW338" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX338" t="n">
         <v>5</v>
       </c>
-      <c r="AX338" t="n">
-        <v>3</v>
-      </c>
       <c r="AY338" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="AZ338" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BA338" t="n">
         <v>7</v>
@@ -74383,13 +74383,13 @@
         <v>1.08</v>
       </c>
       <c r="AR339" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AS339" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="AT339" t="n">
-        <v>3.61</v>
+        <v>3.55</v>
       </c>
       <c r="AU339" t="n">
         <v>10</v>
@@ -74398,16 +74398,16 @@
         <v>10</v>
       </c>
       <c r="AW339" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AX339" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AY339" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AZ339" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BA339" t="n">
         <v>5</v>
@@ -74601,40 +74601,40 @@
         <v>0.42</v>
       </c>
       <c r="AR340" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AS340" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AT340" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="AU340" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV340" t="n">
         <v>3</v>
       </c>
       <c r="AW340" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AX340" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AY340" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AZ340" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="BA340" t="n">
         <v>2</v>
       </c>
       <c r="BB340" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BC340" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD340" t="n">
         <v>1.84</v>
@@ -74819,31 +74819,31 @@
         <v>1.08</v>
       </c>
       <c r="AR341" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="AS341" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AT341" t="n">
-        <v>2.87</v>
+        <v>3.04</v>
       </c>
       <c r="AU341" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV341" t="n">
         <v>6</v>
       </c>
-      <c r="AV341" t="n">
+      <c r="AW341" t="n">
         <v>7</v>
       </c>
-      <c r="AW341" t="n">
-        <v>4</v>
-      </c>
       <c r="AX341" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AY341" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ341" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="BA341" t="n">
         <v>7</v>
@@ -75037,31 +75037,31 @@
         <v>1.67</v>
       </c>
       <c r="AR342" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AS342" t="n">
-        <v>1.75</v>
+        <v>1.52</v>
       </c>
       <c r="AT342" t="n">
-        <v>3.47</v>
+        <v>3.17</v>
       </c>
       <c r="AU342" t="n">
         <v>4</v>
       </c>
       <c r="AV342" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW342" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AX342" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AY342" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ342" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="BA342" t="n">
         <v>2</v>
@@ -75258,10 +75258,10 @@
         <v>1.87</v>
       </c>
       <c r="AS343" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AT343" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="AU343" t="n">
         <v>6</v>
@@ -75473,31 +75473,31 @@
         <v>1.86</v>
       </c>
       <c r="AR344" t="n">
-        <v>1.45</v>
+        <v>1.59</v>
       </c>
       <c r="AS344" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AT344" t="n">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="AU344" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV344" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW344" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AX344" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AY344" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AZ344" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BA344" t="n">
         <v>3</v>
@@ -75691,31 +75691,31 @@
         <v>0.38</v>
       </c>
       <c r="AR345" t="n">
-        <v>1.77</v>
+        <v>1.88</v>
       </c>
       <c r="AS345" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AT345" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="AU345" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV345" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW345" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX345" t="n">
         <v>5</v>
       </c>
-      <c r="AV345" t="n">
-        <v>7</v>
-      </c>
-      <c r="AW345" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX345" t="n">
-        <v>4</v>
-      </c>
       <c r="AY345" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AZ345" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BA345" t="n">
         <v>4</v>
@@ -75909,13 +75909,13 @@
         <v>1.69</v>
       </c>
       <c r="AR346" t="n">
-        <v>1.77</v>
+        <v>1.63</v>
       </c>
       <c r="AS346" t="n">
-        <v>1.65</v>
+        <v>1.42</v>
       </c>
       <c r="AT346" t="n">
-        <v>3.42</v>
+        <v>3.05</v>
       </c>
       <c r="AU346" t="n">
         <v>7</v>
@@ -75924,25 +75924,25 @@
         <v>4</v>
       </c>
       <c r="AW346" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX346" t="n">
         <v>6</v>
       </c>
-      <c r="AX346" t="n">
-        <v>4</v>
-      </c>
       <c r="AY346" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AZ346" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BA346" t="n">
         <v>10</v>
       </c>
       <c r="BB346" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BC346" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD346" t="n">
         <v>1.6</v>
@@ -76127,31 +76127,31 @@
         <v>1.77</v>
       </c>
       <c r="AR347" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AS347" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AT347" t="n">
         <v>2.69</v>
       </c>
       <c r="AU347" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV347" t="n">
         <v>5</v>
       </c>
       <c r="AW347" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AX347" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AY347" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ347" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BA347" t="n">
         <v>6</v>
@@ -76345,31 +76345,31 @@
         <v>0.92</v>
       </c>
       <c r="AR348" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AS348" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AT348" t="n">
-        <v>2.69</v>
+        <v>2.74</v>
       </c>
       <c r="AU348" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV348" t="n">
         <v>6</v>
       </c>
       <c r="AW348" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="AX348" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AY348" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ348" t="n">
         <v>12</v>
-      </c>
-      <c r="AZ348" t="n">
-        <v>9</v>
       </c>
       <c r="BA348" t="n">
         <v>3</v>
@@ -76563,13 +76563,13 @@
         <v>1.08</v>
       </c>
       <c r="AR349" t="n">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="AS349" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AT349" t="n">
-        <v>2.43</v>
+        <v>2.72</v>
       </c>
       <c r="AU349" t="n">
         <v>7</v>
@@ -76578,16 +76578,16 @@
         <v>6</v>
       </c>
       <c r="AW349" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX349" t="n">
         <v>3</v>
       </c>
-      <c r="AX349" t="n">
-        <v>1</v>
-      </c>
       <c r="AY349" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ349" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BA349" t="n">
         <v>2</v>
@@ -76781,31 +76781,31 @@
         <v>1.77</v>
       </c>
       <c r="AR350" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AS350" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="AT350" t="n">
-        <v>3.27</v>
+        <v>3.39</v>
       </c>
       <c r="AU350" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV350" t="n">
         <v>7</v>
       </c>
       <c r="AW350" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AX350" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY350" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AZ350" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA350" t="n">
         <v>9</v>
@@ -76999,31 +76999,31 @@
         <v>1.27</v>
       </c>
       <c r="AR351" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AS351" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="AT351" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AU351" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV351" t="n">
         <v>4</v>
       </c>
-      <c r="AV351" t="n">
+      <c r="AW351" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX351" t="n">
         <v>5</v>
       </c>
-      <c r="AW351" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX351" t="n">
-        <v>2</v>
-      </c>
       <c r="AY351" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ351" t="n">
         <v>9</v>
-      </c>
-      <c r="AZ351" t="n">
-        <v>7</v>
       </c>
       <c r="BA351" t="n">
         <v>4</v>
@@ -77217,19 +77217,19 @@
         <v>1.58</v>
       </c>
       <c r="AR352" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AS352" t="n">
         <v>1.6</v>
       </c>
       <c r="AT352" t="n">
-        <v>3.37</v>
+        <v>3.25</v>
       </c>
       <c r="AU352" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV352" t="n">
         <v>4</v>
-      </c>
-      <c r="AV352" t="n">
-        <v>5</v>
       </c>
       <c r="AW352" t="n">
         <v>4</v>
@@ -77238,10 +77238,10 @@
         <v>1</v>
       </c>
       <c r="AY352" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ352" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA352" t="n">
         <v>2</v>
@@ -77438,28 +77438,28 @@
         <v>1.5</v>
       </c>
       <c r="AS353" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AT353" t="n">
-        <v>3.15</v>
+        <v>3.11</v>
       </c>
       <c r="AU353" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV353" t="n">
         <v>5</v>
       </c>
       <c r="AW353" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AX353" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AY353" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AZ353" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BA353" t="n">
         <v>5</v>
@@ -77653,13 +77653,13 @@
         <v>0.82</v>
       </c>
       <c r="AR354" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AS354" t="n">
-        <v>0.97</v>
+        <v>0.9</v>
       </c>
       <c r="AT354" t="n">
-        <v>2.84</v>
+        <v>2.79</v>
       </c>
       <c r="AU354" t="n">
         <v>12</v>
@@ -77668,16 +77668,16 @@
         <v>2</v>
       </c>
       <c r="AW354" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AX354" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY354" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="AZ354" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA354" t="n">
         <v>11</v>
@@ -77871,31 +77871,31 @@
         <v>1.18</v>
       </c>
       <c r="AR355" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AS355" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AT355" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AU355" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV355" t="n">
         <v>7</v>
       </c>
       <c r="AW355" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AX355" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AY355" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AZ355" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="BA355" t="n">
         <v>3</v>
@@ -78089,31 +78089,31 @@
         <v>1.08</v>
       </c>
       <c r="AR356" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="AS356" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AT356" t="n">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="AU356" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV356" t="n">
         <v>3</v>
       </c>
       <c r="AW356" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AX356" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AY356" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="AZ356" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BA356" t="n">
         <v>3</v>
@@ -78307,13 +78307,13 @@
         <v>1</v>
       </c>
       <c r="AR357" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AS357" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AT357" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="AU357" t="n">
         <v>5</v>
@@ -78322,16 +78322,16 @@
         <v>4</v>
       </c>
       <c r="AW357" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AX357" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AY357" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AZ357" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BA357" t="n">
         <v>2</v>
@@ -78525,13 +78525,13 @@
         <v>0.54</v>
       </c>
       <c r="AR358" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="AS358" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AT358" t="n">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="AU358" t="n">
         <v>8</v>
@@ -78540,16 +78540,16 @@
         <v>4</v>
       </c>
       <c r="AW358" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AX358" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY358" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AZ358" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA358" t="n">
         <v>3</v>
@@ -78743,31 +78743,31 @@
         <v>1.77</v>
       </c>
       <c r="AR359" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="AS359" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AT359" t="n">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="AU359" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV359" t="n">
         <v>5</v>
       </c>
       <c r="AW359" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="AX359" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AY359" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="AZ359" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BA359" t="n">
         <v>10</v>
@@ -78961,40 +78961,40 @@
         <v>1.08</v>
       </c>
       <c r="AR360" t="n">
-        <v>1.45</v>
+        <v>1.64</v>
       </c>
       <c r="AS360" t="n">
-        <v>1.76</v>
+        <v>1.92</v>
       </c>
       <c r="AT360" t="n">
-        <v>3.21</v>
+        <v>3.56</v>
       </c>
       <c r="AU360" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AV360" t="n">
         <v>4</v>
       </c>
       <c r="AW360" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AX360" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AY360" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AZ360" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="BA360" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB360" t="n">
         <v>3</v>
       </c>
       <c r="BC360" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD360" t="n">
         <v>1.49</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
@@ -78098,10 +78098,10 @@
         <v>3.25</v>
       </c>
       <c r="AU356" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV356" t="n">
         <v>5</v>
-      </c>
-      <c r="AV356" t="n">
-        <v>4</v>
       </c>
       <c r="AW356" t="n">
         <v>4</v>
@@ -78110,10 +78110,10 @@
         <v>1</v>
       </c>
       <c r="AY356" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ356" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA356" t="n">
         <v>2</v>
@@ -79860,13 +79860,13 @@
         <v>11</v>
       </c>
       <c r="BA364" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB364" t="n">
         <v>3</v>
       </c>
       <c r="BC364" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD364" t="n">
         <v>1.49</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP365"/>
+  <dimension ref="A1:BP368"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4184,7 +4184,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
@@ -4617,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AQ19" t="n">
         <v>1.45</v>
@@ -5271,7 +5271,7 @@
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ22" t="n">
         <v>1.86</v>
@@ -5492,7 +5492,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR23" t="n">
         <v>0</v>
@@ -8541,7 +8541,7 @@
         <v>3</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AQ37" t="n">
         <v>1.67</v>
@@ -13337,7 +13337,7 @@
         <v>0</v>
       </c>
       <c r="AP59" t="n">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ59" t="n">
         <v>1.58</v>
@@ -13994,7 +13994,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ62" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AR62" t="n">
         <v>1.47</v>
@@ -15084,7 +15084,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ67" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR67" t="n">
         <v>1.51</v>
@@ -15299,7 +15299,7 @@
         <v>2</v>
       </c>
       <c r="AP68" t="n">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ68" t="n">
         <v>0.42</v>
@@ -17043,7 +17043,7 @@
         <v>0.5</v>
       </c>
       <c r="AP76" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AQ76" t="n">
         <v>0.54</v>
@@ -20967,7 +20967,7 @@
         <v>1.33</v>
       </c>
       <c r="AP94" t="n">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ94" t="n">
         <v>1.77</v>
@@ -23150,7 +23150,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ104" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR104" t="n">
         <v>1.82</v>
@@ -24237,7 +24237,7 @@
         <v>0.33</v>
       </c>
       <c r="AP109" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AQ109" t="n">
         <v>0.77</v>
@@ -27510,7 +27510,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ124" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR124" t="n">
         <v>1.35</v>
@@ -27725,10 +27725,10 @@
         <v>0.5</v>
       </c>
       <c r="AP125" t="n">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ125" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AR125" t="n">
         <v>1.71</v>
@@ -27943,7 +27943,7 @@
         <v>1.25</v>
       </c>
       <c r="AP126" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AQ126" t="n">
         <v>1.77</v>
@@ -28161,7 +28161,7 @@
         <v>0.5</v>
       </c>
       <c r="AP127" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AQ127" t="n">
         <v>1.08</v>
@@ -30559,10 +30559,10 @@
         <v>1</v>
       </c>
       <c r="AP138" t="n">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ138" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR138" t="n">
         <v>1.6</v>
@@ -30998,7 +30998,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ140" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AR140" t="n">
         <v>1.75</v>
@@ -34047,7 +34047,7 @@
         <v>1.5</v>
       </c>
       <c r="AP154" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AQ154" t="n">
         <v>1.67</v>
@@ -36666,7 +36666,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ166" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AR166" t="n">
         <v>1.46</v>
@@ -37102,7 +37102,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ168" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR168" t="n">
         <v>1.12</v>
@@ -37317,7 +37317,7 @@
         <v>2.5</v>
       </c>
       <c r="AP169" t="n">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ169" t="n">
         <v>1.45</v>
@@ -40151,7 +40151,7 @@
         <v>2.2</v>
       </c>
       <c r="AP182" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AQ182" t="n">
         <v>1.45</v>
@@ -40587,7 +40587,7 @@
         <v>0.29</v>
       </c>
       <c r="AP184" t="n">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ184" t="n">
         <v>0.38</v>
@@ -41680,7 +41680,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ189" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AR189" t="n">
         <v>1.44</v>
@@ -42767,7 +42767,7 @@
         <v>0.83</v>
       </c>
       <c r="AP194" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AQ194" t="n">
         <v>1</v>
@@ -43857,7 +43857,7 @@
         <v>1.2</v>
       </c>
       <c r="AP199" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AQ199" t="n">
         <v>1.08</v>
@@ -44296,7 +44296,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ201" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR201" t="n">
         <v>1.76</v>
@@ -46909,7 +46909,7 @@
         <v>0.86</v>
       </c>
       <c r="AP213" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AQ213" t="n">
         <v>1.11</v>
@@ -47345,7 +47345,7 @@
         <v>1.83</v>
       </c>
       <c r="AP215" t="n">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ215" t="n">
         <v>1.91</v>
@@ -52798,7 +52798,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ240" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR240" t="n">
         <v>1.75</v>
@@ -53231,7 +53231,7 @@
         <v>1.44</v>
       </c>
       <c r="AP242" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AQ242" t="n">
         <v>1.31</v>
@@ -53452,7 +53452,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ243" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AR243" t="n">
         <v>1.49</v>
@@ -56068,7 +56068,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ255" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AR255" t="n">
         <v>1.7</v>
@@ -56937,7 +56937,7 @@
         <v>1.44</v>
       </c>
       <c r="AP259" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AQ259" t="n">
         <v>1.86</v>
@@ -57155,7 +57155,7 @@
         <v>0.78</v>
       </c>
       <c r="AP260" t="n">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ260" t="n">
         <v>0.77</v>
@@ -58684,7 +58684,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ267" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR267" t="n">
         <v>1.31</v>
@@ -58902,7 +58902,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ268" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AR268" t="n">
         <v>1.71</v>
@@ -59117,7 +59117,7 @@
         <v>1.6</v>
       </c>
       <c r="AP269" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AQ269" t="n">
         <v>1.86</v>
@@ -59335,7 +59335,7 @@
         <v>1.63</v>
       </c>
       <c r="AP270" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AQ270" t="n">
         <v>1.58</v>
@@ -61297,7 +61297,7 @@
         <v>1</v>
       </c>
       <c r="AP279" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AQ279" t="n">
         <v>0.83</v>
@@ -62169,7 +62169,7 @@
         <v>0.88</v>
       </c>
       <c r="AP283" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AQ283" t="n">
         <v>1.08</v>
@@ -65660,7 +65660,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ299" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AR299" t="n">
         <v>1.14</v>
@@ -65875,7 +65875,7 @@
         <v>1.71</v>
       </c>
       <c r="AP300" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AQ300" t="n">
         <v>1.91</v>
@@ -67401,7 +67401,7 @@
         <v>1.88</v>
       </c>
       <c r="AP307" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AQ307" t="n">
         <v>1.91</v>
@@ -67837,7 +67837,7 @@
         <v>0.64</v>
       </c>
       <c r="AP309" t="n">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ309" t="n">
         <v>0.54</v>
@@ -68058,7 +68058,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ310" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AR310" t="n">
         <v>1.28</v>
@@ -70456,7 +70456,7 @@
         <v>1</v>
       </c>
       <c r="AQ321" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR321" t="n">
         <v>1.33</v>
@@ -71546,7 +71546,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ326" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR326" t="n">
         <v>1.47</v>
@@ -71979,7 +71979,7 @@
         <v>0.75</v>
       </c>
       <c r="AP328" t="n">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ328" t="n">
         <v>0.86</v>
@@ -74595,7 +74595,7 @@
         <v>1.58</v>
       </c>
       <c r="AP340" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AQ340" t="n">
         <v>1.69</v>
@@ -74813,7 +74813,7 @@
         <v>1.55</v>
       </c>
       <c r="AP341" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AQ341" t="n">
         <v>1.77</v>
@@ -75034,7 +75034,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ342" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR342" t="n">
         <v>1.69</v>
@@ -77211,7 +77211,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AP352" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AQ352" t="n">
         <v>0.86</v>
@@ -78519,7 +78519,7 @@
         <v>0.91</v>
       </c>
       <c r="AP358" t="n">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ358" t="n">
         <v>0.83</v>
@@ -80124,6 +80124,660 @@
       </c>
       <c r="BP365" t="n">
         <v>1.49</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="1" t="n">
+        <v>365</v>
+      </c>
+      <c r="B366" t="n">
+        <v>7781448</v>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E366" s="2" t="n">
+        <v>45878.85416666666</v>
+      </c>
+      <c r="F366" t="n">
+        <v>0</v>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>Philadelphia Union</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>Toronto</t>
+        </is>
+      </c>
+      <c r="I366" t="n">
+        <v>1</v>
+      </c>
+      <c r="J366" t="n">
+        <v>0</v>
+      </c>
+      <c r="K366" t="n">
+        <v>1</v>
+      </c>
+      <c r="L366" t="n">
+        <v>1</v>
+      </c>
+      <c r="M366" t="n">
+        <v>1</v>
+      </c>
+      <c r="N366" t="n">
+        <v>2</v>
+      </c>
+      <c r="O366" t="inlineStr">
+        <is>
+          <t>['4']</t>
+        </is>
+      </c>
+      <c r="P366" t="inlineStr">
+        <is>
+          <t>['90+1']</t>
+        </is>
+      </c>
+      <c r="Q366" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R366" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S366" t="n">
+        <v>6</v>
+      </c>
+      <c r="T366" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="U366" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V366" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="W366" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X366" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y366" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z366" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AA366" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB366" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AC366" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD366" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE366" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF366" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AG366" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH366" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AI366" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ366" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK366" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AL366" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AM366" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AN366" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AO366" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP366" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AQ366" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR366" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AS366" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AT366" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AU366" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV366" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW366" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX366" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY366" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ366" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA366" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB366" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC366" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD366" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BE366" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="BF366" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG366" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BH366" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="BI366" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ366" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="BK366" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BL366" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BM366" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="BN366" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BO366" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="BP366" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="1" t="n">
+        <v>366</v>
+      </c>
+      <c r="B367" t="n">
+        <v>7781445</v>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E367" s="2" t="n">
+        <v>45878.85416666666</v>
+      </c>
+      <c r="F367" t="n">
+        <v>0</v>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>Montreal Impact</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>Atlanta United FC</t>
+        </is>
+      </c>
+      <c r="I367" t="n">
+        <v>1</v>
+      </c>
+      <c r="J367" t="n">
+        <v>0</v>
+      </c>
+      <c r="K367" t="n">
+        <v>1</v>
+      </c>
+      <c r="L367" t="n">
+        <v>1</v>
+      </c>
+      <c r="M367" t="n">
+        <v>1</v>
+      </c>
+      <c r="N367" t="n">
+        <v>2</v>
+      </c>
+      <c r="O367" t="inlineStr">
+        <is>
+          <t>['40']</t>
+        </is>
+      </c>
+      <c r="P367" t="inlineStr">
+        <is>
+          <t>['87']</t>
+        </is>
+      </c>
+      <c r="Q367" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R367" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S367" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T367" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="U367" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V367" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="W367" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X367" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y367" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z367" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AA367" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB367" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AC367" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD367" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE367" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF367" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AG367" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH367" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AI367" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ367" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AK367" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AL367" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM367" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AN367" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AO367" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AP367" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AQ367" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AR367" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AS367" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AT367" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU367" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV367" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW367" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX367" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY367" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ367" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA367" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB367" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC367" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD367" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BE367" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="BF367" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BG367" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BH367" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BI367" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BJ367" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BK367" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BL367" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BM367" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BN367" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BO367" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BP367" t="n">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="1" t="n">
+        <v>367</v>
+      </c>
+      <c r="B368" t="n">
+        <v>7781446</v>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E368" s="2" t="n">
+        <v>45878.85416666666</v>
+      </c>
+      <c r="F368" t="n">
+        <v>0</v>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>New England Revolution</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>DC United</t>
+        </is>
+      </c>
+      <c r="I368" t="n">
+        <v>0</v>
+      </c>
+      <c r="J368" t="n">
+        <v>0</v>
+      </c>
+      <c r="K368" t="n">
+        <v>0</v>
+      </c>
+      <c r="L368" t="n">
+        <v>2</v>
+      </c>
+      <c r="M368" t="n">
+        <v>0</v>
+      </c>
+      <c r="N368" t="n">
+        <v>2</v>
+      </c>
+      <c r="O368" t="inlineStr">
+        <is>
+          <t>['62', '70']</t>
+        </is>
+      </c>
+      <c r="P368" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q368" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R368" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S368" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T368" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U368" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V368" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="W368" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X368" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y368" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z368" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AA368" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AB368" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC368" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD368" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE368" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF368" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AG368" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH368" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI368" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ368" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK368" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AL368" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM368" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN368" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AO368" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AP368" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AQ368" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AR368" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AS368" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AT368" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AU368" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV368" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW368" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX368" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY368" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ368" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA368" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB368" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC368" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD368" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BE368" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="BF368" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BG368" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH368" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="BI368" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BJ368" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BK368" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BL368" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BM368" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BN368" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BO368" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP368" t="n">
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP368"/>
+  <dimension ref="A1:BP374"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ9" t="n">
         <v>0.92</v>
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ12" t="n">
         <v>0.83</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ13" t="n">
         <v>1</v>
@@ -3748,7 +3748,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -3966,7 +3966,7 @@
         <v>1</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -4838,7 +4838,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR20" t="n">
         <v>0</v>
@@ -5489,7 +5489,7 @@
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ23" t="n">
         <v>0.62</v>
@@ -5707,7 +5707,7 @@
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ24" t="n">
         <v>1.08</v>
@@ -7454,7 +7454,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR32" t="n">
         <v>1.7</v>
@@ -7672,7 +7672,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR33" t="n">
         <v>2.34</v>
@@ -8977,7 +8977,7 @@
         <v>1</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ39" t="n">
         <v>0.83</v>
@@ -9195,7 +9195,7 @@
         <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AQ40" t="n">
         <v>1.69</v>
@@ -9416,7 +9416,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR41" t="n">
         <v>1.52</v>
@@ -9634,7 +9634,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AR42" t="n">
         <v>1.28</v>
@@ -10067,7 +10067,7 @@
         <v>0</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ44" t="n">
         <v>1.77</v>
@@ -12029,7 +12029,7 @@
         <v>1.5</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ53" t="n">
         <v>1.77</v>
@@ -12247,10 +12247,10 @@
         <v>3</v>
       </c>
       <c r="AP54" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR54" t="n">
         <v>1.82</v>
@@ -12683,7 +12683,7 @@
         <v>0</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ56" t="n">
         <v>1.08</v>
@@ -13119,7 +13119,7 @@
         <v>2</v>
       </c>
       <c r="AP58" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ58" t="n">
         <v>0.83</v>
@@ -13340,7 +13340,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ59" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR59" t="n">
         <v>1.52</v>
@@ -15517,10 +15517,10 @@
         <v>0</v>
       </c>
       <c r="AP69" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ69" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR69" t="n">
         <v>1.57</v>
@@ -15956,7 +15956,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ71" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR71" t="n">
         <v>1.75</v>
@@ -16392,7 +16392,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ73" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR73" t="n">
         <v>2.1</v>
@@ -16825,10 +16825,10 @@
         <v>3</v>
       </c>
       <c r="AP75" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ75" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AR75" t="n">
         <v>1.61</v>
@@ -17264,7 +17264,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ77" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR77" t="n">
         <v>0.77</v>
@@ -18351,7 +18351,7 @@
         <v>0.2</v>
       </c>
       <c r="AP82" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ82" t="n">
         <v>0.86</v>
@@ -18569,7 +18569,7 @@
         <v>0</v>
       </c>
       <c r="AP83" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AQ83" t="n">
         <v>0.92</v>
@@ -19444,7 +19444,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ87" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR87" t="n">
         <v>1.67</v>
@@ -19659,7 +19659,7 @@
         <v>0</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ88" t="n">
         <v>1.08</v>
@@ -19877,7 +19877,7 @@
         <v>1.5</v>
       </c>
       <c r="AP89" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ89" t="n">
         <v>1.33</v>
@@ -20098,7 +20098,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ90" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR90" t="n">
         <v>0.95</v>
@@ -20316,7 +20316,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ91" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR91" t="n">
         <v>1.51</v>
@@ -21839,10 +21839,10 @@
         <v>1.5</v>
       </c>
       <c r="AP98" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR98" t="n">
         <v>1.44</v>
@@ -22057,7 +22057,7 @@
         <v>1.33</v>
       </c>
       <c r="AP99" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ99" t="n">
         <v>0.42</v>
@@ -22278,7 +22278,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ100" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR100" t="n">
         <v>1.32</v>
@@ -23147,7 +23147,7 @@
         <v>0.5</v>
       </c>
       <c r="AP104" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ104" t="n">
         <v>0.62</v>
@@ -25109,7 +25109,7 @@
         <v>0.25</v>
       </c>
       <c r="AP113" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AQ113" t="n">
         <v>1.08</v>
@@ -25548,7 +25548,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AR115" t="n">
         <v>1.63</v>
@@ -25766,7 +25766,7 @@
         <v>1</v>
       </c>
       <c r="AQ116" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR116" t="n">
         <v>1.49</v>
@@ -26199,10 +26199,10 @@
         <v>1.33</v>
       </c>
       <c r="AP118" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ118" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR118" t="n">
         <v>1.55</v>
@@ -26417,7 +26417,7 @@
         <v>3</v>
       </c>
       <c r="AP119" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ119" t="n">
         <v>1.91</v>
@@ -26635,7 +26635,7 @@
         <v>2.33</v>
       </c>
       <c r="AP120" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ120" t="n">
         <v>1.45</v>
@@ -26853,7 +26853,7 @@
         <v>0.5</v>
       </c>
       <c r="AP121" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ121" t="n">
         <v>0.38</v>
@@ -27292,7 +27292,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ123" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR123" t="n">
         <v>1.83</v>
@@ -28382,7 +28382,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ128" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AR128" t="n">
         <v>1.4</v>
@@ -28597,7 +28597,7 @@
         <v>1.5</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ129" t="n">
         <v>1.86</v>
@@ -29251,10 +29251,10 @@
         <v>2.33</v>
       </c>
       <c r="AP132" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ132" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR132" t="n">
         <v>1.64</v>
@@ -29690,7 +29690,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ134" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR134" t="n">
         <v>1.18</v>
@@ -29905,7 +29905,7 @@
         <v>0</v>
       </c>
       <c r="AP135" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ135" t="n">
         <v>0.92</v>
@@ -32524,7 +32524,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ147" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR147" t="n">
         <v>1.72</v>
@@ -33178,7 +33178,7 @@
         <v>1</v>
       </c>
       <c r="AQ150" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR150" t="n">
         <v>1.28</v>
@@ -33396,7 +33396,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR151" t="n">
         <v>1.52</v>
@@ -34701,7 +34701,7 @@
         <v>1.6</v>
       </c>
       <c r="AP157" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ157" t="n">
         <v>1.77</v>
@@ -34919,7 +34919,7 @@
         <v>1.2</v>
       </c>
       <c r="AP158" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ158" t="n">
         <v>1.77</v>
@@ -35576,7 +35576,7 @@
         <v>2</v>
       </c>
       <c r="AQ161" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR161" t="n">
         <v>1.55</v>
@@ -35791,10 +35791,10 @@
         <v>2</v>
       </c>
       <c r="AP162" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ162" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR162" t="n">
         <v>1.97</v>
@@ -36445,7 +36445,7 @@
         <v>0.4</v>
       </c>
       <c r="AP165" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ165" t="n">
         <v>0.38</v>
@@ -36663,7 +36663,7 @@
         <v>0.25</v>
       </c>
       <c r="AP166" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ166" t="n">
         <v>0.42</v>
@@ -38407,7 +38407,7 @@
         <v>1</v>
       </c>
       <c r="AP174" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AQ174" t="n">
         <v>1</v>
@@ -39061,10 +39061,10 @@
         <v>1.2</v>
       </c>
       <c r="AP177" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ177" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AR177" t="n">
         <v>1.53</v>
@@ -39718,7 +39718,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ180" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR180" t="n">
         <v>1.9</v>
@@ -41459,7 +41459,7 @@
         <v>0.5</v>
       </c>
       <c r="AP188" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ188" t="n">
         <v>0.92</v>
@@ -41677,7 +41677,7 @@
         <v>0.2</v>
       </c>
       <c r="AP189" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ189" t="n">
         <v>0.42</v>
@@ -41898,7 +41898,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ190" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR190" t="n">
         <v>1.36</v>
@@ -42549,7 +42549,7 @@
         <v>2</v>
       </c>
       <c r="AP193" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ193" t="n">
         <v>1.91</v>
@@ -44511,10 +44511,10 @@
         <v>2.2</v>
       </c>
       <c r="AP202" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ202" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR202" t="n">
         <v>1.48</v>
@@ -44729,10 +44729,10 @@
         <v>0.6</v>
       </c>
       <c r="AP203" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AQ203" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR203" t="n">
         <v>0.9399999999999999</v>
@@ -45822,7 +45822,7 @@
         <v>1</v>
       </c>
       <c r="AQ208" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR208" t="n">
         <v>1.4</v>
@@ -46912,7 +46912,7 @@
         <v>0.58</v>
       </c>
       <c r="AQ213" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR213" t="n">
         <v>1.42</v>
@@ -47130,7 +47130,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ214" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR214" t="n">
         <v>1.8</v>
@@ -47566,7 +47566,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ216" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR216" t="n">
         <v>1.31</v>
@@ -47781,7 +47781,7 @@
         <v>1.57</v>
       </c>
       <c r="AP217" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ217" t="n">
         <v>1.31</v>
@@ -48220,7 +48220,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ219" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR219" t="n">
         <v>1.31</v>
@@ -48653,10 +48653,10 @@
         <v>1</v>
       </c>
       <c r="AP221" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ221" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR221" t="n">
         <v>1.91</v>
@@ -50400,7 +50400,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ229" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR229" t="n">
         <v>1.7</v>
@@ -50836,7 +50836,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ231" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR231" t="n">
         <v>1.72</v>
@@ -51054,7 +51054,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ232" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AR232" t="n">
         <v>1.85</v>
@@ -51269,7 +51269,7 @@
         <v>0.88</v>
       </c>
       <c r="AP233" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ233" t="n">
         <v>1</v>
@@ -52141,7 +52141,7 @@
         <v>1.43</v>
       </c>
       <c r="AP237" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ237" t="n">
         <v>1.08</v>
@@ -53885,7 +53885,7 @@
         <v>2.14</v>
       </c>
       <c r="AP245" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AQ245" t="n">
         <v>1.67</v>
@@ -56501,7 +56501,7 @@
         <v>0.22</v>
       </c>
       <c r="AP257" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ257" t="n">
         <v>0.38</v>
@@ -56722,7 +56722,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ258" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR258" t="n">
         <v>1.72</v>
@@ -57376,7 +57376,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ261" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AR261" t="n">
         <v>1.69</v>
@@ -57591,7 +57591,7 @@
         <v>1.44</v>
       </c>
       <c r="AP262" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ262" t="n">
         <v>1.42</v>
@@ -58027,10 +58027,10 @@
         <v>1.43</v>
       </c>
       <c r="AP264" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ264" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR264" t="n">
         <v>1.51</v>
@@ -58245,7 +58245,7 @@
         <v>0.63</v>
       </c>
       <c r="AP265" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ265" t="n">
         <v>0.54</v>
@@ -59338,7 +59338,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ270" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR270" t="n">
         <v>1.21</v>
@@ -59774,7 +59774,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ272" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR272" t="n">
         <v>1.64</v>
@@ -59989,7 +59989,7 @@
         <v>1.44</v>
       </c>
       <c r="AP273" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ273" t="n">
         <v>1.77</v>
@@ -60207,7 +60207,7 @@
         <v>0.7</v>
       </c>
       <c r="AP274" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ274" t="n">
         <v>0.77</v>
@@ -60425,7 +60425,7 @@
         <v>2</v>
       </c>
       <c r="AP275" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ275" t="n">
         <v>1.67</v>
@@ -60643,7 +60643,7 @@
         <v>1.22</v>
       </c>
       <c r="AP276" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AQ276" t="n">
         <v>1.08</v>
@@ -60864,7 +60864,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ277" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AR277" t="n">
         <v>1.81</v>
@@ -61736,7 +61736,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ281" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR281" t="n">
         <v>1.25</v>
@@ -62390,7 +62390,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ284" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR284" t="n">
         <v>1.14</v>
@@ -62605,7 +62605,7 @@
         <v>0.64</v>
       </c>
       <c r="AP285" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ285" t="n">
         <v>0.77</v>
@@ -62823,10 +62823,10 @@
         <v>1.67</v>
       </c>
       <c r="AP286" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AQ286" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AR286" t="n">
         <v>1.11</v>
@@ -63259,7 +63259,7 @@
         <v>0.8</v>
       </c>
       <c r="AP288" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ288" t="n">
         <v>1</v>
@@ -63477,7 +63477,7 @@
         <v>0.27</v>
       </c>
       <c r="AP289" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ289" t="n">
         <v>0.38</v>
@@ -64134,7 +64134,7 @@
         <v>2</v>
       </c>
       <c r="AQ292" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR292" t="n">
         <v>1.71</v>
@@ -64567,7 +64567,7 @@
         <v>1.6</v>
       </c>
       <c r="AP294" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AQ294" t="n">
         <v>1.77</v>
@@ -65006,7 +65006,7 @@
         <v>1</v>
       </c>
       <c r="AQ296" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR296" t="n">
         <v>1.32</v>
@@ -66750,7 +66750,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ304" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR304" t="n">
         <v>1.62</v>
@@ -66965,7 +66965,7 @@
         <v>0.6</v>
       </c>
       <c r="AP305" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ305" t="n">
         <v>0.54</v>
@@ -68494,7 +68494,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ312" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR312" t="n">
         <v>1.37</v>
@@ -68927,7 +68927,7 @@
         <v>0.9</v>
       </c>
       <c r="AP314" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ314" t="n">
         <v>1.08</v>
@@ -69145,7 +69145,7 @@
         <v>1.45</v>
       </c>
       <c r="AP315" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ315" t="n">
         <v>1.31</v>
@@ -69363,10 +69363,10 @@
         <v>1.8</v>
       </c>
       <c r="AP316" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ316" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AR316" t="n">
         <v>1.48</v>
@@ -70020,7 +70020,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ319" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR319" t="n">
         <v>1.48</v>
@@ -70238,7 +70238,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ320" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AR320" t="n">
         <v>1.46</v>
@@ -70889,10 +70889,10 @@
         <v>1.22</v>
       </c>
       <c r="AP323" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ323" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR323" t="n">
         <v>1.61</v>
@@ -72636,7 +72636,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ331" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR331" t="n">
         <v>1.62</v>
@@ -72854,7 +72854,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ332" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR332" t="n">
         <v>1.58</v>
@@ -73287,7 +73287,7 @@
         <v>1.45</v>
       </c>
       <c r="AP334" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ334" t="n">
         <v>1.42</v>
@@ -75467,7 +75467,7 @@
         <v>0.45</v>
       </c>
       <c r="AP344" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AQ344" t="n">
         <v>0.42</v>
@@ -75685,7 +75685,7 @@
         <v>0.91</v>
       </c>
       <c r="AP345" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ345" t="n">
         <v>1.08</v>
@@ -76778,7 +76778,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ350" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR350" t="n">
         <v>1.54</v>
@@ -77429,7 +77429,7 @@
         <v>0.92</v>
       </c>
       <c r="AP353" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AQ353" t="n">
         <v>1.08</v>
@@ -77868,7 +77868,7 @@
         <v>2</v>
       </c>
       <c r="AQ355" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR355" t="n">
         <v>1.7</v>
@@ -78086,7 +78086,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ356" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR356" t="n">
         <v>1.56</v>
@@ -79391,7 +79391,7 @@
         <v>0.58</v>
       </c>
       <c r="AP362" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ362" t="n">
         <v>0.54</v>
@@ -79609,7 +79609,7 @@
         <v>1.67</v>
       </c>
       <c r="AP363" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ363" t="n">
         <v>1.77</v>
@@ -80778,6 +80778,1314 @@
       </c>
       <c r="BP368" t="n">
         <v>1.26</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="1" t="n">
+        <v>368</v>
+      </c>
+      <c r="B369" t="n">
+        <v>7781450</v>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E369" s="2" t="n">
+        <v>45878.89583333334</v>
+      </c>
+      <c r="F369" t="n">
+        <v>0</v>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>Chicago Fire</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>Los Angeles FC</t>
+        </is>
+      </c>
+      <c r="I369" t="n">
+        <v>1</v>
+      </c>
+      <c r="J369" t="n">
+        <v>1</v>
+      </c>
+      <c r="K369" t="n">
+        <v>2</v>
+      </c>
+      <c r="L369" t="n">
+        <v>2</v>
+      </c>
+      <c r="M369" t="n">
+        <v>2</v>
+      </c>
+      <c r="N369" t="n">
+        <v>4</v>
+      </c>
+      <c r="O369" t="inlineStr">
+        <is>
+          <t>['10', '70']</t>
+        </is>
+      </c>
+      <c r="P369" t="inlineStr">
+        <is>
+          <t>['19', '81']</t>
+        </is>
+      </c>
+      <c r="Q369" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R369" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S369" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T369" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="U369" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V369" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W369" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X369" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y369" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z369" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AA369" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="AB369" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AC369" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD369" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE369" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF369" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AG369" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH369" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI369" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ369" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AK369" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AL369" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM369" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AN369" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AO369" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AP369" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ369" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AR369" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AS369" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AT369" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AU369" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV369" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW369" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX369" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY369" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ369" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA369" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB369" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC369" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD369" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BE369" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="BF369" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BG369" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH369" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BI369" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BJ369" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BK369" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BL369" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BM369" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BN369" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BO369" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="BP369" t="n">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="1" t="n">
+        <v>369</v>
+      </c>
+      <c r="B370" t="n">
+        <v>7781453</v>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E370" s="2" t="n">
+        <v>45878.89583333334</v>
+      </c>
+      <c r="F370" t="n">
+        <v>0</v>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>St. Louis City</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>Nashville SC</t>
+        </is>
+      </c>
+      <c r="I370" t="n">
+        <v>2</v>
+      </c>
+      <c r="J370" t="n">
+        <v>0</v>
+      </c>
+      <c r="K370" t="n">
+        <v>2</v>
+      </c>
+      <c r="L370" t="n">
+        <v>3</v>
+      </c>
+      <c r="M370" t="n">
+        <v>1</v>
+      </c>
+      <c r="N370" t="n">
+        <v>4</v>
+      </c>
+      <c r="O370" t="inlineStr">
+        <is>
+          <t>['23', '39', '66']</t>
+        </is>
+      </c>
+      <c r="P370" t="inlineStr">
+        <is>
+          <t>['85']</t>
+        </is>
+      </c>
+      <c r="Q370" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R370" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S370" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T370" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="U370" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V370" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="W370" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X370" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y370" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z370" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AA370" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AB370" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AC370" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD370" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE370" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF370" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AG370" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AH370" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AI370" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ370" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AK370" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AL370" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AM370" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN370" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AO370" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AP370" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AQ370" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR370" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AS370" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AT370" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AU370" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV370" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW370" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX370" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY370" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ370" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA370" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB370" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC370" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD370" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BE370" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="BF370" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BG370" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BH370" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="BI370" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BJ370" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BK370" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL370" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BM370" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BN370" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BO370" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BP370" t="n">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="1" t="n">
+        <v>370</v>
+      </c>
+      <c r="B371" t="n">
+        <v>7781451</v>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E371" s="2" t="n">
+        <v>45878.89583333334</v>
+      </c>
+      <c r="F371" t="n">
+        <v>0</v>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>FC Dallas</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>Portland Timbers</t>
+        </is>
+      </c>
+      <c r="I371" t="n">
+        <v>1</v>
+      </c>
+      <c r="J371" t="n">
+        <v>0</v>
+      </c>
+      <c r="K371" t="n">
+        <v>1</v>
+      </c>
+      <c r="L371" t="n">
+        <v>2</v>
+      </c>
+      <c r="M371" t="n">
+        <v>0</v>
+      </c>
+      <c r="N371" t="n">
+        <v>2</v>
+      </c>
+      <c r="O371" t="inlineStr">
+        <is>
+          <t>['8', '62']</t>
+        </is>
+      </c>
+      <c r="P371" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q371" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R371" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S371" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T371" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="U371" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V371" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="W371" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X371" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y371" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z371" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AA371" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB371" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AC371" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD371" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE371" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF371" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AG371" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH371" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AI371" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ371" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AK371" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AL371" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM371" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AN371" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AO371" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AP371" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AQ371" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AR371" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AS371" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AT371" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AU371" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV371" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW371" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX371" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY371" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ371" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA371" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB371" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC371" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD371" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BE371" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="BF371" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BG371" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH371" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BI371" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BJ371" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BK371" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BL371" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BM371" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BN371" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO371" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="BP371" t="n">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="1" t="n">
+        <v>371</v>
+      </c>
+      <c r="B372" t="n">
+        <v>7781449</v>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E372" s="2" t="n">
+        <v>45878.89583333334</v>
+      </c>
+      <c r="F372" t="n">
+        <v>0</v>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>Houston Dynamo</t>
+        </is>
+      </c>
+      <c r="I372" t="n">
+        <v>2</v>
+      </c>
+      <c r="J372" t="n">
+        <v>0</v>
+      </c>
+      <c r="K372" t="n">
+        <v>2</v>
+      </c>
+      <c r="L372" t="n">
+        <v>2</v>
+      </c>
+      <c r="M372" t="n">
+        <v>2</v>
+      </c>
+      <c r="N372" t="n">
+        <v>4</v>
+      </c>
+      <c r="O372" t="inlineStr">
+        <is>
+          <t>['31', '41']</t>
+        </is>
+      </c>
+      <c r="P372" t="inlineStr">
+        <is>
+          <t>['80', '89']</t>
+        </is>
+      </c>
+      <c r="Q372" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R372" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S372" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T372" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U372" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V372" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W372" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X372" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y372" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z372" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AA372" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AB372" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AC372" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD372" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE372" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF372" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG372" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AH372" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AI372" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ372" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK372" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL372" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AM372" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AN372" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AO372" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AP372" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ372" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AR372" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AS372" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AT372" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU372" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV372" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW372" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX372" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY372" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ372" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA372" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB372" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC372" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD372" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BE372" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF372" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BG372" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH372" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="BI372" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BJ372" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BK372" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BL372" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BM372" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BN372" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BO372" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BP372" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="1" t="n">
+        <v>372</v>
+      </c>
+      <c r="B373" t="n">
+        <v>7781452</v>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E373" s="2" t="n">
+        <v>45878.90625</v>
+      </c>
+      <c r="F373" t="n">
+        <v>0</v>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>Sporting KC</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="I373" t="n">
+        <v>0</v>
+      </c>
+      <c r="J373" t="n">
+        <v>1</v>
+      </c>
+      <c r="K373" t="n">
+        <v>1</v>
+      </c>
+      <c r="L373" t="n">
+        <v>0</v>
+      </c>
+      <c r="M373" t="n">
+        <v>2</v>
+      </c>
+      <c r="N373" t="n">
+        <v>2</v>
+      </c>
+      <c r="O373" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P373" t="inlineStr">
+        <is>
+          <t>['23', '70']</t>
+        </is>
+      </c>
+      <c r="Q373" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R373" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S373" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T373" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U373" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="V373" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="W373" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="X373" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y373" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z373" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AA373" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="AB373" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC373" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD373" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE373" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF373" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AG373" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH373" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AI373" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ373" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AK373" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AL373" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AM373" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN373" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AO373" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AP373" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ373" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR373" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AS373" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AT373" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AU373" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV373" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW373" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX373" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY373" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ373" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA373" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB373" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC373" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD373" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BE373" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="BF373" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BG373" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BH373" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BI373" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BJ373" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BK373" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BL373" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BM373" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BN373" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BO373" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BP373" t="n">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="1" t="n">
+        <v>373</v>
+      </c>
+      <c r="B374" t="n">
+        <v>7781454</v>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E374" s="2" t="n">
+        <v>45878.97916666666</v>
+      </c>
+      <c r="F374" t="n">
+        <v>0</v>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>SJ Earthquakes</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="I374" t="n">
+        <v>0</v>
+      </c>
+      <c r="J374" t="n">
+        <v>0</v>
+      </c>
+      <c r="K374" t="n">
+        <v>0</v>
+      </c>
+      <c r="L374" t="n">
+        <v>2</v>
+      </c>
+      <c r="M374" t="n">
+        <v>1</v>
+      </c>
+      <c r="N374" t="n">
+        <v>3</v>
+      </c>
+      <c r="O374" t="inlineStr">
+        <is>
+          <t>['54', '90+4']</t>
+        </is>
+      </c>
+      <c r="P374" t="inlineStr">
+        <is>
+          <t>['88']</t>
+        </is>
+      </c>
+      <c r="Q374" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R374" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S374" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T374" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U374" t="n">
+        <v>4</v>
+      </c>
+      <c r="V374" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="W374" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="X374" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y374" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z374" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AA374" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="AB374" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AC374" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD374" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE374" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF374" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AG374" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AH374" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AI374" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AJ374" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AK374" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AL374" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM374" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN374" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AO374" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AP374" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ374" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AR374" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AS374" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AT374" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="AU374" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV374" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW374" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX374" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY374" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ374" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA374" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB374" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC374" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD374" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BE374" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BF374" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="BG374" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BH374" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="BI374" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BJ374" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BK374" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BL374" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BM374" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BN374" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BO374" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BP374" t="n">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP374"/>
+  <dimension ref="A1:BP379"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ5" t="n">
         <v>0.54</v>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ8" t="n">
         <v>1.67</v>
@@ -3094,7 +3094,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -3963,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ16" t="n">
         <v>2</v>
@@ -4402,7 +4402,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR18" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ20" t="n">
         <v>1.46</v>
@@ -5053,7 +5053,7 @@
         <v>1</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ21" t="n">
         <v>1</v>
@@ -5925,7 +5925,7 @@
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ25" t="n">
         <v>0.86</v>
@@ -7236,7 +7236,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AR31" t="n">
         <v>1.26</v>
@@ -8105,7 +8105,7 @@
         <v>0.5</v>
       </c>
       <c r="AP35" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ35" t="n">
         <v>1</v>
@@ -8980,7 +8980,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR39" t="n">
         <v>1.37</v>
@@ -10288,7 +10288,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR45" t="n">
         <v>1.49</v>
@@ -10503,7 +10503,7 @@
         <v>1</v>
       </c>
       <c r="AP46" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ46" t="n">
         <v>0.42</v>
@@ -10939,7 +10939,7 @@
         <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ48" t="n">
         <v>1.77</v>
@@ -12468,7 +12468,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR55" t="n">
         <v>1.09</v>
@@ -12686,7 +12686,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR56" t="n">
         <v>2</v>
@@ -13122,7 +13122,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR58" t="n">
         <v>1.73</v>
@@ -13776,7 +13776,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ61" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AR61" t="n">
         <v>1.53</v>
@@ -13991,7 +13991,7 @@
         <v>0</v>
       </c>
       <c r="AP62" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ62" t="n">
         <v>0.42</v>
@@ -14209,7 +14209,7 @@
         <v>0.5</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ63" t="n">
         <v>0.38</v>
@@ -14863,7 +14863,7 @@
         <v>0.33</v>
       </c>
       <c r="AP66" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ66" t="n">
         <v>1</v>
@@ -15081,7 +15081,7 @@
         <v>1</v>
       </c>
       <c r="AP67" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ67" t="n">
         <v>0.62</v>
@@ -17482,7 +17482,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ78" t="n">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR78" t="n">
         <v>1.36</v>
@@ -18787,10 +18787,10 @@
         <v>1.5</v>
       </c>
       <c r="AP84" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ84" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR84" t="n">
         <v>1.79</v>
@@ -19223,7 +19223,7 @@
         <v>0.5</v>
       </c>
       <c r="AP86" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ86" t="n">
         <v>1.77</v>
@@ -19662,7 +19662,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ88" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR88" t="n">
         <v>2.03</v>
@@ -21185,7 +21185,7 @@
         <v>0.5</v>
       </c>
       <c r="AP95" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ95" t="n">
         <v>1.31</v>
@@ -21621,7 +21621,7 @@
         <v>2.25</v>
       </c>
       <c r="AP97" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ97" t="n">
         <v>1.69</v>
@@ -22496,7 +22496,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ101" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR101" t="n">
         <v>1.62</v>
@@ -22714,7 +22714,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ102" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR102" t="n">
         <v>1.74</v>
@@ -24019,7 +24019,7 @@
         <v>0.33</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ108" t="n">
         <v>0.54</v>
@@ -24240,7 +24240,7 @@
         <v>0.58</v>
       </c>
       <c r="AQ109" t="n">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR109" t="n">
         <v>0</v>
@@ -25112,7 +25112,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ113" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR113" t="n">
         <v>1.09</v>
@@ -25330,7 +25330,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ114" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR114" t="n">
         <v>1.68</v>
@@ -25763,7 +25763,7 @@
         <v>0.67</v>
       </c>
       <c r="AP116" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ116" t="n">
         <v>1.17</v>
@@ -26420,7 +26420,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ119" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AR119" t="n">
         <v>0.85</v>
@@ -27074,7 +27074,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ122" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AR122" t="n">
         <v>1.8</v>
@@ -27507,7 +27507,7 @@
         <v>0.33</v>
       </c>
       <c r="AP124" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ124" t="n">
         <v>0.62</v>
@@ -28818,7 +28818,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ130" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR130" t="n">
         <v>1.32</v>
@@ -29033,7 +29033,7 @@
         <v>2</v>
       </c>
       <c r="AP131" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ131" t="n">
         <v>1.42</v>
@@ -30123,7 +30123,7 @@
         <v>0.75</v>
       </c>
       <c r="AP136" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ136" t="n">
         <v>0.92</v>
@@ -30777,7 +30777,7 @@
         <v>0.29</v>
       </c>
       <c r="AP139" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ139" t="n">
         <v>0.86</v>
@@ -30995,7 +30995,7 @@
         <v>0.33</v>
       </c>
       <c r="AP140" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ140" t="n">
         <v>0.42</v>
@@ -31652,7 +31652,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ143" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR143" t="n">
         <v>1.57</v>
@@ -32306,7 +32306,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ146" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR146" t="n">
         <v>1.7</v>
@@ -32521,7 +32521,7 @@
         <v>2</v>
       </c>
       <c r="AP147" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ147" t="n">
         <v>1.57</v>
@@ -33175,7 +33175,7 @@
         <v>1.75</v>
       </c>
       <c r="AP150" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ150" t="n">
         <v>1.17</v>
@@ -34268,7 +34268,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ155" t="n">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR155" t="n">
         <v>1.52</v>
@@ -34486,7 +34486,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ156" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR156" t="n">
         <v>1.37</v>
@@ -35358,7 +35358,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ160" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR160" t="n">
         <v>1.86</v>
@@ -36881,10 +36881,10 @@
         <v>2.5</v>
       </c>
       <c r="AP167" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AQ167" t="n">
         <v>1.75</v>
-      </c>
-      <c r="AQ167" t="n">
-        <v>1.91</v>
       </c>
       <c r="AR167" t="n">
         <v>1.63</v>
@@ -37535,7 +37535,7 @@
         <v>1.67</v>
       </c>
       <c r="AP170" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ170" t="n">
         <v>1.31</v>
@@ -37971,7 +37971,7 @@
         <v>1.2</v>
       </c>
       <c r="AP172" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ172" t="n">
         <v>1.33</v>
@@ -38189,7 +38189,7 @@
         <v>0.33</v>
       </c>
       <c r="AP173" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ173" t="n">
         <v>0.38</v>
@@ -38410,7 +38410,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ174" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR174" t="n">
         <v>0.93</v>
@@ -38628,7 +38628,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ175" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR175" t="n">
         <v>1.48</v>
@@ -38846,7 +38846,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ176" t="n">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR176" t="n">
         <v>1.79</v>
@@ -40369,10 +40369,10 @@
         <v>0.67</v>
       </c>
       <c r="AP183" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ183" t="n">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR183" t="n">
         <v>1.84</v>
@@ -42116,7 +42116,7 @@
         <v>2</v>
       </c>
       <c r="AQ191" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR191" t="n">
         <v>1.63</v>
@@ -42334,7 +42334,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ192" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR192" t="n">
         <v>1.55</v>
@@ -42552,7 +42552,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ193" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AR193" t="n">
         <v>1.98</v>
@@ -44075,7 +44075,7 @@
         <v>0.83</v>
       </c>
       <c r="AP200" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ200" t="n">
         <v>0.42</v>
@@ -44950,7 +44950,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ204" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR204" t="n">
         <v>1.66</v>
@@ -45168,7 +45168,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ205" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR205" t="n">
         <v>1.17</v>
@@ -45819,7 +45819,7 @@
         <v>0.83</v>
       </c>
       <c r="AP208" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ208" t="n">
         <v>1.1</v>
@@ -47127,7 +47127,7 @@
         <v>1.57</v>
       </c>
       <c r="AP214" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ214" t="n">
         <v>1.17</v>
@@ -47348,7 +47348,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ215" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AR215" t="n">
         <v>1.72</v>
@@ -47999,7 +47999,7 @@
         <v>1</v>
       </c>
       <c r="AP218" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ218" t="n">
         <v>1.33</v>
@@ -49525,7 +49525,7 @@
         <v>1.5</v>
       </c>
       <c r="AP225" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ225" t="n">
         <v>1.42</v>
@@ -50179,10 +50179,10 @@
         <v>0.57</v>
       </c>
       <c r="AP228" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ228" t="n">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR228" t="n">
         <v>1.49</v>
@@ -51272,7 +51272,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ233" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR233" t="n">
         <v>1.54</v>
@@ -51487,7 +51487,7 @@
         <v>1.17</v>
       </c>
       <c r="AP234" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ234" t="n">
         <v>1.08</v>
@@ -51708,7 +51708,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ235" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR235" t="n">
         <v>1.11</v>
@@ -52580,7 +52580,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ239" t="n">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR239" t="n">
         <v>1.29</v>
@@ -52795,7 +52795,7 @@
         <v>0.71</v>
       </c>
       <c r="AP240" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ240" t="n">
         <v>0.62</v>
@@ -53449,7 +53449,7 @@
         <v>0.33</v>
       </c>
       <c r="AP243" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ243" t="n">
         <v>0.42</v>
@@ -53667,7 +53667,7 @@
         <v>1.5</v>
       </c>
       <c r="AP244" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ244" t="n">
         <v>1.69</v>
@@ -54321,10 +54321,10 @@
         <v>0.89</v>
       </c>
       <c r="AP247" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ247" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR247" t="n">
         <v>1.32</v>
@@ -55632,7 +55632,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ253" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR253" t="n">
         <v>1.83</v>
@@ -57158,7 +57158,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ260" t="n">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR260" t="n">
         <v>1.74</v>
@@ -57373,7 +57373,7 @@
         <v>1.29</v>
       </c>
       <c r="AP261" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ261" t="n">
         <v>2</v>
@@ -59771,7 +59771,7 @@
         <v>1.25</v>
       </c>
       <c r="AP272" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ272" t="n">
         <v>1.17</v>
@@ -60210,7 +60210,7 @@
         <v>1</v>
       </c>
       <c r="AQ274" t="n">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR274" t="n">
         <v>1.48</v>
@@ -61300,7 +61300,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ279" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR279" t="n">
         <v>1.21</v>
@@ -61515,7 +61515,7 @@
         <v>1.73</v>
       </c>
       <c r="AP280" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ280" t="n">
         <v>1.86</v>
@@ -61951,7 +61951,7 @@
         <v>1.67</v>
       </c>
       <c r="AP282" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ282" t="n">
         <v>1.77</v>
@@ -62608,7 +62608,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ285" t="n">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR285" t="n">
         <v>1.48</v>
@@ -63262,7 +63262,7 @@
         <v>1</v>
       </c>
       <c r="AQ288" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR288" t="n">
         <v>1.54</v>
@@ -65003,7 +65003,7 @@
         <v>2</v>
       </c>
       <c r="AP296" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ296" t="n">
         <v>1.57</v>
@@ -65439,7 +65439,7 @@
         <v>1.8</v>
       </c>
       <c r="AP298" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ298" t="n">
         <v>1.69</v>
@@ -65878,7 +65878,7 @@
         <v>0.58</v>
       </c>
       <c r="AQ300" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AR300" t="n">
         <v>1.42</v>
@@ -67404,7 +67404,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ307" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AR307" t="n">
         <v>1.37</v>
@@ -67622,7 +67622,7 @@
         <v>2</v>
       </c>
       <c r="AQ308" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR308" t="n">
         <v>1.69</v>
@@ -68273,7 +68273,7 @@
         <v>0.73</v>
       </c>
       <c r="AP311" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ311" t="n">
         <v>0.86</v>
@@ -68709,7 +68709,7 @@
         <v>1.4</v>
       </c>
       <c r="AP313" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ313" t="n">
         <v>1.08</v>
@@ -68930,7 +68930,7 @@
         <v>1</v>
       </c>
       <c r="AQ314" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR314" t="n">
         <v>1.54</v>
@@ -69581,7 +69581,7 @@
         <v>1.44</v>
       </c>
       <c r="AP317" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ317" t="n">
         <v>1.45</v>
@@ -70453,7 +70453,7 @@
         <v>0.89</v>
       </c>
       <c r="AP321" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ321" t="n">
         <v>0.62</v>
@@ -71107,7 +71107,7 @@
         <v>1.42</v>
       </c>
       <c r="AP324" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ324" t="n">
         <v>1.31</v>
@@ -71325,10 +71325,10 @@
         <v>2</v>
       </c>
       <c r="AP325" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ325" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AR325" t="n">
         <v>1.63</v>
@@ -72197,7 +72197,7 @@
         <v>0.7</v>
       </c>
       <c r="AP329" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ329" t="n">
         <v>1.08</v>
@@ -72851,7 +72851,7 @@
         <v>0.88</v>
       </c>
       <c r="AP332" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ332" t="n">
         <v>1.1</v>
@@ -73072,7 +73072,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ333" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR333" t="n">
         <v>1.63</v>
@@ -73723,7 +73723,7 @@
         <v>1</v>
       </c>
       <c r="AP336" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ336" t="n">
         <v>1.33</v>
@@ -73944,7 +73944,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ337" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR337" t="n">
         <v>1.25</v>
@@ -74159,10 +74159,10 @@
         <v>1.8</v>
       </c>
       <c r="AP338" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ338" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AR338" t="n">
         <v>1.66</v>
@@ -74380,7 +74380,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ339" t="n">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR339" t="n">
         <v>1.41</v>
@@ -78522,7 +78522,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ358" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR358" t="n">
         <v>1.78</v>
@@ -79176,7 +79176,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ361" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR361" t="n">
         <v>1.47</v>
@@ -81368,13 +81368,13 @@
         <v>2.55</v>
       </c>
       <c r="AU371" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV371" t="n">
         <v>3</v>
       </c>
       <c r="AW371" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AX371" t="n">
         <v>6</v>
@@ -81804,13 +81804,13 @@
         <v>3.16</v>
       </c>
       <c r="AU373" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AV373" t="n">
         <v>5</v>
       </c>
       <c r="AW373" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AX373" t="n">
         <v>1</v>
@@ -82086,6 +82086,1096 @@
       </c>
       <c r="BP374" t="n">
         <v>1.5</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="1" t="n">
+        <v>374</v>
+      </c>
+      <c r="B375" t="n">
+        <v>7781457</v>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E375" s="2" t="n">
+        <v>45879.79166666666</v>
+      </c>
+      <c r="F375" t="n">
+        <v>0</v>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>New York RB</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="I375" t="n">
+        <v>0</v>
+      </c>
+      <c r="J375" t="n">
+        <v>1</v>
+      </c>
+      <c r="K375" t="n">
+        <v>1</v>
+      </c>
+      <c r="L375" t="n">
+        <v>2</v>
+      </c>
+      <c r="M375" t="n">
+        <v>1</v>
+      </c>
+      <c r="N375" t="n">
+        <v>3</v>
+      </c>
+      <c r="O375" t="inlineStr">
+        <is>
+          <t>['52', '90+9']</t>
+        </is>
+      </c>
+      <c r="P375" t="inlineStr">
+        <is>
+          <t>['3']</t>
+        </is>
+      </c>
+      <c r="Q375" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R375" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S375" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T375" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="U375" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V375" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="W375" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X375" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y375" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z375" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AA375" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="AB375" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AC375" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD375" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE375" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF375" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AG375" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH375" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AI375" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ375" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AK375" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AL375" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AM375" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AN375" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AO375" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP375" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AQ375" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AR375" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AS375" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AT375" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AU375" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV375" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW375" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX375" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY375" t="n">
+        <v>24</v>
+      </c>
+      <c r="AZ375" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA375" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB375" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC375" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD375" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BE375" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF375" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BG375" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BH375" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BI375" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BJ375" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BK375" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BL375" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BM375" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BN375" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO375" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BP375" t="n">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="1" t="n">
+        <v>375</v>
+      </c>
+      <c r="B376" t="n">
+        <v>7781456</v>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E376" s="2" t="n">
+        <v>45879.79166666666</v>
+      </c>
+      <c r="F376" t="n">
+        <v>0</v>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>Minnesota United</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>Colorado Rapids</t>
+        </is>
+      </c>
+      <c r="I376" t="n">
+        <v>0</v>
+      </c>
+      <c r="J376" t="n">
+        <v>0</v>
+      </c>
+      <c r="K376" t="n">
+        <v>0</v>
+      </c>
+      <c r="L376" t="n">
+        <v>1</v>
+      </c>
+      <c r="M376" t="n">
+        <v>2</v>
+      </c>
+      <c r="N376" t="n">
+        <v>3</v>
+      </c>
+      <c r="O376" t="inlineStr">
+        <is>
+          <t>['73']</t>
+        </is>
+      </c>
+      <c r="P376" t="inlineStr">
+        <is>
+          <t>['60', '70']</t>
+        </is>
+      </c>
+      <c r="Q376" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R376" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S376" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="T376" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U376" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="V376" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W376" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X376" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y376" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z376" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA376" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="AB376" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AC376" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD376" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE376" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF376" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG376" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AH376" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AI376" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ376" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AK376" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AL376" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM376" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AN376" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AO376" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AP376" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AQ376" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR376" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AS376" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AT376" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AU376" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV376" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW376" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX376" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY376" t="n">
+        <v>23</v>
+      </c>
+      <c r="AZ376" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA376" t="n">
+        <v>13</v>
+      </c>
+      <c r="BB376" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC376" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD376" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BE376" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="BF376" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BG376" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH376" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="BI376" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ376" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BK376" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BL376" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BM376" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BN376" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BO376" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BP376" t="n">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="1" t="n">
+        <v>376</v>
+      </c>
+      <c r="B377" t="n">
+        <v>7781455</v>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E377" s="2" t="n">
+        <v>45879.79166666666</v>
+      </c>
+      <c r="F377" t="n">
+        <v>0</v>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>FC Cincinnati</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="I377" t="n">
+        <v>0</v>
+      </c>
+      <c r="J377" t="n">
+        <v>0</v>
+      </c>
+      <c r="K377" t="n">
+        <v>0</v>
+      </c>
+      <c r="L377" t="n">
+        <v>0</v>
+      </c>
+      <c r="M377" t="n">
+        <v>1</v>
+      </c>
+      <c r="N377" t="n">
+        <v>1</v>
+      </c>
+      <c r="O377" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P377" t="inlineStr">
+        <is>
+          <t>['85']</t>
+        </is>
+      </c>
+      <c r="Q377" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R377" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S377" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T377" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U377" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V377" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="W377" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X377" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y377" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z377" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AA377" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB377" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="AC377" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD377" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE377" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF377" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AG377" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH377" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AI377" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ377" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AK377" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL377" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM377" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN377" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AO377" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AP377" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AQ377" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AR377" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AS377" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AT377" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AU377" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV377" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW377" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX377" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY377" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ377" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA377" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB377" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC377" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD377" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BE377" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF377" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="BG377" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BH377" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="BI377" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BJ377" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BK377" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="BL377" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BM377" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BN377" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BO377" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BP377" t="n">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="1" t="n">
+        <v>377</v>
+      </c>
+      <c r="B378" t="n">
+        <v>7781458</v>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E378" s="2" t="n">
+        <v>45879.875</v>
+      </c>
+      <c r="F378" t="n">
+        <v>0</v>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>Orlando City</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>Inter Miami</t>
+        </is>
+      </c>
+      <c r="I378" t="n">
+        <v>1</v>
+      </c>
+      <c r="J378" t="n">
+        <v>1</v>
+      </c>
+      <c r="K378" t="n">
+        <v>2</v>
+      </c>
+      <c r="L378" t="n">
+        <v>4</v>
+      </c>
+      <c r="M378" t="n">
+        <v>1</v>
+      </c>
+      <c r="N378" t="n">
+        <v>5</v>
+      </c>
+      <c r="O378" t="inlineStr">
+        <is>
+          <t>['2', '50', '58', '88']</t>
+        </is>
+      </c>
+      <c r="P378" t="inlineStr">
+        <is>
+          <t>['5']</t>
+        </is>
+      </c>
+      <c r="Q378" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R378" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="S378" t="n">
+        <v>4</v>
+      </c>
+      <c r="T378" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U378" t="n">
+        <v>4</v>
+      </c>
+      <c r="V378" t="n">
+        <v>2</v>
+      </c>
+      <c r="W378" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="X378" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y378" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z378" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AA378" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB378" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AC378" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD378" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE378" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF378" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AG378" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AH378" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AI378" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ378" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AK378" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AL378" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AM378" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AN378" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO378" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AP378" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AQ378" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AR378" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS378" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AT378" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AU378" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV378" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW378" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX378" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY378" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ378" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA378" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB378" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC378" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD378" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BE378" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="BF378" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BG378" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BH378" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="BI378" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BJ378" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BK378" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BL378" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BM378" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BN378" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BO378" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="BP378" t="n">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="1" t="n">
+        <v>378</v>
+      </c>
+      <c r="B379" t="n">
+        <v>7781459</v>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E379" s="2" t="n">
+        <v>45879.95833333334</v>
+      </c>
+      <c r="F379" t="n">
+        <v>0</v>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>LA Galaxy</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>Seattle Sounders</t>
+        </is>
+      </c>
+      <c r="I379" t="n">
+        <v>0</v>
+      </c>
+      <c r="J379" t="n">
+        <v>2</v>
+      </c>
+      <c r="K379" t="n">
+        <v>2</v>
+      </c>
+      <c r="L379" t="n">
+        <v>0</v>
+      </c>
+      <c r="M379" t="n">
+        <v>4</v>
+      </c>
+      <c r="N379" t="n">
+        <v>4</v>
+      </c>
+      <c r="O379" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P379" t="inlineStr">
+        <is>
+          <t>['25', '37', '54', '85']</t>
+        </is>
+      </c>
+      <c r="Q379" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R379" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S379" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T379" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="U379" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V379" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="W379" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X379" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y379" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z379" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AA379" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB379" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AC379" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD379" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE379" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF379" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AG379" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH379" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI379" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ379" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AK379" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AL379" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AM379" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AN379" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO379" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AP379" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AQ379" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AR379" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AS379" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AT379" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AU379" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV379" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW379" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX379" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY379" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ379" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA379" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB379" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC379" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD379" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BE379" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="BF379" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BG379" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH379" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BI379" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BJ379" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="BK379" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BL379" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BM379" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BN379" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BO379" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="BP379" t="n">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
@@ -81150,13 +81150,13 @@
         <v>3.14</v>
       </c>
       <c r="AU370" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV370" t="n">
         <v>6</v>
       </c>
       <c r="AW370" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX370" t="n">
         <v>12</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP379"/>
+  <dimension ref="A1:BP381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ3" t="n">
         <v>1.08</v>
@@ -3312,7 +3312,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ17" t="n">
         <v>0.42</v>
@@ -7018,7 +7018,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR30" t="n">
         <v>0</v>
@@ -10285,7 +10285,7 @@
         <v>1</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ45" t="n">
         <v>0.93</v>
@@ -11375,7 +11375,7 @@
         <v>0</v>
       </c>
       <c r="AP50" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ50" t="n">
         <v>1.86</v>
@@ -12468,7 +12468,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ55" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR55" t="n">
         <v>1.09</v>
@@ -13558,7 +13558,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ60" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR60" t="n">
         <v>0.8100000000000001</v>
@@ -14212,7 +14212,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ63" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR63" t="n">
         <v>1.28</v>
@@ -14427,7 +14427,7 @@
         <v>3</v>
       </c>
       <c r="AP64" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ64" t="n">
         <v>1.08</v>
@@ -17697,7 +17697,7 @@
         <v>3</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ79" t="n">
         <v>1.67</v>
@@ -18790,7 +18790,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ84" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR84" t="n">
         <v>1.79</v>
@@ -20313,7 +20313,7 @@
         <v>1.5</v>
       </c>
       <c r="AP91" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ91" t="n">
         <v>1.46</v>
@@ -20534,7 +20534,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ92" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR92" t="n">
         <v>1.22</v>
@@ -23365,7 +23365,7 @@
         <v>0.25</v>
       </c>
       <c r="AP105" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ105" t="n">
         <v>1</v>
@@ -25330,7 +25330,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ114" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR114" t="n">
         <v>1.68</v>
@@ -26856,7 +26856,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ121" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR121" t="n">
         <v>1.37</v>
@@ -28379,7 +28379,7 @@
         <v>1.5</v>
       </c>
       <c r="AP128" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ128" t="n">
         <v>2</v>
@@ -31213,7 +31213,7 @@
         <v>1</v>
       </c>
       <c r="AP141" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ141" t="n">
         <v>1.31</v>
@@ -31652,7 +31652,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ143" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR143" t="n">
         <v>1.57</v>
@@ -32739,7 +32739,7 @@
         <v>1.8</v>
       </c>
       <c r="AP148" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ148" t="n">
         <v>1.42</v>
@@ -33829,7 +33829,7 @@
         <v>0.5</v>
       </c>
       <c r="AP153" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ153" t="n">
         <v>0.54</v>
@@ -35358,7 +35358,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ160" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR160" t="n">
         <v>1.86</v>
@@ -36448,7 +36448,7 @@
         <v>1</v>
       </c>
       <c r="AQ165" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR165" t="n">
         <v>1.47</v>
@@ -38192,7 +38192,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ173" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR173" t="n">
         <v>1.36</v>
@@ -38410,7 +38410,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ174" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR174" t="n">
         <v>0.93</v>
@@ -40590,7 +40590,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ184" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR184" t="n">
         <v>1.58</v>
@@ -43639,7 +43639,7 @@
         <v>1.5</v>
       </c>
       <c r="AP198" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ198" t="n">
         <v>1.69</v>
@@ -44950,7 +44950,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ204" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR204" t="n">
         <v>1.66</v>
@@ -45601,7 +45601,7 @@
         <v>1.17</v>
       </c>
       <c r="AP207" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ207" t="n">
         <v>1.77</v>
@@ -46258,7 +46258,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ210" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR210" t="n">
         <v>1.62</v>
@@ -46473,7 +46473,7 @@
         <v>2</v>
       </c>
       <c r="AP211" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ211" t="n">
         <v>1.45</v>
@@ -49961,7 +49961,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP227" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ227" t="n">
         <v>0.86</v>
@@ -51272,7 +51272,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ233" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR233" t="n">
         <v>1.54</v>
@@ -53013,7 +53013,7 @@
         <v>1.71</v>
       </c>
       <c r="AP241" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ241" t="n">
         <v>1.45</v>
@@ -54324,7 +54324,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ247" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR247" t="n">
         <v>1.32</v>
@@ -56504,7 +56504,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ257" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR257" t="n">
         <v>1.55</v>
@@ -61082,7 +61082,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ278" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR278" t="n">
         <v>1.5</v>
@@ -63262,7 +63262,7 @@
         <v>1</v>
       </c>
       <c r="AQ288" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR288" t="n">
         <v>1.54</v>
@@ -63480,7 +63480,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ289" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR289" t="n">
         <v>1.91</v>
@@ -65221,7 +65221,7 @@
         <v>1.6</v>
       </c>
       <c r="AP297" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ297" t="n">
         <v>1.77</v>
@@ -68491,7 +68491,7 @@
         <v>1.9</v>
       </c>
       <c r="AP312" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ312" t="n">
         <v>1.46</v>
@@ -69799,7 +69799,7 @@
         <v>0.78</v>
       </c>
       <c r="AP318" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ318" t="n">
         <v>1.08</v>
@@ -71543,7 +71543,7 @@
         <v>0.8</v>
       </c>
       <c r="AP326" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ326" t="n">
         <v>0.62</v>
@@ -73944,7 +73944,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ337" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR337" t="n">
         <v>1.25</v>
@@ -76560,7 +76560,7 @@
         <v>2</v>
       </c>
       <c r="AQ349" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR349" t="n">
         <v>1.77</v>
@@ -78301,7 +78301,7 @@
         <v>1.92</v>
       </c>
       <c r="AP357" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ357" t="n">
         <v>1.86</v>
@@ -78955,7 +78955,7 @@
         <v>1.1</v>
       </c>
       <c r="AP360" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ360" t="n">
         <v>1</v>
@@ -82228,7 +82228,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ375" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR375" t="n">
         <v>1.61</v>
@@ -83176,6 +83176,442 @@
       </c>
       <c r="BP379" t="n">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="1" t="n">
+        <v>379</v>
+      </c>
+      <c r="B380" t="n">
+        <v>7781461</v>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E380" s="2" t="n">
+        <v>45885.85416666666</v>
+      </c>
+      <c r="F380" t="n">
+        <v>0</v>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>Inter Miami</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>LA Galaxy</t>
+        </is>
+      </c>
+      <c r="I380" t="n">
+        <v>1</v>
+      </c>
+      <c r="J380" t="n">
+        <v>0</v>
+      </c>
+      <c r="K380" t="n">
+        <v>1</v>
+      </c>
+      <c r="L380" t="n">
+        <v>3</v>
+      </c>
+      <c r="M380" t="n">
+        <v>1</v>
+      </c>
+      <c r="N380" t="n">
+        <v>4</v>
+      </c>
+      <c r="O380" t="inlineStr">
+        <is>
+          <t>['43', '84', '89']</t>
+        </is>
+      </c>
+      <c r="P380" t="inlineStr">
+        <is>
+          <t>['59']</t>
+        </is>
+      </c>
+      <c r="Q380" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R380" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="S380" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T380" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="U380" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="V380" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="W380" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="X380" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y380" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z380" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA380" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB380" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AC380" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD380" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE380" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF380" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AG380" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AH380" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AI380" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ380" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AK380" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AL380" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AM380" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AN380" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AO380" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AP380" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ380" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AR380" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AS380" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AT380" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AU380" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV380" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW380" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX380" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY380" t="n">
+        <v>29</v>
+      </c>
+      <c r="AZ380" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA380" t="n">
+        <v>13</v>
+      </c>
+      <c r="BB380" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC380" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD380" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BE380" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF380" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BG380" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH380" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI380" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BJ380" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BK380" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BL380" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BM380" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BN380" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BO380" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BP380" t="n">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="1" t="n">
+        <v>380</v>
+      </c>
+      <c r="B381" t="n">
+        <v>7781460</v>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E381" s="2" t="n">
+        <v>45885.85416666666</v>
+      </c>
+      <c r="F381" t="n">
+        <v>0</v>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="I381" t="n">
+        <v>1</v>
+      </c>
+      <c r="J381" t="n">
+        <v>0</v>
+      </c>
+      <c r="K381" t="n">
+        <v>1</v>
+      </c>
+      <c r="L381" t="n">
+        <v>1</v>
+      </c>
+      <c r="M381" t="n">
+        <v>0</v>
+      </c>
+      <c r="N381" t="n">
+        <v>1</v>
+      </c>
+      <c r="O381" t="inlineStr">
+        <is>
+          <t>['35']</t>
+        </is>
+      </c>
+      <c r="P381" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q381" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R381" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S381" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T381" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="U381" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V381" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="W381" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X381" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y381" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z381" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA381" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB381" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AC381" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD381" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE381" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF381" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AG381" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AH381" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AI381" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ381" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AK381" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL381" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM381" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN381" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AO381" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AP381" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AQ381" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AR381" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AS381" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AT381" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AU381" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV381" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW381" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX381" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY381" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ381" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA381" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB381" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC381" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD381" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BE381" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF381" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BG381" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH381" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI381" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BJ381" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BK381" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BL381" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BM381" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BN381" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BO381" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BP381" t="n">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP381"/>
+  <dimension ref="A1:BP391"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2219,10 +2219,10 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2437,10 +2437,10 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -2658,7 +2658,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -3745,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ15" t="n">
         <v>1.57</v>
@@ -4184,7 +4184,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
@@ -4402,7 +4402,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR18" t="n">
         <v>0</v>
@@ -4617,10 +4617,10 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR19" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ20" t="n">
         <v>1.46</v>
@@ -5053,7 +5053,7 @@
         <v>1</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ21" t="n">
         <v>1</v>
@@ -5274,7 +5274,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AR22" t="n">
         <v>0</v>
@@ -5489,10 +5489,10 @@
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR23" t="n">
         <v>0</v>
@@ -5925,7 +5925,7 @@
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ25" t="n">
         <v>0.86</v>
@@ -6143,10 +6143,10 @@
         <v>3</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR26" t="n">
         <v>0</v>
@@ -6579,7 +6579,7 @@
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ28" t="n">
         <v>1.33</v>
@@ -6800,7 +6800,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR29" t="n">
         <v>0</v>
@@ -7672,7 +7672,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR33" t="n">
         <v>2.34</v>
@@ -8326,7 +8326,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR36" t="n">
         <v>1.1</v>
@@ -8541,10 +8541,10 @@
         <v>3</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR37" t="n">
         <v>0.71</v>
@@ -8977,7 +8977,7 @@
         <v>1</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ39" t="n">
         <v>1</v>
@@ -10506,7 +10506,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR46" t="n">
         <v>0.79</v>
@@ -10721,7 +10721,7 @@
         <v>1.5</v>
       </c>
       <c r="AP47" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AQ47" t="n">
         <v>1.69</v>
@@ -10939,7 +10939,7 @@
         <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ48" t="n">
         <v>1.77</v>
@@ -11378,7 +11378,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AR50" t="n">
         <v>1.16</v>
@@ -12686,7 +12686,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR56" t="n">
         <v>2</v>
@@ -12904,7 +12904,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR57" t="n">
         <v>1.41</v>
@@ -13555,7 +13555,7 @@
         <v>0</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ60" t="n">
         <v>0.36</v>
@@ -13994,7 +13994,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ62" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR62" t="n">
         <v>1.47</v>
@@ -14209,7 +14209,7 @@
         <v>0.5</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ63" t="n">
         <v>0.36</v>
@@ -14863,7 +14863,7 @@
         <v>0.33</v>
       </c>
       <c r="AP66" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ66" t="n">
         <v>1</v>
@@ -15081,10 +15081,10 @@
         <v>1</v>
       </c>
       <c r="AP67" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ67" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR67" t="n">
         <v>1.51</v>
@@ -15302,7 +15302,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ68" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR68" t="n">
         <v>1.35</v>
@@ -15520,7 +15520,7 @@
         <v>1</v>
       </c>
       <c r="AQ69" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR69" t="n">
         <v>1.57</v>
@@ -15953,7 +15953,7 @@
         <v>0</v>
       </c>
       <c r="AP71" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ71" t="n">
         <v>1.17</v>
@@ -16174,7 +16174,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ72" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR72" t="n">
         <v>1.28</v>
@@ -16825,7 +16825,7 @@
         <v>3</v>
       </c>
       <c r="AP75" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ75" t="n">
         <v>2</v>
@@ -17043,7 +17043,7 @@
         <v>0.5</v>
       </c>
       <c r="AP76" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ76" t="n">
         <v>0.54</v>
@@ -17261,7 +17261,7 @@
         <v>3</v>
       </c>
       <c r="AP77" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AQ77" t="n">
         <v>1.57</v>
@@ -17479,7 +17479,7 @@
         <v>0.5</v>
       </c>
       <c r="AP78" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ78" t="n">
         <v>0.93</v>
@@ -17700,7 +17700,7 @@
         <v>2</v>
       </c>
       <c r="AQ79" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR79" t="n">
         <v>1.02</v>
@@ -17918,7 +17918,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ80" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR80" t="n">
         <v>1.47</v>
@@ -18351,7 +18351,7 @@
         <v>0.2</v>
       </c>
       <c r="AP82" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ82" t="n">
         <v>0.86</v>
@@ -18572,7 +18572,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ83" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR83" t="n">
         <v>1.25</v>
@@ -18787,7 +18787,7 @@
         <v>1.5</v>
       </c>
       <c r="AP84" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ84" t="n">
         <v>0.86</v>
@@ -19008,7 +19008,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ85" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AR85" t="n">
         <v>1.74</v>
@@ -19444,7 +19444,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ87" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR87" t="n">
         <v>1.67</v>
@@ -19662,7 +19662,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ88" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR88" t="n">
         <v>2.03</v>
@@ -20095,7 +20095,7 @@
         <v>1</v>
       </c>
       <c r="AP90" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ90" t="n">
         <v>1.17</v>
@@ -20752,7 +20752,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ93" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR93" t="n">
         <v>1.55</v>
@@ -21621,7 +21621,7 @@
         <v>2.25</v>
       </c>
       <c r="AP97" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ97" t="n">
         <v>1.69</v>
@@ -21839,7 +21839,7 @@
         <v>1.5</v>
       </c>
       <c r="AP98" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ98" t="n">
         <v>1.17</v>
@@ -22060,7 +22060,7 @@
         <v>1</v>
       </c>
       <c r="AQ99" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR99" t="n">
         <v>1.57</v>
@@ -22278,7 +22278,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ100" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR100" t="n">
         <v>1.32</v>
@@ -22714,7 +22714,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ102" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR102" t="n">
         <v>1.74</v>
@@ -23150,7 +23150,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ104" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR104" t="n">
         <v>1.82</v>
@@ -23583,7 +23583,7 @@
         <v>1.75</v>
       </c>
       <c r="AP106" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AQ106" t="n">
         <v>1.77</v>
@@ -24019,7 +24019,7 @@
         <v>0.33</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ108" t="n">
         <v>0.54</v>
@@ -24237,7 +24237,7 @@
         <v>0.33</v>
       </c>
       <c r="AP109" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AQ109" t="n">
         <v>0.93</v>
@@ -24676,7 +24676,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ111" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AR111" t="n">
         <v>1.4</v>
@@ -24894,7 +24894,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ112" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR112" t="n">
         <v>1.82</v>
@@ -25112,7 +25112,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ113" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR113" t="n">
         <v>1.09</v>
@@ -25545,7 +25545,7 @@
         <v>2</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ115" t="n">
         <v>2</v>
@@ -26417,7 +26417,7 @@
         <v>3</v>
       </c>
       <c r="AP119" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ119" t="n">
         <v>1.75</v>
@@ -26638,7 +26638,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ120" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR120" t="n">
         <v>1.71</v>
@@ -26853,7 +26853,7 @@
         <v>0.5</v>
       </c>
       <c r="AP121" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ121" t="n">
         <v>0.36</v>
@@ -27507,10 +27507,10 @@
         <v>0.33</v>
       </c>
       <c r="AP124" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ124" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR124" t="n">
         <v>1.35</v>
@@ -27728,7 +27728,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ125" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR125" t="n">
         <v>1.71</v>
@@ -27943,7 +27943,7 @@
         <v>1.25</v>
       </c>
       <c r="AP126" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AQ126" t="n">
         <v>1.77</v>
@@ -28161,7 +28161,7 @@
         <v>0.5</v>
       </c>
       <c r="AP127" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ127" t="n">
         <v>1.08</v>
@@ -28597,10 +28597,10 @@
         <v>1.5</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ129" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AR129" t="n">
         <v>1.16</v>
@@ -29033,10 +29033,10 @@
         <v>2</v>
       </c>
       <c r="AP131" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ131" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR131" t="n">
         <v>1.72</v>
@@ -29687,10 +29687,10 @@
         <v>0.75</v>
       </c>
       <c r="AP134" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ134" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR134" t="n">
         <v>1.18</v>
@@ -29908,7 +29908,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ135" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR135" t="n">
         <v>1.91</v>
@@ -30126,7 +30126,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ136" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR136" t="n">
         <v>1.62</v>
@@ -30341,7 +30341,7 @@
         <v>0.4</v>
       </c>
       <c r="AP137" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AQ137" t="n">
         <v>1.08</v>
@@ -30562,7 +30562,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ138" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR138" t="n">
         <v>1.6</v>
@@ -30777,7 +30777,7 @@
         <v>0.29</v>
       </c>
       <c r="AP139" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ139" t="n">
         <v>0.86</v>
@@ -30995,10 +30995,10 @@
         <v>0.33</v>
       </c>
       <c r="AP140" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ140" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR140" t="n">
         <v>1.75</v>
@@ -32303,10 +32303,10 @@
         <v>0.8</v>
       </c>
       <c r="AP146" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ146" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR146" t="n">
         <v>1.7</v>
@@ -32521,7 +32521,7 @@
         <v>2</v>
       </c>
       <c r="AP147" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ147" t="n">
         <v>1.57</v>
@@ -32742,7 +32742,7 @@
         <v>2</v>
       </c>
       <c r="AQ148" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR148" t="n">
         <v>1.42</v>
@@ -32960,7 +32960,7 @@
         <v>2</v>
       </c>
       <c r="AQ149" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR149" t="n">
         <v>1.35</v>
@@ -33611,7 +33611,7 @@
         <v>1.4</v>
       </c>
       <c r="AP152" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AQ152" t="n">
         <v>1.31</v>
@@ -34047,10 +34047,10 @@
         <v>1.5</v>
       </c>
       <c r="AP154" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AQ154" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR154" t="n">
         <v>1.93</v>
@@ -34701,7 +34701,7 @@
         <v>1.6</v>
       </c>
       <c r="AP157" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ157" t="n">
         <v>1.77</v>
@@ -34919,7 +34919,7 @@
         <v>1.2</v>
       </c>
       <c r="AP158" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ158" t="n">
         <v>1.77</v>
@@ -35140,7 +35140,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ159" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR159" t="n">
         <v>1.56</v>
@@ -36012,7 +36012,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ163" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR163" t="n">
         <v>1.74</v>
@@ -36230,7 +36230,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ164" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AR164" t="n">
         <v>1.68</v>
@@ -36663,10 +36663,10 @@
         <v>0.25</v>
       </c>
       <c r="AP166" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ166" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR166" t="n">
         <v>1.46</v>
@@ -36881,7 +36881,7 @@
         <v>2.5</v>
       </c>
       <c r="AP167" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ167" t="n">
         <v>1.75</v>
@@ -37099,10 +37099,10 @@
         <v>0.8</v>
       </c>
       <c r="AP168" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AQ168" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR168" t="n">
         <v>1.12</v>
@@ -37320,7 +37320,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ169" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR169" t="n">
         <v>1.55</v>
@@ -37535,7 +37535,7 @@
         <v>1.67</v>
       </c>
       <c r="AP170" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ170" t="n">
         <v>1.31</v>
@@ -38189,7 +38189,7 @@
         <v>0.33</v>
       </c>
       <c r="AP173" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ173" t="n">
         <v>0.36</v>
@@ -38628,7 +38628,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ175" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR175" t="n">
         <v>1.48</v>
@@ -39279,7 +39279,7 @@
         <v>0.75</v>
       </c>
       <c r="AP178" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ178" t="n">
         <v>1.08</v>
@@ -39497,10 +39497,10 @@
         <v>0.6</v>
       </c>
       <c r="AP179" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ179" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR179" t="n">
         <v>1.14</v>
@@ -39718,7 +39718,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ180" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR180" t="n">
         <v>1.9</v>
@@ -40151,10 +40151,10 @@
         <v>2.2</v>
       </c>
       <c r="AP182" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AQ182" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR182" t="n">
         <v>1.76</v>
@@ -40369,7 +40369,7 @@
         <v>0.67</v>
       </c>
       <c r="AP183" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ183" t="n">
         <v>0.93</v>
@@ -40805,10 +40805,10 @@
         <v>1.5</v>
       </c>
       <c r="AP185" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AQ185" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AR185" t="n">
         <v>1.31</v>
@@ -41462,7 +41462,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ188" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR188" t="n">
         <v>1.54</v>
@@ -41677,10 +41677,10 @@
         <v>0.2</v>
       </c>
       <c r="AP189" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ189" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR189" t="n">
         <v>1.44</v>
@@ -42116,7 +42116,7 @@
         <v>2</v>
       </c>
       <c r="AQ191" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR191" t="n">
         <v>1.63</v>
@@ -42767,7 +42767,7 @@
         <v>0.83</v>
       </c>
       <c r="AP194" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AQ194" t="n">
         <v>1</v>
@@ -43206,7 +43206,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ196" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AR196" t="n">
         <v>1.61</v>
@@ -43424,7 +43424,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ197" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR197" t="n">
         <v>1.39</v>
@@ -43857,7 +43857,7 @@
         <v>1.2</v>
       </c>
       <c r="AP199" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ199" t="n">
         <v>1.08</v>
@@ -44075,10 +44075,10 @@
         <v>0.83</v>
       </c>
       <c r="AP200" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ200" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR200" t="n">
         <v>1.56</v>
@@ -44296,7 +44296,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ201" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR201" t="n">
         <v>1.76</v>
@@ -44511,7 +44511,7 @@
         <v>2.2</v>
       </c>
       <c r="AP202" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ202" t="n">
         <v>1.57</v>
@@ -44947,7 +44947,7 @@
         <v>1</v>
       </c>
       <c r="AP204" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ204" t="n">
         <v>0.86</v>
@@ -45165,10 +45165,10 @@
         <v>1</v>
       </c>
       <c r="AP205" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ205" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR205" t="n">
         <v>1.17</v>
@@ -45386,7 +45386,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ206" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR206" t="n">
         <v>1.65</v>
@@ -45822,7 +45822,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ208" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR208" t="n">
         <v>1.4</v>
@@ -46040,7 +46040,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ209" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR209" t="n">
         <v>1.92</v>
@@ -46476,7 +46476,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ211" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR211" t="n">
         <v>1.55</v>
@@ -46909,10 +46909,10 @@
         <v>0.86</v>
       </c>
       <c r="AP213" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AQ213" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR213" t="n">
         <v>1.42</v>
@@ -47127,7 +47127,7 @@
         <v>1.57</v>
       </c>
       <c r="AP214" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ214" t="n">
         <v>1.17</v>
@@ -47563,7 +47563,7 @@
         <v>0.8</v>
       </c>
       <c r="AP216" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AQ216" t="n">
         <v>1.46</v>
@@ -47999,7 +47999,7 @@
         <v>1</v>
       </c>
       <c r="AP218" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ218" t="n">
         <v>1.33</v>
@@ -48435,10 +48435,10 @@
         <v>0.71</v>
       </c>
       <c r="AP220" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ220" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR220" t="n">
         <v>1.56</v>
@@ -49092,7 +49092,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ223" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AR223" t="n">
         <v>1.44</v>
@@ -49528,7 +49528,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ225" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR225" t="n">
         <v>1.75</v>
@@ -50179,7 +50179,7 @@
         <v>0.57</v>
       </c>
       <c r="AP228" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ228" t="n">
         <v>0.93</v>
@@ -50615,10 +50615,10 @@
         <v>2</v>
       </c>
       <c r="AP230" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AQ230" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR230" t="n">
         <v>1.29</v>
@@ -51269,7 +51269,7 @@
         <v>0.88</v>
       </c>
       <c r="AP233" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ233" t="n">
         <v>0.86</v>
@@ -51705,7 +51705,7 @@
         <v>1.14</v>
       </c>
       <c r="AP235" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ235" t="n">
         <v>1</v>
@@ -52577,7 +52577,7 @@
         <v>0.5</v>
       </c>
       <c r="AP239" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AQ239" t="n">
         <v>0.93</v>
@@ -52798,7 +52798,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ240" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR240" t="n">
         <v>1.75</v>
@@ -53016,7 +53016,7 @@
         <v>2</v>
       </c>
       <c r="AQ241" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR241" t="n">
         <v>1.37</v>
@@ -53231,7 +53231,7 @@
         <v>1.44</v>
       </c>
       <c r="AP242" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AQ242" t="n">
         <v>1.31</v>
@@ -53449,10 +53449,10 @@
         <v>0.33</v>
       </c>
       <c r="AP243" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ243" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR243" t="n">
         <v>1.49</v>
@@ -53667,7 +53667,7 @@
         <v>1.5</v>
       </c>
       <c r="AP244" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ244" t="n">
         <v>1.69</v>
@@ -53888,7 +53888,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ245" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR245" t="n">
         <v>1.06</v>
@@ -54106,7 +54106,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ246" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR246" t="n">
         <v>1.59</v>
@@ -55193,7 +55193,7 @@
         <v>0.88</v>
       </c>
       <c r="AP251" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ251" t="n">
         <v>1.33</v>
@@ -55411,10 +55411,10 @@
         <v>0.63</v>
       </c>
       <c r="AP252" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ252" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR252" t="n">
         <v>1.11</v>
@@ -55632,7 +55632,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ253" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR253" t="n">
         <v>1.83</v>
@@ -55850,7 +55850,7 @@
         <v>2</v>
       </c>
       <c r="AQ254" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR254" t="n">
         <v>1.64</v>
@@ -56068,7 +56068,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ255" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR255" t="n">
         <v>1.7</v>
@@ -56283,7 +56283,7 @@
         <v>1.25</v>
       </c>
       <c r="AP256" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ256" t="n">
         <v>1.08</v>
@@ -56937,10 +56937,10 @@
         <v>1.44</v>
       </c>
       <c r="AP259" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ259" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AR259" t="n">
         <v>1.2</v>
@@ -57373,7 +57373,7 @@
         <v>1.29</v>
       </c>
       <c r="AP261" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ261" t="n">
         <v>2</v>
@@ -57594,7 +57594,7 @@
         <v>1</v>
       </c>
       <c r="AQ262" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR262" t="n">
         <v>1.48</v>
@@ -58027,7 +58027,7 @@
         <v>1.43</v>
       </c>
       <c r="AP264" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ264" t="n">
         <v>1.46</v>
@@ -58245,7 +58245,7 @@
         <v>0.63</v>
       </c>
       <c r="AP265" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ265" t="n">
         <v>0.54</v>
@@ -58463,7 +58463,7 @@
         <v>1.25</v>
       </c>
       <c r="AP266" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ266" t="n">
         <v>1.77</v>
@@ -58684,7 +58684,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ267" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR267" t="n">
         <v>1.31</v>
@@ -58902,7 +58902,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ268" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR268" t="n">
         <v>1.71</v>
@@ -59117,10 +59117,10 @@
         <v>1.6</v>
       </c>
       <c r="AP269" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AQ269" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AR269" t="n">
         <v>1.42</v>
@@ -59335,7 +59335,7 @@
         <v>1.63</v>
       </c>
       <c r="AP270" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ270" t="n">
         <v>1.46</v>
@@ -59553,7 +59553,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP271" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AQ271" t="n">
         <v>0.54</v>
@@ -59771,7 +59771,7 @@
         <v>1.25</v>
       </c>
       <c r="AP272" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ272" t="n">
         <v>1.17</v>
@@ -60425,10 +60425,10 @@
         <v>2</v>
       </c>
       <c r="AP275" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ275" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR275" t="n">
         <v>1.51</v>
@@ -61079,7 +61079,7 @@
         <v>0.3</v>
       </c>
       <c r="AP278" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ278" t="n">
         <v>0.36</v>
@@ -61297,7 +61297,7 @@
         <v>1</v>
       </c>
       <c r="AP279" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ279" t="n">
         <v>1</v>
@@ -61515,10 +61515,10 @@
         <v>1.73</v>
       </c>
       <c r="AP280" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ280" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AR280" t="n">
         <v>1.78</v>
@@ -61733,7 +61733,7 @@
         <v>1.38</v>
       </c>
       <c r="AP281" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AQ281" t="n">
         <v>1.17</v>
@@ -61951,7 +61951,7 @@
         <v>1.67</v>
       </c>
       <c r="AP282" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ282" t="n">
         <v>1.77</v>
@@ -62169,7 +62169,7 @@
         <v>0.88</v>
       </c>
       <c r="AP283" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AQ283" t="n">
         <v>1.08</v>
@@ -62605,7 +62605,7 @@
         <v>0.64</v>
       </c>
       <c r="AP285" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ285" t="n">
         <v>0.93</v>
@@ -63044,7 +63044,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ287" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR287" t="n">
         <v>1.59</v>
@@ -63916,7 +63916,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ291" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR291" t="n">
         <v>1.77</v>
@@ -64785,10 +64785,10 @@
         <v>0.8</v>
       </c>
       <c r="AP295" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ295" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR295" t="n">
         <v>1.44</v>
@@ -65660,7 +65660,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ299" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR299" t="n">
         <v>1.14</v>
@@ -65875,7 +65875,7 @@
         <v>1.71</v>
       </c>
       <c r="AP300" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AQ300" t="n">
         <v>1.75</v>
@@ -66096,7 +66096,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ301" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR301" t="n">
         <v>1.74</v>
@@ -66314,7 +66314,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ302" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR302" t="n">
         <v>1.41</v>
@@ -66529,7 +66529,7 @@
         <v>1.6</v>
       </c>
       <c r="AP303" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ303" t="n">
         <v>1.31</v>
@@ -67186,7 +67186,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ306" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR306" t="n">
         <v>1.72</v>
@@ -67401,7 +67401,7 @@
         <v>1.88</v>
       </c>
       <c r="AP307" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ307" t="n">
         <v>1.75</v>
@@ -68055,10 +68055,10 @@
         <v>0.3</v>
       </c>
       <c r="AP310" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AQ310" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR310" t="n">
         <v>1.28</v>
@@ -68273,7 +68273,7 @@
         <v>0.73</v>
       </c>
       <c r="AP311" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ311" t="n">
         <v>0.86</v>
@@ -68709,7 +68709,7 @@
         <v>1.4</v>
       </c>
       <c r="AP313" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ313" t="n">
         <v>1.08</v>
@@ -68930,7 +68930,7 @@
         <v>1</v>
       </c>
       <c r="AQ314" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR314" t="n">
         <v>1.54</v>
@@ -69145,7 +69145,7 @@
         <v>1.45</v>
       </c>
       <c r="AP315" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ315" t="n">
         <v>1.31</v>
@@ -69363,7 +69363,7 @@
         <v>1.8</v>
       </c>
       <c r="AP316" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ316" t="n">
         <v>2</v>
@@ -69584,7 +69584,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ317" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR317" t="n">
         <v>1.67</v>
@@ -70017,7 +70017,7 @@
         <v>1.8</v>
       </c>
       <c r="AP319" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ319" t="n">
         <v>1.57</v>
@@ -70456,7 +70456,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ321" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR321" t="n">
         <v>1.33</v>
@@ -70674,7 +70674,7 @@
         <v>2</v>
       </c>
       <c r="AQ322" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR322" t="n">
         <v>1.72</v>
@@ -71107,7 +71107,7 @@
         <v>1.42</v>
       </c>
       <c r="AP324" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ324" t="n">
         <v>1.31</v>
@@ -71546,7 +71546,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ326" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR326" t="n">
         <v>1.47</v>
@@ -72197,7 +72197,7 @@
         <v>0.7</v>
       </c>
       <c r="AP329" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ329" t="n">
         <v>1.08</v>
@@ -72418,7 +72418,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ330" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR330" t="n">
         <v>1.74</v>
@@ -72851,10 +72851,10 @@
         <v>0.88</v>
       </c>
       <c r="AP332" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ332" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR332" t="n">
         <v>1.58</v>
@@ -73290,7 +73290,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ334" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR334" t="n">
         <v>1.82</v>
@@ -73941,7 +73941,7 @@
         <v>0.82</v>
       </c>
       <c r="AP337" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ337" t="n">
         <v>0.86</v>
@@ -74159,7 +74159,7 @@
         <v>1.8</v>
       </c>
       <c r="AP338" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ338" t="n">
         <v>1.75</v>
@@ -74595,7 +74595,7 @@
         <v>1.58</v>
       </c>
       <c r="AP340" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AQ340" t="n">
         <v>1.69</v>
@@ -74813,7 +74813,7 @@
         <v>1.55</v>
       </c>
       <c r="AP341" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ341" t="n">
         <v>1.77</v>
@@ -75034,7 +75034,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ342" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR342" t="n">
         <v>1.69</v>
@@ -75470,7 +75470,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ344" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR344" t="n">
         <v>1.22</v>
@@ -75906,7 +75906,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ346" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR346" t="n">
         <v>1.57</v>
@@ -76342,7 +76342,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ348" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AR348" t="n">
         <v>1.48</v>
@@ -76993,7 +76993,7 @@
         <v>1.73</v>
       </c>
       <c r="AP351" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ351" t="n">
         <v>1.77</v>
@@ -77211,7 +77211,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AP352" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ352" t="n">
         <v>0.86</v>
@@ -78304,7 +78304,7 @@
         <v>2</v>
       </c>
       <c r="AQ357" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AR357" t="n">
         <v>1.37</v>
@@ -79176,7 +79176,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ361" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR361" t="n">
         <v>1.47</v>
@@ -79391,7 +79391,7 @@
         <v>0.58</v>
       </c>
       <c r="AP362" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ362" t="n">
         <v>0.54</v>
@@ -80048,7 +80048,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ365" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR365" t="n">
         <v>1.8</v>
@@ -80481,10 +80481,10 @@
         <v>0.36</v>
       </c>
       <c r="AP367" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AQ367" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR367" t="n">
         <v>1.48</v>
@@ -80699,10 +80699,10 @@
         <v>0.67</v>
       </c>
       <c r="AP368" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ368" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR368" t="n">
         <v>1.44</v>
@@ -80917,10 +80917,10 @@
         <v>1.11</v>
       </c>
       <c r="AP369" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ369" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR369" t="n">
         <v>1.52</v>
@@ -81571,7 +81571,7 @@
         <v>1.18</v>
       </c>
       <c r="AP372" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ372" t="n">
         <v>1.17</v>
@@ -82225,7 +82225,7 @@
         <v>1</v>
       </c>
       <c r="AP375" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ375" t="n">
         <v>0.86</v>
@@ -82443,7 +82443,7 @@
         <v>0.83</v>
       </c>
       <c r="AP376" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ376" t="n">
         <v>1</v>
@@ -82879,7 +82879,7 @@
         <v>1.91</v>
       </c>
       <c r="AP378" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ378" t="n">
         <v>1.75</v>
@@ -83100,7 +83100,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ379" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR379" t="n">
         <v>1.35</v>
@@ -83401,7 +83401,7 @@
         <v>380</v>
       </c>
       <c r="B381" t="n">
-        <v>7781460</v>
+        <v>7781466</v>
       </c>
       <c r="C381" t="inlineStr">
         <is>
@@ -83421,19 +83421,19 @@
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="I381" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J381" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K381" t="n">
         <v>1</v>
@@ -83442,176 +83442,2356 @@
         <v>1</v>
       </c>
       <c r="M381" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N381" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O381" t="inlineStr">
         <is>
-          <t>['35']</t>
+          <t>['77']</t>
         </is>
       </c>
       <c r="P381" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['8']</t>
         </is>
       </c>
       <c r="Q381" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="R381" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S381" t="n">
-        <v>3.75</v>
+        <v>2.5</v>
       </c>
       <c r="T381" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="U381" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="V381" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="W381" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="X381" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="Y381" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z381" t="n">
-        <v>1.95</v>
+        <v>3.45</v>
       </c>
       <c r="AA381" t="n">
         <v>3.5</v>
       </c>
       <c r="AB381" t="n">
-        <v>3.11</v>
+        <v>1.84</v>
       </c>
       <c r="AC381" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AD381" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="AE381" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF381" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AG381" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AH381" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AI381" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AJ381" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AK381" t="n">
-        <v>1.33</v>
+        <v>1.83</v>
       </c>
       <c r="AL381" t="n">
         <v>1.22</v>
       </c>
       <c r="AM381" t="n">
-        <v>1.7</v>
+        <v>1.25</v>
       </c>
       <c r="AN381" t="n">
-        <v>2.33</v>
+        <v>0.77</v>
       </c>
       <c r="AO381" t="n">
-        <v>0.92</v>
+        <v>1.45</v>
       </c>
       <c r="AP381" t="n">
-        <v>2.38</v>
+        <v>0.79</v>
       </c>
       <c r="AQ381" t="n">
-        <v>0.86</v>
+        <v>1.42</v>
       </c>
       <c r="AR381" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="AS381" t="n">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="AT381" t="n">
-        <v>2.87</v>
+        <v>2.59</v>
       </c>
       <c r="AU381" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV381" t="n">
         <v>7</v>
       </c>
       <c r="AW381" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX381" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY381" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ381" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA381" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB381" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC381" t="n">
         <v>9</v>
       </c>
-      <c r="AX381" t="n">
+      <c r="BD381" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BE381" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF381" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BG381" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BH381" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BI381" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BJ381" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BK381" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BL381" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BM381" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BN381" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BO381" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BP381" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="1" t="n">
+        <v>381</v>
+      </c>
+      <c r="B382" t="n">
+        <v>7781464</v>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E382" s="2" t="n">
+        <v>45885.85416666666</v>
+      </c>
+      <c r="F382" t="n">
+        <v>0</v>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>New York RB</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>Philadelphia Union</t>
+        </is>
+      </c>
+      <c r="I382" t="n">
+        <v>0</v>
+      </c>
+      <c r="J382" t="n">
+        <v>0</v>
+      </c>
+      <c r="K382" t="n">
+        <v>0</v>
+      </c>
+      <c r="L382" t="n">
+        <v>1</v>
+      </c>
+      <c r="M382" t="n">
+        <v>0</v>
+      </c>
+      <c r="N382" t="n">
+        <v>1</v>
+      </c>
+      <c r="O382" t="inlineStr">
+        <is>
+          <t>['74']</t>
+        </is>
+      </c>
+      <c r="P382" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q382" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R382" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S382" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T382" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U382" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V382" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="W382" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X382" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y382" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z382" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AA382" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AB382" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AC382" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD382" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE382" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF382" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AG382" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH382" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AI382" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ382" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AK382" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL382" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM382" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AN382" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AO382" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AP382" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AQ382" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AR382" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AS382" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AT382" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AU382" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV382" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW382" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX382" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY382" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ382" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA382" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB382" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC382" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD382" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BE382" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF382" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BG382" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH382" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BI382" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BJ382" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BK382" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BL382" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BM382" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BN382" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BO382" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BP382" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="1" t="n">
+        <v>382</v>
+      </c>
+      <c r="B383" t="n">
+        <v>7781463</v>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E383" s="2" t="n">
+        <v>45885.85416666666</v>
+      </c>
+      <c r="F383" t="n">
+        <v>0</v>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>New England Revolution</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>Los Angeles FC</t>
+        </is>
+      </c>
+      <c r="I383" t="n">
+        <v>0</v>
+      </c>
+      <c r="J383" t="n">
+        <v>0</v>
+      </c>
+      <c r="K383" t="n">
+        <v>0</v>
+      </c>
+      <c r="L383" t="n">
+        <v>0</v>
+      </c>
+      <c r="M383" t="n">
+        <v>2</v>
+      </c>
+      <c r="N383" t="n">
+        <v>2</v>
+      </c>
+      <c r="O383" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P383" t="inlineStr">
+        <is>
+          <t>['51', '90+4']</t>
+        </is>
+      </c>
+      <c r="Q383" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R383" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S383" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T383" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U383" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V383" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W383" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X383" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y383" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z383" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AA383" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="AB383" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AC383" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD383" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE383" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF383" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AG383" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH383" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AI383" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ383" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AK383" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL383" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM383" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN383" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AO383" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AP383" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AQ383" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AR383" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AS383" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AT383" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AU383" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV383" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW383" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX383" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY383" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ383" t="n">
         <v>12</v>
       </c>
-      <c r="AY381" t="n">
+      <c r="BA383" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB383" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC383" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD383" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BE383" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF383" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BG383" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH383" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BI383" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BJ383" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BK383" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BL383" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BM383" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BN383" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BO383" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BP383" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="1" t="n">
+        <v>383</v>
+      </c>
+      <c r="B384" t="n">
+        <v>7781462</v>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E384" s="2" t="n">
+        <v>45885.85416666666</v>
+      </c>
+      <c r="F384" t="n">
+        <v>0</v>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>Montreal Impact</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>DC United</t>
+        </is>
+      </c>
+      <c r="I384" t="n">
+        <v>1</v>
+      </c>
+      <c r="J384" t="n">
+        <v>1</v>
+      </c>
+      <c r="K384" t="n">
+        <v>2</v>
+      </c>
+      <c r="L384" t="n">
+        <v>1</v>
+      </c>
+      <c r="M384" t="n">
+        <v>1</v>
+      </c>
+      <c r="N384" t="n">
+        <v>2</v>
+      </c>
+      <c r="O384" t="inlineStr">
+        <is>
+          <t>['41']</t>
+        </is>
+      </c>
+      <c r="P384" t="inlineStr">
+        <is>
+          <t>['28']</t>
+        </is>
+      </c>
+      <c r="Q384" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R384" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S384" t="n">
+        <v>4</v>
+      </c>
+      <c r="T384" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U384" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V384" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W384" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X384" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y384" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z384" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AA384" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="AB384" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AC384" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD384" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE384" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF384" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AG384" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH384" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI384" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ384" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AK384" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL384" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM384" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AN384" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AO384" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AP384" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AQ384" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AR384" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AS384" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AT384" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AU384" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV384" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW384" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX384" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY384" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ384" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA384" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB384" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC384" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD384" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BE384" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF384" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BG384" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH384" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BI384" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BJ384" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BK384" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BL384" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BM384" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BN384" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BO384" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BP384" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="1" t="n">
+        <v>384</v>
+      </c>
+      <c r="B385" t="n">
+        <v>7781460</v>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E385" s="2" t="n">
+        <v>45885.85416666666</v>
+      </c>
+      <c r="F385" t="n">
+        <v>0</v>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="I385" t="n">
+        <v>1</v>
+      </c>
+      <c r="J385" t="n">
+        <v>0</v>
+      </c>
+      <c r="K385" t="n">
+        <v>1</v>
+      </c>
+      <c r="L385" t="n">
+        <v>1</v>
+      </c>
+      <c r="M385" t="n">
+        <v>0</v>
+      </c>
+      <c r="N385" t="n">
+        <v>1</v>
+      </c>
+      <c r="O385" t="inlineStr">
+        <is>
+          <t>['35']</t>
+        </is>
+      </c>
+      <c r="P385" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q385" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R385" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S385" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T385" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="U385" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V385" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="W385" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X385" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y385" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z385" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA385" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB385" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AC385" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD385" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE385" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF385" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AG385" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AH385" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AI385" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ385" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AK385" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL385" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM385" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN385" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AO385" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AP385" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AQ385" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AR385" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AS385" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AT385" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AU385" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV385" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW385" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX385" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY385" t="n">
         <v>11</v>
       </c>
-      <c r="AZ381" t="n">
+      <c r="AZ385" t="n">
         <v>19</v>
       </c>
-      <c r="BA381" t="n">
+      <c r="BA385" t="n">
         <v>3</v>
       </c>
-      <c r="BB381" t="n">
+      <c r="BB385" t="n">
         <v>4</v>
       </c>
-      <c r="BC381" t="n">
+      <c r="BC385" t="n">
         <v>7</v>
       </c>
-      <c r="BD381" t="n">
+      <c r="BD385" t="n">
         <v>1.77</v>
       </c>
-      <c r="BE381" t="n">
+      <c r="BE385" t="n">
         <v>8</v>
       </c>
-      <c r="BF381" t="n">
+      <c r="BF385" t="n">
         <v>2.5</v>
       </c>
-      <c r="BG381" t="n">
+      <c r="BG385" t="n">
         <v>1.24</v>
       </c>
-      <c r="BH381" t="n">
+      <c r="BH385" t="n">
         <v>3.5</v>
       </c>
-      <c r="BI381" t="n">
+      <c r="BI385" t="n">
         <v>1.44</v>
       </c>
-      <c r="BJ381" t="n">
+      <c r="BJ385" t="n">
         <v>2.55</v>
       </c>
-      <c r="BK381" t="n">
+      <c r="BK385" t="n">
         <v>1.73</v>
       </c>
-      <c r="BL381" t="n">
+      <c r="BL385" t="n">
         <v>1.96</v>
       </c>
-      <c r="BM381" t="n">
+      <c r="BM385" t="n">
         <v>2.18</v>
       </c>
-      <c r="BN381" t="n">
+      <c r="BN385" t="n">
         <v>1.58</v>
       </c>
-      <c r="BO381" t="n">
+      <c r="BO385" t="n">
         <v>2.85</v>
       </c>
-      <c r="BP381" t="n">
+      <c r="BP385" t="n">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="1" t="n">
+        <v>385</v>
+      </c>
+      <c r="B386" t="n">
+        <v>7781468</v>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E386" s="2" t="n">
+        <v>45885.89583333334</v>
+      </c>
+      <c r="F386" t="n">
+        <v>0</v>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>Chicago Fire</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>St. Louis City</t>
+        </is>
+      </c>
+      <c r="I386" t="n">
+        <v>1</v>
+      </c>
+      <c r="J386" t="n">
+        <v>0</v>
+      </c>
+      <c r="K386" t="n">
+        <v>1</v>
+      </c>
+      <c r="L386" t="n">
+        <v>3</v>
+      </c>
+      <c r="M386" t="n">
+        <v>2</v>
+      </c>
+      <c r="N386" t="n">
+        <v>5</v>
+      </c>
+      <c r="O386" t="inlineStr">
+        <is>
+          <t>['16', '67', '87']</t>
+        </is>
+      </c>
+      <c r="P386" t="inlineStr">
+        <is>
+          <t>['47', '59']</t>
+        </is>
+      </c>
+      <c r="Q386" t="n">
+        <v>2</v>
+      </c>
+      <c r="R386" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="S386" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="T386" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U386" t="n">
+        <v>4</v>
+      </c>
+      <c r="V386" t="n">
+        <v>2</v>
+      </c>
+      <c r="W386" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="X386" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y386" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z386" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA386" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AB386" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AC386" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD386" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE386" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF386" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AG386" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH386" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AI386" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ386" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AK386" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AL386" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AM386" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AN386" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AO386" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AP386" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AQ386" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AR386" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AS386" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AT386" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AU386" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV386" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW386" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX386" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY386" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ386" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA386" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB386" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC386" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD386" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BE386" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF386" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BG386" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH386" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BI386" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BJ386" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BK386" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BL386" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BM386" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BN386" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BO386" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BP386" t="n">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="1" t="n">
+        <v>386</v>
+      </c>
+      <c r="B387" t="n">
+        <v>7781467</v>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E387" s="2" t="n">
+        <v>45885.89583333334</v>
+      </c>
+      <c r="F387" t="n">
+        <v>0</v>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>FC Dallas</t>
+        </is>
+      </c>
+      <c r="I387" t="n">
+        <v>0</v>
+      </c>
+      <c r="J387" t="n">
+        <v>1</v>
+      </c>
+      <c r="K387" t="n">
+        <v>1</v>
+      </c>
+      <c r="L387" t="n">
+        <v>1</v>
+      </c>
+      <c r="M387" t="n">
+        <v>1</v>
+      </c>
+      <c r="N387" t="n">
+        <v>2</v>
+      </c>
+      <c r="O387" t="inlineStr">
+        <is>
+          <t>['51']</t>
+        </is>
+      </c>
+      <c r="P387" t="inlineStr">
+        <is>
+          <t>['37']</t>
+        </is>
+      </c>
+      <c r="Q387" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R387" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S387" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T387" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U387" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V387" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W387" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X387" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y387" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z387" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AA387" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AB387" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AC387" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD387" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE387" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF387" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG387" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH387" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AI387" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ387" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK387" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL387" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM387" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AN387" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO387" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AP387" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AQ387" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR387" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AS387" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AT387" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AU387" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV387" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW387" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX387" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY387" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ387" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA387" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB387" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC387" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD387" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BE387" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF387" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BG387" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH387" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BI387" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ387" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BK387" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BL387" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BM387" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BN387" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BO387" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BP387" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="1" t="n">
+        <v>387</v>
+      </c>
+      <c r="B388" t="n">
+        <v>7781469</v>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E388" s="2" t="n">
+        <v>45885.89583333334</v>
+      </c>
+      <c r="F388" t="n">
+        <v>0</v>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>Minnesota United</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>Seattle Sounders</t>
+        </is>
+      </c>
+      <c r="I388" t="n">
+        <v>0</v>
+      </c>
+      <c r="J388" t="n">
+        <v>0</v>
+      </c>
+      <c r="K388" t="n">
+        <v>0</v>
+      </c>
+      <c r="L388" t="n">
+        <v>1</v>
+      </c>
+      <c r="M388" t="n">
+        <v>0</v>
+      </c>
+      <c r="N388" t="n">
+        <v>1</v>
+      </c>
+      <c r="O388" t="inlineStr">
+        <is>
+          <t>['73']</t>
+        </is>
+      </c>
+      <c r="P388" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q388" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R388" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S388" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T388" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U388" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V388" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W388" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X388" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y388" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z388" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AA388" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AB388" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AC388" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD388" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE388" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF388" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AG388" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH388" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI388" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ388" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AK388" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL388" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM388" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AN388" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AO388" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AP388" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AQ388" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AR388" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AS388" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AT388" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AU388" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV388" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW388" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX388" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY388" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ388" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA388" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB388" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC388" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD388" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BE388" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF388" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BG388" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH388" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BI388" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BJ388" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BK388" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BL388" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BM388" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BN388" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BO388" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BP388" t="n">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="1" t="n">
+        <v>388</v>
+      </c>
+      <c r="B389" t="n">
+        <v>7781470</v>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E389" s="2" t="n">
+        <v>45885.9375</v>
+      </c>
+      <c r="F389" t="n">
+        <v>0</v>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>Colorado Rapids</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>Atlanta United FC</t>
+        </is>
+      </c>
+      <c r="I389" t="n">
+        <v>1</v>
+      </c>
+      <c r="J389" t="n">
+        <v>1</v>
+      </c>
+      <c r="K389" t="n">
+        <v>2</v>
+      </c>
+      <c r="L389" t="n">
+        <v>3</v>
+      </c>
+      <c r="M389" t="n">
+        <v>1</v>
+      </c>
+      <c r="N389" t="n">
+        <v>4</v>
+      </c>
+      <c r="O389" t="inlineStr">
+        <is>
+          <t>['18', '64', '71']</t>
+        </is>
+      </c>
+      <c r="P389" t="inlineStr">
+        <is>
+          <t>['20']</t>
+        </is>
+      </c>
+      <c r="Q389" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R389" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S389" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T389" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U389" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="V389" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W389" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X389" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y389" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z389" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AA389" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="AB389" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AC389" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD389" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE389" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF389" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG389" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH389" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AI389" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ389" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AK389" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL389" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM389" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AN389" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AO389" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AP389" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AQ389" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AR389" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AS389" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AT389" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU389" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV389" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW389" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX389" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY389" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ389" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA389" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB389" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC389" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD389" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BE389" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF389" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BG389" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH389" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BI389" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BJ389" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BK389" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BL389" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BM389" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BN389" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BO389" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BP389" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="1" t="n">
+        <v>389</v>
+      </c>
+      <c r="B390" t="n">
+        <v>7781471</v>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E390" s="2" t="n">
+        <v>45885.97916666666</v>
+      </c>
+      <c r="F390" t="n">
+        <v>0</v>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>Portland Timbers</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>FC Cincinnati</t>
+        </is>
+      </c>
+      <c r="I390" t="n">
+        <v>1</v>
+      </c>
+      <c r="J390" t="n">
+        <v>3</v>
+      </c>
+      <c r="K390" t="n">
+        <v>4</v>
+      </c>
+      <c r="L390" t="n">
+        <v>2</v>
+      </c>
+      <c r="M390" t="n">
+        <v>3</v>
+      </c>
+      <c r="N390" t="n">
+        <v>5</v>
+      </c>
+      <c r="O390" t="inlineStr">
+        <is>
+          <t>['38', '68']</t>
+        </is>
+      </c>
+      <c r="P390" t="inlineStr">
+        <is>
+          <t>['10', '25', '36']</t>
+        </is>
+      </c>
+      <c r="Q390" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R390" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S390" t="n">
+        <v>3</v>
+      </c>
+      <c r="T390" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U390" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V390" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W390" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X390" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y390" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z390" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AA390" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB390" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AC390" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD390" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE390" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF390" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AG390" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AH390" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AI390" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ390" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AK390" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AL390" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM390" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AN390" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AO390" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AP390" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AQ390" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AR390" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AS390" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AT390" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AU390" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV390" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW390" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX390" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY390" t="n">
+        <v>24</v>
+      </c>
+      <c r="AZ390" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA390" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB390" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC390" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD390" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BE390" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF390" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG390" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BH390" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI390" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ390" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BK390" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BL390" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BM390" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BN390" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BO390" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BP390" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="1" t="n">
+        <v>390</v>
+      </c>
+      <c r="B391" t="n">
+        <v>7781465</v>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E391" s="2" t="n">
+        <v>45885.98819444444</v>
+      </c>
+      <c r="F391" t="n">
+        <v>0</v>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>Orlando City</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>Sporting KC</t>
+        </is>
+      </c>
+      <c r="I391" t="n">
+        <v>1</v>
+      </c>
+      <c r="J391" t="n">
+        <v>1</v>
+      </c>
+      <c r="K391" t="n">
+        <v>2</v>
+      </c>
+      <c r="L391" t="n">
+        <v>3</v>
+      </c>
+      <c r="M391" t="n">
+        <v>1</v>
+      </c>
+      <c r="N391" t="n">
+        <v>4</v>
+      </c>
+      <c r="O391" t="inlineStr">
+        <is>
+          <t>['2', '76', '83']</t>
+        </is>
+      </c>
+      <c r="P391" t="inlineStr">
+        <is>
+          <t>['25']</t>
+        </is>
+      </c>
+      <c r="Q391" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R391" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="S391" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T391" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="U391" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="V391" t="n">
+        <v>2</v>
+      </c>
+      <c r="W391" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="X391" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y391" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z391" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AA391" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AB391" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AC391" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD391" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE391" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF391" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AG391" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH391" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AI391" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ391" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AK391" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AL391" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AM391" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AN391" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AO391" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AP391" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AQ391" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AR391" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS391" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AT391" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AU391" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV391" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW391" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX391" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY391" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ391" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA391" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB391" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC391" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD391" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BE391" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF391" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BG391" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH391" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BI391" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BJ391" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BK391" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BL391" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BM391" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BN391" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BO391" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BP391" t="n">
+        <v>1.41</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
@@ -58060,13 +58060,13 @@
         <v>11</v>
       </c>
       <c r="BA264" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BB264" t="n">
         <v>4</v>
       </c>
       <c r="BC264" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BD264" t="n">
         <v>2.13</v>
@@ -59344,10 +59344,10 @@
         <v>1.21</v>
       </c>
       <c r="AS270" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="AT270" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="AU270" t="n">
         <v>4</v>
@@ -60431,13 +60431,13 @@
         <v>1.54</v>
       </c>
       <c r="AR275" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AS275" t="n">
         <v>1.62</v>
       </c>
       <c r="AT275" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="AU275" t="n">
         <v>2</v>
@@ -61548,13 +61548,13 @@
         <v>9</v>
       </c>
       <c r="BA280" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB280" t="n">
         <v>2</v>
       </c>
       <c r="BC280" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD280" t="n">
         <v>1.68</v>
@@ -62396,10 +62396,10 @@
         <v>1.14</v>
       </c>
       <c r="AS284" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AT284" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="AU284" t="n">
         <v>1</v>
@@ -62611,13 +62611,13 @@
         <v>0.93</v>
       </c>
       <c r="AR285" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AS285" t="n">
         <v>1.15</v>
       </c>
       <c r="AT285" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="AU285" t="n">
         <v>5</v>
@@ -65663,13 +65663,13 @@
         <v>0.38</v>
       </c>
       <c r="AR299" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AS299" t="n">
         <v>1.19</v>
       </c>
       <c r="AT299" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AU299" t="n">
         <v>1</v>
@@ -65908,13 +65908,13 @@
         <v>15</v>
       </c>
       <c r="BA300" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB300" t="n">
         <v>2</v>
       </c>
       <c r="BC300" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD300" t="n">
         <v>1.9</v>
@@ -67219,10 +67219,10 @@
         <v>2</v>
       </c>
       <c r="BB306" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BC306" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BD306" t="n">
         <v>1.67</v>
@@ -67407,13 +67407,13 @@
         <v>1.75</v>
       </c>
       <c r="AR307" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AS307" t="n">
         <v>1.31</v>
       </c>
       <c r="AT307" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="AU307" t="n">
         <v>6</v>
@@ -68500,10 +68500,10 @@
         <v>1.37</v>
       </c>
       <c r="AS312" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AT312" t="n">
-        <v>2.84</v>
+        <v>2.77</v>
       </c>
       <c r="AU312" t="n">
         <v>5</v>
@@ -69369,13 +69369,13 @@
         <v>2</v>
       </c>
       <c r="AR316" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AS316" t="n">
         <v>1.62</v>
       </c>
       <c r="AT316" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="AU316" t="n">
         <v>4</v>
@@ -72421,13 +72421,13 @@
         <v>1.42</v>
       </c>
       <c r="AR330" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="AS330" t="n">
         <v>1.29</v>
       </c>
       <c r="AT330" t="n">
-        <v>3.03</v>
+        <v>2.98</v>
       </c>
       <c r="AU330" t="n">
         <v>4</v>
@@ -74819,13 +74819,13 @@
         <v>1.77</v>
       </c>
       <c r="AR341" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AS341" t="n">
         <v>1.45</v>
       </c>
       <c r="AT341" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="AU341" t="n">
         <v>3</v>
@@ -75912,10 +75912,10 @@
         <v>1.57</v>
       </c>
       <c r="AS346" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AT346" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="AU346" t="n">
         <v>3</v>
@@ -76127,13 +76127,13 @@
         <v>1</v>
       </c>
       <c r="AR347" t="n">
-        <v>1.74</v>
+        <v>1.64</v>
       </c>
       <c r="AS347" t="n">
         <v>1</v>
       </c>
       <c r="AT347" t="n">
-        <v>2.74</v>
+        <v>2.64</v>
       </c>
       <c r="AU347" t="n">
         <v>5</v>
@@ -77217,13 +77217,13 @@
         <v>0.86</v>
       </c>
       <c r="AR352" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AS352" t="n">
         <v>1.15</v>
       </c>
       <c r="AT352" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="AU352" t="n">
         <v>2</v>
@@ -78092,10 +78092,10 @@
         <v>1.56</v>
       </c>
       <c r="AS356" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AT356" t="n">
-        <v>3.03</v>
+        <v>2.92</v>
       </c>
       <c r="AU356" t="n">
         <v>3</v>
@@ -78307,13 +78307,13 @@
         <v>1.93</v>
       </c>
       <c r="AR357" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AS357" t="n">
         <v>1.5</v>
       </c>
       <c r="AT357" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="AU357" t="n">
         <v>4</v>
@@ -78743,13 +78743,13 @@
         <v>1.33</v>
       </c>
       <c r="AR359" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AS359" t="n">
         <v>1.03</v>
       </c>
       <c r="AT359" t="n">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="AU359" t="n">
         <v>7</v>
@@ -78964,10 +78964,10 @@
         <v>1.52</v>
       </c>
       <c r="AS360" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AT360" t="n">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="AU360" t="n">
         <v>4</v>
@@ -79397,13 +79397,13 @@
         <v>0.54</v>
       </c>
       <c r="AR362" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AS362" t="n">
         <v>1.09</v>
       </c>
       <c r="AT362" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="AU362" t="n">
         <v>7</v>
@@ -80272,10 +80272,10 @@
         <v>1.86</v>
       </c>
       <c r="AS366" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AT366" t="n">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="AU366" t="n">
         <v>4</v>
@@ -80705,13 +80705,13 @@
         <v>0.64</v>
       </c>
       <c r="AR368" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AS368" t="n">
         <v>1.29</v>
       </c>
       <c r="AT368" t="n">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="AU368" t="n">
         <v>3</v>
@@ -80923,13 +80923,13 @@
         <v>1.27</v>
       </c>
       <c r="AR369" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AS369" t="n">
         <v>1.38</v>
       </c>
       <c r="AT369" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="AU369" t="n">
         <v>3</v>
@@ -81144,10 +81144,10 @@
         <v>1.67</v>
       </c>
       <c r="AS370" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="AT370" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="AU370" t="n">
         <v>8</v>
@@ -83321,13 +83321,13 @@
         <v>0.36</v>
       </c>
       <c r="AR380" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AS380" t="n">
         <v>1.19</v>
       </c>
       <c r="AT380" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="AU380" t="n">
         <v>8</v>
@@ -83542,10 +83542,10 @@
         <v>1.3</v>
       </c>
       <c r="AS381" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AT381" t="n">
-        <v>2.59</v>
+        <v>2.68</v>
       </c>
       <c r="AU381" t="n">
         <v>3</v>
@@ -83760,10 +83760,10 @@
         <v>1.67</v>
       </c>
       <c r="AS382" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AT382" t="n">
-        <v>3.06</v>
+        <v>3.03</v>
       </c>
       <c r="AU382" t="n">
         <v>2</v>
@@ -83975,13 +83975,13 @@
         <v>1.27</v>
       </c>
       <c r="AR383" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AS383" t="n">
         <v>1.39</v>
       </c>
       <c r="AT383" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="AU383" t="n">
         <v>5</v>
@@ -84491,7 +84491,7 @@
         <v>385</v>
       </c>
       <c r="B386" t="n">
-        <v>7781468</v>
+        <v>7781467</v>
       </c>
       <c r="C386" t="inlineStr">
         <is>
@@ -84511,197 +84511,197 @@
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="I386" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J386" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K386" t="n">
         <v>1</v>
       </c>
       <c r="L386" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M386" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N386" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O386" t="inlineStr">
         <is>
-          <t>['16', '67', '87']</t>
+          <t>['51']</t>
         </is>
       </c>
       <c r="P386" t="inlineStr">
         <is>
-          <t>['47', '59']</t>
+          <t>['37']</t>
         </is>
       </c>
       <c r="Q386" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="R386" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="S386" t="n">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="T386" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U386" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V386" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W386" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X386" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y386" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z386" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AA386" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AB386" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AC386" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD386" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE386" t="n">
         <v>1.22</v>
       </c>
-      <c r="U386" t="n">
+      <c r="AF386" t="n">
         <v>4</v>
       </c>
-      <c r="V386" t="n">
-        <v>2</v>
-      </c>
-      <c r="W386" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="X386" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="Y386" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z386" t="n">
+      <c r="AG386" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH386" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AI386" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ386" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK386" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL386" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM386" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AN386" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO386" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AP386" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AQ386" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR386" t="n">
         <v>1.53</v>
       </c>
-      <c r="AA386" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AB386" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AC386" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AD386" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE386" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF386" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AG386" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH386" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AI386" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AJ386" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AK386" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AL386" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AM386" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AN386" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AO386" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="AP386" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AQ386" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="AR386" t="n">
-        <v>1.49</v>
-      </c>
       <c r="AS386" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="AT386" t="n">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="AU386" t="n">
         <v>5</v>
       </c>
       <c r="AV386" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AW386" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="AX386" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY386" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ386" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA386" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB386" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC386" t="n">
         <v>9</v>
       </c>
-      <c r="AY386" t="n">
-        <v>19</v>
-      </c>
-      <c r="AZ386" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA386" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB386" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC386" t="n">
-        <v>7</v>
-      </c>
       <c r="BD386" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="BE386" t="n">
         <v>8.5</v>
       </c>
       <c r="BF386" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="BG386" t="n">
         <v>1.2</v>
       </c>
       <c r="BH386" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BI386" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="BJ386" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="BK386" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="BL386" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="BM386" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="BN386" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="BO386" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="BP386" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="387">
@@ -84709,7 +84709,7 @@
         <v>386</v>
       </c>
       <c r="B387" t="n">
-        <v>7781467</v>
+        <v>7781469</v>
       </c>
       <c r="C387" t="inlineStr">
         <is>
@@ -84729,56 +84729,56 @@
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="I387" t="n">
         <v>0</v>
       </c>
       <c r="J387" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K387" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L387" t="n">
         <v>1</v>
       </c>
       <c r="M387" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N387" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O387" t="inlineStr">
         <is>
-          <t>['51']</t>
+          <t>['73']</t>
         </is>
       </c>
       <c r="P387" t="inlineStr">
         <is>
-          <t>['37']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q387" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="R387" t="n">
         <v>2.3</v>
       </c>
       <c r="S387" t="n">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="T387" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="U387" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="V387" t="n">
         <v>2.5</v>
@@ -84787,139 +84787,139 @@
         <v>1.5</v>
       </c>
       <c r="X387" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="Y387" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z387" t="n">
-        <v>1.81</v>
+        <v>2.11</v>
       </c>
       <c r="AA387" t="n">
-        <v>3.52</v>
+        <v>3.36</v>
       </c>
       <c r="AB387" t="n">
-        <v>3.55</v>
+        <v>2.86</v>
       </c>
       <c r="AC387" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AD387" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="AE387" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF387" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AG387" t="n">
         <v>1.7</v>
       </c>
       <c r="AH387" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AI387" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AJ387" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AK387" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL387" t="n">
         <v>1.25</v>
       </c>
-      <c r="AL387" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AM387" t="n">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AN387" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AO387" t="n">
-        <v>1.42</v>
+        <v>1.23</v>
       </c>
       <c r="AP387" t="n">
-        <v>1.46</v>
+        <v>1.71</v>
       </c>
       <c r="AQ387" t="n">
-        <v>1.38</v>
+        <v>1.14</v>
       </c>
       <c r="AR387" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AS387" t="n">
-        <v>1.21</v>
+        <v>1.45</v>
       </c>
       <c r="AT387" t="n">
-        <v>2.74</v>
+        <v>3.07</v>
       </c>
       <c r="AU387" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV387" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AW387" t="n">
         <v>7</v>
       </c>
       <c r="AX387" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AY387" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ387" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="BA387" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BB387" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="BC387" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BD387" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="BE387" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="BF387" t="n">
-        <v>3.1</v>
+        <v>2.04</v>
       </c>
       <c r="BG387" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="BH387" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="BI387" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="BJ387" t="n">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="BK387" t="n">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="BL387" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="BM387" t="n">
-        <v>2.04</v>
+        <v>1.86</v>
       </c>
       <c r="BN387" t="n">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="BO387" t="n">
-        <v>2.63</v>
+        <v>2.33</v>
       </c>
       <c r="BP387" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="388">
@@ -84927,7 +84927,7 @@
         <v>387</v>
       </c>
       <c r="B388" t="n">
-        <v>7781469</v>
+        <v>7781470</v>
       </c>
       <c r="C388" t="inlineStr">
         <is>
@@ -84940,204 +84940,204 @@
         </is>
       </c>
       <c r="E388" s="2" t="n">
-        <v>45885.89583333334</v>
+        <v>45885.9375</v>
       </c>
       <c r="F388" t="n">
         <v>0</v>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="I388" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J388" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K388" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L388" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M388" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N388" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O388" t="inlineStr">
         <is>
-          <t>['73']</t>
+          <t>['18', '64', '71']</t>
         </is>
       </c>
       <c r="P388" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['20']</t>
         </is>
       </c>
       <c r="Q388" t="n">
         <v>2.75</v>
       </c>
       <c r="R388" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S388" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="T388" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="U388" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="V388" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="W388" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="X388" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="Y388" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="Z388" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="AA388" t="n">
-        <v>3.36</v>
+        <v>3.66</v>
       </c>
       <c r="AB388" t="n">
-        <v>2.86</v>
+        <v>2.67</v>
       </c>
       <c r="AC388" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AD388" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="AE388" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AF388" t="n">
-        <v>3.95</v>
+        <v>5</v>
       </c>
       <c r="AG388" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AH388" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AI388" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AJ388" t="n">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="AK388" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL388" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AM388" t="n">
         <v>1.65</v>
       </c>
       <c r="AN388" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="AO388" t="n">
-        <v>1.23</v>
+        <v>0.42</v>
       </c>
       <c r="AP388" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="AQ388" t="n">
-        <v>1.14</v>
+        <v>0.38</v>
       </c>
       <c r="AR388" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="AS388" t="n">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="AT388" t="n">
-        <v>3.07</v>
+        <v>2.7</v>
       </c>
       <c r="AU388" t="n">
         <v>3</v>
       </c>
       <c r="AV388" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AW388" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX388" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY388" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ388" t="n">
         <v>11</v>
-      </c>
-      <c r="AY388" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ388" t="n">
-        <v>15</v>
       </c>
       <c r="BA388" t="n">
         <v>3</v>
       </c>
       <c r="BB388" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="BC388" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="BD388" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="BE388" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="BF388" t="n">
-        <v>2.04</v>
+        <v>2.33</v>
       </c>
       <c r="BG388" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="BH388" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="BI388" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="BJ388" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="BK388" t="n">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="BL388" t="n">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="BM388" t="n">
-        <v>1.86</v>
+        <v>2.08</v>
       </c>
       <c r="BN388" t="n">
-        <v>1.82</v>
+        <v>1.66</v>
       </c>
       <c r="BO388" t="n">
-        <v>2.33</v>
+        <v>2.65</v>
       </c>
       <c r="BP388" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="389">
@@ -85145,7 +85145,7 @@
         <v>388</v>
       </c>
       <c r="B389" t="n">
-        <v>7781470</v>
+        <v>7781468</v>
       </c>
       <c r="C389" t="inlineStr">
         <is>
@@ -85158,204 +85158,204 @@
         </is>
       </c>
       <c r="E389" s="2" t="n">
-        <v>45885.9375</v>
+        <v>45885.95972222222</v>
       </c>
       <c r="F389" t="n">
         <v>0</v>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="I389" t="n">
         <v>1</v>
       </c>
       <c r="J389" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K389" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L389" t="n">
         <v>3</v>
       </c>
       <c r="M389" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N389" t="n">
+        <v>5</v>
+      </c>
+      <c r="O389" t="inlineStr">
+        <is>
+          <t>['16', '67', '87']</t>
+        </is>
+      </c>
+      <c r="P389" t="inlineStr">
+        <is>
+          <t>['47', '59']</t>
+        </is>
+      </c>
+      <c r="Q389" t="n">
+        <v>2</v>
+      </c>
+      <c r="R389" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="S389" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="T389" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U389" t="n">
         <v>4</v>
       </c>
-      <c r="O389" t="inlineStr">
-        <is>
-          <t>['18', '64', '71']</t>
-        </is>
-      </c>
-      <c r="P389" t="inlineStr">
-        <is>
-          <t>['20']</t>
-        </is>
-      </c>
-      <c r="Q389" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R389" t="n">
+      <c r="V389" t="n">
+        <v>2</v>
+      </c>
+      <c r="W389" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="X389" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y389" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z389" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA389" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AB389" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AC389" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD389" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE389" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF389" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AG389" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH389" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AI389" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ389" t="n">
         <v>2.5</v>
       </c>
-      <c r="S389" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T389" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="U389" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="V389" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W389" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="X389" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y389" t="n">
+      <c r="AK389" t="n">
         <v>1.17</v>
       </c>
-      <c r="Z389" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AA389" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="AB389" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AC389" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AD389" t="n">
-        <v>10</v>
-      </c>
-      <c r="AE389" t="n">
+      <c r="AL389" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AM389" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AN389" t="n">
         <v>1.17</v>
-      </c>
-      <c r="AF389" t="n">
-        <v>5</v>
-      </c>
-      <c r="AG389" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AH389" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AI389" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AJ389" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AK389" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AL389" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AM389" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AN389" t="n">
-        <v>1.54</v>
       </c>
       <c r="AO389" t="n">
         <v>0.42</v>
       </c>
       <c r="AP389" t="n">
-        <v>1.64</v>
+        <v>1.31</v>
       </c>
       <c r="AQ389" t="n">
         <v>0.38</v>
       </c>
       <c r="AR389" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AS389" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AT389" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AU389" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV389" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AW389" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="AX389" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY389" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="AZ389" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BA389" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BB389" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BC389" t="n">
         <v>7</v>
       </c>
       <c r="BD389" t="n">
-        <v>1.87</v>
+        <v>1.47</v>
       </c>
       <c r="BE389" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="BF389" t="n">
-        <v>2.33</v>
+        <v>3.35</v>
       </c>
       <c r="BG389" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="BH389" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="BI389" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="BJ389" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="BK389" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="BL389" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="BM389" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="BN389" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="BO389" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="BP389" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="390">

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP391"/>
+  <dimension ref="A1:BP394"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ13" t="n">
         <v>0.86</v>
@@ -3966,7 +3966,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ16" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -4838,7 +4838,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR20" t="n">
         <v>0</v>
@@ -7015,7 +7015,7 @@
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ30" t="n">
         <v>0.36</v>
@@ -7454,7 +7454,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR32" t="n">
         <v>1.7</v>
@@ -8759,7 +8759,7 @@
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ38" t="n">
         <v>1.77</v>
@@ -9634,7 +9634,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ42" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR42" t="n">
         <v>1.28</v>
@@ -9849,7 +9849,7 @@
         <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ43" t="n">
         <v>0.86</v>
@@ -10067,7 +10067,7 @@
         <v>0</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ44" t="n">
         <v>1.77</v>
@@ -11811,7 +11811,7 @@
         <v>1</v>
       </c>
       <c r="AP52" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ52" t="n">
         <v>1.31</v>
@@ -13119,7 +13119,7 @@
         <v>2</v>
       </c>
       <c r="AP58" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ58" t="n">
         <v>1</v>
@@ -13340,7 +13340,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ59" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR59" t="n">
         <v>1.52</v>
@@ -16392,7 +16392,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ73" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR73" t="n">
         <v>2.1</v>
@@ -16607,7 +16607,7 @@
         <v>2</v>
       </c>
       <c r="AP74" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ74" t="n">
         <v>1.69</v>
@@ -16828,7 +16828,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ75" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR75" t="n">
         <v>1.61</v>
@@ -19659,7 +19659,7 @@
         <v>0</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ88" t="n">
         <v>1.14</v>
@@ -20098,7 +20098,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ90" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR90" t="n">
         <v>0.95</v>
@@ -20316,7 +20316,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ91" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR91" t="n">
         <v>1.51</v>
@@ -22493,7 +22493,7 @@
         <v>2.33</v>
       </c>
       <c r="AP101" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ101" t="n">
         <v>1</v>
@@ -22929,7 +22929,7 @@
         <v>1.33</v>
       </c>
       <c r="AP103" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ103" t="n">
         <v>1.77</v>
@@ -23147,7 +23147,7 @@
         <v>0.5</v>
       </c>
       <c r="AP104" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ104" t="n">
         <v>0.64</v>
@@ -24455,7 +24455,7 @@
         <v>2</v>
       </c>
       <c r="AP110" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ110" t="n">
         <v>1.33</v>
@@ -24891,7 +24891,7 @@
         <v>2</v>
       </c>
       <c r="AP112" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ112" t="n">
         <v>1.54</v>
@@ -25548,7 +25548,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ115" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR115" t="n">
         <v>1.63</v>
@@ -25766,7 +25766,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ116" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR116" t="n">
         <v>1.49</v>
@@ -27292,7 +27292,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ123" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR123" t="n">
         <v>1.83</v>
@@ -28382,7 +28382,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ128" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR128" t="n">
         <v>1.4</v>
@@ -29905,7 +29905,7 @@
         <v>0</v>
       </c>
       <c r="AP135" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ135" t="n">
         <v>0.85</v>
@@ -33396,7 +33396,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR151" t="n">
         <v>1.52</v>
@@ -35355,7 +35355,7 @@
         <v>1.2</v>
       </c>
       <c r="AP160" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ160" t="n">
         <v>0.86</v>
@@ -35576,7 +35576,7 @@
         <v>2</v>
       </c>
       <c r="AQ161" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR161" t="n">
         <v>1.55</v>
@@ -35791,7 +35791,7 @@
         <v>2</v>
       </c>
       <c r="AP162" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ162" t="n">
         <v>1.17</v>
@@ -36227,7 +36227,7 @@
         <v>1.8</v>
       </c>
       <c r="AP164" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ164" t="n">
         <v>1.93</v>
@@ -37753,7 +37753,7 @@
         <v>0.25</v>
       </c>
       <c r="AP171" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ171" t="n">
         <v>0.86</v>
@@ -39064,7 +39064,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ177" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR177" t="n">
         <v>1.53</v>
@@ -39715,7 +39715,7 @@
         <v>0.8</v>
       </c>
       <c r="AP180" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ180" t="n">
         <v>1.27</v>
@@ -42549,7 +42549,7 @@
         <v>2</v>
       </c>
       <c r="AP193" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ193" t="n">
         <v>1.75</v>
@@ -42985,7 +42985,7 @@
         <v>0.33</v>
       </c>
       <c r="AP195" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ195" t="n">
         <v>0.54</v>
@@ -44732,7 +44732,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ203" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR203" t="n">
         <v>0.9399999999999999</v>
@@ -47566,7 +47566,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ216" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR216" t="n">
         <v>1.31</v>
@@ -48653,10 +48653,10 @@
         <v>1</v>
       </c>
       <c r="AP221" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ221" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR221" t="n">
         <v>1.91</v>
@@ -48871,7 +48871,7 @@
         <v>1.71</v>
       </c>
       <c r="AP222" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ222" t="n">
         <v>1.69</v>
@@ -50397,10 +50397,10 @@
         <v>1</v>
       </c>
       <c r="AP229" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ229" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR229" t="n">
         <v>1.7</v>
@@ -50836,7 +50836,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ231" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR231" t="n">
         <v>1.72</v>
@@ -51054,7 +51054,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ232" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR232" t="n">
         <v>1.85</v>
@@ -51923,7 +51923,7 @@
         <v>1.57</v>
       </c>
       <c r="AP236" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ236" t="n">
         <v>1.77</v>
@@ -55629,7 +55629,7 @@
         <v>1</v>
       </c>
       <c r="AP253" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ253" t="n">
         <v>1.14</v>
@@ -56065,7 +56065,7 @@
         <v>0.29</v>
       </c>
       <c r="AP255" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ255" t="n">
         <v>0.38</v>
@@ -57376,7 +57376,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ261" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR261" t="n">
         <v>1.69</v>
@@ -58030,7 +58030,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ264" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR264" t="n">
         <v>1.51</v>
@@ -59338,7 +59338,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ270" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR270" t="n">
         <v>1.21</v>
@@ -59774,7 +59774,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ272" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR272" t="n">
         <v>1.64</v>
@@ -60861,10 +60861,10 @@
         <v>1.5</v>
       </c>
       <c r="AP277" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ277" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR277" t="n">
         <v>1.81</v>
@@ -62390,7 +62390,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ284" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR284" t="n">
         <v>1.14</v>
@@ -62826,7 +62826,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ286" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR286" t="n">
         <v>1.11</v>
@@ -63477,7 +63477,7 @@
         <v>0.27</v>
       </c>
       <c r="AP289" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ289" t="n">
         <v>0.36</v>
@@ -64349,7 +64349,7 @@
         <v>1.14</v>
       </c>
       <c r="AP293" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ293" t="n">
         <v>1</v>
@@ -66750,7 +66750,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ304" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR304" t="n">
         <v>1.62</v>
@@ -66965,7 +66965,7 @@
         <v>0.6</v>
       </c>
       <c r="AP305" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ305" t="n">
         <v>0.54</v>
@@ -68494,7 +68494,7 @@
         <v>2</v>
       </c>
       <c r="AQ312" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR312" t="n">
         <v>1.37</v>
@@ -69366,7 +69366,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ316" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR316" t="n">
         <v>1.49</v>
@@ -70238,7 +70238,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ320" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR320" t="n">
         <v>1.46</v>
@@ -73287,7 +73287,7 @@
         <v>1.45</v>
       </c>
       <c r="AP334" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ334" t="n">
         <v>1.38</v>
@@ -78086,7 +78086,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ356" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR356" t="n">
         <v>1.56</v>
@@ -80045,7 +80045,7 @@
         <v>1</v>
       </c>
       <c r="AP365" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ365" t="n">
         <v>0.85</v>
@@ -81138,7 +81138,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ370" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR370" t="n">
         <v>1.67</v>
@@ -81574,7 +81574,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ372" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR372" t="n">
         <v>1.52</v>
@@ -81792,7 +81792,7 @@
         <v>1</v>
       </c>
       <c r="AQ373" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR373" t="n">
         <v>1.6</v>
@@ -82007,7 +82007,7 @@
         <v>1.69</v>
       </c>
       <c r="AP374" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ374" t="n">
         <v>1.57</v>
@@ -85792,6 +85792,660 @@
       </c>
       <c r="BP391" t="n">
         <v>1.41</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="1" t="n">
+        <v>391</v>
+      </c>
+      <c r="B392" t="n">
+        <v>7781472</v>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E392" s="2" t="n">
+        <v>45886.75</v>
+      </c>
+      <c r="F392" t="n">
+        <v>0</v>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>Nashville SC</t>
+        </is>
+      </c>
+      <c r="I392" t="n">
+        <v>1</v>
+      </c>
+      <c r="J392" t="n">
+        <v>1</v>
+      </c>
+      <c r="K392" t="n">
+        <v>2</v>
+      </c>
+      <c r="L392" t="n">
+        <v>2</v>
+      </c>
+      <c r="M392" t="n">
+        <v>1</v>
+      </c>
+      <c r="N392" t="n">
+        <v>3</v>
+      </c>
+      <c r="O392" t="inlineStr">
+        <is>
+          <t>['40', '77']</t>
+        </is>
+      </c>
+      <c r="P392" t="inlineStr">
+        <is>
+          <t>['10']</t>
+        </is>
+      </c>
+      <c r="Q392" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R392" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S392" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T392" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U392" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="V392" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="W392" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X392" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="Y392" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z392" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AA392" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AB392" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AC392" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD392" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE392" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF392" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AG392" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH392" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AI392" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ392" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK392" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL392" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM392" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AN392" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AO392" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AP392" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AQ392" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR392" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AS392" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AT392" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AU392" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV392" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW392" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX392" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY392" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ392" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA392" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB392" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC392" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD392" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BE392" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF392" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BG392" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH392" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BI392" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BJ392" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BK392" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BL392" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BM392" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN392" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BO392" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BP392" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="1" t="n">
+        <v>392</v>
+      </c>
+      <c r="B393" t="n">
+        <v>7781473</v>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E393" s="2" t="n">
+        <v>45886.83333333334</v>
+      </c>
+      <c r="F393" t="n">
+        <v>0</v>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>SJ Earthquakes</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="I393" t="n">
+        <v>0</v>
+      </c>
+      <c r="J393" t="n">
+        <v>0</v>
+      </c>
+      <c r="K393" t="n">
+        <v>0</v>
+      </c>
+      <c r="L393" t="n">
+        <v>1</v>
+      </c>
+      <c r="M393" t="n">
+        <v>2</v>
+      </c>
+      <c r="N393" t="n">
+        <v>3</v>
+      </c>
+      <c r="O393" t="inlineStr">
+        <is>
+          <t>['72']</t>
+        </is>
+      </c>
+      <c r="P393" t="inlineStr">
+        <is>
+          <t>['81', '84']</t>
+        </is>
+      </c>
+      <c r="Q393" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R393" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S393" t="n">
+        <v>3</v>
+      </c>
+      <c r="T393" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U393" t="n">
+        <v>4</v>
+      </c>
+      <c r="V393" t="n">
+        <v>2</v>
+      </c>
+      <c r="W393" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="X393" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y393" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z393" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AA393" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB393" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AC393" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD393" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE393" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF393" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AG393" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AH393" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AI393" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AJ393" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AK393" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL393" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM393" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN393" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AO393" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP393" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ393" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AR393" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AS393" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AT393" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="AU393" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV393" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW393" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX393" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY393" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ393" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA393" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB393" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC393" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD393" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BE393" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF393" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BG393" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH393" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BI393" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BJ393" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BK393" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BL393" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BM393" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BN393" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BO393" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BP393" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="1" t="n">
+        <v>393</v>
+      </c>
+      <c r="B394" t="n">
+        <v>7781474</v>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E394" s="2" t="n">
+        <v>45886.91666666666</v>
+      </c>
+      <c r="F394" t="n">
+        <v>0</v>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>Houston Dynamo</t>
+        </is>
+      </c>
+      <c r="I394" t="n">
+        <v>1</v>
+      </c>
+      <c r="J394" t="n">
+        <v>0</v>
+      </c>
+      <c r="K394" t="n">
+        <v>1</v>
+      </c>
+      <c r="L394" t="n">
+        <v>1</v>
+      </c>
+      <c r="M394" t="n">
+        <v>1</v>
+      </c>
+      <c r="N394" t="n">
+        <v>2</v>
+      </c>
+      <c r="O394" t="inlineStr">
+        <is>
+          <t>['6']</t>
+        </is>
+      </c>
+      <c r="P394" t="inlineStr">
+        <is>
+          <t>['90+1']</t>
+        </is>
+      </c>
+      <c r="Q394" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R394" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S394" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="T394" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U394" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V394" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W394" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X394" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y394" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z394" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AA394" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AB394" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AC394" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD394" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE394" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF394" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AG394" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AH394" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI394" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ394" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK394" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL394" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AM394" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AN394" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AO394" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AP394" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ394" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AR394" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AS394" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AT394" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU394" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV394" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW394" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX394" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY394" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ394" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA394" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB394" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC394" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD394" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BE394" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF394" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BG394" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BH394" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BI394" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BJ394" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BK394" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BL394" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BM394" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BN394" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BO394" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BP394" t="n">
+        <v>1.52</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
@@ -84441,10 +84441,10 @@
         <v>3</v>
       </c>
       <c r="BB385" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BC385" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD385" t="n">
         <v>1.77</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
@@ -85967,10 +85967,10 @@
         <v>2</v>
       </c>
       <c r="BB392" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC392" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD392" t="n">
         <v>1.89</v>
@@ -86382,13 +86382,13 @@
         <v>3.05</v>
       </c>
       <c r="AU394" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV394" t="n">
         <v>2</v>
       </c>
       <c r="AW394" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX394" t="n">
         <v>10</v>
@@ -86400,13 +86400,13 @@
         <v>12</v>
       </c>
       <c r="BA394" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB394" t="n">
         <v>4</v>
       </c>
       <c r="BC394" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD394" t="n">
         <v>1.47</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
@@ -46052,22 +46052,22 @@
         <v>3.12</v>
       </c>
       <c r="AU209" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV209" t="n">
         <v>5</v>
       </c>
       <c r="AW209" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AX209" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AY209" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AZ209" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA209" t="n">
         <v>4</v>
@@ -46270,22 +46270,22 @@
         <v>2.73</v>
       </c>
       <c r="AU210" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV210" t="n">
         <v>1</v>
       </c>
       <c r="AW210" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AX210" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY210" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ210" t="n">
         <v>7</v>
-      </c>
-      <c r="AY210" t="n">
-        <v>16</v>
-      </c>
-      <c r="AZ210" t="n">
-        <v>8</v>
       </c>
       <c r="BA210" t="n">
         <v>6</v>
@@ -46488,22 +46488,22 @@
         <v>2.79</v>
       </c>
       <c r="AU211" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV211" t="n">
         <v>7</v>
       </c>
       <c r="AW211" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AX211" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AY211" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ211" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA211" t="n">
         <v>7</v>
@@ -46706,22 +46706,22 @@
         <v>2.3</v>
       </c>
       <c r="AU212" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AV212" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX212" t="n">
         <v>3</v>
       </c>
-      <c r="AW212" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX212" t="n">
-        <v>1</v>
-      </c>
       <c r="AY212" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AZ212" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="BA212" t="n">
         <v>4</v>
@@ -46930,16 +46930,16 @@
         <v>8</v>
       </c>
       <c r="AW213" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AX213" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY213" t="n">
         <v>11</v>
       </c>
-      <c r="AY213" t="n">
-        <v>13</v>
-      </c>
       <c r="AZ213" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BA213" t="n">
         <v>5</v>
@@ -47142,22 +47142,22 @@
         <v>3.23</v>
       </c>
       <c r="AU214" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV214" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW214" t="n">
         <v>6</v>
       </c>
-      <c r="AV214" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW214" t="n">
-        <v>8</v>
-      </c>
       <c r="AX214" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AY214" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AZ214" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BA214" t="n">
         <v>1</v>
@@ -47363,19 +47363,19 @@
         <v>8</v>
       </c>
       <c r="AV215" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW215" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX215" t="n">
         <v>4</v>
       </c>
-      <c r="AW215" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX215" t="n">
-        <v>7</v>
-      </c>
       <c r="AY215" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ215" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA215" t="n">
         <v>8</v>
@@ -47578,22 +47578,22 @@
         <v>2.68</v>
       </c>
       <c r="AU216" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV216" t="n">
         <v>6</v>
       </c>
       <c r="AW216" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX216" t="n">
         <v>6</v>
       </c>
-      <c r="AX216" t="n">
+      <c r="AY216" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ216" t="n">
         <v>12</v>
-      </c>
-      <c r="AY216" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ216" t="n">
-        <v>18</v>
       </c>
       <c r="BA216" t="n">
         <v>3</v>
@@ -47799,19 +47799,19 @@
         <v>5</v>
       </c>
       <c r="AV217" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW217" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AX217" t="n">
         <v>5</v>
       </c>
       <c r="AY217" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AZ217" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA217" t="n">
         <v>5</v>
@@ -48020,16 +48020,16 @@
         <v>3</v>
       </c>
       <c r="AW218" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AX218" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY218" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ218" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA218" t="n">
         <v>4</v>
@@ -48232,22 +48232,22 @@
         <v>2.82</v>
       </c>
       <c r="AU219" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV219" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW219" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AX219" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AY219" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ219" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA219" t="n">
         <v>8</v>
@@ -48453,19 +48453,19 @@
         <v>5</v>
       </c>
       <c r="AV220" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AW220" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AX220" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY220" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ220" t="n">
         <v>11</v>
-      </c>
-      <c r="AY220" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ220" t="n">
-        <v>14</v>
       </c>
       <c r="BA220" t="n">
         <v>3</v>
@@ -48671,19 +48671,19 @@
         <v>8</v>
       </c>
       <c r="AV221" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW221" t="n">
         <v>5</v>
       </c>
-      <c r="AW221" t="n">
-        <v>7</v>
-      </c>
       <c r="AX221" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AY221" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ221" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="BA221" t="n">
         <v>11</v>
@@ -48892,16 +48892,16 @@
         <v>3</v>
       </c>
       <c r="AW222" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AX222" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY222" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AZ222" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA222" t="n">
         <v>11</v>
@@ -49107,19 +49107,19 @@
         <v>7</v>
       </c>
       <c r="AV223" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AW223" t="n">
         <v>4</v>
       </c>
       <c r="AX223" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AY223" t="n">
         <v>11</v>
       </c>
       <c r="AZ223" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA223" t="n">
         <v>2</v>
@@ -49313,13 +49313,13 @@
         <v>1.77</v>
       </c>
       <c r="AR224" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AS224" t="n">
         <v>1.28</v>
       </c>
       <c r="AT224" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="AU224" t="n">
         <v>5</v>
@@ -49534,10 +49534,10 @@
         <v>1.75</v>
       </c>
       <c r="AS225" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AT225" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="AU225" t="n">
         <v>6</v>
@@ -49749,13 +49749,13 @@
         <v>1.31</v>
       </c>
       <c r="AR226" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AS226" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AT226" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="AU226" t="n">
         <v>4</v>
@@ -50403,13 +50403,13 @@
         <v>1.15</v>
       </c>
       <c r="AR229" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AS229" t="n">
-        <v>1.02</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AT229" t="n">
-        <v>2.72</v>
+        <v>2.59</v>
       </c>
       <c r="AU229" t="n">
         <v>1</v>
@@ -50621,13 +50621,13 @@
         <v>1.54</v>
       </c>
       <c r="AR230" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AS230" t="n">
         <v>1.62</v>
       </c>
       <c r="AT230" t="n">
-        <v>2.91</v>
+        <v>2.84</v>
       </c>
       <c r="AU230" t="n">
         <v>4</v>
@@ -50842,10 +50842,10 @@
         <v>1.72</v>
       </c>
       <c r="AS231" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="AT231" t="n">
-        <v>3.19</v>
+        <v>3.07</v>
       </c>
       <c r="AU231" t="n">
         <v>5</v>
@@ -51057,13 +51057,13 @@
         <v>2.08</v>
       </c>
       <c r="AR232" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AS232" t="n">
         <v>1.53</v>
       </c>
       <c r="AT232" t="n">
-        <v>3.38</v>
+        <v>3.37</v>
       </c>
       <c r="AU232" t="n">
         <v>5</v>
@@ -52150,10 +52150,10 @@
         <v>1.55</v>
       </c>
       <c r="AS237" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AT237" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="AU237" t="n">
         <v>4</v>
@@ -52583,13 +52583,13 @@
         <v>0.93</v>
       </c>
       <c r="AR239" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AS239" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AT239" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AU239" t="n">
         <v>2</v>
@@ -53019,13 +53019,13 @@
         <v>1.42</v>
       </c>
       <c r="AR241" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AS241" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AT241" t="n">
-        <v>2.68</v>
+        <v>2.57</v>
       </c>
       <c r="AU241" t="n">
         <v>7</v>
@@ -53237,13 +53237,13 @@
         <v>1.31</v>
       </c>
       <c r="AR242" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AS242" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AT242" t="n">
-        <v>2.74</v>
+        <v>2.65</v>
       </c>
       <c r="AU242" t="n">
         <v>2</v>
@@ -53455,13 +53455,13 @@
         <v>0.38</v>
       </c>
       <c r="AR243" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="AS243" t="n">
         <v>1.26</v>
       </c>
       <c r="AT243" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="AU243" t="n">
         <v>3</v>
@@ -53673,13 +53673,13 @@
         <v>1.69</v>
       </c>
       <c r="AR244" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="AS244" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AT244" t="n">
-        <v>3.24</v>
+        <v>3.16</v>
       </c>
       <c r="AU244" t="n">
         <v>5</v>
@@ -53894,10 +53894,10 @@
         <v>1.06</v>
       </c>
       <c r="AS245" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AT245" t="n">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="AU245" t="n">
         <v>2</v>
@@ -54327,13 +54327,13 @@
         <v>0.86</v>
       </c>
       <c r="AR247" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AS247" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AT247" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="AU247" t="n">
         <v>5</v>
@@ -54545,22 +54545,22 @@
         <v>1.33</v>
       </c>
       <c r="AR248" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="AS248" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AT248" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="AU248" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AV248" t="n">
         <v>2</v>
       </c>
       <c r="AW248" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AX248" t="n">
         <v>6</v>
@@ -54763,13 +54763,13 @@
         <v>1.77</v>
       </c>
       <c r="AR249" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AS249" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AT249" t="n">
-        <v>3.06</v>
+        <v>2.95</v>
       </c>
       <c r="AU249" t="n">
         <v>2</v>
@@ -54793,10 +54793,10 @@
         <v>9</v>
       </c>
       <c r="BB249" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BC249" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD249" t="n">
         <v>1.44</v>
@@ -54981,25 +54981,25 @@
         <v>1.69</v>
       </c>
       <c r="AR250" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AS250" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="AT250" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="AU250" t="n">
         <v>3</v>
       </c>
       <c r="AV250" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AW250" t="n">
         <v>12</v>
       </c>
       <c r="AX250" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AY250" t="n">
         <v>15</v>
@@ -55199,22 +55199,22 @@
         <v>1.33</v>
       </c>
       <c r="AR251" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AS251" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AT251" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="AU251" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AV251" t="n">
         <v>6</v>
       </c>
       <c r="AW251" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AX251" t="n">
         <v>5</v>
@@ -55417,25 +55417,25 @@
         <v>0.38</v>
       </c>
       <c r="AR252" t="n">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="AS252" t="n">
-        <v>1.03</v>
+        <v>0.99</v>
       </c>
       <c r="AT252" t="n">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="AU252" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AV252" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AW252" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AX252" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="AY252" t="n">
         <v>18</v>
@@ -55635,31 +55635,31 @@
         <v>1.14</v>
       </c>
       <c r="AR253" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AS253" t="n">
         <v>1.43</v>
       </c>
       <c r="AT253" t="n">
-        <v>3.26</v>
+        <v>3.28</v>
       </c>
       <c r="AU253" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV253" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW253" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AX253" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AY253" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AZ253" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="BA253" t="n">
         <v>3</v>
@@ -55862,19 +55862,19 @@
         <v>2.85</v>
       </c>
       <c r="AU254" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AV254" t="n">
         <v>2</v>
       </c>
       <c r="AW254" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="AX254" t="n">
         <v>3</v>
       </c>
       <c r="AY254" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AZ254" t="n">
         <v>5</v>
@@ -56071,28 +56071,28 @@
         <v>0.38</v>
       </c>
       <c r="AR255" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="AS255" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AT255" t="n">
-        <v>2.96</v>
+        <v>2.78</v>
       </c>
       <c r="AU255" t="n">
         <v>6</v>
       </c>
       <c r="AV255" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW255" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX255" t="n">
         <v>3</v>
       </c>
-      <c r="AW255" t="n">
-        <v>3</v>
-      </c>
-      <c r="AX255" t="n">
-        <v>4</v>
-      </c>
       <c r="AY255" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AZ255" t="n">
         <v>7</v>
@@ -56289,31 +56289,31 @@
         <v>1.08</v>
       </c>
       <c r="AR256" t="n">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="AS256" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AT256" t="n">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="AU256" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AV256" t="n">
         <v>6</v>
       </c>
       <c r="AW256" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AX256" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AY256" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ256" t="n">
         <v>14</v>
-      </c>
-      <c r="AZ256" t="n">
-        <v>16</v>
       </c>
       <c r="BA256" t="n">
         <v>8</v>
@@ -56507,13 +56507,13 @@
         <v>0.36</v>
       </c>
       <c r="AR257" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AS257" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AT257" t="n">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="AU257" t="n">
         <v>5</v>
@@ -56522,16 +56522,16 @@
         <v>6</v>
       </c>
       <c r="AW257" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AX257" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY257" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ257" t="n">
         <v>10</v>
-      </c>
-      <c r="AY257" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ257" t="n">
-        <v>16</v>
       </c>
       <c r="BA257" t="n">
         <v>4</v>
@@ -56725,31 +56725,31 @@
         <v>1.57</v>
       </c>
       <c r="AR258" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AS258" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AT258" t="n">
-        <v>3.24</v>
+        <v>3.28</v>
       </c>
       <c r="AU258" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AV258" t="n">
         <v>3</v>
       </c>
       <c r="AW258" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX258" t="n">
         <v>3</v>
       </c>
-      <c r="AX258" t="n">
-        <v>5</v>
-      </c>
       <c r="AY258" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AZ258" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA258" t="n">
         <v>4</v>
@@ -56946,22 +56946,22 @@
         <v>1.2</v>
       </c>
       <c r="AS259" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AT259" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="AU259" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV259" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AW259" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX259" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AY259" t="n">
         <v>10</v>
@@ -57161,25 +57161,25 @@
         <v>0.93</v>
       </c>
       <c r="AR260" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AS260" t="n">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AT260" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="AU260" t="n">
         <v>9</v>
       </c>
       <c r="AV260" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW260" t="n">
         <v>10</v>
       </c>
       <c r="AX260" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY260" t="n">
         <v>19</v>
@@ -57379,25 +57379,25 @@
         <v>2.08</v>
       </c>
       <c r="AR261" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AS261" t="n">
         <v>1.58</v>
       </c>
       <c r="AT261" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="AU261" t="n">
         <v>6</v>
       </c>
       <c r="AV261" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AW261" t="n">
         <v>4</v>
       </c>
       <c r="AX261" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AY261" t="n">
         <v>10</v>
@@ -57597,25 +57597,25 @@
         <v>1.38</v>
       </c>
       <c r="AR262" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AS262" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AT262" t="n">
-        <v>2.73</v>
+        <v>2.64</v>
       </c>
       <c r="AU262" t="n">
         <v>5</v>
       </c>
       <c r="AV262" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AW262" t="n">
         <v>6</v>
       </c>
       <c r="AX262" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AY262" t="n">
         <v>11</v>
@@ -57815,25 +57815,25 @@
         <v>0.86</v>
       </c>
       <c r="AR263" t="n">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="AS263" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AT263" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="AU263" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV263" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW263" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX263" t="n">
         <v>3</v>
-      </c>
-      <c r="AV263" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW263" t="n">
-        <v>15</v>
-      </c>
-      <c r="AX263" t="n">
-        <v>5</v>
       </c>
       <c r="AY263" t="n">
         <v>18</v>
@@ -58036,10 +58036,10 @@
         <v>1.51</v>
       </c>
       <c r="AS264" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AT264" t="n">
-        <v>2.98</v>
+        <v>2.89</v>
       </c>
       <c r="AU264" t="n">
         <v>7</v>
@@ -58060,13 +58060,13 @@
         <v>11</v>
       </c>
       <c r="BA264" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BB264" t="n">
         <v>4</v>
       </c>
       <c r="BC264" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BD264" t="n">
         <v>2.13</v>
@@ -58251,25 +58251,25 @@
         <v>0.54</v>
       </c>
       <c r="AR265" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AS265" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AT265" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="AU265" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AV265" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AW265" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AX265" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AY265" t="n">
         <v>6</v>
@@ -58469,28 +58469,28 @@
         <v>1.77</v>
       </c>
       <c r="AR266" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AS266" t="n">
         <v>1.28</v>
       </c>
       <c r="AT266" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="AU266" t="n">
         <v>2</v>
       </c>
       <c r="AV266" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW266" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX266" t="n">
         <v>4</v>
       </c>
-      <c r="AW266" t="n">
-        <v>12</v>
-      </c>
-      <c r="AX266" t="n">
-        <v>3</v>
-      </c>
       <c r="AY266" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AZ266" t="n">
         <v>7</v>
@@ -58687,22 +58687,22 @@
         <v>0.64</v>
       </c>
       <c r="AR267" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AS267" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="AT267" t="n">
-        <v>2.83</v>
+        <v>2.79</v>
       </c>
       <c r="AU267" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AV267" t="n">
         <v>1</v>
       </c>
       <c r="AW267" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AX267" t="n">
         <v>7</v>
@@ -58905,25 +58905,25 @@
         <v>0.38</v>
       </c>
       <c r="AR268" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AS268" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AT268" t="n">
-        <v>2.93</v>
+        <v>2.84</v>
       </c>
       <c r="AU268" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV268" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW268" t="n">
         <v>9</v>
       </c>
-      <c r="AV268" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW268" t="n">
-        <v>10</v>
-      </c>
       <c r="AX268" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY268" t="n">
         <v>19</v>
@@ -59123,25 +59123,25 @@
         <v>1.93</v>
       </c>
       <c r="AR269" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="AS269" t="n">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="AT269" t="n">
-        <v>2.93</v>
+        <v>2.78</v>
       </c>
       <c r="AU269" t="n">
         <v>4</v>
       </c>
       <c r="AV269" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AW269" t="n">
         <v>6</v>
       </c>
       <c r="AX269" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AY269" t="n">
         <v>10</v>
@@ -59341,13 +59341,13 @@
         <v>1.36</v>
       </c>
       <c r="AR270" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AS270" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="AT270" t="n">
-        <v>2.64</v>
+        <v>2.51</v>
       </c>
       <c r="AU270" t="n">
         <v>4</v>
@@ -59559,25 +59559,25 @@
         <v>0.54</v>
       </c>
       <c r="AR271" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AS271" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AT271" t="n">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AU271" t="n">
         <v>2</v>
       </c>
       <c r="AV271" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AW271" t="n">
         <v>11</v>
       </c>
       <c r="AX271" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AY271" t="n">
         <v>13</v>
@@ -59777,25 +59777,25 @@
         <v>1.15</v>
       </c>
       <c r="AR272" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AS272" t="n">
-        <v>1.02</v>
+        <v>0.95</v>
       </c>
       <c r="AT272" t="n">
-        <v>2.66</v>
+        <v>2.57</v>
       </c>
       <c r="AU272" t="n">
         <v>4</v>
       </c>
       <c r="AV272" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW272" t="n">
         <v>5</v>
       </c>
       <c r="AX272" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY272" t="n">
         <v>9</v>
@@ -59995,25 +59995,25 @@
         <v>1.77</v>
       </c>
       <c r="AR273" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AS273" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AT273" t="n">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="AU273" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV273" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW273" t="n">
         <v>11</v>
       </c>
-      <c r="AV273" t="n">
-        <v>18</v>
-      </c>
-      <c r="AW273" t="n">
-        <v>5</v>
-      </c>
       <c r="AX273" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AY273" t="n">
         <v>16</v>
@@ -60213,22 +60213,22 @@
         <v>0.93</v>
       </c>
       <c r="AR274" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AS274" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AT274" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="AU274" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AV274" t="n">
         <v>5</v>
       </c>
       <c r="AW274" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AX274" t="n">
         <v>15</v>
@@ -60434,22 +60434,22 @@
         <v>1.52</v>
       </c>
       <c r="AS275" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AT275" t="n">
-        <v>3.14</v>
+        <v>3.19</v>
       </c>
       <c r="AU275" t="n">
         <v>2</v>
       </c>
       <c r="AV275" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AW275" t="n">
         <v>13</v>
       </c>
       <c r="AX275" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AY275" t="n">
         <v>15</v>
@@ -60649,25 +60649,25 @@
         <v>1.08</v>
       </c>
       <c r="AR276" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AS276" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AT276" t="n">
-        <v>2.69</v>
+        <v>2.61</v>
       </c>
       <c r="AU276" t="n">
         <v>8</v>
       </c>
       <c r="AV276" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AW276" t="n">
         <v>2</v>
       </c>
       <c r="AX276" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AY276" t="n">
         <v>10</v>
@@ -60867,22 +60867,22 @@
         <v>2.08</v>
       </c>
       <c r="AR277" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AS277" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AT277" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AU277" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV277" t="n">
         <v>8</v>
       </c>
       <c r="AW277" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX277" t="n">
         <v>4</v>
@@ -61085,25 +61085,25 @@
         <v>0.36</v>
       </c>
       <c r="AR278" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AS278" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AT278" t="n">
-        <v>2.65</v>
+        <v>2.58</v>
       </c>
       <c r="AU278" t="n">
         <v>4</v>
       </c>
       <c r="AV278" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AW278" t="n">
         <v>4</v>
       </c>
       <c r="AX278" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AY278" t="n">
         <v>8</v>
@@ -61303,25 +61303,25 @@
         <v>1</v>
       </c>
       <c r="AR279" t="n">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="AS279" t="n">
-        <v>0.86</v>
+        <v>0.9</v>
       </c>
       <c r="AT279" t="n">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="AU279" t="n">
         <v>10</v>
       </c>
       <c r="AV279" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW279" t="n">
         <v>8</v>
       </c>
       <c r="AX279" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY279" t="n">
         <v>18</v>
@@ -61521,13 +61521,13 @@
         <v>1.93</v>
       </c>
       <c r="AR280" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AS280" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AT280" t="n">
-        <v>3.34</v>
+        <v>3.22</v>
       </c>
       <c r="AU280" t="n">
         <v>3</v>
@@ -61739,22 +61739,22 @@
         <v>1.17</v>
       </c>
       <c r="AR281" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AS281" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AT281" t="n">
-        <v>2.63</v>
+        <v>2.41</v>
       </c>
       <c r="AU281" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV281" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW281" t="n">
         <v>6</v>
-      </c>
-      <c r="AV281" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW281" t="n">
-        <v>7</v>
       </c>
       <c r="AX281" t="n">
         <v>5</v>
@@ -61957,13 +61957,13 @@
         <v>1.77</v>
       </c>
       <c r="AR282" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="AS282" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AT282" t="n">
-        <v>2.82</v>
+        <v>2.58</v>
       </c>
       <c r="AU282" t="n">
         <v>7</v>
@@ -62175,13 +62175,13 @@
         <v>1.08</v>
       </c>
       <c r="AR283" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AS283" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AT283" t="n">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="AU283" t="n">
         <v>6</v>
@@ -62393,13 +62393,13 @@
         <v>1.36</v>
       </c>
       <c r="AR284" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AS284" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AT284" t="n">
-        <v>2.62</v>
+        <v>2.49</v>
       </c>
       <c r="AU284" t="n">
         <v>1</v>
@@ -62614,10 +62614,10 @@
         <v>1.5</v>
       </c>
       <c r="AS285" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AT285" t="n">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="AU285" t="n">
         <v>5</v>
@@ -62829,25 +62829,25 @@
         <v>2.08</v>
       </c>
       <c r="AR286" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AS286" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AT286" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="AU286" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV286" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW286" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX286" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY286" t="n">
         <v>15</v>
@@ -63047,13 +63047,13 @@
         <v>0.38</v>
       </c>
       <c r="AR287" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AS287" t="n">
-        <v>1.03</v>
+        <v>0.99</v>
       </c>
       <c r="AT287" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="AU287" t="n">
         <v>6</v>
@@ -63265,25 +63265,25 @@
         <v>0.86</v>
       </c>
       <c r="AR288" t="n">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="AS288" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AT288" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="AU288" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV288" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW288" t="n">
         <v>8</v>
       </c>
-      <c r="AW288" t="n">
-        <v>7</v>
-      </c>
       <c r="AX288" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY288" t="n">
         <v>13</v>
@@ -63483,25 +63483,25 @@
         <v>0.36</v>
       </c>
       <c r="AR289" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AS289" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AT289" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="AU289" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV289" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW289" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX289" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY289" t="n">
         <v>13</v>
@@ -63701,13 +63701,13 @@
         <v>1.33</v>
       </c>
       <c r="AR290" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AS290" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AT290" t="n">
-        <v>2.77</v>
+        <v>2.71</v>
       </c>
       <c r="AU290" t="n">
         <v>6</v>
@@ -63919,25 +63919,25 @@
         <v>1.54</v>
       </c>
       <c r="AR291" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AS291" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AT291" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="AU291" t="n">
         <v>3</v>
       </c>
       <c r="AV291" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW291" t="n">
         <v>4</v>
       </c>
       <c r="AX291" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY291" t="n">
         <v>7</v>
@@ -64092,16 +64092,16 @@
         <v>3.39</v>
       </c>
       <c r="AC292" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AD292" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AE292" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF292" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AG292" t="n">
         <v>1.9</v>
@@ -64116,13 +64116,13 @@
         <v>2.1</v>
       </c>
       <c r="AK292" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL292" t="n">
         <v>0</v>
       </c>
       <c r="AM292" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AN292" t="n">
         <v>2.38</v>
@@ -64137,22 +64137,22 @@
         <v>1.57</v>
       </c>
       <c r="AR292" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AS292" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AT292" t="n">
-        <v>3.15</v>
+        <v>3.07</v>
       </c>
       <c r="AU292" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV292" t="n">
         <v>1</v>
       </c>
       <c r="AW292" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX292" t="n">
         <v>4</v>
@@ -64173,43 +64173,43 @@
         <v>11</v>
       </c>
       <c r="BD292" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BE292" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="BF292" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BG292" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BH292" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BI292" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BJ292" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BK292" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BL292" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BM292" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BN292" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="BO292" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="BP292" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="293">
@@ -64355,25 +64355,25 @@
         <v>1</v>
       </c>
       <c r="AR293" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AS293" t="n">
         <v>1.04</v>
       </c>
       <c r="AT293" t="n">
-        <v>2.69</v>
+        <v>2.54</v>
       </c>
       <c r="AU293" t="n">
         <v>6</v>
       </c>
       <c r="AV293" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AW293" t="n">
         <v>5</v>
       </c>
       <c r="AX293" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AY293" t="n">
         <v>11</v>
@@ -64573,25 +64573,25 @@
         <v>1.77</v>
       </c>
       <c r="AR294" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AS294" t="n">
         <v>1.18</v>
       </c>
-      <c r="AS294" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AT294" t="n">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="AU294" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AV294" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AW294" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AX294" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AY294" t="n">
         <v>15</v>
@@ -64791,22 +64791,22 @@
         <v>0.85</v>
       </c>
       <c r="AR295" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AS295" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AT295" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="AU295" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AV295" t="n">
         <v>2</v>
       </c>
       <c r="AW295" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AX295" t="n">
         <v>3</v>
@@ -65009,22 +65009,22 @@
         <v>1.57</v>
       </c>
       <c r="AR296" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AS296" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AT296" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="AU296" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AV296" t="n">
         <v>1</v>
       </c>
       <c r="AW296" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AX296" t="n">
         <v>4</v>
@@ -65227,25 +65227,25 @@
         <v>1.77</v>
       </c>
       <c r="AR297" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AS297" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="AT297" t="n">
-        <v>3.02</v>
+        <v>2.94</v>
       </c>
       <c r="AU297" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV297" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AW297" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AX297" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AY297" t="n">
         <v>11</v>
@@ -65445,25 +65445,25 @@
         <v>1.69</v>
       </c>
       <c r="AR298" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AS298" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AT298" t="n">
-        <v>3.25</v>
+        <v>3.07</v>
       </c>
       <c r="AU298" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV298" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AW298" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX298" t="n">
         <v>10</v>
-      </c>
-      <c r="AX298" t="n">
-        <v>12</v>
       </c>
       <c r="AY298" t="n">
         <v>13</v>
@@ -65663,22 +65663,22 @@
         <v>0.38</v>
       </c>
       <c r="AR299" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AS299" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AT299" t="n">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="AU299" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV299" t="n">
         <v>1</v>
       </c>
       <c r="AW299" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX299" t="n">
         <v>5</v>
@@ -65881,25 +65881,25 @@
         <v>1.75</v>
       </c>
       <c r="AR300" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AS300" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AT300" t="n">
-        <v>2.61</v>
+        <v>2.47</v>
       </c>
       <c r="AU300" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV300" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AW300" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX300" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AY300" t="n">
         <v>13</v>
@@ -66099,13 +66099,13 @@
         <v>1.54</v>
       </c>
       <c r="AR301" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="AS301" t="n">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="AT301" t="n">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="AU301" t="n">
         <v>4</v>
@@ -66317,22 +66317,22 @@
         <v>0.38</v>
       </c>
       <c r="AR302" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AS302" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AT302" t="n">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="AU302" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AV302" t="n">
         <v>5</v>
       </c>
       <c r="AW302" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AX302" t="n">
         <v>13</v>
@@ -66535,13 +66535,13 @@
         <v>1.31</v>
       </c>
       <c r="AR303" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AS303" t="n">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="AT303" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="AU303" t="n">
         <v>5</v>
@@ -66753,22 +66753,22 @@
         <v>1.15</v>
       </c>
       <c r="AR304" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AS304" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AT304" t="n">
-        <v>2.67</v>
+        <v>2.56</v>
       </c>
       <c r="AU304" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV304" t="n">
         <v>5</v>
       </c>
       <c r="AW304" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX304" t="n">
         <v>2</v>
@@ -66971,25 +66971,25 @@
         <v>0.54</v>
       </c>
       <c r="AR305" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AS305" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AT305" t="n">
         <v>2.92</v>
       </c>
       <c r="AU305" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV305" t="n">
         <v>4</v>
       </c>
-      <c r="AV305" t="n">
-        <v>5</v>
-      </c>
       <c r="AW305" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX305" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY305" t="n">
         <v>15</v>
@@ -67189,13 +67189,13 @@
         <v>1.42</v>
       </c>
       <c r="AR306" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AS306" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="AT306" t="n">
-        <v>3.03</v>
+        <v>2.86</v>
       </c>
       <c r="AU306" t="n">
         <v>2</v>
@@ -67219,10 +67219,10 @@
         <v>2</v>
       </c>
       <c r="BB306" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BC306" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BD306" t="n">
         <v>1.67</v>
@@ -67407,25 +67407,25 @@
         <v>1.75</v>
       </c>
       <c r="AR307" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AS307" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AT307" t="n">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="AU307" t="n">
         <v>6</v>
       </c>
       <c r="AV307" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW307" t="n">
         <v>10</v>
       </c>
       <c r="AX307" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY307" t="n">
         <v>16</v>
@@ -67625,13 +67625,13 @@
         <v>1</v>
       </c>
       <c r="AR308" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AS308" t="n">
-        <v>0.87</v>
+        <v>0.91</v>
       </c>
       <c r="AT308" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="AU308" t="n">
         <v>5</v>
@@ -67843,22 +67843,22 @@
         <v>0.54</v>
       </c>
       <c r="AR309" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="AS309" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AT309" t="n">
-        <v>2.89</v>
+        <v>2.83</v>
       </c>
       <c r="AU309" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV309" t="n">
         <v>1</v>
       </c>
       <c r="AW309" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX309" t="n">
         <v>7</v>
@@ -68061,25 +68061,25 @@
         <v>0.38</v>
       </c>
       <c r="AR310" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AS310" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AT310" t="n">
-        <v>2.44</v>
+        <v>2.25</v>
       </c>
       <c r="AU310" t="n">
         <v>5</v>
       </c>
       <c r="AV310" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW310" t="n">
         <v>8</v>
       </c>
       <c r="AX310" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY310" t="n">
         <v>13</v>
@@ -68279,25 +68279,25 @@
         <v>0.86</v>
       </c>
       <c r="AR311" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AS311" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AT311" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="AU311" t="n">
         <v>4</v>
       </c>
       <c r="AV311" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW311" t="n">
         <v>6</v>
       </c>
       <c r="AX311" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY311" t="n">
         <v>10</v>
@@ -68497,13 +68497,13 @@
         <v>1.36</v>
       </c>
       <c r="AR312" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AS312" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AT312" t="n">
-        <v>2.77</v>
+        <v>2.66</v>
       </c>
       <c r="AU312" t="n">
         <v>5</v>
@@ -68715,13 +68715,13 @@
         <v>1.08</v>
       </c>
       <c r="AR313" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AS313" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AT313" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="AU313" t="n">
         <v>6</v>
@@ -68933,25 +68933,25 @@
         <v>1.14</v>
       </c>
       <c r="AR314" t="n">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="AS314" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="AT314" t="n">
-        <v>2.93</v>
+        <v>2.83</v>
       </c>
       <c r="AU314" t="n">
         <v>9</v>
       </c>
       <c r="AV314" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW314" t="n">
         <v>14</v>
       </c>
       <c r="AX314" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY314" t="n">
         <v>23</v>
@@ -69151,13 +69151,13 @@
         <v>1.31</v>
       </c>
       <c r="AR315" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AS315" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AT315" t="n">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="AU315" t="n">
         <v>4</v>
@@ -69372,10 +69372,10 @@
         <v>1.49</v>
       </c>
       <c r="AS316" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AT316" t="n">
-        <v>3.11</v>
+        <v>3.08</v>
       </c>
       <c r="AU316" t="n">
         <v>4</v>
@@ -69587,25 +69587,25 @@
         <v>1.42</v>
       </c>
       <c r="AR317" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AS317" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AT317" t="n">
-        <v>2.96</v>
+        <v>2.79</v>
       </c>
       <c r="AU317" t="n">
         <v>4</v>
       </c>
       <c r="AV317" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW317" t="n">
         <v>9</v>
       </c>
       <c r="AX317" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY317" t="n">
         <v>13</v>
@@ -69808,28 +69808,28 @@
         <v>1.54</v>
       </c>
       <c r="AS318" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AT318" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="AU318" t="n">
         <v>3</v>
       </c>
       <c r="AV318" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AW318" t="n">
         <v>4</v>
       </c>
       <c r="AX318" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="AY318" t="n">
         <v>7</v>
       </c>
       <c r="AZ318" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="BA318" t="n">
         <v>3</v>
@@ -70023,22 +70023,22 @@
         <v>1.57</v>
       </c>
       <c r="AR319" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AS319" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AT319" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="AU319" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AV319" t="n">
         <v>2</v>
       </c>
       <c r="AW319" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AX319" t="n">
         <v>12</v>
@@ -70241,25 +70241,25 @@
         <v>1.15</v>
       </c>
       <c r="AR320" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AS320" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AT320" t="n">
-        <v>2.51</v>
+        <v>2.43</v>
       </c>
       <c r="AU320" t="n">
         <v>5</v>
       </c>
       <c r="AV320" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW320" t="n">
         <v>12</v>
       </c>
       <c r="AX320" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY320" t="n">
         <v>17</v>
@@ -70462,10 +70462,10 @@
         <v>1.33</v>
       </c>
       <c r="AS321" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AT321" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="AU321" t="n">
         <v>5</v>
@@ -70677,22 +70677,22 @@
         <v>1.38</v>
       </c>
       <c r="AR322" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AS322" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AT322" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="AU322" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV322" t="n">
         <v>1</v>
       </c>
       <c r="AW322" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX322" t="n">
         <v>9</v>
@@ -70895,25 +70895,25 @@
         <v>1.17</v>
       </c>
       <c r="AR323" t="n">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="AS323" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AT323" t="n">
-        <v>2.9</v>
+        <v>2.74</v>
       </c>
       <c r="AU323" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AV323" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW323" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AX323" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY323" t="n">
         <v>20</v>
@@ -71113,25 +71113,25 @@
         <v>1.31</v>
       </c>
       <c r="AR324" t="n">
-        <v>1.61</v>
+        <v>1.4</v>
       </c>
       <c r="AS324" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AT324" t="n">
-        <v>2.99</v>
+        <v>2.68</v>
       </c>
       <c r="AU324" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV324" t="n">
         <v>6</v>
       </c>
-      <c r="AV324" t="n">
-        <v>8</v>
-      </c>
       <c r="AW324" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AX324" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AY324" t="n">
         <v>21</v>
@@ -71331,25 +71331,25 @@
         <v>1.75</v>
       </c>
       <c r="AR325" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="AS325" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AT325" t="n">
-        <v>2.93</v>
+        <v>2.81</v>
       </c>
       <c r="AU325" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV325" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW325" t="n">
         <v>5</v>
       </c>
-      <c r="AV325" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW325" t="n">
-        <v>6</v>
-      </c>
       <c r="AX325" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY325" t="n">
         <v>11</v>
@@ -71549,22 +71549,22 @@
         <v>0.64</v>
       </c>
       <c r="AR326" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AS326" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AT326" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="AU326" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV326" t="n">
         <v>1</v>
       </c>
       <c r="AW326" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX326" t="n">
         <v>10</v>
@@ -71767,25 +71767,25 @@
         <v>1.69</v>
       </c>
       <c r="AR327" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AS327" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="AT327" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="AU327" t="n">
         <v>4</v>
       </c>
       <c r="AV327" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW327" t="n">
         <v>6</v>
       </c>
       <c r="AX327" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY327" t="n">
         <v>10</v>
@@ -71985,13 +71985,13 @@
         <v>0.86</v>
       </c>
       <c r="AR328" t="n">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="AS328" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AT328" t="n">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="AU328" t="n">
         <v>6</v>
@@ -72203,22 +72203,22 @@
         <v>1.08</v>
       </c>
       <c r="AR329" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AS329" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AT329" t="n">
-        <v>2.93</v>
+        <v>2.84</v>
       </c>
       <c r="AU329" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV329" t="n">
         <v>4</v>
       </c>
       <c r="AW329" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX329" t="n">
         <v>7</v>
@@ -72421,13 +72421,13 @@
         <v>1.42</v>
       </c>
       <c r="AR330" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AS330" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AT330" t="n">
-        <v>2.98</v>
+        <v>2.84</v>
       </c>
       <c r="AU330" t="n">
         <v>4</v>
@@ -72639,25 +72639,25 @@
         <v>1.57</v>
       </c>
       <c r="AR331" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AS331" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AT331" t="n">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="AU331" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV331" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW331" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX331" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY331" t="n">
         <v>11</v>
@@ -72857,22 +72857,22 @@
         <v>1.27</v>
       </c>
       <c r="AR332" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AS332" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AT332" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AU332" t="n">
         <v>3</v>
-      </c>
-      <c r="AU332" t="n">
-        <v>2</v>
       </c>
       <c r="AV332" t="n">
         <v>6</v>
       </c>
       <c r="AW332" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX332" t="n">
         <v>1</v>
@@ -73075,25 +73075,25 @@
         <v>1</v>
       </c>
       <c r="AR333" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AS333" t="n">
-        <v>0.83</v>
+        <v>0.87</v>
       </c>
       <c r="AT333" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="AU333" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV333" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW333" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX333" t="n">
         <v>4</v>
-      </c>
-      <c r="AV333" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW333" t="n">
-        <v>12</v>
-      </c>
-      <c r="AX333" t="n">
-        <v>10</v>
       </c>
       <c r="AY333" t="n">
         <v>16</v>
@@ -73293,25 +73293,25 @@
         <v>1.38</v>
       </c>
       <c r="AR334" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AS334" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AT334" t="n">
-        <v>3.04</v>
+        <v>3.01</v>
       </c>
       <c r="AU334" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV334" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AW334" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX334" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AY334" t="n">
         <v>13</v>
@@ -73511,25 +73511,25 @@
         <v>1</v>
       </c>
       <c r="AR335" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="AS335" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AT335" t="n">
-        <v>2.72</v>
+        <v>2.65</v>
       </c>
       <c r="AU335" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV335" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW335" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX335" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY335" t="n">
         <v>7</v>
@@ -73732,22 +73732,22 @@
         <v>1.37</v>
       </c>
       <c r="AS336" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AT336" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="AU336" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AV336" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AW336" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AX336" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AY336" t="n">
         <v>16</v>
@@ -73947,25 +73947,25 @@
         <v>0.86</v>
       </c>
       <c r="AR337" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AS337" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AT337" t="n">
-        <v>2.77</v>
+        <v>2.83</v>
       </c>
       <c r="AU337" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV337" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AW337" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX337" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AY337" t="n">
         <v>12</v>
@@ -74165,22 +74165,22 @@
         <v>1.75</v>
       </c>
       <c r="AR338" t="n">
-        <v>1.66</v>
+        <v>1.44</v>
       </c>
       <c r="AS338" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AT338" t="n">
-        <v>2.93</v>
+        <v>2.65</v>
       </c>
       <c r="AU338" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV338" t="n">
         <v>8</v>
       </c>
       <c r="AW338" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX338" t="n">
         <v>5</v>
@@ -74386,22 +74386,22 @@
         <v>1.41</v>
       </c>
       <c r="AS339" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AT339" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AU339" t="n">
         <v>6</v>
       </c>
       <c r="AV339" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW339" t="n">
         <v>13</v>
       </c>
       <c r="AX339" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY339" t="n">
         <v>19</v>
@@ -74601,13 +74601,13 @@
         <v>1.69</v>
       </c>
       <c r="AR340" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AS340" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AT340" t="n">
-        <v>2.98</v>
+        <v>2.85</v>
       </c>
       <c r="AU340" t="n">
         <v>4</v>
@@ -74819,13 +74819,13 @@
         <v>1.77</v>
       </c>
       <c r="AR341" t="n">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="AS341" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AT341" t="n">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="AU341" t="n">
         <v>3</v>
@@ -75037,22 +75037,22 @@
         <v>0.64</v>
       </c>
       <c r="AR342" t="n">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="AS342" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AT342" t="n">
-        <v>3.05</v>
+        <v>2.97</v>
       </c>
       <c r="AU342" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV342" t="n">
         <v>1</v>
       </c>
       <c r="AW342" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AX342" t="n">
         <v>5</v>
@@ -75258,10 +75258,10 @@
         <v>1.6</v>
       </c>
       <c r="AS343" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AT343" t="n">
-        <v>3.35</v>
+        <v>3.27</v>
       </c>
       <c r="AU343" t="n">
         <v>9</v>
@@ -75473,22 +75473,22 @@
         <v>0.38</v>
       </c>
       <c r="AR344" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AS344" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AT344" t="n">
-        <v>2.31</v>
+        <v>2.24</v>
       </c>
       <c r="AU344" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV344" t="n">
         <v>2</v>
       </c>
       <c r="AW344" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX344" t="n">
         <v>14</v>
@@ -75691,25 +75691,25 @@
         <v>1.08</v>
       </c>
       <c r="AR345" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="AS345" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AT345" t="n">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="AU345" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV345" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW345" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AX345" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY345" t="n">
         <v>11</v>
@@ -75909,25 +75909,25 @@
         <v>1.54</v>
       </c>
       <c r="AR346" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AS346" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="AT346" t="n">
-        <v>2.96</v>
+        <v>3.08</v>
       </c>
       <c r="AU346" t="n">
         <v>3</v>
       </c>
       <c r="AV346" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW346" t="n">
         <v>8</v>
       </c>
       <c r="AX346" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY346" t="n">
         <v>11</v>
@@ -76127,13 +76127,13 @@
         <v>1</v>
       </c>
       <c r="AR347" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AS347" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="AT347" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="AU347" t="n">
         <v>5</v>
@@ -76345,25 +76345,25 @@
         <v>1.93</v>
       </c>
       <c r="AR348" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AS348" t="n">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="AT348" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AU348" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV348" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW348" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX348" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY348" t="n">
         <v>17</v>
@@ -76563,25 +76563,25 @@
         <v>0.36</v>
       </c>
       <c r="AR349" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AS349" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AT349" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="AU349" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV349" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW349" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX349" t="n">
         <v>5</v>
-      </c>
-      <c r="AX349" t="n">
-        <v>4</v>
       </c>
       <c r="AY349" t="n">
         <v>8</v>
@@ -76781,13 +76781,13 @@
         <v>1.57</v>
       </c>
       <c r="AR350" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="AS350" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AT350" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="AU350" t="n">
         <v>6</v>
@@ -76999,22 +76999,22 @@
         <v>1.77</v>
       </c>
       <c r="AR351" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AS351" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="AT351" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="AU351" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV351" t="n">
         <v>4</v>
       </c>
       <c r="AW351" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX351" t="n">
         <v>12</v>
@@ -77217,22 +77217,22 @@
         <v>0.86</v>
       </c>
       <c r="AR352" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AS352" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AT352" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AU352" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV352" t="n">
         <v>5</v>
       </c>
       <c r="AW352" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AX352" t="n">
         <v>6</v>
@@ -77435,13 +77435,13 @@
         <v>1.08</v>
       </c>
       <c r="AR353" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AS353" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AT353" t="n">
-        <v>2.53</v>
+        <v>2.47</v>
       </c>
       <c r="AU353" t="n">
         <v>6</v>
@@ -77653,22 +77653,22 @@
         <v>1.77</v>
       </c>
       <c r="AR354" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AS354" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AT354" t="n">
-        <v>3.17</v>
+        <v>3.09</v>
       </c>
       <c r="AU354" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV354" t="n">
         <v>6</v>
       </c>
       <c r="AW354" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX354" t="n">
         <v>4</v>
@@ -77871,25 +77871,25 @@
         <v>1.17</v>
       </c>
       <c r="AR355" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AS355" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AT355" t="n">
-        <v>2.97</v>
+        <v>2.91</v>
       </c>
       <c r="AU355" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AV355" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW355" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AX355" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY355" t="n">
         <v>12</v>
@@ -78089,13 +78089,13 @@
         <v>1.36</v>
       </c>
       <c r="AR356" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AS356" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AT356" t="n">
-        <v>2.92</v>
+        <v>2.77</v>
       </c>
       <c r="AU356" t="n">
         <v>3</v>
@@ -78307,22 +78307,22 @@
         <v>1.93</v>
       </c>
       <c r="AR357" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AS357" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AT357" t="n">
-        <v>2.85</v>
+        <v>2.74</v>
       </c>
       <c r="AU357" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV357" t="n">
         <v>4</v>
       </c>
       <c r="AW357" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX357" t="n">
         <v>4</v>
@@ -78525,13 +78525,13 @@
         <v>1</v>
       </c>
       <c r="AR358" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AS358" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="AT358" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="AU358" t="n">
         <v>11</v>
@@ -78743,22 +78743,22 @@
         <v>1.33</v>
       </c>
       <c r="AR359" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AS359" t="n">
         <v>1.03</v>
       </c>
       <c r="AT359" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="AU359" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV359" t="n">
         <v>6</v>
       </c>
       <c r="AW359" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX359" t="n">
         <v>9</v>
@@ -78961,13 +78961,13 @@
         <v>1</v>
       </c>
       <c r="AR360" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AS360" t="n">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="AT360" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="AU360" t="n">
         <v>4</v>
@@ -79182,19 +79182,19 @@
         <v>1.47</v>
       </c>
       <c r="AS361" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AT361" t="n">
-        <v>2.87</v>
+        <v>2.84</v>
       </c>
       <c r="AU361" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV361" t="n">
         <v>2</v>
       </c>
       <c r="AW361" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AX361" t="n">
         <v>6</v>
@@ -79400,10 +79400,10 @@
         <v>1.52</v>
       </c>
       <c r="AS362" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AT362" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="AU362" t="n">
         <v>7</v>
@@ -79615,22 +79615,22 @@
         <v>1.77</v>
       </c>
       <c r="AR363" t="n">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
       <c r="AS363" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="AT363" t="n">
-        <v>3.02</v>
+        <v>2.85</v>
       </c>
       <c r="AU363" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV363" t="n">
         <v>4</v>
       </c>
       <c r="AW363" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX363" t="n">
         <v>4</v>
@@ -79833,22 +79833,22 @@
         <v>1.08</v>
       </c>
       <c r="AR364" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AS364" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AT364" t="n">
-        <v>3.32</v>
+        <v>3.21</v>
       </c>
       <c r="AU364" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV364" t="n">
         <v>3</v>
       </c>
       <c r="AW364" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AX364" t="n">
         <v>6</v>
@@ -80051,22 +80051,22 @@
         <v>0.85</v>
       </c>
       <c r="AR365" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AS365" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AT365" t="n">
         <v>2.91</v>
       </c>
       <c r="AU365" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV365" t="n">
         <v>3</v>
       </c>
       <c r="AW365" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX365" t="n">
         <v>8</v>
@@ -80269,22 +80269,22 @@
         <v>1</v>
       </c>
       <c r="AR366" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="AS366" t="n">
         <v>1.01</v>
       </c>
       <c r="AT366" t="n">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="AU366" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV366" t="n">
         <v>4</v>
       </c>
       <c r="AW366" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX366" t="n">
         <v>6</v>
@@ -80487,22 +80487,22 @@
         <v>0.38</v>
       </c>
       <c r="AR367" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="AS367" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AT367" t="n">
-        <v>2.65</v>
+        <v>2.47</v>
       </c>
       <c r="AU367" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV367" t="n">
         <v>5</v>
       </c>
       <c r="AW367" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX367" t="n">
         <v>12</v>
@@ -80705,13 +80705,13 @@
         <v>0.64</v>
       </c>
       <c r="AR368" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="AS368" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AT368" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="AU368" t="n">
         <v>3</v>
@@ -80926,10 +80926,10 @@
         <v>1.53</v>
       </c>
       <c r="AS369" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AT369" t="n">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="AU369" t="n">
         <v>3</v>
@@ -81141,13 +81141,13 @@
         <v>1.36</v>
       </c>
       <c r="AR370" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="AS370" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AT370" t="n">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="AU370" t="n">
         <v>8</v>
@@ -81359,22 +81359,22 @@
         <v>1.17</v>
       </c>
       <c r="AR371" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AS371" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AT371" t="n">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="AU371" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV371" t="n">
         <v>3</v>
       </c>
       <c r="AW371" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX371" t="n">
         <v>6</v>
@@ -81577,25 +81577,25 @@
         <v>1.15</v>
       </c>
       <c r="AR372" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AS372" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AT372" t="n">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="AU372" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AV372" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AW372" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AX372" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AY372" t="n">
         <v>12</v>
@@ -81795,22 +81795,22 @@
         <v>2.08</v>
       </c>
       <c r="AR373" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AS373" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AT373" t="n">
-        <v>3.16</v>
+        <v>3.11</v>
       </c>
       <c r="AU373" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AV373" t="n">
         <v>5</v>
       </c>
       <c r="AW373" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AX373" t="n">
         <v>1</v>
@@ -82013,13 +82013,13 @@
         <v>1.57</v>
       </c>
       <c r="AR374" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AS374" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AT374" t="n">
-        <v>3.03</v>
+        <v>2.99</v>
       </c>
       <c r="AU374" t="n">
         <v>5</v>
@@ -82231,22 +82231,22 @@
         <v>0.86</v>
       </c>
       <c r="AR375" t="n">
-        <v>1.61</v>
+        <v>1.39</v>
       </c>
       <c r="AS375" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AT375" t="n">
-        <v>3.06</v>
+        <v>2.85</v>
       </c>
       <c r="AU375" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV375" t="n">
         <v>3</v>
       </c>
       <c r="AW375" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX375" t="n">
         <v>4</v>
@@ -82449,13 +82449,13 @@
         <v>1</v>
       </c>
       <c r="AR376" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AS376" t="n">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
       <c r="AT376" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AU376" t="n">
         <v>9</v>
@@ -82667,13 +82667,13 @@
         <v>0.93</v>
       </c>
       <c r="AR377" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AS377" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AT377" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="AU377" t="n">
         <v>7</v>
@@ -82885,25 +82885,25 @@
         <v>1.75</v>
       </c>
       <c r="AR378" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AS378" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AT378" t="n">
-        <v>3.11</v>
+        <v>2.97</v>
       </c>
       <c r="AU378" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV378" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW378" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX378" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY378" t="n">
         <v>21</v>
@@ -83103,25 +83103,25 @@
         <v>1.14</v>
       </c>
       <c r="AR379" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AS379" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="AT379" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="AU379" t="n">
         <v>3</v>
       </c>
       <c r="AV379" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW379" t="n">
         <v>5</v>
       </c>
       <c r="AX379" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY379" t="n">
         <v>8</v>
@@ -83321,13 +83321,13 @@
         <v>0.36</v>
       </c>
       <c r="AR380" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AS380" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AT380" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AU380" t="n">
         <v>8</v>
@@ -83539,13 +83539,13 @@
         <v>1.42</v>
       </c>
       <c r="AR381" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AS381" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AT381" t="n">
-        <v>2.68</v>
+        <v>2.44</v>
       </c>
       <c r="AU381" t="n">
         <v>3</v>
@@ -83757,31 +83757,31 @@
         <v>1.54</v>
       </c>
       <c r="AR382" t="n">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="AS382" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AT382" t="n">
-        <v>3.03</v>
+        <v>2.91</v>
       </c>
       <c r="AU382" t="n">
         <v>2</v>
       </c>
       <c r="AV382" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW382" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX382" t="n">
         <v>5</v>
       </c>
-      <c r="AX382" t="n">
-        <v>8</v>
-      </c>
       <c r="AY382" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AZ382" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA382" t="n">
         <v>1</v>
@@ -83975,13 +83975,13 @@
         <v>1.27</v>
       </c>
       <c r="AR383" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="AS383" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="AT383" t="n">
-        <v>2.81</v>
+        <v>2.69</v>
       </c>
       <c r="AU383" t="n">
         <v>5</v>
@@ -84193,25 +84193,25 @@
         <v>0.64</v>
       </c>
       <c r="AR384" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AS384" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AT384" t="n">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="AU384" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV384" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AW384" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX384" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AY384" t="n">
         <v>9</v>
@@ -84411,13 +84411,13 @@
         <v>0.86</v>
       </c>
       <c r="AR385" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AS385" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AT385" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="AU385" t="n">
         <v>2</v>
@@ -84629,22 +84629,22 @@
         <v>1.38</v>
       </c>
       <c r="AR386" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AS386" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AT386" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="AU386" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV386" t="n">
         <v>2</v>
       </c>
       <c r="AW386" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX386" t="n">
         <v>5</v>
@@ -84850,22 +84850,22 @@
         <v>1.62</v>
       </c>
       <c r="AS387" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AT387" t="n">
-        <v>3.07</v>
+        <v>3.03</v>
       </c>
       <c r="AU387" t="n">
         <v>3</v>
       </c>
       <c r="AV387" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW387" t="n">
         <v>7</v>
       </c>
       <c r="AX387" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY387" t="n">
         <v>10</v>
@@ -85065,25 +85065,25 @@
         <v>0.38</v>
       </c>
       <c r="AR388" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="AS388" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AT388" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="AU388" t="n">
         <v>3</v>
       </c>
       <c r="AV388" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW388" t="n">
         <v>6</v>
       </c>
       <c r="AX388" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY388" t="n">
         <v>9</v>
@@ -85286,22 +85286,22 @@
         <v>1.5</v>
       </c>
       <c r="AS389" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AT389" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AU389" t="n">
         <v>5</v>
       </c>
       <c r="AV389" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW389" t="n">
         <v>14</v>
       </c>
       <c r="AX389" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY389" t="n">
         <v>19</v>
@@ -85310,13 +85310,13 @@
         <v>13</v>
       </c>
       <c r="BA389" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB389" t="n">
         <v>2</v>
       </c>
       <c r="BC389" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD389" t="n">
         <v>1.47</v>
@@ -85501,25 +85501,25 @@
         <v>1.93</v>
       </c>
       <c r="AR390" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AS390" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AT390" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="AU390" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV390" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW390" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX390" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY390" t="n">
         <v>24</v>
@@ -85719,13 +85719,13 @@
         <v>0.85</v>
       </c>
       <c r="AR391" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AS391" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AT391" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="AU391" t="n">
         <v>7</v>
@@ -85937,13 +85937,13 @@
         <v>1.36</v>
       </c>
       <c r="AR392" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="AS392" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="AT392" t="n">
-        <v>2.99</v>
+        <v>2.76</v>
       </c>
       <c r="AU392" t="n">
         <v>4</v>
@@ -86158,10 +86158,10 @@
         <v>1.76</v>
       </c>
       <c r="AS393" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="AT393" t="n">
-        <v>3.27</v>
+        <v>3.24</v>
       </c>
       <c r="AU393" t="n">
         <v>4</v>
@@ -86373,13 +86373,13 @@
         <v>1.15</v>
       </c>
       <c r="AR394" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AS394" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AT394" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="AU394" t="n">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP402"/>
+  <dimension ref="A1:BP406"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,7 +914,7 @@
         <v>2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -2876,7 +2876,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -3963,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ16" t="n">
         <v>2.08</v>
@@ -4399,7 +4399,7 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ18" t="n">
         <v>1.14</v>
@@ -6361,10 +6361,10 @@
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR27" t="n">
         <v>0</v>
@@ -7015,7 +7015,7 @@
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ30" t="n">
         <v>0.36</v>
@@ -9198,7 +9198,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR40" t="n">
         <v>1.46</v>
@@ -9416,7 +9416,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR41" t="n">
         <v>1.37</v>
@@ -9631,7 +9631,7 @@
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ42" t="n">
         <v>0.86</v>
@@ -9849,7 +9849,7 @@
         <v>3</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ43" t="n">
         <v>2.08</v>
@@ -10070,7 +10070,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR44" t="n">
         <v>1.69</v>
@@ -10503,10 +10503,10 @@
         <v>1</v>
       </c>
       <c r="AP46" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR46" t="n">
         <v>0.91</v>
@@ -12032,7 +12032,7 @@
         <v>1</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR53" t="n">
         <v>1.81</v>
@@ -12904,7 +12904,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR57" t="n">
         <v>1.67</v>
@@ -13119,7 +13119,7 @@
         <v>3</v>
       </c>
       <c r="AP58" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ58" t="n">
         <v>1.42</v>
@@ -14648,7 +14648,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ65" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR65" t="n">
         <v>1.6</v>
@@ -15953,7 +15953,7 @@
         <v>2</v>
       </c>
       <c r="AP71" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ71" t="n">
         <v>1.38</v>
@@ -16174,7 +16174,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ72" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR72" t="n">
         <v>1.81</v>
@@ -16607,7 +16607,7 @@
         <v>2</v>
       </c>
       <c r="AP74" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ74" t="n">
         <v>1.57</v>
@@ -19441,7 +19441,7 @@
         <v>0.5</v>
       </c>
       <c r="AP87" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ87" t="n">
         <v>1.64</v>
@@ -19659,7 +19659,7 @@
         <v>1.5</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ88" t="n">
         <v>1.25</v>
@@ -20531,7 +20531,7 @@
         <v>0.67</v>
       </c>
       <c r="AP92" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ92" t="n">
         <v>0.36</v>
@@ -21842,7 +21842,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR98" t="n">
         <v>1.51</v>
@@ -22278,7 +22278,7 @@
         <v>1</v>
       </c>
       <c r="AQ100" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR100" t="n">
         <v>1.63</v>
@@ -22493,10 +22493,10 @@
         <v>2.33</v>
       </c>
       <c r="AP101" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ101" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR101" t="n">
         <v>1.59</v>
@@ -22711,7 +22711,7 @@
         <v>0.33</v>
       </c>
       <c r="AP102" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ102" t="n">
         <v>1.14</v>
@@ -22932,7 +22932,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ103" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR103" t="n">
         <v>1.67</v>
@@ -23586,7 +23586,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ106" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR106" t="n">
         <v>0.85</v>
@@ -24673,7 +24673,7 @@
         <v>2</v>
       </c>
       <c r="AP111" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ111" t="n">
         <v>1.23</v>
@@ -25763,7 +25763,7 @@
         <v>0.67</v>
       </c>
       <c r="AP116" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ116" t="n">
         <v>1.15</v>
@@ -26202,7 +26202,7 @@
         <v>1</v>
       </c>
       <c r="AQ118" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR118" t="n">
         <v>1.59</v>
@@ -29036,7 +29036,7 @@
         <v>1</v>
       </c>
       <c r="AQ131" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR131" t="n">
         <v>1.25</v>
@@ -29469,7 +29469,7 @@
         <v>0.4</v>
       </c>
       <c r="AP133" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ133" t="n">
         <v>1</v>
@@ -31649,7 +31649,7 @@
         <v>0.75</v>
       </c>
       <c r="AP143" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ143" t="n">
         <v>0.86</v>
@@ -32960,7 +32960,7 @@
         <v>2</v>
       </c>
       <c r="AQ149" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR149" t="n">
         <v>1.59</v>
@@ -33175,10 +33175,10 @@
         <v>1.75</v>
       </c>
       <c r="AP150" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ150" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR150" t="n">
         <v>1.33</v>
@@ -34268,7 +34268,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ155" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR155" t="n">
         <v>1.34</v>
@@ -34704,7 +34704,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ157" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR157" t="n">
         <v>1.48</v>
@@ -35137,7 +35137,7 @@
         <v>2</v>
       </c>
       <c r="AP159" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ159" t="n">
         <v>1.38</v>
@@ -35355,7 +35355,7 @@
         <v>1.2</v>
       </c>
       <c r="AP160" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ160" t="n">
         <v>0.86</v>
@@ -35576,7 +35576,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ161" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR161" t="n">
         <v>2.02</v>
@@ -36012,7 +36012,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ163" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR163" t="n">
         <v>1.77</v>
@@ -39715,7 +39715,7 @@
         <v>0.8</v>
       </c>
       <c r="AP180" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ180" t="n">
         <v>1.25</v>
@@ -41244,7 +41244,7 @@
         <v>1</v>
       </c>
       <c r="AQ187" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR187" t="n">
         <v>1.38</v>
@@ -41895,10 +41895,10 @@
         <v>1.67</v>
       </c>
       <c r="AP190" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ190" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR190" t="n">
         <v>1.39</v>
@@ -42549,10 +42549,10 @@
         <v>1.33</v>
       </c>
       <c r="AP193" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ193" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR193" t="n">
         <v>1.66</v>
@@ -44078,7 +44078,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ200" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR200" t="n">
         <v>1.51</v>
@@ -45383,7 +45383,7 @@
         <v>0.57</v>
       </c>
       <c r="AP206" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ206" t="n">
         <v>0.85</v>
@@ -45819,7 +45819,7 @@
         <v>0.83</v>
       </c>
       <c r="AP208" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ208" t="n">
         <v>1.25</v>
@@ -46255,7 +46255,7 @@
         <v>0.25</v>
       </c>
       <c r="AP210" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ210" t="n">
         <v>0.36</v>
@@ -46912,7 +46912,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ213" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR213" t="n">
         <v>1.71</v>
@@ -48220,7 +48220,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ219" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR219" t="n">
         <v>1.57</v>
@@ -48435,7 +48435,7 @@
         <v>2</v>
       </c>
       <c r="AP220" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ220" t="n">
         <v>1.57</v>
@@ -51487,7 +51487,7 @@
         <v>1.17</v>
       </c>
       <c r="AP234" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ234" t="n">
         <v>1.21</v>
@@ -51705,10 +51705,10 @@
         <v>1.57</v>
       </c>
       <c r="AP235" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ235" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR235" t="n">
         <v>1.83</v>
@@ -51926,7 +51926,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ236" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR236" t="n">
         <v>1.1</v>
@@ -54321,7 +54321,7 @@
         <v>1</v>
       </c>
       <c r="AP247" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ247" t="n">
         <v>1.23</v>
@@ -54539,7 +54539,7 @@
         <v>0.89</v>
       </c>
       <c r="AP248" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ248" t="n">
         <v>0.86</v>
@@ -54760,7 +54760,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ249" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR249" t="n">
         <v>1.8</v>
@@ -55414,7 +55414,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ252" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR252" t="n">
         <v>1.29</v>
@@ -55629,7 +55629,7 @@
         <v>1</v>
       </c>
       <c r="AP253" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ253" t="n">
         <v>1.14</v>
@@ -58463,7 +58463,7 @@
         <v>1</v>
       </c>
       <c r="AP266" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ266" t="n">
         <v>0.64</v>
@@ -61079,7 +61079,7 @@
         <v>1.5</v>
       </c>
       <c r="AP278" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ278" t="n">
         <v>2.08</v>
@@ -61518,7 +61518,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ280" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR280" t="n">
         <v>1.33</v>
@@ -61736,7 +61736,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ281" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR281" t="n">
         <v>1.12</v>
@@ -62172,7 +62172,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ283" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR283" t="n">
         <v>0.98</v>
@@ -62608,7 +62608,7 @@
         <v>1</v>
       </c>
       <c r="AQ285" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR285" t="n">
         <v>1.57</v>
@@ -64570,7 +64570,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ294" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR294" t="n">
         <v>1.09</v>
@@ -65003,7 +65003,7 @@
         <v>2</v>
       </c>
       <c r="AP296" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ296" t="n">
         <v>1.57</v>
@@ -66311,10 +66311,10 @@
         <v>0.5</v>
       </c>
       <c r="AP302" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ302" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR302" t="n">
         <v>1.41</v>
@@ -66747,7 +66747,7 @@
         <v>1.11</v>
       </c>
       <c r="AP304" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ304" t="n">
         <v>1.15</v>
@@ -67622,7 +67622,7 @@
         <v>2</v>
       </c>
       <c r="AQ308" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR308" t="n">
         <v>1.85</v>
@@ -70235,7 +70235,7 @@
         <v>1.3</v>
       </c>
       <c r="AP320" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ320" t="n">
         <v>1.15</v>
@@ -70671,7 +70671,7 @@
         <v>0.89</v>
       </c>
       <c r="AP322" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ322" t="n">
         <v>0.64</v>
@@ -70892,7 +70892,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ323" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR323" t="n">
         <v>1.55</v>
@@ -73072,7 +73072,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ333" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR333" t="n">
         <v>1.66</v>
@@ -73287,7 +73287,7 @@
         <v>1</v>
       </c>
       <c r="AP334" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ334" t="n">
         <v>1.23</v>
@@ -73723,7 +73723,7 @@
         <v>1</v>
       </c>
       <c r="AP336" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ336" t="n">
         <v>1</v>
@@ -75688,7 +75688,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ345" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR345" t="n">
         <v>1.16</v>
@@ -76339,7 +76339,7 @@
         <v>1.83</v>
       </c>
       <c r="AP348" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ348" t="n">
         <v>1.93</v>
@@ -76557,7 +76557,7 @@
         <v>1.75</v>
       </c>
       <c r="AP349" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ349" t="n">
         <v>1.57</v>
@@ -76996,7 +76996,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ351" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR351" t="n">
         <v>1.32</v>
@@ -77865,7 +77865,7 @@
         <v>1.55</v>
       </c>
       <c r="AP355" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ355" t="n">
         <v>1.21</v>
@@ -78086,7 +78086,7 @@
         <v>2</v>
       </c>
       <c r="AQ356" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR356" t="n">
         <v>1.86</v>
@@ -78958,7 +78958,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ360" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR360" t="n">
         <v>1.71</v>
@@ -79394,7 +79394,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ362" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR362" t="n">
         <v>1.63</v>
@@ -79827,7 +79827,7 @@
         <v>1.17</v>
       </c>
       <c r="AP364" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ364" t="n">
         <v>1.21</v>
@@ -80045,7 +80045,7 @@
         <v>1</v>
       </c>
       <c r="AP365" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ365" t="n">
         <v>0.85</v>
@@ -81356,7 +81356,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ371" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR371" t="n">
         <v>1.24</v>
@@ -82228,7 +82228,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ375" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR375" t="n">
         <v>1.5</v>
@@ -83097,7 +83097,7 @@
         <v>1.08</v>
       </c>
       <c r="AP379" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ379" t="n">
         <v>1.14</v>
@@ -84626,7 +84626,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ386" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR386" t="n">
         <v>1.54</v>
@@ -86367,7 +86367,7 @@
         <v>1.17</v>
       </c>
       <c r="AP394" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ394" t="n">
         <v>1.15</v>
@@ -88190,6 +88190,878 @@
       </c>
       <c r="BP402" t="n">
         <v>1.29</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="1" t="n">
+        <v>402</v>
+      </c>
+      <c r="B403" t="n">
+        <v>8229828</v>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E403" s="2" t="n">
+        <v>45892.9375</v>
+      </c>
+      <c r="F403" t="n">
+        <v>0</v>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>St. Louis City</t>
+        </is>
+      </c>
+      <c r="I403" t="n">
+        <v>1</v>
+      </c>
+      <c r="J403" t="n">
+        <v>1</v>
+      </c>
+      <c r="K403" t="n">
+        <v>2</v>
+      </c>
+      <c r="L403" t="n">
+        <v>3</v>
+      </c>
+      <c r="M403" t="n">
+        <v>2</v>
+      </c>
+      <c r="N403" t="n">
+        <v>5</v>
+      </c>
+      <c r="O403" t="inlineStr">
+        <is>
+          <t>['45+4', '79', '90+14']</t>
+        </is>
+      </c>
+      <c r="P403" t="inlineStr">
+        <is>
+          <t>['13', '73']</t>
+        </is>
+      </c>
+      <c r="Q403" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R403" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="S403" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="T403" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="U403" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="V403" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="W403" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X403" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y403" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z403" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AA403" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AB403" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AC403" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD403" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE403" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF403" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AG403" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AH403" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AI403" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AJ403" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AK403" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AL403" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM403" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AN403" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO403" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AP403" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AQ403" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AR403" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS403" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AT403" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AU403" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV403" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW403" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX403" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY403" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ403" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA403" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB403" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC403" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD403" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BE403" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF403" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="BG403" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH403" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI403" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BJ403" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BK403" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BL403" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BM403" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BN403" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BO403" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BP403" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="1" t="n">
+        <v>403</v>
+      </c>
+      <c r="B404" t="n">
+        <v>8229826</v>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E404" s="2" t="n">
+        <v>45892.9375</v>
+      </c>
+      <c r="F404" t="n">
+        <v>0</v>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>Minnesota United</t>
+        </is>
+      </c>
+      <c r="I404" t="n">
+        <v>1</v>
+      </c>
+      <c r="J404" t="n">
+        <v>2</v>
+      </c>
+      <c r="K404" t="n">
+        <v>3</v>
+      </c>
+      <c r="L404" t="n">
+        <v>1</v>
+      </c>
+      <c r="M404" t="n">
+        <v>3</v>
+      </c>
+      <c r="N404" t="n">
+        <v>4</v>
+      </c>
+      <c r="O404" t="inlineStr">
+        <is>
+          <t>['15']</t>
+        </is>
+      </c>
+      <c r="P404" t="inlineStr">
+        <is>
+          <t>['6', '36', '51']</t>
+        </is>
+      </c>
+      <c r="Q404" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R404" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S404" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T404" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U404" t="n">
+        <v>3</v>
+      </c>
+      <c r="V404" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W404" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X404" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y404" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z404" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AA404" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB404" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AC404" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD404" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE404" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AF404" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AG404" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH404" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI404" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ404" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AK404" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL404" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM404" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AN404" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AO404" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AP404" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AQ404" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AR404" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AS404" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AT404" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU404" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV404" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW404" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX404" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY404" t="n">
+        <v>27</v>
+      </c>
+      <c r="AZ404" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA404" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB404" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC404" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD404" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BE404" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="BF404" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BG404" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH404" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="BI404" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ404" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BK404" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BL404" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BM404" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BN404" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BO404" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BP404" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="1" t="n">
+        <v>404</v>
+      </c>
+      <c r="B405" t="n">
+        <v>8229822</v>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E405" s="2" t="n">
+        <v>45892.97916666666</v>
+      </c>
+      <c r="F405" t="n">
+        <v>0</v>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>Portland Timbers</t>
+        </is>
+      </c>
+      <c r="I405" t="n">
+        <v>0</v>
+      </c>
+      <c r="J405" t="n">
+        <v>0</v>
+      </c>
+      <c r="K405" t="n">
+        <v>0</v>
+      </c>
+      <c r="L405" t="n">
+        <v>0</v>
+      </c>
+      <c r="M405" t="n">
+        <v>0</v>
+      </c>
+      <c r="N405" t="n">
+        <v>0</v>
+      </c>
+      <c r="O405" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P405" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q405" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R405" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S405" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T405" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U405" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V405" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="W405" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X405" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Y405" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z405" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA405" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB405" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AC405" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD405" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE405" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF405" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AG405" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH405" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AI405" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ405" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK405" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL405" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM405" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AN405" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AO405" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AP405" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AQ405" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AR405" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AS405" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AT405" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU405" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV405" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW405" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX405" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY405" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ405" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA405" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB405" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC405" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD405" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BE405" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF405" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="BG405" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BH405" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BI405" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BJ405" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BK405" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BL405" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BM405" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BN405" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BO405" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP405" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="1" t="n">
+        <v>405</v>
+      </c>
+      <c r="B406" t="n">
+        <v>8229815</v>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E406" s="2" t="n">
+        <v>45892.97916666666</v>
+      </c>
+      <c r="F406" t="n">
+        <v>0</v>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>LA Galaxy</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>Colorado Rapids</t>
+        </is>
+      </c>
+      <c r="I406" t="n">
+        <v>1</v>
+      </c>
+      <c r="J406" t="n">
+        <v>0</v>
+      </c>
+      <c r="K406" t="n">
+        <v>1</v>
+      </c>
+      <c r="L406" t="n">
+        <v>3</v>
+      </c>
+      <c r="M406" t="n">
+        <v>0</v>
+      </c>
+      <c r="N406" t="n">
+        <v>3</v>
+      </c>
+      <c r="O406" t="inlineStr">
+        <is>
+          <t>['7', '55', '75']</t>
+        </is>
+      </c>
+      <c r="P406" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q406" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R406" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S406" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T406" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="U406" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V406" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="W406" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X406" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Y406" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z406" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AA406" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB406" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AC406" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD406" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE406" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF406" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AG406" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AH406" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AI406" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AJ406" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AK406" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL406" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM406" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AN406" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AO406" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP406" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AQ406" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AR406" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AS406" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AT406" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AU406" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV406" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW406" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX406" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY406" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ406" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA406" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB406" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC406" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD406" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BE406" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="BF406" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="BG406" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BH406" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI406" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BJ406" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BK406" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BL406" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BM406" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BN406" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BO406" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BP406" t="n">
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP406"/>
+  <dimension ref="A1:BP409"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1132,7 +1132,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ7" t="n">
         <v>0.86</v>
@@ -3094,7 +3094,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ14" t="n">
         <v>0.93</v>
@@ -4181,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ17" t="n">
         <v>0.38</v>
@@ -7669,7 +7669,7 @@
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ33" t="n">
         <v>1.25</v>
@@ -8323,10 +8323,10 @@
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR36" t="n">
         <v>1.73</v>
@@ -8762,7 +8762,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR38" t="n">
         <v>0.97</v>
@@ -11375,7 +11375,7 @@
         <v>0</v>
       </c>
       <c r="AP50" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ50" t="n">
         <v>1.93</v>
@@ -13773,7 +13773,7 @@
         <v>3</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ61" t="n">
         <v>1.69</v>
@@ -14463,10 +14463,10 @@
         <v>1</v>
       </c>
       <c r="BB64" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD64" t="n">
         <v>1.55</v>
@@ -15299,7 +15299,7 @@
         <v>3</v>
       </c>
       <c r="AP68" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ68" t="n">
         <v>1.21</v>
@@ -16389,7 +16389,7 @@
         <v>1</v>
       </c>
       <c r="AP73" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ73" t="n">
         <v>1.15</v>
@@ -17264,7 +17264,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ77" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR77" t="n">
         <v>0.78</v>
@@ -17915,7 +17915,7 @@
         <v>0.67</v>
       </c>
       <c r="AP80" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ80" t="n">
         <v>1.21</v>
@@ -18572,7 +18572,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ83" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR83" t="n">
         <v>1.15</v>
@@ -20313,7 +20313,7 @@
         <v>1.5</v>
       </c>
       <c r="AP91" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ91" t="n">
         <v>1.21</v>
@@ -21621,7 +21621,7 @@
         <v>2.33</v>
       </c>
       <c r="AP97" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ97" t="n">
         <v>1.38</v>
@@ -22093,10 +22093,10 @@
         <v>9</v>
       </c>
       <c r="BB99" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BC99" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD99" t="n">
         <v>1.82</v>
@@ -23401,10 +23401,10 @@
         <v>10</v>
       </c>
       <c r="BB105" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC105" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD105" t="n">
         <v>1.5</v>
@@ -23801,7 +23801,7 @@
         <v>0.33</v>
       </c>
       <c r="AP107" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ107" t="n">
         <v>1.43</v>
@@ -24022,7 +24022,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ108" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR108" t="n">
         <v>1.8</v>
@@ -27725,7 +27725,7 @@
         <v>1</v>
       </c>
       <c r="AP125" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ125" t="n">
         <v>1.21</v>
@@ -27758,13 +27758,13 @@
         <v>12</v>
       </c>
       <c r="BA125" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB125" t="n">
         <v>7</v>
       </c>
       <c r="BC125" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD125" t="n">
         <v>1.44</v>
@@ -28379,7 +28379,7 @@
         <v>1.5</v>
       </c>
       <c r="AP128" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ128" t="n">
         <v>2.08</v>
@@ -29908,7 +29908,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ135" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR135" t="n">
         <v>1.97</v>
@@ -30126,7 +30126,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ136" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR136" t="n">
         <v>1.49</v>
@@ -31431,7 +31431,7 @@
         <v>1</v>
       </c>
       <c r="AP142" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ142" t="n">
         <v>1.43</v>
@@ -33393,7 +33393,7 @@
         <v>0.75</v>
       </c>
       <c r="AP151" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ151" t="n">
         <v>1.21</v>
@@ -34486,7 +34486,7 @@
         <v>2</v>
       </c>
       <c r="AQ156" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR156" t="n">
         <v>1.42</v>
@@ -36009,7 +36009,7 @@
         <v>1</v>
       </c>
       <c r="AP163" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ163" t="n">
         <v>0.36</v>
@@ -39500,7 +39500,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ179" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR179" t="n">
         <v>1.19</v>
@@ -41026,7 +41026,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ186" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR186" t="n">
         <v>2.02</v>
@@ -41462,7 +41462,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ188" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR188" t="n">
         <v>1.52</v>
@@ -42988,7 +42988,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ195" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR195" t="n">
         <v>1.68</v>
@@ -43421,7 +43421,7 @@
         <v>1.5</v>
       </c>
       <c r="AP197" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ197" t="n">
         <v>1.57</v>
@@ -43857,7 +43857,7 @@
         <v>1.8</v>
       </c>
       <c r="AP199" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ199" t="n">
         <v>1.54</v>
@@ -45386,7 +45386,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ206" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR206" t="n">
         <v>1.81</v>
@@ -46037,7 +46037,7 @@
         <v>1.71</v>
       </c>
       <c r="AP209" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ209" t="n">
         <v>1.38</v>
@@ -46691,7 +46691,7 @@
         <v>2</v>
       </c>
       <c r="AP212" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ212" t="n">
         <v>1.42</v>
@@ -47566,7 +47566,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ216" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR216" t="n">
         <v>1.15</v>
@@ -49089,7 +49089,7 @@
         <v>1.63</v>
       </c>
       <c r="AP223" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ223" t="n">
         <v>1.93</v>
@@ -49307,7 +49307,7 @@
         <v>1.43</v>
       </c>
       <c r="AP224" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ224" t="n">
         <v>1.64</v>
@@ -51051,7 +51051,7 @@
         <v>1.5</v>
       </c>
       <c r="AP232" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ232" t="n">
         <v>2.08</v>
@@ -53888,7 +53888,7 @@
         <v>1</v>
       </c>
       <c r="AQ245" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR245" t="n">
         <v>1.48</v>
@@ -54757,7 +54757,7 @@
         <v>1.5</v>
       </c>
       <c r="AP249" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ249" t="n">
         <v>1.86</v>
@@ -55850,7 +55850,7 @@
         <v>2</v>
       </c>
       <c r="AQ254" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR254" t="n">
         <v>1.83</v>
@@ -57812,7 +57812,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ263" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR263" t="n">
         <v>1.53</v>
@@ -58060,13 +58060,13 @@
         <v>11</v>
       </c>
       <c r="BA264" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BB264" t="n">
         <v>4</v>
       </c>
       <c r="BC264" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BD264" t="n">
         <v>2.25</v>
@@ -59120,7 +59120,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ269" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR269" t="n">
         <v>1.14</v>
@@ -63695,7 +63695,7 @@
         <v>1.11</v>
       </c>
       <c r="AP290" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ290" t="n">
         <v>1.23</v>
@@ -64788,7 +64788,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ295" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR295" t="n">
         <v>1.47</v>
@@ -65221,7 +65221,7 @@
         <v>1.6</v>
       </c>
       <c r="AP297" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ297" t="n">
         <v>1.64</v>
@@ -66532,7 +66532,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ303" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR303" t="n">
         <v>1.86</v>
@@ -67183,7 +67183,7 @@
         <v>1.5</v>
       </c>
       <c r="AP306" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ306" t="n">
         <v>1.42</v>
@@ -67219,10 +67219,10 @@
         <v>2</v>
       </c>
       <c r="BB306" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BC306" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BD306" t="n">
         <v>1.7</v>
@@ -67837,7 +67837,7 @@
         <v>0.78</v>
       </c>
       <c r="AP309" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ309" t="n">
         <v>1.21</v>
@@ -68276,7 +68276,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ311" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR311" t="n">
         <v>1.72</v>
@@ -71543,7 +71543,7 @@
         <v>0.8</v>
       </c>
       <c r="AP326" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ326" t="n">
         <v>0.64</v>
@@ -71761,7 +71761,7 @@
         <v>1.64</v>
       </c>
       <c r="AP327" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ327" t="n">
         <v>1.57</v>
@@ -73069,7 +73069,7 @@
         <v>0.9</v>
       </c>
       <c r="AP333" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ333" t="n">
         <v>0.93</v>
@@ -74377,7 +74377,7 @@
         <v>0.58</v>
       </c>
       <c r="AP339" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ339" t="n">
         <v>0.93</v>
@@ -75249,7 +75249,7 @@
         <v>1.27</v>
       </c>
       <c r="AP343" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ343" t="n">
         <v>1.21</v>
@@ -78519,7 +78519,7 @@
         <v>1.09</v>
       </c>
       <c r="AP358" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ358" t="n">
         <v>1.14</v>
@@ -79173,7 +79173,7 @@
         <v>1.1</v>
       </c>
       <c r="AP361" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ361" t="n">
         <v>1</v>
@@ -79612,7 +79612,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ363" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR363" t="n">
         <v>1.56</v>
@@ -80048,7 +80048,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ365" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR365" t="n">
         <v>1.81</v>
@@ -84405,7 +84405,7 @@
         <v>0.92</v>
       </c>
       <c r="AP385" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ385" t="n">
         <v>0.86</v>
@@ -85716,7 +85716,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ391" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR391" t="n">
         <v>1.77</v>
@@ -87042,13 +87042,13 @@
         <v>4</v>
       </c>
       <c r="AW397" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX397" t="n">
         <v>6</v>
       </c>
       <c r="AY397" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ397" t="n">
         <v>10</v>
@@ -87260,13 +87260,13 @@
         <v>5</v>
       </c>
       <c r="AW398" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX398" t="n">
         <v>6</v>
       </c>
       <c r="AY398" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ398" t="n">
         <v>11</v>
@@ -87708,13 +87708,13 @@
         <v>12</v>
       </c>
       <c r="BA400" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB400" t="n">
         <v>4</v>
       </c>
       <c r="BC400" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD400" t="n">
         <v>1.4</v>
@@ -87917,13 +87917,13 @@
         <v>8</v>
       </c>
       <c r="AX401" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY401" t="n">
         <v>10</v>
       </c>
       <c r="AZ401" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA401" t="n">
         <v>1</v>
@@ -88347,7 +88347,7 @@
         <v>7</v>
       </c>
       <c r="AV403" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW403" t="n">
         <v>15</v>
@@ -88359,7 +88359,7 @@
         <v>22</v>
       </c>
       <c r="AZ403" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA403" t="n">
         <v>11</v>
@@ -88789,13 +88789,13 @@
         <v>11</v>
       </c>
       <c r="AX405" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY405" t="n">
         <v>12</v>
       </c>
       <c r="AZ405" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA405" t="n">
         <v>6</v>
@@ -89062,6 +89062,660 @@
       </c>
       <c r="BP406" t="n">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="1" t="n">
+        <v>406</v>
+      </c>
+      <c r="B407" t="n">
+        <v>8229825</v>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E407" s="2" t="n">
+        <v>45893.70833333334</v>
+      </c>
+      <c r="F407" t="n">
+        <v>0</v>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>Atlanta United FC</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>Toronto</t>
+        </is>
+      </c>
+      <c r="I407" t="n">
+        <v>0</v>
+      </c>
+      <c r="J407" t="n">
+        <v>0</v>
+      </c>
+      <c r="K407" t="n">
+        <v>0</v>
+      </c>
+      <c r="L407" t="n">
+        <v>0</v>
+      </c>
+      <c r="M407" t="n">
+        <v>0</v>
+      </c>
+      <c r="N407" t="n">
+        <v>0</v>
+      </c>
+      <c r="O407" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P407" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q407" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R407" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S407" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T407" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="U407" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V407" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W407" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X407" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y407" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z407" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA407" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AB407" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AC407" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD407" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE407" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF407" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AG407" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AH407" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AI407" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ407" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AK407" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AL407" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM407" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AN407" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AO407" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP407" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ407" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR407" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AS407" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AT407" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AU407" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV407" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW407" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX407" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY407" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ407" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA407" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB407" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC407" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD407" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BE407" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF407" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BG407" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BH407" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI407" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BJ407" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BK407" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL407" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BM407" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BN407" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BO407" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BP407" t="n">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="1" t="n">
+        <v>407</v>
+      </c>
+      <c r="B408" t="n">
+        <v>8229809</v>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E408" s="2" t="n">
+        <v>45893.83333333334</v>
+      </c>
+      <c r="F408" t="n">
+        <v>0</v>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>New York RB</t>
+        </is>
+      </c>
+      <c r="I408" t="n">
+        <v>1</v>
+      </c>
+      <c r="J408" t="n">
+        <v>0</v>
+      </c>
+      <c r="K408" t="n">
+        <v>1</v>
+      </c>
+      <c r="L408" t="n">
+        <v>1</v>
+      </c>
+      <c r="M408" t="n">
+        <v>0</v>
+      </c>
+      <c r="N408" t="n">
+        <v>1</v>
+      </c>
+      <c r="O408" t="inlineStr">
+        <is>
+          <t>['30']</t>
+        </is>
+      </c>
+      <c r="P408" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q408" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R408" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S408" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T408" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="U408" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V408" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="W408" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X408" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Y408" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z408" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AA408" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="AB408" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AC408" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD408" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE408" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF408" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="AG408" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AH408" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AI408" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AJ408" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AK408" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL408" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM408" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AN408" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AO408" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AP408" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AQ408" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AR408" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AS408" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AT408" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AU408" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV408" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW408" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX408" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY408" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ408" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA408" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB408" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC408" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD408" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BE408" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF408" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BG408" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BH408" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BI408" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BJ408" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BK408" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BL408" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BM408" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BN408" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BO408" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BP408" t="n">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="1" t="n">
+        <v>408</v>
+      </c>
+      <c r="B409" t="n">
+        <v>8229833</v>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E409" s="2" t="n">
+        <v>45893.92708333334</v>
+      </c>
+      <c r="F409" t="n">
+        <v>0</v>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>Seattle Sounders</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>Sporting KC</t>
+        </is>
+      </c>
+      <c r="I409" t="n">
+        <v>2</v>
+      </c>
+      <c r="J409" t="n">
+        <v>1</v>
+      </c>
+      <c r="K409" t="n">
+        <v>3</v>
+      </c>
+      <c r="L409" t="n">
+        <v>5</v>
+      </c>
+      <c r="M409" t="n">
+        <v>2</v>
+      </c>
+      <c r="N409" t="n">
+        <v>7</v>
+      </c>
+      <c r="O409" t="inlineStr">
+        <is>
+          <t>['11', '45+1', '50', '61', '75']</t>
+        </is>
+      </c>
+      <c r="P409" t="inlineStr">
+        <is>
+          <t>['36', '53']</t>
+        </is>
+      </c>
+      <c r="Q409" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="R409" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S409" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="T409" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="U409" t="n">
+        <v>4</v>
+      </c>
+      <c r="V409" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="W409" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="X409" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y409" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z409" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA409" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AB409" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC409" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD409" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE409" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF409" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AG409" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AH409" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AI409" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ409" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AK409" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AL409" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM409" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AN409" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AO409" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AP409" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AQ409" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AR409" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AS409" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AT409" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AU409" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV409" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW409" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX409" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY409" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ409" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA409" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB409" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC409" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD409" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BE409" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF409" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="BG409" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH409" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI409" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BJ409" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BK409" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BL409" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BM409" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BN409" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO409" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BP409" t="n">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
@@ -58060,13 +58060,13 @@
         <v>11</v>
       </c>
       <c r="BA264" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BB264" t="n">
         <v>4</v>
       </c>
       <c r="BC264" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BD264" t="n">
         <v>2.25</v>
@@ -67219,10 +67219,10 @@
         <v>2</v>
       </c>
       <c r="BB306" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BC306" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BD306" t="n">
         <v>1.7</v>
@@ -87257,7 +87257,7 @@
         <v>6</v>
       </c>
       <c r="AV398" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW398" t="n">
         <v>15</v>
@@ -87269,7 +87269,7 @@
         <v>21</v>
       </c>
       <c r="AZ398" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA398" t="n">
         <v>2</v>
@@ -87481,13 +87481,13 @@
         <v>9</v>
       </c>
       <c r="AX399" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY399" t="n">
         <v>11</v>
       </c>
       <c r="AZ399" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA399" t="n">
         <v>5</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
@@ -21925,7 +21925,7 @@
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>8229375</v>
+        <v>8229350</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -21945,12 +21945,12 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="I99" t="n">
@@ -21963,17 +21963,17 @@
         <v>0</v>
       </c>
       <c r="L99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M99" t="n">
         <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>['57']</t>
+          <t>['71', '88']</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -21982,160 +21982,160 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="R99" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S99" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="T99" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="U99" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="V99" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="W99" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="X99" t="n">
         <v>5.8</v>
       </c>
       <c r="Y99" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z99" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AA99" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="AB99" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AC99" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AD99" t="n">
-        <v>9.300000000000001</v>
+        <v>11</v>
       </c>
       <c r="AE99" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AF99" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AG99" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AH99" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AI99" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AJ99" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="AK99" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AL99" t="n">
         <v>0</v>
       </c>
       <c r="AM99" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AN99" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AO99" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AP99" t="n">
         <v>1</v>
       </c>
       <c r="AQ99" t="n">
-        <v>1.25</v>
+        <v>0.36</v>
       </c>
       <c r="AR99" t="n">
-        <v>1.23</v>
+        <v>1.63</v>
       </c>
       <c r="AS99" t="n">
-        <v>1.01</v>
+        <v>0.76</v>
       </c>
       <c r="AT99" t="n">
-        <v>2.24</v>
+        <v>2.39</v>
       </c>
       <c r="AU99" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AV99" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AW99" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AX99" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY99" t="n">
         <v>11</v>
       </c>
       <c r="AZ99" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA99" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="BB99" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BC99" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="BD99" t="n">
-        <v>1.82</v>
+        <v>1.62</v>
       </c>
       <c r="BE99" t="n">
         <v>8.5</v>
       </c>
       <c r="BF99" t="n">
-        <v>2.54</v>
+        <v>3</v>
       </c>
       <c r="BG99" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="BH99" t="n">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="BI99" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="BJ99" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BK99" t="n">
         <v>1.73</v>
       </c>
       <c r="BL99" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="BM99" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="BN99" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="BO99" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="BP99" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="100">
@@ -22143,7 +22143,7 @@
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>8229350</v>
+        <v>8229375</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -22156,19 +22156,19 @@
         </is>
       </c>
       <c r="E100" s="2" t="n">
-        <v>45752.89583333334</v>
+        <v>45752.91666666666</v>
       </c>
       <c r="F100" t="n">
         <v>0</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="I100" t="n">
@@ -22181,17 +22181,17 @@
         <v>0</v>
       </c>
       <c r="L100" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M100" t="n">
         <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>['71', '88']</t>
+          <t>['57']</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -22200,160 +22200,160 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="R100" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S100" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="T100" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="U100" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="V100" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="W100" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="X100" t="n">
         <v>5.8</v>
       </c>
       <c r="Y100" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z100" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AA100" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="AB100" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AC100" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AD100" t="n">
-        <v>11</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE100" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AF100" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AG100" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AH100" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AI100" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AJ100" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="AK100" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AL100" t="n">
         <v>0</v>
       </c>
       <c r="AM100" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AN100" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AO100" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AP100" t="n">
         <v>1</v>
       </c>
       <c r="AQ100" t="n">
-        <v>0.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR100" t="n">
-        <v>1.63</v>
+        <v>1.23</v>
       </c>
       <c r="AS100" t="n">
-        <v>0.76</v>
+        <v>1.01</v>
       </c>
       <c r="AT100" t="n">
-        <v>2.39</v>
+        <v>2.24</v>
       </c>
       <c r="AU100" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AV100" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AW100" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AX100" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY100" t="n">
         <v>11</v>
       </c>
       <c r="AZ100" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA100" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="BB100" t="n">
         <v>4</v>
       </c>
       <c r="BC100" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="BD100" t="n">
-        <v>1.62</v>
+        <v>1.82</v>
       </c>
       <c r="BE100" t="n">
         <v>8.5</v>
       </c>
       <c r="BF100" t="n">
-        <v>3</v>
+        <v>2.54</v>
       </c>
       <c r="BG100" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="BH100" t="n">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="BI100" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="BJ100" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="BK100" t="n">
         <v>1.73</v>
       </c>
       <c r="BL100" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="BM100" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="BN100" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="BO100" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="BP100" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="101">
@@ -81003,7 +81003,7 @@
         <v>369</v>
       </c>
       <c r="B370" t="n">
-        <v>8229790</v>
+        <v>8229800</v>
       </c>
       <c r="C370" t="inlineStr">
         <is>
@@ -81023,194 +81023,194 @@
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="I370" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J370" t="n">
         <v>0</v>
       </c>
       <c r="K370" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L370" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M370" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N370" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O370" t="inlineStr">
         <is>
-          <t>['23', '39', '66']</t>
+          <t>['8', '62']</t>
         </is>
       </c>
       <c r="P370" t="inlineStr">
         <is>
-          <t>['85']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q370" t="n">
-        <v>3.4</v>
+        <v>2.55</v>
       </c>
       <c r="R370" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S370" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="T370" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="U370" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="V370" t="n">
         <v>2.45</v>
       </c>
       <c r="W370" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="X370" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y370" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z370" t="n">
-        <v>3.1</v>
+        <v>2.12</v>
       </c>
       <c r="AA370" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AB370" t="n">
-        <v>2.08</v>
+        <v>3.45</v>
       </c>
       <c r="AC370" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AD370" t="n">
-        <v>13</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AE370" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AF370" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="AG370" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH370" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AI370" t="n">
         <v>1.62</v>
       </c>
-      <c r="AH370" t="n">
+      <c r="AJ370" t="n">
         <v>2.2</v>
       </c>
-      <c r="AI370" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AJ370" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AK370" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AL370" t="n">
         <v>0</v>
       </c>
       <c r="AM370" t="n">
-        <v>1.39</v>
+        <v>1.73</v>
       </c>
       <c r="AN370" t="n">
-        <v>1.08</v>
+        <v>0.67</v>
       </c>
       <c r="AO370" t="n">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="AP370" t="n">
-        <v>1.23</v>
+        <v>0.86</v>
       </c>
       <c r="AQ370" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AR370" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AS370" t="n">
         <v>1.21</v>
       </c>
-      <c r="AR370" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AS370" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AT370" t="n">
-        <v>2.87</v>
+        <v>2.45</v>
       </c>
       <c r="AU370" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AV370" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AW370" t="n">
         <v>5</v>
       </c>
       <c r="AX370" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY370" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ370" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA370" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB370" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC370" t="n">
         <v>12</v>
       </c>
-      <c r="AY370" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ370" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA370" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB370" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC370" t="n">
-        <v>11</v>
-      </c>
       <c r="BD370" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="BE370" t="n">
-        <v>6.25</v>
+        <v>7.5</v>
       </c>
       <c r="BF370" t="n">
-        <v>1.9</v>
+        <v>2.48</v>
       </c>
       <c r="BG370" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="BH370" t="n">
-        <v>2.75</v>
+        <v>3.08</v>
       </c>
       <c r="BI370" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="BJ370" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="BK370" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="BL370" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="BM370" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="BN370" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="BO370" t="n">
-        <v>3.7</v>
+        <v>3.48</v>
       </c>
       <c r="BP370" t="n">
         <v>1.22</v>
@@ -81221,7 +81221,7 @@
         <v>370</v>
       </c>
       <c r="B371" t="n">
-        <v>8229800</v>
+        <v>8229333</v>
       </c>
       <c r="C371" t="inlineStr">
         <is>
@@ -81241,197 +81241,197 @@
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="I371" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J371" t="n">
         <v>0</v>
       </c>
       <c r="K371" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L371" t="n">
         <v>2</v>
       </c>
       <c r="M371" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N371" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O371" t="inlineStr">
         <is>
-          <t>['8', '62']</t>
+          <t>['31', '41']</t>
         </is>
       </c>
       <c r="P371" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['80', '89']</t>
         </is>
       </c>
       <c r="Q371" t="n">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="R371" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S371" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="T371" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="U371" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V371" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="W371" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X371" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="Y371" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z371" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA371" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB371" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AC371" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD371" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE371" t="n">
         <v>1.3</v>
       </c>
-      <c r="U371" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="V371" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="W371" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="X371" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="Y371" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z371" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AA371" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AB371" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AC371" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AD371" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AE371" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AF371" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="AG371" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH371" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI371" t="n">
         <v>1.75</v>
       </c>
-      <c r="AH371" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AI371" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AJ371" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AK371" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AL371" t="n">
         <v>0</v>
       </c>
       <c r="AM371" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AN371" t="n">
-        <v>0.67</v>
+        <v>1.55</v>
       </c>
       <c r="AO371" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AP371" t="n">
-        <v>0.86</v>
+        <v>1.46</v>
       </c>
       <c r="AQ371" t="n">
         <v>1.15</v>
       </c>
       <c r="AR371" t="n">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="AS371" t="n">
-        <v>1.21</v>
+        <v>1.06</v>
       </c>
       <c r="AT371" t="n">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="AU371" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV371" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AW371" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX371" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY371" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ371" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA371" t="n">
         <v>5</v>
       </c>
-      <c r="AX371" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY371" t="n">
+      <c r="BB371" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC371" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD371" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BE371" t="n">
         <v>8</v>
       </c>
-      <c r="AZ371" t="n">
-        <v>9</v>
-      </c>
-      <c r="BA371" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB371" t="n">
-        <v>9</v>
-      </c>
-      <c r="BC371" t="n">
-        <v>12</v>
-      </c>
-      <c r="BD371" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BE371" t="n">
-        <v>7.5</v>
-      </c>
       <c r="BF371" t="n">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="BG371" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="BH371" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BI371" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BJ371" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BK371" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BL371" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BM371" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BN371" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BO371" t="n">
         <v>3.08</v>
       </c>
-      <c r="BI371" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="BJ371" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="BK371" t="n">
-        <v>2</v>
-      </c>
-      <c r="BL371" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BM371" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BN371" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="BO371" t="n">
-        <v>3.48</v>
-      </c>
       <c r="BP371" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="372">
@@ -81439,7 +81439,7 @@
         <v>371</v>
       </c>
       <c r="B372" t="n">
-        <v>8229333</v>
+        <v>8229790</v>
       </c>
       <c r="C372" t="inlineStr">
         <is>
@@ -81459,12 +81459,12 @@
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="I372" t="n">
@@ -81477,179 +81477,179 @@
         <v>2</v>
       </c>
       <c r="L372" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M372" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N372" t="n">
         <v>4</v>
       </c>
       <c r="O372" t="inlineStr">
         <is>
-          <t>['31', '41']</t>
+          <t>['23', '39', '66']</t>
         </is>
       </c>
       <c r="P372" t="inlineStr">
         <is>
-          <t>['80', '89']</t>
+          <t>['85']</t>
         </is>
       </c>
       <c r="Q372" t="n">
-        <v>2.25</v>
+        <v>3.4</v>
       </c>
       <c r="R372" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="S372" t="n">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="T372" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="U372" t="n">
-        <v>2.8</v>
+        <v>3.35</v>
       </c>
       <c r="V372" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="W372" t="n">
-        <v>1.4</v>
+        <v>1.58</v>
       </c>
       <c r="X372" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="Y372" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z372" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA372" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB372" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AC372" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD372" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE372" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF372" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AG372" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH372" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AI372" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ372" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK372" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL372" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM372" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AN372" t="n">
         <v>1.08</v>
       </c>
-      <c r="Z372" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA372" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB372" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AC372" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AD372" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AE372" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF372" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AG372" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH372" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AI372" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AJ372" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK372" t="n">
+      <c r="AO372" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AP372" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AQ372" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AR372" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AS372" t="n">
         <v>1.25</v>
       </c>
-      <c r="AL372" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM372" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AN372" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AO372" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AP372" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AQ372" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AR372" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AS372" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AT372" t="n">
-        <v>2.56</v>
+        <v>2.87</v>
       </c>
       <c r="AU372" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AV372" t="n">
         <v>6</v>
       </c>
       <c r="AW372" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AX372" t="n">
         <v>12</v>
       </c>
       <c r="AY372" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ372" t="n">
         <v>18</v>
       </c>
       <c r="BA372" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB372" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BC372" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BD372" t="n">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="BE372" t="n">
-        <v>8</v>
+        <v>6.25</v>
       </c>
       <c r="BF372" t="n">
-        <v>2.55</v>
+        <v>1.9</v>
       </c>
       <c r="BG372" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="BH372" t="n">
-        <v>3.42</v>
+        <v>2.75</v>
       </c>
       <c r="BI372" t="n">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="BJ372" t="n">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="BK372" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="BL372" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="BM372" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="BN372" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="BO372" t="n">
-        <v>3.08</v>
+        <v>3.7</v>
       </c>
       <c r="BP372" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="373">
@@ -83183,7 +83183,7 @@
         <v>379</v>
       </c>
       <c r="B380" t="n">
-        <v>8229772</v>
+        <v>8229805</v>
       </c>
       <c r="C380" t="inlineStr">
         <is>
@@ -83203,101 +83203,101 @@
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="I380" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J380" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K380" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L380" t="n">
         <v>1</v>
       </c>
       <c r="M380" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N380" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O380" t="inlineStr">
         <is>
-          <t>['74']</t>
+          <t>['40']</t>
         </is>
       </c>
       <c r="P380" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['28']</t>
         </is>
       </c>
       <c r="Q380" t="n">
-        <v>2.94</v>
+        <v>2.45</v>
       </c>
       <c r="R380" t="n">
         <v>2.15</v>
       </c>
       <c r="S380" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="T380" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="U380" t="n">
         <v>3.1</v>
       </c>
       <c r="V380" t="n">
-        <v>2.65</v>
+        <v>2.38</v>
       </c>
       <c r="W380" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="X380" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="Y380" t="n">
         <v>1.12</v>
       </c>
       <c r="Z380" t="n">
-        <v>2.75</v>
+        <v>2.12</v>
       </c>
       <c r="AA380" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="AB380" t="n">
-        <v>2.79</v>
+        <v>3.35</v>
       </c>
       <c r="AC380" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AD380" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AE380" t="n">
         <v>1.2</v>
       </c>
       <c r="AF380" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AG380" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AH380" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AI380" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AJ380" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AK380" t="n">
         <v>1.3</v>
@@ -83306,94 +83306,94 @@
         <v>0</v>
       </c>
       <c r="AM380" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AN380" t="n">
-        <v>2.23</v>
+        <v>0.58</v>
       </c>
       <c r="AO380" t="n">
-        <v>1.67</v>
+        <v>0.62</v>
       </c>
       <c r="AP380" t="n">
-        <v>2.29</v>
+        <v>0.79</v>
       </c>
       <c r="AQ380" t="n">
-        <v>1.54</v>
+        <v>0.64</v>
       </c>
       <c r="AR380" t="n">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="AS380" t="n">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="AT380" t="n">
-        <v>2.86</v>
+        <v>2.5</v>
       </c>
       <c r="AU380" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV380" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AW380" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX380" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AY380" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ380" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA380" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB380" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC380" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD380" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BE380" t="n">
         <v>7</v>
       </c>
-      <c r="AZ380" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA380" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB380" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC380" t="n">
-        <v>3</v>
-      </c>
-      <c r="BD380" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="BE380" t="n">
-        <v>6.25</v>
-      </c>
       <c r="BF380" t="n">
-        <v>1.9</v>
+        <v>2.87</v>
       </c>
       <c r="BG380" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="BH380" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="BI380" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="BJ380" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="BK380" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="BL380" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="BM380" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="BN380" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="BO380" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="BP380" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="381">
@@ -83401,7 +83401,7 @@
         <v>380</v>
       </c>
       <c r="B381" t="n">
-        <v>8229805</v>
+        <v>8229772</v>
       </c>
       <c r="C381" t="inlineStr">
         <is>
@@ -83421,101 +83421,101 @@
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="I381" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J381" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K381" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L381" t="n">
         <v>1</v>
       </c>
       <c r="M381" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N381" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O381" t="inlineStr">
         <is>
-          <t>['40']</t>
+          <t>['74']</t>
         </is>
       </c>
       <c r="P381" t="inlineStr">
         <is>
-          <t>['28']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q381" t="n">
-        <v>2.45</v>
+        <v>2.94</v>
       </c>
       <c r="R381" t="n">
         <v>2.15</v>
       </c>
       <c r="S381" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="T381" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="U381" t="n">
         <v>3.1</v>
       </c>
       <c r="V381" t="n">
-        <v>2.38</v>
+        <v>2.65</v>
       </c>
       <c r="W381" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="X381" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="Y381" t="n">
         <v>1.12</v>
       </c>
       <c r="Z381" t="n">
-        <v>2.12</v>
+        <v>2.75</v>
       </c>
       <c r="AA381" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="AB381" t="n">
-        <v>3.35</v>
+        <v>2.79</v>
       </c>
       <c r="AC381" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AD381" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AE381" t="n">
         <v>1.2</v>
       </c>
       <c r="AF381" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AG381" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AH381" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AI381" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AJ381" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AK381" t="n">
         <v>1.3</v>
@@ -83524,94 +83524,94 @@
         <v>0</v>
       </c>
       <c r="AM381" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AN381" t="n">
-        <v>0.58</v>
+        <v>2.23</v>
       </c>
       <c r="AO381" t="n">
-        <v>0.62</v>
+        <v>1.67</v>
       </c>
       <c r="AP381" t="n">
-        <v>0.79</v>
+        <v>2.29</v>
       </c>
       <c r="AQ381" t="n">
-        <v>0.64</v>
+        <v>1.54</v>
       </c>
       <c r="AR381" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AS381" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AT381" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AU381" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV381" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW381" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX381" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY381" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ381" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA381" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB381" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC381" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD381" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BE381" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="BF381" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BG381" t="n">
         <v>1.28</v>
       </c>
-      <c r="AS381" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AT381" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AU381" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV381" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW381" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX381" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY381" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ381" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA381" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB381" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC381" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD381" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BE381" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF381" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="BG381" t="n">
-        <v>1.38</v>
-      </c>
       <c r="BH381" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="BI381" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="BJ381" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="BK381" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="BL381" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="BM381" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="BN381" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="BO381" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="BP381" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="382">
@@ -83837,7 +83837,7 @@
         <v>382</v>
       </c>
       <c r="B383" t="n">
-        <v>8229622</v>
+        <v>8229803</v>
       </c>
       <c r="C383" t="inlineStr">
         <is>
@@ -83857,12 +83857,12 @@
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="I383" t="n">
@@ -83875,179 +83875,179 @@
         <v>1</v>
       </c>
       <c r="L383" t="n">
+        <v>1</v>
+      </c>
+      <c r="M383" t="n">
+        <v>0</v>
+      </c>
+      <c r="N383" t="n">
+        <v>1</v>
+      </c>
+      <c r="O383" t="inlineStr">
+        <is>
+          <t>['35']</t>
+        </is>
+      </c>
+      <c r="P383" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q383" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R383" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S383" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T383" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="U383" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V383" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W383" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X383" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="Y383" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z383" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA383" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB383" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AC383" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD383" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE383" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AF383" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AG383" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH383" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI383" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ383" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK383" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL383" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM383" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AN383" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AO383" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AP383" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AQ383" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AR383" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AS383" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AT383" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AU383" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV383" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW383" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX383" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY383" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ383" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA383" t="n">
         <v>3</v>
       </c>
-      <c r="M383" t="n">
-        <v>1</v>
-      </c>
-      <c r="N383" t="n">
-        <v>4</v>
-      </c>
-      <c r="O383" t="inlineStr">
-        <is>
-          <t>['43', '84', '89']</t>
-        </is>
-      </c>
-      <c r="P383" t="inlineStr">
-        <is>
-          <t>['59']</t>
-        </is>
-      </c>
-      <c r="Q383" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="R383" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="S383" t="n">
+      <c r="BB383" t="n">
         <v>5</v>
       </c>
-      <c r="T383" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="U383" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="V383" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="W383" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="X383" t="n">
+      <c r="BC383" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD383" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BE383" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF383" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BG383" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BH383" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BI383" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BJ383" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK383" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL383" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BM383" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BN383" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BO383" t="n">
         <v>3.8</v>
       </c>
-      <c r="Y383" t="n">
+      <c r="BP383" t="n">
         <v>1.22</v>
-      </c>
-      <c r="Z383" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA383" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AB383" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AC383" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AD383" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE383" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF383" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AG383" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH383" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AI383" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AJ383" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AK383" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AL383" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM383" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AN383" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AO383" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="AP383" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ383" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="AR383" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AS383" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AT383" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AU383" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV383" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW383" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX383" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY383" t="n">
-        <v>29</v>
-      </c>
-      <c r="AZ383" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA383" t="n">
-        <v>13</v>
-      </c>
-      <c r="BB383" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC383" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD383" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BE383" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="BF383" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BG383" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BH383" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BI383" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BJ383" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BK383" t="n">
-        <v>2</v>
-      </c>
-      <c r="BL383" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BM383" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BN383" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="BO383" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BP383" t="n">
-        <v>1.29</v>
       </c>
     </row>
     <row r="384">
@@ -84273,7 +84273,7 @@
         <v>384</v>
       </c>
       <c r="B385" t="n">
-        <v>8229803</v>
+        <v>8229622</v>
       </c>
       <c r="C385" t="inlineStr">
         <is>
@@ -84293,12 +84293,12 @@
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="I385" t="n">
@@ -84311,179 +84311,179 @@
         <v>1</v>
       </c>
       <c r="L385" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M385" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N385" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O385" t="inlineStr">
         <is>
-          <t>['35']</t>
+          <t>['43', '84', '89']</t>
         </is>
       </c>
       <c r="P385" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['59']</t>
         </is>
       </c>
       <c r="Q385" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="R385" t="n">
-        <v>2.38</v>
+        <v>2.68</v>
       </c>
       <c r="S385" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="T385" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="U385" t="n">
-        <v>3.1</v>
+        <v>4.33</v>
       </c>
       <c r="V385" t="n">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="W385" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="X385" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y385" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z385" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA385" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AB385" t="n">
         <v>5.4</v>
       </c>
-      <c r="Y385" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z385" t="n">
+      <c r="AC385" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD385" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE385" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF385" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AG385" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH385" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AI385" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AJ385" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AK385" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AL385" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM385" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AN385" t="n">
         <v>1.91</v>
       </c>
-      <c r="AA385" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB385" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AC385" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AD385" t="n">
+      <c r="AO385" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AP385" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ385" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AR385" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AS385" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AT385" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AU385" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV385" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW385" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX385" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY385" t="n">
+        <v>29</v>
+      </c>
+      <c r="AZ385" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA385" t="n">
         <v>13</v>
       </c>
-      <c r="AE385" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AF385" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AG385" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH385" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AI385" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AJ385" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AK385" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AL385" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM385" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AN385" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AO385" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="AP385" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AQ385" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="AR385" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AS385" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AT385" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AU385" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV385" t="n">
-        <v>7</v>
-      </c>
-      <c r="AW385" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX385" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY385" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ385" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA385" t="n">
-        <v>3</v>
-      </c>
       <c r="BB385" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BC385" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="BD385" t="n">
-        <v>1.78</v>
+        <v>1.42</v>
       </c>
       <c r="BE385" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="BF385" t="n">
-        <v>2.6</v>
+        <v>3.75</v>
       </c>
       <c r="BG385" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="BH385" t="n">
-        <v>2.62</v>
+        <v>3.2</v>
       </c>
       <c r="BI385" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BJ385" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BK385" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL385" t="n">
         <v>1.73</v>
       </c>
-      <c r="BJ385" t="n">
-        <v>2</v>
-      </c>
-      <c r="BK385" t="n">
-        <v>2</v>
-      </c>
-      <c r="BL385" t="n">
-        <v>1.62</v>
-      </c>
       <c r="BM385" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="BN385" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="BO385" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="BP385" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="386">
@@ -86453,7 +86453,7 @@
         <v>394</v>
       </c>
       <c r="B395" t="n">
-        <v>8229830</v>
+        <v>8229824</v>
       </c>
       <c r="C395" t="inlineStr">
         <is>
@@ -86473,197 +86473,197 @@
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="I395" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J395" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K395" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L395" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M395" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N395" t="n">
+        <v>1</v>
+      </c>
+      <c r="O395" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P395" t="inlineStr">
+        <is>
+          <t>['55']</t>
+        </is>
+      </c>
+      <c r="Q395" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R395" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="S395" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T395" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="U395" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V395" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W395" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X395" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y395" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z395" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA395" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB395" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AC395" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD395" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE395" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF395" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AG395" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AH395" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AI395" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AJ395" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AK395" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AL395" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM395" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AN395" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AO395" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AP395" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AQ395" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AR395" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AS395" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AT395" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AU395" t="n">
         <v>5</v>
       </c>
-      <c r="O395" t="inlineStr">
-        <is>
-          <t>['9', '45+3', '67']</t>
-        </is>
-      </c>
-      <c r="P395" t="inlineStr">
-        <is>
-          <t>['39', '77']</t>
-        </is>
-      </c>
-      <c r="Q395" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R395" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S395" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T395" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="U395" t="n">
-        <v>3</v>
-      </c>
-      <c r="V395" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="W395" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X395" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="Y395" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z395" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA395" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="AB395" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC395" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AD395" t="n">
+      <c r="AV395" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW395" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX395" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY395" t="n">
         <v>10</v>
-      </c>
-      <c r="AE395" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF395" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AG395" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AH395" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AI395" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AJ395" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AK395" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AL395" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM395" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AN395" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="AO395" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AP395" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="AQ395" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AR395" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AS395" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AT395" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AU395" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV395" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW395" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX395" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY395" t="n">
-        <v>13</v>
       </c>
       <c r="AZ395" t="n">
         <v>10</v>
       </c>
       <c r="BA395" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BB395" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BC395" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="BD395" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="BE395" t="n">
-        <v>6.25</v>
+        <v>7.5</v>
       </c>
       <c r="BF395" t="n">
-        <v>2.35</v>
+        <v>3.1</v>
       </c>
       <c r="BG395" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="BH395" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="BI395" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="BJ395" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="BK395" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="BL395" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="BM395" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="BN395" t="n">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="BO395" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="BP395" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="396">
@@ -86671,7 +86671,7 @@
         <v>395</v>
       </c>
       <c r="B396" t="n">
-        <v>8229827</v>
+        <v>8229823</v>
       </c>
       <c r="C396" t="inlineStr">
         <is>
@@ -86691,197 +86691,197 @@
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="I396" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J396" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K396" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L396" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M396" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N396" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O396" t="inlineStr">
         <is>
-          <t>['34', '64', '73', '80']</t>
+          <t>['71']</t>
         </is>
       </c>
       <c r="P396" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['25', '39']</t>
         </is>
       </c>
       <c r="Q396" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="R396" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="S396" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="T396" t="n">
         <v>1.25</v>
       </c>
       <c r="U396" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="V396" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="W396" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="X396" t="n">
-        <v>4.7</v>
+        <v>4.33</v>
       </c>
       <c r="Y396" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z396" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AA396" t="n">
-        <v>3.9</v>
+        <v>4.45</v>
       </c>
       <c r="AB396" t="n">
-        <v>3.85</v>
+        <v>5.6</v>
       </c>
       <c r="AC396" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AD396" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AE396" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF396" t="n">
-        <v>5.62</v>
+        <v>5.25</v>
       </c>
       <c r="AG396" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AH396" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="AI396" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AJ396" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AK396" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AL396" t="n">
         <v>0</v>
       </c>
       <c r="AM396" t="n">
-        <v>2.11</v>
+        <v>2.5</v>
       </c>
       <c r="AN396" t="n">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="AO396" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AP396" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AQ396" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR396" t="n">
         <v>1.69</v>
       </c>
-      <c r="AP396" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AQ396" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AR396" t="n">
-        <v>1.76</v>
-      </c>
       <c r="AS396" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AT396" t="n">
-        <v>3.21</v>
+        <v>3.05</v>
       </c>
       <c r="AU396" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AV396" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AW396" t="n">
         <v>15</v>
       </c>
       <c r="AX396" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY396" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ396" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA396" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB396" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC396" t="n">
         <v>5</v>
       </c>
-      <c r="AY396" t="n">
-        <v>23</v>
-      </c>
-      <c r="AZ396" t="n">
-        <v>7</v>
-      </c>
-      <c r="BA396" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB396" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC396" t="n">
-        <v>10</v>
-      </c>
       <c r="BD396" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="BE396" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="BF396" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BG396" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BH396" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI396" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BJ396" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BK396" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BL396" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM396" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BN396" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BO396" t="n">
         <v>3.2</v>
       </c>
-      <c r="BG396" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="BH396" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BI396" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BJ396" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BK396" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="BL396" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BM396" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BN396" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BO396" t="n">
-        <v>3.5</v>
-      </c>
       <c r="BP396" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="397">
@@ -86889,7 +86889,7 @@
         <v>396</v>
       </c>
       <c r="B397" t="n">
-        <v>8229824</v>
+        <v>8229831</v>
       </c>
       <c r="C397" t="inlineStr">
         <is>
@@ -86909,197 +86909,197 @@
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="I397" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J397" t="n">
         <v>0</v>
       </c>
       <c r="K397" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L397" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M397" t="n">
         <v>1</v>
       </c>
       <c r="N397" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O397" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['13']</t>
         </is>
       </c>
       <c r="P397" t="inlineStr">
         <is>
-          <t>['55']</t>
+          <t>['64']</t>
         </is>
       </c>
       <c r="Q397" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="R397" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="S397" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T397" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U397" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="V397" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="W397" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="X397" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y397" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z397" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA397" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB397" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC397" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD397" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE397" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF397" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG397" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AH397" t="n">
         <v>2.4</v>
       </c>
-      <c r="R397" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="S397" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T397" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="U397" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="V397" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W397" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="X397" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Y397" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z397" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA397" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AB397" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AC397" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AD397" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AE397" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AF397" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AG397" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AH397" t="n">
+      <c r="AI397" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ397" t="n">
         <v>2.1</v>
       </c>
-      <c r="AI397" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AJ397" t="n">
-        <v>2.48</v>
-      </c>
       <c r="AK397" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AL397" t="n">
         <v>0</v>
       </c>
       <c r="AM397" t="n">
-        <v>1.83</v>
+        <v>1.35</v>
       </c>
       <c r="AN397" t="n">
-        <v>1.92</v>
+        <v>0.85</v>
       </c>
       <c r="AO397" t="n">
-        <v>1.08</v>
+        <v>1.75</v>
       </c>
       <c r="AP397" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AQ397" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AR397" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AS397" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AT397" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AU397" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV397" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW397" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX397" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY397" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ397" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA397" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB397" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC397" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD397" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BE397" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF397" t="n">
         <v>1.77</v>
       </c>
-      <c r="AQ397" t="n">
+      <c r="BG397" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BH397" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BI397" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BJ397" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BK397" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="BL397" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BM397" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BN397" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BO397" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BP397" t="n">
         <v>1.21</v>
-      </c>
-      <c r="AR397" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AS397" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AT397" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AU397" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV397" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW397" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX397" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY397" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ397" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA397" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB397" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC397" t="n">
-        <v>8</v>
-      </c>
-      <c r="BD397" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BE397" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="BF397" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BG397" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BH397" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BI397" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BJ397" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BK397" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BL397" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BM397" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="BN397" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="BO397" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BP397" t="n">
-        <v>1.22</v>
       </c>
     </row>
     <row r="398">
@@ -87107,7 +87107,7 @@
         <v>397</v>
       </c>
       <c r="B398" t="n">
-        <v>8229823</v>
+        <v>8229827</v>
       </c>
       <c r="C398" t="inlineStr">
         <is>
@@ -87127,197 +87127,197 @@
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="I398" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J398" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K398" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L398" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M398" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N398" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O398" t="inlineStr">
         <is>
-          <t>['71']</t>
+          <t>['34', '64', '73', '80']</t>
         </is>
       </c>
       <c r="P398" t="inlineStr">
         <is>
-          <t>['25', '39']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q398" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="R398" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="S398" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="T398" t="n">
         <v>1.25</v>
       </c>
       <c r="U398" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="V398" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="W398" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="X398" t="n">
-        <v>4.33</v>
+        <v>4.7</v>
       </c>
       <c r="Y398" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z398" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA398" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB398" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AC398" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD398" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE398" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF398" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="AG398" t="n">
         <v>1.53</v>
       </c>
-      <c r="AA398" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AB398" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AC398" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AD398" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE398" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF398" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AG398" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AH398" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="AI398" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ398" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AK398" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL398" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM398" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AN398" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AO398" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AP398" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AQ398" t="n">
         <v>1.57</v>
       </c>
-      <c r="AJ398" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AK398" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AL398" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM398" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AN398" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO398" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AP398" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AQ398" t="n">
-        <v>1.43</v>
-      </c>
       <c r="AR398" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AS398" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AT398" t="n">
-        <v>3.05</v>
+        <v>3.21</v>
       </c>
       <c r="AU398" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AV398" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AW398" t="n">
         <v>15</v>
       </c>
       <c r="AX398" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY398" t="n">
+        <v>23</v>
+      </c>
+      <c r="AZ398" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA398" t="n">
         <v>6</v>
       </c>
-      <c r="AY398" t="n">
-        <v>21</v>
-      </c>
-      <c r="AZ398" t="n">
+      <c r="BB398" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC398" t="n">
         <v>10</v>
       </c>
-      <c r="BA398" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB398" t="n">
-        <v>3</v>
-      </c>
-      <c r="BC398" t="n">
-        <v>5</v>
-      </c>
       <c r="BD398" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="BE398" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="BF398" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="BG398" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="BH398" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="BI398" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="BJ398" t="n">
-        <v>2.25</v>
+        <v>2.48</v>
       </c>
       <c r="BK398" t="n">
-        <v>2.11</v>
+        <v>1.87</v>
       </c>
       <c r="BL398" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="BM398" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="BN398" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="BO398" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="BP398" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="399">
@@ -87325,7 +87325,7 @@
         <v>398</v>
       </c>
       <c r="B399" t="n">
-        <v>8229831</v>
+        <v>8229830</v>
       </c>
       <c r="C399" t="inlineStr">
         <is>
@@ -87345,197 +87345,197 @@
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="I399" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J399" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K399" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L399" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M399" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N399" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O399" t="inlineStr">
         <is>
-          <t>['13']</t>
+          <t>['9', '45+3', '67']</t>
         </is>
       </c>
       <c r="P399" t="inlineStr">
         <is>
-          <t>['64']</t>
+          <t>['39', '77']</t>
         </is>
       </c>
       <c r="Q399" t="n">
-        <v>3.36</v>
+        <v>3.4</v>
       </c>
       <c r="R399" t="n">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="S399" t="n">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="T399" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="U399" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="V399" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="W399" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="X399" t="n">
-        <v>4.33</v>
+        <v>5.8</v>
       </c>
       <c r="Y399" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="Z399" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AA399" t="n">
-        <v>3.3</v>
+        <v>3.53</v>
       </c>
       <c r="AB399" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="AC399" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AD399" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AE399" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AF399" t="n">
         <v>3.5</v>
       </c>
       <c r="AG399" t="n">
-        <v>1.47</v>
+        <v>1.86</v>
       </c>
       <c r="AH399" t="n">
-        <v>2.4</v>
+        <v>2.01</v>
       </c>
       <c r="AI399" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AJ399" t="n">
         <v>2.1</v>
       </c>
       <c r="AK399" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AL399" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM399" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AN399" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AO399" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AP399" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AQ399" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AR399" t="n">
         <v>1.25</v>
       </c>
-      <c r="AL399" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM399" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AN399" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="AO399" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AP399" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="AQ399" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AR399" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AS399" t="n">
-        <v>1.29</v>
+        <v>1.11</v>
       </c>
       <c r="AT399" t="n">
-        <v>2.47</v>
+        <v>2.36</v>
       </c>
       <c r="AU399" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AV399" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AW399" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AX399" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY399" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ399" t="n">
         <v>10</v>
       </c>
-      <c r="AY399" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ399" t="n">
-        <v>13</v>
-      </c>
       <c r="BA399" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BB399" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="BC399" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="BD399" t="n">
-        <v>2.42</v>
+        <v>1.85</v>
       </c>
       <c r="BE399" t="n">
-        <v>8.199999999999999</v>
+        <v>6.25</v>
       </c>
       <c r="BF399" t="n">
-        <v>1.77</v>
+        <v>2.35</v>
       </c>
       <c r="BG399" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="BH399" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="BI399" t="n">
-        <v>1.76</v>
+        <v>1.53</v>
       </c>
       <c r="BJ399" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="BK399" t="n">
-        <v>2.51</v>
+        <v>1.95</v>
       </c>
       <c r="BL399" t="n">
         <v>1.73</v>
       </c>
       <c r="BM399" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="BN399" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="BO399" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="BP399" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="400">
@@ -87761,7 +87761,7 @@
         <v>400</v>
       </c>
       <c r="B401" t="n">
-        <v>8229832</v>
+        <v>8229834</v>
       </c>
       <c r="C401" t="inlineStr">
         <is>
@@ -87781,101 +87781,101 @@
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="I401" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J401" t="n">
         <v>1</v>
       </c>
       <c r="K401" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L401" t="n">
         <v>1</v>
       </c>
       <c r="M401" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N401" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O401" t="inlineStr">
         <is>
-          <t>['13']</t>
+          <t>['72']</t>
         </is>
       </c>
       <c r="P401" t="inlineStr">
         <is>
-          <t>['6']</t>
+          <t>['28', '64']</t>
         </is>
       </c>
       <c r="Q401" t="n">
-        <v>3.75</v>
+        <v>2.61</v>
       </c>
       <c r="R401" t="n">
-        <v>2.3</v>
+        <v>2.53</v>
       </c>
       <c r="S401" t="n">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="T401" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="U401" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="V401" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="W401" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="X401" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="Y401" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z401" t="n">
-        <v>4</v>
+        <v>2.08</v>
       </c>
       <c r="AA401" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AB401" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="AC401" t="n">
         <v>1.02</v>
       </c>
       <c r="AD401" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AE401" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AF401" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="AG401" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="AH401" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AI401" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AJ401" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AK401" t="n">
         <v>1.29</v>
@@ -87884,94 +87884,94 @@
         <v>0</v>
       </c>
       <c r="AM401" t="n">
-        <v>1.3</v>
+        <v>1.78</v>
       </c>
       <c r="AN401" t="n">
-        <v>0.85</v>
+        <v>1.08</v>
       </c>
       <c r="AO401" t="n">
-        <v>1.27</v>
+        <v>1.08</v>
       </c>
       <c r="AP401" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AQ401" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AR401" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AS401" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AT401" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="AU401" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV401" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW401" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX401" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY401" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ401" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA401" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB401" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC401" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD401" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BE401" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF401" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BG401" t="n">
         <v>1.22</v>
       </c>
-      <c r="AS401" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AT401" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AU401" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV401" t="n">
-        <v>7</v>
-      </c>
-      <c r="AW401" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX401" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY401" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ401" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA401" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB401" t="n">
-        <v>11</v>
-      </c>
-      <c r="BC401" t="n">
-        <v>12</v>
-      </c>
-      <c r="BD401" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BE401" t="n">
-        <v>6</v>
-      </c>
-      <c r="BF401" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="BG401" t="n">
-        <v>1.36</v>
-      </c>
       <c r="BH401" t="n">
-        <v>2.75</v>
+        <v>3.7</v>
       </c>
       <c r="BI401" t="n">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="BJ401" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="BK401" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="BL401" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="BM401" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="BN401" t="n">
-        <v>1.32</v>
+        <v>1.51</v>
       </c>
       <c r="BO401" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="BP401" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="402">
@@ -87979,7 +87979,7 @@
         <v>401</v>
       </c>
       <c r="B402" t="n">
-        <v>8229834</v>
+        <v>8229832</v>
       </c>
       <c r="C402" t="inlineStr">
         <is>
@@ -87999,101 +87999,101 @@
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="I402" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J402" t="n">
         <v>1</v>
       </c>
       <c r="K402" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L402" t="n">
         <v>1</v>
       </c>
       <c r="M402" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N402" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O402" t="inlineStr">
         <is>
-          <t>['72']</t>
+          <t>['13']</t>
         </is>
       </c>
       <c r="P402" t="inlineStr">
         <is>
-          <t>['28', '64']</t>
+          <t>['6']</t>
         </is>
       </c>
       <c r="Q402" t="n">
-        <v>2.61</v>
+        <v>3.75</v>
       </c>
       <c r="R402" t="n">
-        <v>2.53</v>
+        <v>2.3</v>
       </c>
       <c r="S402" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="T402" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="U402" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="V402" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="W402" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="X402" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="Y402" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z402" t="n">
-        <v>2.08</v>
+        <v>4</v>
       </c>
       <c r="AA402" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AB402" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="AC402" t="n">
         <v>1.02</v>
       </c>
       <c r="AD402" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AE402" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AF402" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="AG402" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="AH402" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AI402" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="AJ402" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AK402" t="n">
         <v>1.29</v>
@@ -88102,94 +88102,94 @@
         <v>0</v>
       </c>
       <c r="AM402" t="n">
-        <v>1.78</v>
+        <v>1.3</v>
       </c>
       <c r="AN402" t="n">
-        <v>1.08</v>
+        <v>0.85</v>
       </c>
       <c r="AO402" t="n">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="AP402" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AQ402" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AR402" t="n">
-        <v>1.52</v>
+        <v>1.22</v>
       </c>
       <c r="AS402" t="n">
-        <v>1.65</v>
+        <v>1.37</v>
       </c>
       <c r="AT402" t="n">
-        <v>3.17</v>
+        <v>2.59</v>
       </c>
       <c r="AU402" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV402" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AW402" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX402" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY402" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ402" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA402" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB402" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC402" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD402" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BE402" t="n">
         <v>6</v>
       </c>
-      <c r="AY402" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ402" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA402" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB402" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC402" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD402" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="BE402" t="n">
-        <v>8.5</v>
-      </c>
       <c r="BF402" t="n">
-        <v>2.55</v>
+        <v>1.66</v>
       </c>
       <c r="BG402" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="BH402" t="n">
-        <v>3.7</v>
+        <v>2.75</v>
       </c>
       <c r="BI402" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="BJ402" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="BK402" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="BL402" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="BM402" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="BN402" t="n">
-        <v>1.51</v>
+        <v>1.32</v>
       </c>
       <c r="BO402" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="BP402" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="403">
@@ -88197,7 +88197,7 @@
         <v>402</v>
       </c>
       <c r="B403" t="n">
-        <v>8229828</v>
+        <v>8229826</v>
       </c>
       <c r="C403" t="inlineStr">
         <is>
@@ -88217,197 +88217,197 @@
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="I403" t="n">
         <v>1</v>
       </c>
       <c r="J403" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K403" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L403" t="n">
+        <v>1</v>
+      </c>
+      <c r="M403" t="n">
         <v>3</v>
       </c>
-      <c r="M403" t="n">
-        <v>2</v>
-      </c>
       <c r="N403" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O403" t="inlineStr">
         <is>
-          <t>['45+4', '79', '90+14']</t>
+          <t>['15']</t>
         </is>
       </c>
       <c r="P403" t="inlineStr">
         <is>
-          <t>['13', '73']</t>
+          <t>['6', '36', '51']</t>
         </is>
       </c>
       <c r="Q403" t="n">
-        <v>1.92</v>
+        <v>2.75</v>
       </c>
       <c r="R403" t="n">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="S403" t="n">
-        <v>5.25</v>
+        <v>3.4</v>
       </c>
       <c r="T403" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="U403" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="V403" t="n">
-        <v>2.11</v>
+        <v>2.4</v>
       </c>
       <c r="W403" t="n">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="X403" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="Y403" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="Z403" t="n">
-        <v>1.41</v>
+        <v>2.33</v>
       </c>
       <c r="AA403" t="n">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="AB403" t="n">
-        <v>6.4</v>
+        <v>2.82</v>
       </c>
       <c r="AC403" t="n">
         <v>1.01</v>
       </c>
       <c r="AD403" t="n">
-        <v>15.5</v>
+        <v>10</v>
       </c>
       <c r="AE403" t="n">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="AF403" t="n">
-        <v>5.25</v>
+        <v>3.8</v>
       </c>
       <c r="AG403" t="n">
-        <v>1.42</v>
+        <v>1.73</v>
       </c>
       <c r="AH403" t="n">
-        <v>3.1</v>
+        <v>2.15</v>
       </c>
       <c r="AI403" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AJ403" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AK403" t="n">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="AL403" t="n">
         <v>0</v>
       </c>
       <c r="AM403" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AN403" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AO403" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AP403" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AQ403" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AR403" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AS403" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AT403" t="n">
         <v>2.75</v>
       </c>
-      <c r="AN403" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO403" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="AP403" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AQ403" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="AR403" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AS403" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AT403" t="n">
-        <v>2.91</v>
-      </c>
       <c r="AU403" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV403" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW403" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AX403" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY403" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AZ403" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA403" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB403" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC403" t="n">
         <v>11</v>
       </c>
-      <c r="BA403" t="n">
-        <v>11</v>
-      </c>
-      <c r="BB403" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC403" t="n">
-        <v>12</v>
-      </c>
       <c r="BD403" t="n">
-        <v>1.4</v>
+        <v>1.66</v>
       </c>
       <c r="BE403" t="n">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="BF403" t="n">
-        <v>3.54</v>
+        <v>2.6</v>
       </c>
       <c r="BG403" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BH403" t="n">
-        <v>3.5</v>
+        <v>3.88</v>
       </c>
       <c r="BI403" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="BJ403" t="n">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="BK403" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="BL403" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="BM403" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="BN403" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="BO403" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="BP403" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="404">
@@ -88415,7 +88415,7 @@
         <v>403</v>
       </c>
       <c r="B404" t="n">
-        <v>8229826</v>
+        <v>8229828</v>
       </c>
       <c r="C404" t="inlineStr">
         <is>
@@ -88435,197 +88435,197 @@
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="I404" t="n">
         <v>1</v>
       </c>
       <c r="J404" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K404" t="n">
+        <v>2</v>
+      </c>
+      <c r="L404" t="n">
         <v>3</v>
       </c>
-      <c r="L404" t="n">
-        <v>1</v>
-      </c>
       <c r="M404" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N404" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O404" t="inlineStr">
         <is>
-          <t>['15']</t>
+          <t>['45+4', '79', '90+14']</t>
         </is>
       </c>
       <c r="P404" t="inlineStr">
         <is>
-          <t>['6', '36', '51']</t>
+          <t>['13', '73']</t>
         </is>
       </c>
       <c r="Q404" t="n">
-        <v>2.75</v>
+        <v>1.92</v>
       </c>
       <c r="R404" t="n">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="S404" t="n">
-        <v>3.4</v>
+        <v>5.25</v>
       </c>
       <c r="T404" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="U404" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="V404" t="n">
-        <v>2.4</v>
+        <v>2.11</v>
       </c>
       <c r="W404" t="n">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="X404" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="Y404" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="Z404" t="n">
-        <v>2.33</v>
+        <v>1.41</v>
       </c>
       <c r="AA404" t="n">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="AB404" t="n">
-        <v>2.82</v>
+        <v>6.4</v>
       </c>
       <c r="AC404" t="n">
         <v>1.01</v>
       </c>
       <c r="AD404" t="n">
-        <v>10</v>
+        <v>15.5</v>
       </c>
       <c r="AE404" t="n">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="AF404" t="n">
-        <v>3.8</v>
+        <v>5.25</v>
       </c>
       <c r="AG404" t="n">
-        <v>1.73</v>
+        <v>1.42</v>
       </c>
       <c r="AH404" t="n">
-        <v>2.15</v>
+        <v>3.1</v>
       </c>
       <c r="AI404" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AJ404" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AK404" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AL404" t="n">
         <v>0</v>
       </c>
       <c r="AM404" t="n">
-        <v>1.65</v>
+        <v>2.75</v>
       </c>
       <c r="AN404" t="n">
-        <v>1.58</v>
+        <v>2</v>
       </c>
       <c r="AO404" t="n">
-        <v>1.77</v>
+        <v>0.38</v>
       </c>
       <c r="AP404" t="n">
-        <v>1.46</v>
+        <v>2.08</v>
       </c>
       <c r="AQ404" t="n">
-        <v>1.86</v>
+        <v>0.36</v>
       </c>
       <c r="AR404" t="n">
-        <v>1.48</v>
+        <v>1.8</v>
       </c>
       <c r="AS404" t="n">
-        <v>1.27</v>
+        <v>1.11</v>
       </c>
       <c r="AT404" t="n">
-        <v>2.75</v>
+        <v>2.91</v>
       </c>
       <c r="AU404" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV404" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW404" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AX404" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY404" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AZ404" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BA404" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="BB404" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BC404" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD404" t="n">
-        <v>1.66</v>
+        <v>1.4</v>
       </c>
       <c r="BE404" t="n">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="BF404" t="n">
-        <v>2.6</v>
+        <v>3.54</v>
       </c>
       <c r="BG404" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BH404" t="n">
-        <v>3.88</v>
+        <v>3.5</v>
       </c>
       <c r="BI404" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="BJ404" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="BK404" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="BL404" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="BM404" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="BN404" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="BO404" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="BP404" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="405">

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
@@ -80785,7 +80785,7 @@
         <v>368</v>
       </c>
       <c r="B369" t="n">
-        <v>8229334</v>
+        <v>8229333</v>
       </c>
       <c r="C369" t="inlineStr">
         <is>
@@ -80805,19 +80805,19 @@
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="I369" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J369" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K369" t="n">
         <v>2</v>
@@ -80833,106 +80833,106 @@
       </c>
       <c r="O369" t="inlineStr">
         <is>
-          <t>['10', '70']</t>
+          <t>['31', '41']</t>
         </is>
       </c>
       <c r="P369" t="inlineStr">
         <is>
-          <t>['19', '81']</t>
+          <t>['80', '89']</t>
         </is>
       </c>
       <c r="Q369" t="n">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="R369" t="n">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="S369" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T369" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="U369" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V369" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="W369" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X369" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="Y369" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z369" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA369" t="n">
         <v>3.4</v>
       </c>
-      <c r="T369" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="U369" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V369" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="W369" t="n">
+      <c r="AB369" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AC369" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD369" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE369" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF369" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG369" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH369" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI369" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ369" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK369" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL369" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM369" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN369" t="n">
         <v>1.55</v>
       </c>
-      <c r="X369" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="Y369" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z369" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA369" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AB369" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AC369" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD369" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE369" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AF369" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AG369" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AH369" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AI369" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AJ369" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AK369" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AL369" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM369" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AN369" t="n">
+      <c r="AO369" t="n">
         <v>1.18</v>
       </c>
-      <c r="AO369" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AP369" t="n">
-        <v>1.31</v>
+        <v>1.46</v>
       </c>
       <c r="AQ369" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR369" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AS369" t="n">
-        <v>1.34</v>
+        <v>1.06</v>
       </c>
       <c r="AT369" t="n">
-        <v>2.91</v>
+        <v>2.56</v>
       </c>
       <c r="AU369" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV369" t="n">
         <v>6</v>
@@ -80941,61 +80941,61 @@
         <v>8</v>
       </c>
       <c r="AX369" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AY369" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ369" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="BA369" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BB369" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BC369" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BD369" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="BE369" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="BF369" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="BG369" t="n">
         <v>1.28</v>
       </c>
       <c r="BH369" t="n">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="BI369" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="BJ369" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="BK369" t="n">
-        <v>1.75</v>
+        <v>2.06</v>
       </c>
       <c r="BL369" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="BM369" t="n">
         <v>2.32</v>
       </c>
       <c r="BN369" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="BO369" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="BP369" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="370">
@@ -81003,7 +81003,7 @@
         <v>369</v>
       </c>
       <c r="B370" t="n">
-        <v>8229800</v>
+        <v>8229790</v>
       </c>
       <c r="C370" t="inlineStr">
         <is>
@@ -81023,194 +81023,194 @@
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="I370" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J370" t="n">
         <v>0</v>
       </c>
       <c r="K370" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L370" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M370" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N370" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O370" t="inlineStr">
         <is>
-          <t>['8', '62']</t>
+          <t>['23', '39', '66']</t>
         </is>
       </c>
       <c r="P370" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['85']</t>
         </is>
       </c>
       <c r="Q370" t="n">
-        <v>2.55</v>
+        <v>3.4</v>
       </c>
       <c r="R370" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S370" t="n">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="T370" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="U370" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="V370" t="n">
         <v>2.45</v>
       </c>
       <c r="W370" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="X370" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Y370" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z370" t="n">
-        <v>2.12</v>
+        <v>3.1</v>
       </c>
       <c r="AA370" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AB370" t="n">
-        <v>3.45</v>
+        <v>2.08</v>
       </c>
       <c r="AC370" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AD370" t="n">
-        <v>9.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="AE370" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AF370" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="AG370" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AH370" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AI370" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ370" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK370" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL370" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM370" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AN370" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AO370" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AP370" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AQ370" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AR370" t="n">
         <v>1.62</v>
       </c>
-      <c r="AJ370" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AK370" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AL370" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM370" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AN370" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AO370" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AP370" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="AQ370" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AR370" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AS370" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AT370" t="n">
-        <v>2.45</v>
+        <v>2.87</v>
       </c>
       <c r="AU370" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AV370" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AW370" t="n">
         <v>5</v>
       </c>
       <c r="AX370" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AY370" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AZ370" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="BA370" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB370" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BC370" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD370" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="BE370" t="n">
-        <v>7.5</v>
+        <v>6.25</v>
       </c>
       <c r="BF370" t="n">
-        <v>2.48</v>
+        <v>1.9</v>
       </c>
       <c r="BG370" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="BH370" t="n">
-        <v>3.08</v>
+        <v>2.75</v>
       </c>
       <c r="BI370" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="BJ370" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="BK370" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="BL370" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="BM370" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="BN370" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="BO370" t="n">
-        <v>3.48</v>
+        <v>3.7</v>
       </c>
       <c r="BP370" t="n">
         <v>1.22</v>
@@ -81221,7 +81221,7 @@
         <v>370</v>
       </c>
       <c r="B371" t="n">
-        <v>8229333</v>
+        <v>8229800</v>
       </c>
       <c r="C371" t="inlineStr">
         <is>
@@ -81241,197 +81241,197 @@
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="I371" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J371" t="n">
         <v>0</v>
       </c>
       <c r="K371" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L371" t="n">
         <v>2</v>
       </c>
       <c r="M371" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N371" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O371" t="inlineStr">
         <is>
-          <t>['31', '41']</t>
+          <t>['8', '62']</t>
         </is>
       </c>
       <c r="P371" t="inlineStr">
         <is>
-          <t>['80', '89']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q371" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R371" t="n">
         <v>2.25</v>
       </c>
-      <c r="R371" t="n">
-        <v>2.15</v>
-      </c>
       <c r="S371" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="T371" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="U371" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="V371" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="W371" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="X371" t="n">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="Y371" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z371" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AA371" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="AB371" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="AC371" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AD371" t="n">
-        <v>9.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AE371" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AF371" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="AG371" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AH371" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AI371" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AJ371" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AK371" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AL371" t="n">
         <v>0</v>
       </c>
       <c r="AM371" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AN371" t="n">
-        <v>1.55</v>
+        <v>0.67</v>
       </c>
       <c r="AO371" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AP371" t="n">
-        <v>1.46</v>
+        <v>0.86</v>
       </c>
       <c r="AQ371" t="n">
         <v>1.15</v>
       </c>
       <c r="AR371" t="n">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="AS371" t="n">
-        <v>1.06</v>
+        <v>1.21</v>
       </c>
       <c r="AT371" t="n">
-        <v>2.56</v>
+        <v>2.45</v>
       </c>
       <c r="AU371" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV371" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW371" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX371" t="n">
         <v>6</v>
       </c>
-      <c r="AW371" t="n">
+      <c r="AY371" t="n">
         <v>8</v>
       </c>
-      <c r="AX371" t="n">
+      <c r="AZ371" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA371" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB371" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC371" t="n">
         <v>12</v>
       </c>
-      <c r="AY371" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ371" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA371" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB371" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC371" t="n">
-        <v>9</v>
-      </c>
       <c r="BD371" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="BE371" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="BF371" t="n">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="BG371" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="BH371" t="n">
-        <v>3.42</v>
+        <v>3.08</v>
       </c>
       <c r="BI371" t="n">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="BJ371" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="BK371" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="BL371" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="BM371" t="n">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="BN371" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="BO371" t="n">
-        <v>3.08</v>
+        <v>3.48</v>
       </c>
       <c r="BP371" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="372">
@@ -81439,7 +81439,7 @@
         <v>371</v>
       </c>
       <c r="B372" t="n">
-        <v>8229790</v>
+        <v>8229334</v>
       </c>
       <c r="C372" t="inlineStr">
         <is>
@@ -81459,197 +81459,197 @@
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="I372" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J372" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K372" t="n">
         <v>2</v>
       </c>
       <c r="L372" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M372" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N372" t="n">
         <v>4</v>
       </c>
       <c r="O372" t="inlineStr">
         <is>
-          <t>['23', '39', '66']</t>
+          <t>['10', '70']</t>
         </is>
       </c>
       <c r="P372" t="inlineStr">
         <is>
-          <t>['85']</t>
+          <t>['19', '81']</t>
         </is>
       </c>
       <c r="Q372" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R372" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="S372" t="n">
         <v>3.4</v>
       </c>
-      <c r="R372" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S372" t="n">
-        <v>2.5</v>
-      </c>
       <c r="T372" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="U372" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="V372" t="n">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="W372" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="X372" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="Y372" t="n">
         <v>1.13</v>
       </c>
       <c r="Z372" t="n">
-        <v>3.1</v>
+        <v>2.35</v>
       </c>
       <c r="AA372" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="AB372" t="n">
-        <v>2.08</v>
+        <v>2.9</v>
       </c>
       <c r="AC372" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AD372" t="n">
         <v>13</v>
       </c>
       <c r="AE372" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AF372" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AG372" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH372" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AI372" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ372" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AK372" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL372" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM372" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN372" t="n">
         <v>1.18</v>
       </c>
-      <c r="AF372" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AG372" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AH372" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AI372" t="n">
+      <c r="AO372" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AP372" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AQ372" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR372" t="n">
         <v>1.57</v>
       </c>
-      <c r="AJ372" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AK372" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AL372" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM372" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AN372" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AO372" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AP372" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AQ372" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AR372" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AS372" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AT372" t="n">
-        <v>2.87</v>
+        <v>2.91</v>
       </c>
       <c r="AU372" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AV372" t="n">
         <v>6</v>
       </c>
       <c r="AW372" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AX372" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY372" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ372" t="n">
         <v>12</v>
       </c>
-      <c r="AY372" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ372" t="n">
-        <v>18</v>
-      </c>
       <c r="BA372" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BB372" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC372" t="n">
         <v>7</v>
       </c>
-      <c r="BC372" t="n">
-        <v>11</v>
-      </c>
       <c r="BD372" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="BE372" t="n">
-        <v>6.25</v>
+        <v>7.5</v>
       </c>
       <c r="BF372" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="BG372" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="BH372" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="BI372" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="BJ372" t="n">
-        <v>2.21</v>
+        <v>2.5</v>
       </c>
       <c r="BK372" t="n">
-        <v>1.97</v>
+        <v>1.75</v>
       </c>
       <c r="BL372" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="BM372" t="n">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="BN372" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="BO372" t="n">
-        <v>3.7</v>
+        <v>3.05</v>
       </c>
       <c r="BP372" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="373">
@@ -82093,7 +82093,7 @@
         <v>374</v>
       </c>
       <c r="B375" t="n">
-        <v>8229477</v>
+        <v>8229483</v>
       </c>
       <c r="C375" t="inlineStr">
         <is>
@@ -82113,12 +82113,12 @@
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="I375" t="n">
@@ -82131,179 +82131,179 @@
         <v>0</v>
       </c>
       <c r="L375" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M375" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N375" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O375" t="inlineStr">
         <is>
-          <t>['73']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P375" t="inlineStr">
         <is>
-          <t>['60', '70']</t>
+          <t>['85']</t>
         </is>
       </c>
       <c r="Q375" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="R375" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="S375" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="T375" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="U375" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="V375" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="W375" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X375" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Y375" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z375" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA375" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AB375" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AC375" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD375" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE375" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF375" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG375" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH375" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AI375" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ375" t="n">
         <v>2.2</v>
       </c>
-      <c r="W375" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="X375" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="Y375" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z375" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA375" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB375" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AC375" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AD375" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE375" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AF375" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AG375" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AH375" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AI375" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AJ375" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AK375" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AL375" t="n">
         <v>0</v>
       </c>
       <c r="AM375" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AN375" t="n">
-        <v>1.75</v>
+        <v>2.09</v>
       </c>
       <c r="AO375" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AP375" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="AQ375" t="n">
         <v>0.93</v>
       </c>
       <c r="AR375" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AS375" t="n">
-        <v>0.95</v>
+        <v>1.1</v>
       </c>
       <c r="AT375" t="n">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="AU375" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV375" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW375" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX375" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY375" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ375" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA375" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB375" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC375" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD375" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BE375" t="n">
         <v>9</v>
       </c>
-      <c r="AV375" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW375" t="n">
-        <v>13</v>
-      </c>
-      <c r="AX375" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY375" t="n">
-        <v>22</v>
-      </c>
-      <c r="AZ375" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA375" t="n">
-        <v>13</v>
-      </c>
-      <c r="BB375" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC375" t="n">
-        <v>17</v>
-      </c>
-      <c r="BD375" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BE375" t="n">
-        <v>8</v>
-      </c>
       <c r="BF375" t="n">
-        <v>2.92</v>
+        <v>3.9</v>
       </c>
       <c r="BG375" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="BH375" t="n">
-        <v>4.05</v>
+        <v>2.69</v>
       </c>
       <c r="BI375" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="BJ375" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BK375" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BL375" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BM375" t="n">
         <v>2.5</v>
       </c>
-      <c r="BK375" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BL375" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BM375" t="n">
-        <v>2.2</v>
-      </c>
       <c r="BN375" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="BO375" t="n">
-        <v>2.55</v>
+        <v>3.75</v>
       </c>
       <c r="BP375" t="n">
-        <v>1.46</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="376">
@@ -82311,7 +82311,7 @@
         <v>375</v>
       </c>
       <c r="B376" t="n">
-        <v>8229483</v>
+        <v>8229491</v>
       </c>
       <c r="C376" t="inlineStr">
         <is>
@@ -82331,131 +82331,131 @@
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="I376" t="n">
         <v>0</v>
       </c>
       <c r="J376" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K376" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L376" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M376" t="n">
         <v>1</v>
       </c>
       <c r="N376" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O376" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['52', '90+9']</t>
         </is>
       </c>
       <c r="P376" t="inlineStr">
         <is>
-          <t>['85']</t>
+          <t>['3']</t>
         </is>
       </c>
       <c r="Q376" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="R376" t="n">
-        <v>2.54</v>
+        <v>2.32</v>
       </c>
       <c r="S376" t="n">
-        <v>4.5</v>
+        <v>3.32</v>
       </c>
       <c r="T376" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="U376" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="V376" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="W376" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="X376" t="n">
-        <v>5.25</v>
+        <v>5.4</v>
       </c>
       <c r="Y376" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z376" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AA376" t="n">
-        <v>3.92</v>
+        <v>3.55</v>
       </c>
       <c r="AB376" t="n">
-        <v>4.25</v>
+        <v>3.15</v>
       </c>
       <c r="AC376" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AD376" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AE376" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AF376" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="AG376" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AH376" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AI376" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AJ376" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AK376" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AL376" t="n">
         <v>0</v>
       </c>
       <c r="AM376" t="n">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="AN376" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AO376" t="n">
-        <v>0.77</v>
+        <v>1</v>
       </c>
       <c r="AP376" t="n">
-        <v>1.77</v>
+        <v>2.29</v>
       </c>
       <c r="AQ376" t="n">
-        <v>0.93</v>
+        <v>0.86</v>
       </c>
       <c r="AR376" t="n">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="AS376" t="n">
-        <v>1.1</v>
+        <v>1.52</v>
       </c>
       <c r="AT376" t="n">
-        <v>2.58</v>
+        <v>2.89</v>
       </c>
       <c r="AU376" t="n">
         <v>7</v>
@@ -82464,61 +82464,61 @@
         <v>3</v>
       </c>
       <c r="AW376" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AX376" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY376" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AZ376" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA376" t="n">
         <v>5</v>
       </c>
       <c r="BB376" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BC376" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BD376" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="BE376" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="BF376" t="n">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="BG376" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="BH376" t="n">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="BI376" t="n">
-        <v>1.51</v>
+        <v>1.65</v>
       </c>
       <c r="BJ376" t="n">
         <v>2.1</v>
       </c>
       <c r="BK376" t="n">
-        <v>1.97</v>
+        <v>2.45</v>
       </c>
       <c r="BL376" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="BM376" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="BN376" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="BO376" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="BP376" t="n">
         <v>1.24</v>
@@ -82529,7 +82529,7 @@
         <v>376</v>
       </c>
       <c r="B377" t="n">
-        <v>8229491</v>
+        <v>8229477</v>
       </c>
       <c r="C377" t="inlineStr">
         <is>
@@ -82549,197 +82549,197 @@
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="I377" t="n">
         <v>0</v>
       </c>
       <c r="J377" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K377" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L377" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M377" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N377" t="n">
         <v>3</v>
       </c>
       <c r="O377" t="inlineStr">
         <is>
-          <t>['52', '90+9']</t>
+          <t>['73']</t>
         </is>
       </c>
       <c r="P377" t="inlineStr">
         <is>
-          <t>['3']</t>
+          <t>['60', '70']</t>
         </is>
       </c>
       <c r="Q377" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R377" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="S377" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T377" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U377" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="V377" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W377" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="X377" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y377" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z377" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA377" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB377" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AC377" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD377" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE377" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF377" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AG377" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AH377" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AI377" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ377" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AK377" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL377" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM377" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AN377" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AO377" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AP377" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AQ377" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AR377" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS377" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AT377" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AU377" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV377" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW377" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX377" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY377" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ377" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA377" t="n">
+        <v>13</v>
+      </c>
+      <c r="BB377" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC377" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD377" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BE377" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF377" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BG377" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BH377" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="BI377" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ377" t="n">
         <v>2.5</v>
       </c>
-      <c r="R377" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="S377" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="T377" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="U377" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="V377" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="W377" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="X377" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="Y377" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z377" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA377" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AB377" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AC377" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AD377" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE377" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF377" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AG377" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AH377" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AI377" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AJ377" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AK377" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AL377" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM377" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AN377" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AO377" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP377" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AQ377" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="AR377" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AS377" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AT377" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AU377" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV377" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW377" t="n">
-        <v>17</v>
-      </c>
-      <c r="AX377" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY377" t="n">
-        <v>24</v>
-      </c>
-      <c r="AZ377" t="n">
-        <v>7</v>
-      </c>
-      <c r="BA377" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB377" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC377" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD377" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BE377" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="BF377" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BG377" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BH377" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="BI377" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BJ377" t="n">
-        <v>2.1</v>
-      </c>
       <c r="BK377" t="n">
-        <v>2.45</v>
+        <v>1.75</v>
       </c>
       <c r="BL377" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="BM377" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="BN377" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="BO377" t="n">
-        <v>3.6</v>
+        <v>2.55</v>
       </c>
       <c r="BP377" t="n">
-        <v>1.24</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="378">
@@ -83401,7 +83401,7 @@
         <v>380</v>
       </c>
       <c r="B381" t="n">
-        <v>8229772</v>
+        <v>8229622</v>
       </c>
       <c r="C381" t="inlineStr">
         <is>
@@ -83421,197 +83421,197 @@
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="I381" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J381" t="n">
         <v>0</v>
       </c>
       <c r="K381" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L381" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M381" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N381" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O381" t="inlineStr">
         <is>
-          <t>['74']</t>
+          <t>['43', '84', '89']</t>
         </is>
       </c>
       <c r="P381" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['59']</t>
         </is>
       </c>
       <c r="Q381" t="n">
-        <v>2.94</v>
+        <v>1.93</v>
       </c>
       <c r="R381" t="n">
-        <v>2.15</v>
+        <v>2.68</v>
       </c>
       <c r="S381" t="n">
+        <v>5</v>
+      </c>
+      <c r="T381" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="U381" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="V381" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="W381" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="X381" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y381" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z381" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA381" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AB381" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AC381" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD381" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE381" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF381" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AG381" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH381" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AI381" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AJ381" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AK381" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AL381" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM381" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AN381" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AO381" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AP381" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ381" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AR381" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AS381" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AT381" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AU381" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV381" t="n">
         <v>3</v>
       </c>
-      <c r="T381" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="U381" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="V381" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="W381" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="X381" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Y381" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z381" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA381" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB381" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="AC381" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AD381" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE381" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AF381" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG381" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AH381" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AI381" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AJ381" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AK381" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AL381" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM381" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AN381" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AO381" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AP381" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AQ381" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AR381" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AS381" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AT381" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AU381" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV381" t="n">
-        <v>1</v>
-      </c>
       <c r="AW381" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX381" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY381" t="n">
+        <v>29</v>
+      </c>
+      <c r="AZ381" t="n">
         <v>5</v>
       </c>
-      <c r="AX381" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY381" t="n">
-        <v>7</v>
-      </c>
-      <c r="AZ381" t="n">
-        <v>11</v>
-      </c>
       <c r="BA381" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="BB381" t="n">
         <v>2</v>
       </c>
       <c r="BC381" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="BD381" t="n">
-        <v>2.06</v>
+        <v>1.42</v>
       </c>
       <c r="BE381" t="n">
-        <v>6.25</v>
+        <v>7.5</v>
       </c>
       <c r="BF381" t="n">
-        <v>1.9</v>
+        <v>3.75</v>
       </c>
       <c r="BG381" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="BH381" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI381" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BJ381" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BK381" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL381" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BM381" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BN381" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BO381" t="n">
         <v>3.3</v>
       </c>
-      <c r="BI381" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BJ381" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BK381" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BL381" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BM381" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BN381" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="BO381" t="n">
-        <v>3.05</v>
-      </c>
       <c r="BP381" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="382">
@@ -83837,7 +83837,7 @@
         <v>382</v>
       </c>
       <c r="B383" t="n">
-        <v>8229803</v>
+        <v>8229623</v>
       </c>
       <c r="C383" t="inlineStr">
         <is>
@@ -83857,197 +83857,197 @@
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="I383" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J383" t="n">
         <v>0</v>
       </c>
       <c r="K383" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L383" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M383" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N383" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O383" t="inlineStr">
         <is>
-          <t>['35']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P383" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['51', '90+4']</t>
         </is>
       </c>
       <c r="Q383" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R383" t="n">
         <v>2.25</v>
       </c>
-      <c r="R383" t="n">
-        <v>2.38</v>
-      </c>
       <c r="S383" t="n">
-        <v>3.9</v>
+        <v>2.55</v>
       </c>
       <c r="T383" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="U383" t="n">
-        <v>3.1</v>
+        <v>3.32</v>
       </c>
       <c r="V383" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W383" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X383" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Y383" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z383" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA383" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB383" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AC383" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD383" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE383" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF383" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AG383" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH383" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AI383" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ383" t="n">
         <v>2.25</v>
       </c>
-      <c r="W383" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="X383" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="Y383" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z383" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AA383" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB383" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AC383" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AD383" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE383" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AF383" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AG383" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH383" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AI383" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AJ383" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AK383" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AL383" t="n">
         <v>0</v>
       </c>
       <c r="AM383" t="n">
-        <v>1.94</v>
+        <v>1.27</v>
       </c>
       <c r="AN383" t="n">
-        <v>2.33</v>
+        <v>0.92</v>
       </c>
       <c r="AO383" t="n">
-        <v>0.92</v>
+        <v>1.1</v>
       </c>
       <c r="AP383" t="n">
-        <v>2.43</v>
+        <v>0.85</v>
       </c>
       <c r="AQ383" t="n">
-        <v>0.86</v>
+        <v>1.25</v>
       </c>
       <c r="AR383" t="n">
-        <v>1.43</v>
+        <v>1.27</v>
       </c>
       <c r="AS383" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AT383" t="n">
-        <v>2.89</v>
+        <v>2.63</v>
       </c>
       <c r="AU383" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AV383" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW383" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AX383" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="AY383" t="n">
         <v>11</v>
       </c>
       <c r="AZ383" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="BA383" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB383" t="n">
         <v>3</v>
       </c>
-      <c r="BB383" t="n">
-        <v>5</v>
-      </c>
       <c r="BC383" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD383" t="n">
-        <v>1.78</v>
+        <v>2.15</v>
       </c>
       <c r="BE383" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="BF383" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="BG383" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="BH383" t="n">
-        <v>2.62</v>
+        <v>3.2</v>
       </c>
       <c r="BI383" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="BJ383" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="BK383" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="BL383" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="BM383" t="n">
-        <v>2.8</v>
+        <v>2.23</v>
       </c>
       <c r="BN383" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="BO383" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="BP383" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="384">
@@ -84055,7 +84055,7 @@
         <v>383</v>
       </c>
       <c r="B384" t="n">
-        <v>8229623</v>
+        <v>8229803</v>
       </c>
       <c r="C384" t="inlineStr">
         <is>
@@ -84075,197 +84075,197 @@
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="I384" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J384" t="n">
         <v>0</v>
       </c>
       <c r="K384" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L384" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M384" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N384" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O384" t="inlineStr">
         <is>
+          <t>['35']</t>
+        </is>
+      </c>
+      <c r="P384" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="P384" t="inlineStr">
-        <is>
-          <t>['51', '90+4']</t>
-        </is>
-      </c>
       <c r="Q384" t="n">
-        <v>3.8</v>
+        <v>2.25</v>
       </c>
       <c r="R384" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S384" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T384" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="U384" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V384" t="n">
         <v>2.25</v>
       </c>
-      <c r="S384" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T384" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="U384" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="V384" t="n">
-        <v>2.2</v>
-      </c>
       <c r="W384" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="X384" t="n">
-        <v>5.25</v>
+        <v>5.4</v>
       </c>
       <c r="Y384" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z384" t="n">
-        <v>3.2</v>
+        <v>1.91</v>
       </c>
       <c r="AA384" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AB384" t="n">
-        <v>2.08</v>
+        <v>3.5</v>
       </c>
       <c r="AC384" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AD384" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE384" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AF384" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AG384" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH384" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI384" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ384" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK384" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL384" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM384" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AN384" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AO384" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AP384" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AQ384" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AR384" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AS384" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AT384" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AU384" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV384" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW384" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX384" t="n">
         <v>12</v>
-      </c>
-      <c r="AE384" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AF384" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AG384" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AH384" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AI384" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AJ384" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AK384" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AL384" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM384" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN384" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="AO384" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AP384" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="AQ384" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AR384" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AS384" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AT384" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AU384" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV384" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW384" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX384" t="n">
-        <v>6</v>
       </c>
       <c r="AY384" t="n">
         <v>11</v>
       </c>
       <c r="AZ384" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="BA384" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB384" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BC384" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD384" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BE384" t="n">
         <v>7</v>
       </c>
-      <c r="BD384" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="BE384" t="n">
-        <v>7.5</v>
-      </c>
       <c r="BF384" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="BG384" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="BH384" t="n">
-        <v>3.2</v>
+        <v>2.62</v>
       </c>
       <c r="BI384" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="BJ384" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="BK384" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="BL384" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="BM384" t="n">
-        <v>2.23</v>
+        <v>2.8</v>
       </c>
       <c r="BN384" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="BO384" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="BP384" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="385">
@@ -84273,7 +84273,7 @@
         <v>384</v>
       </c>
       <c r="B385" t="n">
-        <v>8229622</v>
+        <v>8229772</v>
       </c>
       <c r="C385" t="inlineStr">
         <is>
@@ -84293,197 +84293,197 @@
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="I385" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J385" t="n">
         <v>0</v>
       </c>
       <c r="K385" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L385" t="n">
+        <v>1</v>
+      </c>
+      <c r="M385" t="n">
+        <v>0</v>
+      </c>
+      <c r="N385" t="n">
+        <v>1</v>
+      </c>
+      <c r="O385" t="inlineStr">
+        <is>
+          <t>['74']</t>
+        </is>
+      </c>
+      <c r="P385" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q385" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="R385" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S385" t="n">
         <v>3</v>
       </c>
-      <c r="M385" t="n">
-        <v>1</v>
-      </c>
-      <c r="N385" t="n">
+      <c r="T385" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="U385" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V385" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="W385" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X385" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y385" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z385" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA385" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB385" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AC385" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD385" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE385" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF385" t="n">
         <v>4</v>
       </c>
-      <c r="O385" t="inlineStr">
-        <is>
-          <t>['43', '84', '89']</t>
-        </is>
-      </c>
-      <c r="P385" t="inlineStr">
-        <is>
-          <t>['59']</t>
-        </is>
-      </c>
-      <c r="Q385" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="R385" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="S385" t="n">
+      <c r="AG385" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH385" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI385" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ385" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK385" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL385" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM385" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN385" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AO385" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AP385" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AQ385" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AR385" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AS385" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AT385" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AU385" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV385" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW385" t="n">
         <v>5</v>
       </c>
-      <c r="T385" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="U385" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="V385" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="W385" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="X385" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Y385" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z385" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA385" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AB385" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AC385" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AD385" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE385" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF385" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AG385" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH385" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AI385" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AJ385" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AK385" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AL385" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM385" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AN385" t="n">
+      <c r="AX385" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY385" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ385" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA385" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB385" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC385" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD385" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BE385" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="BF385" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BG385" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH385" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI385" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BJ385" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BK385" t="n">
         <v>1.91</v>
       </c>
-      <c r="AO385" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="AP385" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ385" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="AR385" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AS385" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AT385" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AU385" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV385" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW385" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX385" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY385" t="n">
-        <v>29</v>
-      </c>
-      <c r="AZ385" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA385" t="n">
-        <v>13</v>
-      </c>
-      <c r="BB385" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC385" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD385" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BE385" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="BF385" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BG385" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BH385" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BI385" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BJ385" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BK385" t="n">
-        <v>2</v>
-      </c>
       <c r="BL385" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="BM385" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="BN385" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="BO385" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="BP385" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="386">
@@ -84491,7 +84491,7 @@
         <v>385</v>
       </c>
       <c r="B386" t="n">
-        <v>8229438</v>
+        <v>8229372</v>
       </c>
       <c r="C386" t="inlineStr">
         <is>
@@ -84511,197 +84511,197 @@
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="I386" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J386" t="n">
         <v>0</v>
       </c>
       <c r="K386" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L386" t="n">
+        <v>1</v>
+      </c>
+      <c r="M386" t="n">
+        <v>0</v>
+      </c>
+      <c r="N386" t="n">
+        <v>1</v>
+      </c>
+      <c r="O386" t="inlineStr">
+        <is>
+          <t>['73']</t>
+        </is>
+      </c>
+      <c r="P386" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q386" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R386" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S386" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T386" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U386" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="V386" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="W386" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X386" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y386" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z386" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA386" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="AB386" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AC386" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD386" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE386" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF386" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="AG386" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AH386" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AI386" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ386" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AK386" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL386" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM386" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN386" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AO386" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AP386" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AQ386" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AR386" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AS386" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AT386" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AU386" t="n">
         <v>3</v>
       </c>
-      <c r="M386" t="n">
-        <v>2</v>
-      </c>
-      <c r="N386" t="n">
+      <c r="AV386" t="n">
         <v>5</v>
       </c>
-      <c r="O386" t="inlineStr">
-        <is>
-          <t>['16', '67', '87']</t>
-        </is>
-      </c>
-      <c r="P386" t="inlineStr">
-        <is>
-          <t>['47', '59']</t>
-        </is>
-      </c>
-      <c r="Q386" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="R386" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="S386" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="T386" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="U386" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="V386" t="n">
-        <v>2</v>
-      </c>
-      <c r="W386" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="X386" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Y386" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z386" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA386" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AB386" t="n">
-        <v>4.59</v>
-      </c>
-      <c r="AC386" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AD386" t="n">
-        <v>10</v>
-      </c>
-      <c r="AE386" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF386" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG386" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH386" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AI386" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AJ386" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AK386" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AL386" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM386" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AN386" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AO386" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="AP386" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AQ386" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="AR386" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AS386" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AT386" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AU386" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV386" t="n">
-        <v>3</v>
-      </c>
       <c r="AW386" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="AX386" t="n">
         <v>10</v>
       </c>
       <c r="AY386" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AZ386" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BA386" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BB386" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="BC386" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BD386" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BE386" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF386" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BG386" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH386" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BI386" t="n">
         <v>1.5</v>
       </c>
-      <c r="BE386" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF386" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BG386" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BH386" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BI386" t="n">
-        <v>1.47</v>
-      </c>
       <c r="BJ386" t="n">
-        <v>2.58</v>
+        <v>2.35</v>
       </c>
       <c r="BK386" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="BL386" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="BM386" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="BN386" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="BO386" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="BP386" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="387">
@@ -84927,7 +84927,7 @@
         <v>387</v>
       </c>
       <c r="B388" t="n">
-        <v>8229372</v>
+        <v>8229438</v>
       </c>
       <c r="C388" t="inlineStr">
         <is>
@@ -84947,197 +84947,197 @@
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="I388" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J388" t="n">
         <v>0</v>
       </c>
       <c r="K388" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L388" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M388" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N388" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O388" t="inlineStr">
         <is>
-          <t>['73']</t>
+          <t>['16', '67', '87']</t>
         </is>
       </c>
       <c r="P388" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['47', '59']</t>
         </is>
       </c>
       <c r="Q388" t="n">
-        <v>2.65</v>
+        <v>1.83</v>
       </c>
       <c r="R388" t="n">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="S388" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="T388" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="U388" t="n">
-        <v>3.08</v>
+        <v>3.8</v>
       </c>
       <c r="V388" t="n">
-        <v>2.42</v>
+        <v>2</v>
       </c>
       <c r="W388" t="n">
-        <v>1.47</v>
+        <v>1.7</v>
       </c>
       <c r="X388" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y388" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z388" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA388" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AB388" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="AC388" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD388" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE388" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF388" t="n">
         <v>6</v>
       </c>
-      <c r="Y388" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z388" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA388" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="AB388" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AC388" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AD388" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE388" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AF388" t="n">
-        <v>4.31</v>
-      </c>
       <c r="AG388" t="n">
-        <v>1.78</v>
+        <v>1.36</v>
       </c>
       <c r="AH388" t="n">
-        <v>2.12</v>
+        <v>3.2</v>
       </c>
       <c r="AI388" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AJ388" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AK388" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AL388" t="n">
         <v>0</v>
       </c>
       <c r="AM388" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="AN388" t="n">
-        <v>1.62</v>
+        <v>1.17</v>
       </c>
       <c r="AO388" t="n">
-        <v>1.23</v>
+        <v>0.42</v>
       </c>
       <c r="AP388" t="n">
-        <v>1.71</v>
+        <v>1.31</v>
       </c>
       <c r="AQ388" t="n">
-        <v>1.14</v>
+        <v>0.36</v>
       </c>
       <c r="AR388" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AS388" t="n">
-        <v>1.5</v>
+        <v>1.09</v>
       </c>
       <c r="AT388" t="n">
-        <v>3.08</v>
+        <v>2.63</v>
       </c>
       <c r="AU388" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV388" t="n">
         <v>3</v>
       </c>
-      <c r="AV388" t="n">
-        <v>5</v>
-      </c>
       <c r="AW388" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AX388" t="n">
         <v>10</v>
       </c>
       <c r="AY388" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="AZ388" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA388" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BB388" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC388" t="n">
         <v>8</v>
       </c>
-      <c r="BC388" t="n">
-        <v>11</v>
-      </c>
       <c r="BD388" t="n">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="BE388" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BF388" t="n">
-        <v>2.45</v>
+        <v>3.2</v>
       </c>
       <c r="BG388" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="BH388" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="BI388" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="BJ388" t="n">
-        <v>2.35</v>
+        <v>2.58</v>
       </c>
       <c r="BK388" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="BL388" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="BM388" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="BN388" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="BO388" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="BP388" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="389">
@@ -86453,7 +86453,7 @@
         <v>394</v>
       </c>
       <c r="B395" t="n">
-        <v>8229824</v>
+        <v>8229823</v>
       </c>
       <c r="C395" t="inlineStr">
         <is>
@@ -86473,197 +86473,197 @@
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="I395" t="n">
         <v>0</v>
       </c>
       <c r="J395" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K395" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L395" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M395" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N395" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O395" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['71']</t>
         </is>
       </c>
       <c r="P395" t="inlineStr">
         <is>
-          <t>['55']</t>
+          <t>['25', '39']</t>
         </is>
       </c>
       <c r="Q395" t="n">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="R395" t="n">
-        <v>2.46</v>
+        <v>2.7</v>
       </c>
       <c r="S395" t="n">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="T395" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="U395" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="V395" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="W395" t="n">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="X395" t="n">
-        <v>5.5</v>
+        <v>4.33</v>
       </c>
       <c r="Y395" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="Z395" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA395" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AB395" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AC395" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD395" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE395" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF395" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AG395" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AH395" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AI395" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ395" t="n">
         <v>2.25</v>
       </c>
-      <c r="AA395" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AB395" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AC395" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AD395" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AE395" t="n">
+      <c r="AK395" t="n">
         <v>1.2</v>
       </c>
-      <c r="AF395" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AG395" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AH395" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AI395" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AJ395" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AK395" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AL395" t="n">
         <v>0</v>
       </c>
       <c r="AM395" t="n">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="AN395" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AO395" t="n">
-        <v>1.08</v>
+        <v>1.31</v>
       </c>
       <c r="AP395" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AQ395" t="n">
-        <v>1.21</v>
+        <v>1.43</v>
       </c>
       <c r="AR395" t="n">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="AS395" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AT395" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="AU395" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV395" t="n">
         <v>4</v>
       </c>
       <c r="AW395" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="AX395" t="n">
         <v>6</v>
       </c>
       <c r="AY395" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="AZ395" t="n">
         <v>10</v>
       </c>
       <c r="BA395" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BB395" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC395" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BD395" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="BE395" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="BF395" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="BG395" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BH395" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI395" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BJ395" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BK395" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BL395" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM395" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BN395" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BO395" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP395" t="n">
         <v>1.3</v>
-      </c>
-      <c r="BH395" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BI395" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BJ395" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BK395" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BL395" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BM395" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="BN395" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="BO395" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BP395" t="n">
-        <v>1.22</v>
       </c>
     </row>
     <row r="396">
@@ -86671,7 +86671,7 @@
         <v>395</v>
       </c>
       <c r="B396" t="n">
-        <v>8229823</v>
+        <v>8229824</v>
       </c>
       <c r="C396" t="inlineStr">
         <is>
@@ -86691,197 +86691,197 @@
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="I396" t="n">
         <v>0</v>
       </c>
       <c r="J396" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K396" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L396" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M396" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N396" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O396" t="inlineStr">
         <is>
-          <t>['71']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P396" t="inlineStr">
         <is>
-          <t>['25', '39']</t>
+          <t>['55']</t>
         </is>
       </c>
       <c r="Q396" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="R396" t="n">
-        <v>2.7</v>
+        <v>2.46</v>
       </c>
       <c r="S396" t="n">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="T396" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="U396" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V396" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W396" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X396" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y396" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z396" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA396" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB396" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AC396" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD396" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE396" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF396" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AG396" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AH396" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AI396" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AJ396" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AK396" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AL396" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM396" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AN396" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AO396" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AP396" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AQ396" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AR396" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AS396" t="n">
         <v>1.25</v>
       </c>
-      <c r="U396" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="V396" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="W396" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="X396" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="Y396" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z396" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA396" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AB396" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AC396" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AD396" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE396" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF396" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AG396" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AH396" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AI396" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AJ396" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AK396" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AL396" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM396" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AN396" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO396" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AP396" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AQ396" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AR396" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AS396" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AT396" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="AU396" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV396" t="n">
         <v>4</v>
       </c>
       <c r="AW396" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="AX396" t="n">
         <v>6</v>
       </c>
       <c r="AY396" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="AZ396" t="n">
         <v>10</v>
       </c>
       <c r="BA396" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BB396" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC396" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BD396" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="BE396" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="BF396" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="BG396" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="BH396" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="BI396" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="BJ396" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="BK396" t="n">
-        <v>2.11</v>
+        <v>2.02</v>
       </c>
       <c r="BL396" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="BM396" t="n">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="BN396" t="n">
-        <v>1.54</v>
+        <v>1.39</v>
       </c>
       <c r="BO396" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="BP396" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="397">
@@ -87543,7 +87543,7 @@
         <v>399</v>
       </c>
       <c r="B400" t="n">
-        <v>8229829</v>
+        <v>8229832</v>
       </c>
       <c r="C400" t="inlineStr">
         <is>
@@ -87563,197 +87563,197 @@
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="I400" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J400" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K400" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L400" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M400" t="n">
         <v>1</v>
       </c>
       <c r="N400" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O400" t="inlineStr">
         <is>
-          <t>['2', '17', '40', '43', '90+4']</t>
+          <t>['13']</t>
         </is>
       </c>
       <c r="P400" t="inlineStr">
         <is>
-          <t>['76']</t>
+          <t>['6']</t>
         </is>
       </c>
       <c r="Q400" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R400" t="n">
         <v>2.3</v>
       </c>
-      <c r="R400" t="n">
-        <v>2.38</v>
-      </c>
       <c r="S400" t="n">
-        <v>3.9</v>
+        <v>2.3</v>
       </c>
       <c r="T400" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="U400" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="V400" t="n">
         <v>2.4</v>
       </c>
       <c r="W400" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="X400" t="n">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="Y400" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z400" t="n">
-        <v>1.71</v>
+        <v>4</v>
       </c>
       <c r="AA400" t="n">
         <v>3.8</v>
       </c>
       <c r="AB400" t="n">
-        <v>4.2</v>
+        <v>1.8</v>
       </c>
       <c r="AC400" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AD400" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AE400" t="n">
         <v>1.22</v>
       </c>
       <c r="AF400" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="AG400" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AH400" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="AI400" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AJ400" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AK400" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL400" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM400" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN400" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AO400" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AP400" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AQ400" t="n">
         <v>1.25</v>
       </c>
-      <c r="AL400" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM400" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AN400" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AO400" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AP400" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AQ400" t="n">
-        <v>1.64</v>
-      </c>
       <c r="AR400" t="n">
-        <v>1.73</v>
+        <v>1.22</v>
       </c>
       <c r="AS400" t="n">
-        <v>1.51</v>
+        <v>1.37</v>
       </c>
       <c r="AT400" t="n">
-        <v>3.24</v>
+        <v>2.59</v>
       </c>
       <c r="AU400" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AV400" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AW400" t="n">
         <v>8</v>
       </c>
       <c r="AX400" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AY400" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="AZ400" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA400" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB400" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC400" t="n">
         <v>12</v>
       </c>
-      <c r="BA400" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB400" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC400" t="n">
-        <v>9</v>
-      </c>
       <c r="BD400" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="BE400" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BF400" t="n">
-        <v>3.35</v>
+        <v>1.66</v>
       </c>
       <c r="BG400" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="BH400" t="n">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="BI400" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="BJ400" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="BK400" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="BL400" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="BM400" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="BN400" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="BO400" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="BP400" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="401">
@@ -87761,7 +87761,7 @@
         <v>400</v>
       </c>
       <c r="B401" t="n">
-        <v>8229834</v>
+        <v>8229829</v>
       </c>
       <c r="C401" t="inlineStr">
         <is>
@@ -87781,197 +87781,197 @@
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="I401" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J401" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K401" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L401" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M401" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N401" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O401" t="inlineStr">
         <is>
-          <t>['72']</t>
+          <t>['2', '17', '40', '43', '90+4']</t>
         </is>
       </c>
       <c r="P401" t="inlineStr">
         <is>
-          <t>['28', '64']</t>
+          <t>['76']</t>
         </is>
       </c>
       <c r="Q401" t="n">
-        <v>2.61</v>
+        <v>2.3</v>
       </c>
       <c r="R401" t="n">
-        <v>2.53</v>
+        <v>2.38</v>
       </c>
       <c r="S401" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="T401" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="U401" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="V401" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="W401" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X401" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Y401" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z401" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AA401" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB401" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AC401" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD401" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE401" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF401" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AG401" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH401" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AI401" t="n">
         <v>1.57</v>
       </c>
-      <c r="X401" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="Y401" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z401" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AA401" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AB401" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AC401" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AD401" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE401" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF401" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AG401" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AH401" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AI401" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AJ401" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AK401" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AL401" t="n">
         <v>0</v>
       </c>
       <c r="AM401" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="AN401" t="n">
-        <v>1.08</v>
+        <v>2.31</v>
       </c>
       <c r="AO401" t="n">
-        <v>1.08</v>
+        <v>1.77</v>
       </c>
       <c r="AP401" t="n">
-        <v>1</v>
+        <v>2.36</v>
       </c>
       <c r="AQ401" t="n">
-        <v>1.21</v>
+        <v>1.64</v>
       </c>
       <c r="AR401" t="n">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="AS401" t="n">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="AT401" t="n">
-        <v>3.17</v>
+        <v>3.24</v>
       </c>
       <c r="AU401" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AV401" t="n">
         <v>4</v>
       </c>
       <c r="AW401" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX401" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AY401" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AZ401" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BA401" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB401" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC401" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD401" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BE401" t="n">
         <v>8</v>
       </c>
-      <c r="BB401" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC401" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD401" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="BE401" t="n">
-        <v>8.5</v>
-      </c>
       <c r="BF401" t="n">
-        <v>2.55</v>
+        <v>3.35</v>
       </c>
       <c r="BG401" t="n">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="BH401" t="n">
-        <v>3.7</v>
+        <v>2.87</v>
       </c>
       <c r="BI401" t="n">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="BJ401" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="BK401" t="n">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="BL401" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="BM401" t="n">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="BN401" t="n">
-        <v>1.51</v>
+        <v>1.34</v>
       </c>
       <c r="BO401" t="n">
         <v>3.1</v>
       </c>
       <c r="BP401" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="402">
@@ -87979,7 +87979,7 @@
         <v>401</v>
       </c>
       <c r="B402" t="n">
-        <v>8229832</v>
+        <v>8229834</v>
       </c>
       <c r="C402" t="inlineStr">
         <is>
@@ -87999,101 +87999,101 @@
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="I402" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J402" t="n">
         <v>1</v>
       </c>
       <c r="K402" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L402" t="n">
         <v>1</v>
       </c>
       <c r="M402" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N402" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O402" t="inlineStr">
         <is>
-          <t>['13']</t>
+          <t>['72']</t>
         </is>
       </c>
       <c r="P402" t="inlineStr">
         <is>
-          <t>['6']</t>
+          <t>['28', '64']</t>
         </is>
       </c>
       <c r="Q402" t="n">
-        <v>3.75</v>
+        <v>2.61</v>
       </c>
       <c r="R402" t="n">
-        <v>2.3</v>
+        <v>2.53</v>
       </c>
       <c r="S402" t="n">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="T402" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="U402" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="V402" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="W402" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="X402" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="Y402" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z402" t="n">
-        <v>4</v>
+        <v>2.08</v>
       </c>
       <c r="AA402" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AB402" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="AC402" t="n">
         <v>1.02</v>
       </c>
       <c r="AD402" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AE402" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AF402" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="AG402" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="AH402" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AI402" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AJ402" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AK402" t="n">
         <v>1.29</v>
@@ -88102,94 +88102,94 @@
         <v>0</v>
       </c>
       <c r="AM402" t="n">
-        <v>1.3</v>
+        <v>1.78</v>
       </c>
       <c r="AN402" t="n">
-        <v>0.85</v>
+        <v>1.08</v>
       </c>
       <c r="AO402" t="n">
-        <v>1.27</v>
+        <v>1.08</v>
       </c>
       <c r="AP402" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AQ402" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AR402" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AS402" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AT402" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="AU402" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV402" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW402" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX402" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY402" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ402" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA402" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB402" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC402" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD402" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BE402" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF402" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BG402" t="n">
         <v>1.22</v>
       </c>
-      <c r="AS402" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AT402" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AU402" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV402" t="n">
-        <v>7</v>
-      </c>
-      <c r="AW402" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX402" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY402" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ402" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA402" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB402" t="n">
-        <v>11</v>
-      </c>
-      <c r="BC402" t="n">
-        <v>12</v>
-      </c>
-      <c r="BD402" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BE402" t="n">
-        <v>6</v>
-      </c>
-      <c r="BF402" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="BG402" t="n">
-        <v>1.36</v>
-      </c>
       <c r="BH402" t="n">
-        <v>2.75</v>
+        <v>3.7</v>
       </c>
       <c r="BI402" t="n">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="BJ402" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="BK402" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="BL402" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="BM402" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="BN402" t="n">
-        <v>1.32</v>
+        <v>1.51</v>
       </c>
       <c r="BO402" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="BP402" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="403">

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
@@ -14463,10 +14463,10 @@
         <v>1</v>
       </c>
       <c r="BB64" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC64" t="n">
         <v>11</v>
-      </c>
-      <c r="BC64" t="n">
-        <v>12</v>
       </c>
       <c r="BD64" t="n">
         <v>1.55</v>
@@ -23401,10 +23401,10 @@
         <v>10</v>
       </c>
       <c r="BB105" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC105" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD105" t="n">
         <v>1.5</v>
@@ -27758,13 +27758,13 @@
         <v>12</v>
       </c>
       <c r="BA125" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB125" t="n">
         <v>7</v>
       </c>
       <c r="BC125" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD125" t="n">
         <v>1.44</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP409"/>
+  <dimension ref="A1:BP414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ3" t="n">
         <v>0.5</v>
@@ -2004,7 +2004,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -4835,10 +4835,10 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR20" t="n">
         <v>0</v>
@@ -5053,7 +5053,7 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AQ21" t="n">
         <v>1.21</v>
@@ -5492,7 +5492,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR23" t="n">
         <v>0</v>
@@ -5710,7 +5710,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR24" t="n">
         <v>0</v>
@@ -7887,7 +7887,7 @@
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ34" t="n">
         <v>1.64</v>
@@ -8105,7 +8105,7 @@
         <v>0.5</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ35" t="n">
         <v>1</v>
@@ -8541,10 +8541,10 @@
         <v>3</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR37" t="n">
         <v>0.59</v>
@@ -9634,7 +9634,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR42" t="n">
         <v>1.79</v>
@@ -10288,7 +10288,7 @@
         <v>2</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR45" t="n">
         <v>1.61</v>
@@ -10721,7 +10721,7 @@
         <v>1.5</v>
       </c>
       <c r="AP47" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AQ47" t="n">
         <v>1.57</v>
@@ -10939,7 +10939,7 @@
         <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AQ48" t="n">
         <v>1.64</v>
@@ -11593,7 +11593,7 @@
         <v>1</v>
       </c>
       <c r="AP51" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ51" t="n">
         <v>1.43</v>
@@ -11814,7 +11814,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ52" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR52" t="n">
         <v>1.13</v>
@@ -13122,7 +13122,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ58" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR58" t="n">
         <v>1.41</v>
@@ -13991,7 +13991,7 @@
         <v>0</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ62" t="n">
         <v>0.38</v>
@@ -14430,7 +14430,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ64" t="n">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR64" t="n">
         <v>1.64</v>
@@ -14863,7 +14863,7 @@
         <v>0.33</v>
       </c>
       <c r="AP66" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AQ66" t="n">
         <v>1</v>
@@ -15520,7 +15520,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ69" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR69" t="n">
         <v>2.09</v>
@@ -17043,7 +17043,7 @@
         <v>3</v>
       </c>
       <c r="AP76" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AQ76" t="n">
         <v>1.57</v>
@@ -17261,7 +17261,7 @@
         <v>0.5</v>
       </c>
       <c r="AP77" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ77" t="n">
         <v>0.5</v>
@@ -17482,7 +17482,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ78" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR78" t="n">
         <v>1.39</v>
@@ -17700,7 +17700,7 @@
         <v>2</v>
       </c>
       <c r="AQ79" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR79" t="n">
         <v>1.08</v>
@@ -18136,7 +18136,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR81" t="n">
         <v>1.35</v>
@@ -18354,7 +18354,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ82" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR82" t="n">
         <v>1.22</v>
@@ -20749,7 +20749,7 @@
         <v>2.25</v>
       </c>
       <c r="AP93" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AQ93" t="n">
         <v>1.57</v>
@@ -20967,7 +20967,7 @@
         <v>0.5</v>
       </c>
       <c r="AP94" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ94" t="n">
         <v>1.43</v>
@@ -21188,7 +21188,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ95" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR95" t="n">
         <v>1.81</v>
@@ -22929,7 +22929,7 @@
         <v>1.33</v>
       </c>
       <c r="AP103" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ103" t="n">
         <v>1.86</v>
@@ -23150,7 +23150,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ104" t="n">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR104" t="n">
         <v>1.9</v>
@@ -23583,7 +23583,7 @@
         <v>1.75</v>
       </c>
       <c r="AP106" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AQ106" t="n">
         <v>1.86</v>
@@ -24237,10 +24237,10 @@
         <v>2</v>
       </c>
       <c r="AP109" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ109" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR109" t="n">
         <v>1.99</v>
@@ -24458,7 +24458,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ110" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR110" t="n">
         <v>0</v>
@@ -26638,7 +26638,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ120" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR120" t="n">
         <v>1.69</v>
@@ -27943,10 +27943,10 @@
         <v>0.33</v>
       </c>
       <c r="AP126" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AQ126" t="n">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR126" t="n">
         <v>1.45</v>
@@ -28161,7 +28161,7 @@
         <v>0.5</v>
       </c>
       <c r="AP127" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ127" t="n">
         <v>1.21</v>
@@ -30123,7 +30123,7 @@
         <v>0.75</v>
       </c>
       <c r="AP136" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ136" t="n">
         <v>0.79</v>
@@ -30341,7 +30341,7 @@
         <v>0.4</v>
       </c>
       <c r="AP137" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AQ137" t="n">
         <v>1.21</v>
@@ -30559,10 +30559,10 @@
         <v>0.29</v>
       </c>
       <c r="AP138" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AQ138" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR138" t="n">
         <v>1.34</v>
@@ -30780,7 +30780,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ139" t="n">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR139" t="n">
         <v>1.67</v>
@@ -33611,7 +33611,7 @@
         <v>1.4</v>
       </c>
       <c r="AP152" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AQ152" t="n">
         <v>1.43</v>
@@ -33832,7 +33832,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ153" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR153" t="n">
         <v>1.64</v>
@@ -34050,7 +34050,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ154" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR154" t="n">
         <v>1.63</v>
@@ -36227,7 +36227,7 @@
         <v>1.8</v>
       </c>
       <c r="AP164" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ164" t="n">
         <v>1.93</v>
@@ -36881,10 +36881,10 @@
         <v>0.8</v>
       </c>
       <c r="AP167" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AQ167" t="n">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR167" t="n">
         <v>1.16</v>
@@ -37535,7 +37535,7 @@
         <v>0.33</v>
       </c>
       <c r="AP170" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AQ170" t="n">
         <v>0.36</v>
@@ -37753,10 +37753,10 @@
         <v>0.25</v>
       </c>
       <c r="AP171" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ171" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR171" t="n">
         <v>1.83</v>
@@ -37971,7 +37971,7 @@
         <v>1.2</v>
       </c>
       <c r="AP172" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ172" t="n">
         <v>1.23</v>
@@ -38192,7 +38192,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ173" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR173" t="n">
         <v>1.67</v>
@@ -38410,7 +38410,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ174" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR174" t="n">
         <v>2.08</v>
@@ -40154,7 +40154,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ182" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR182" t="n">
         <v>1.41</v>
@@ -40372,7 +40372,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ183" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR183" t="n">
         <v>1.81</v>
@@ -40805,7 +40805,7 @@
         <v>1.5</v>
       </c>
       <c r="AP185" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AQ185" t="n">
         <v>1.93</v>
@@ -42985,7 +42985,7 @@
         <v>0.33</v>
       </c>
       <c r="AP195" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ195" t="n">
         <v>0.5</v>
@@ -43639,7 +43639,7 @@
         <v>1.2</v>
       </c>
       <c r="AP198" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ198" t="n">
         <v>1.21</v>
@@ -43860,7 +43860,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ199" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR199" t="n">
         <v>1.42</v>
@@ -44296,7 +44296,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ201" t="n">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR201" t="n">
         <v>1.97</v>
@@ -46473,7 +46473,7 @@
         <v>0.8</v>
       </c>
       <c r="AP211" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AQ211" t="n">
         <v>1.21</v>
@@ -46694,7 +46694,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ212" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR212" t="n">
         <v>1.48</v>
@@ -48871,7 +48871,7 @@
         <v>1.71</v>
       </c>
       <c r="AP222" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ222" t="n">
         <v>1.57</v>
@@ -49525,7 +49525,7 @@
         <v>1.5</v>
       </c>
       <c r="AP225" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ225" t="n">
         <v>1.38</v>
@@ -49743,10 +49743,10 @@
         <v>0.57</v>
       </c>
       <c r="AP226" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AQ226" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR226" t="n">
         <v>1.45</v>
@@ -49964,7 +49964,7 @@
         <v>2</v>
       </c>
       <c r="AQ227" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR227" t="n">
         <v>1.44</v>
@@ -50179,10 +50179,10 @@
         <v>2</v>
       </c>
       <c r="AP228" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AQ228" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR228" t="n">
         <v>1.25</v>
@@ -50397,7 +50397,7 @@
         <v>1</v>
       </c>
       <c r="AP229" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ229" t="n">
         <v>1.15</v>
@@ -52580,7 +52580,7 @@
         <v>2</v>
       </c>
       <c r="AQ239" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR239" t="n">
         <v>1.41</v>
@@ -52795,10 +52795,10 @@
         <v>0.5</v>
       </c>
       <c r="AP240" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AQ240" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR240" t="n">
         <v>1.21</v>
@@ -53231,10 +53231,10 @@
         <v>0.71</v>
       </c>
       <c r="AP242" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ242" t="n">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR242" t="n">
         <v>1.63</v>
@@ -53667,7 +53667,7 @@
         <v>0.33</v>
       </c>
       <c r="AP244" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AQ244" t="n">
         <v>0.38</v>
@@ -54106,7 +54106,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ246" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR246" t="n">
         <v>1.02</v>
@@ -56065,7 +56065,7 @@
         <v>0.29</v>
       </c>
       <c r="AP255" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ255" t="n">
         <v>0.38</v>
@@ -56940,7 +56940,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ259" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR259" t="n">
         <v>1.7</v>
@@ -57155,7 +57155,7 @@
         <v>1.44</v>
       </c>
       <c r="AP260" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ260" t="n">
         <v>1.93</v>
@@ -58248,7 +58248,7 @@
         <v>1</v>
       </c>
       <c r="AQ265" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR265" t="n">
         <v>1.57</v>
@@ -58466,7 +58466,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ266" t="n">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR266" t="n">
         <v>1.34</v>
@@ -58899,7 +58899,7 @@
         <v>1.38</v>
       </c>
       <c r="AP268" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ268" t="n">
         <v>1.21</v>
@@ -59117,7 +59117,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP269" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AQ269" t="n">
         <v>0.5</v>
@@ -60210,7 +60210,7 @@
         <v>1</v>
       </c>
       <c r="AQ274" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR274" t="n">
         <v>1.38</v>
@@ -60646,7 +60646,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ276" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR276" t="n">
         <v>1.59</v>
@@ -61515,7 +61515,7 @@
         <v>1.67</v>
       </c>
       <c r="AP280" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AQ280" t="n">
         <v>1.86</v>
@@ -61733,7 +61733,7 @@
         <v>1.38</v>
       </c>
       <c r="AP281" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AQ281" t="n">
         <v>1.15</v>
@@ -62169,7 +62169,7 @@
         <v>1</v>
       </c>
       <c r="AP283" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ283" t="n">
         <v>0.93</v>
@@ -63044,7 +63044,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ287" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR287" t="n">
         <v>1.56</v>
@@ -63916,7 +63916,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ291" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR291" t="n">
         <v>1.67</v>
@@ -64349,7 +64349,7 @@
         <v>1.14</v>
       </c>
       <c r="AP293" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ293" t="n">
         <v>1</v>
@@ -65657,7 +65657,7 @@
         <v>1.8</v>
       </c>
       <c r="AP299" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ299" t="n">
         <v>1.57</v>
@@ -66096,7 +66096,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ301" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR301" t="n">
         <v>1.87</v>
@@ -67186,7 +67186,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ306" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR306" t="n">
         <v>1.74</v>
@@ -67401,7 +67401,7 @@
         <v>1.88</v>
       </c>
       <c r="AP307" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ307" t="n">
         <v>1.69</v>
@@ -68055,7 +68055,7 @@
         <v>0.3</v>
       </c>
       <c r="AP310" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AQ310" t="n">
         <v>0.38</v>
@@ -68494,7 +68494,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ312" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR312" t="n">
         <v>1.71</v>
@@ -69799,10 +69799,10 @@
         <v>1.44</v>
       </c>
       <c r="AP318" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ318" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR318" t="n">
         <v>1.51</v>
@@ -70674,7 +70674,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ322" t="n">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR322" t="n">
         <v>1.41</v>
@@ -71110,7 +71110,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ324" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR324" t="n">
         <v>1.7</v>
@@ -71325,7 +71325,7 @@
         <v>1.42</v>
       </c>
       <c r="AP325" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AQ325" t="n">
         <v>1.43</v>
@@ -71546,7 +71546,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ326" t="n">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR326" t="n">
         <v>1.42</v>
@@ -71979,7 +71979,7 @@
         <v>2</v>
       </c>
       <c r="AP328" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ328" t="n">
         <v>1.69</v>
@@ -72418,7 +72418,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ330" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR330" t="n">
         <v>1.82</v>
@@ -74159,7 +74159,7 @@
         <v>1.55</v>
       </c>
       <c r="AP338" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ338" t="n">
         <v>1.64</v>
@@ -74380,7 +74380,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ339" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR339" t="n">
         <v>1.35</v>
@@ -74598,7 +74598,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ340" t="n">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR340" t="n">
         <v>1.6</v>
@@ -75031,7 +75031,7 @@
         <v>1.8</v>
       </c>
       <c r="AP342" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AQ342" t="n">
         <v>1.69</v>
@@ -75906,7 +75906,7 @@
         <v>1</v>
       </c>
       <c r="AQ346" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR346" t="n">
         <v>1.55</v>
@@ -77211,10 +77211,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AP352" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ352" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR352" t="n">
         <v>1.21</v>
@@ -80263,10 +80263,10 @@
         <v>0.67</v>
       </c>
       <c r="AP366" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ366" t="n">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR366" t="n">
         <v>1.26</v>
@@ -82225,10 +82225,10 @@
         <v>0.77</v>
       </c>
       <c r="AP375" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ375" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR375" t="n">
         <v>1.48</v>
@@ -82443,7 +82443,7 @@
         <v>1</v>
       </c>
       <c r="AP376" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AQ376" t="n">
         <v>0.86</v>
@@ -83318,7 +83318,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ380" t="n">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR380" t="n">
         <v>1.28</v>
@@ -83751,10 +83751,10 @@
         <v>1.45</v>
       </c>
       <c r="AP382" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AQ382" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR382" t="n">
         <v>1.17</v>
@@ -83969,7 +83969,7 @@
         <v>1.1</v>
       </c>
       <c r="AP383" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ383" t="n">
         <v>1.25</v>
@@ -84405,10 +84405,10 @@
         <v>1.67</v>
       </c>
       <c r="AP385" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AQ385" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR385" t="n">
         <v>1.45</v>
@@ -85931,7 +85931,7 @@
         <v>1.31</v>
       </c>
       <c r="AP392" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ392" t="n">
         <v>1.21</v>
@@ -86803,7 +86803,7 @@
         <v>1.08</v>
       </c>
       <c r="AP396" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ396" t="n">
         <v>1.21</v>
@@ -89716,6 +89716,1096 @@
       </c>
       <c r="BP409" t="n">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="1" t="n">
+        <v>409</v>
+      </c>
+      <c r="B410" t="n">
+        <v>8229806</v>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E410" s="2" t="n">
+        <v>45899.85416666666</v>
+      </c>
+      <c r="F410" t="n">
+        <v>0</v>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>Toronto</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>Montreal Impact</t>
+        </is>
+      </c>
+      <c r="I410" t="n">
+        <v>0</v>
+      </c>
+      <c r="J410" t="n">
+        <v>0</v>
+      </c>
+      <c r="K410" t="n">
+        <v>0</v>
+      </c>
+      <c r="L410" t="n">
+        <v>1</v>
+      </c>
+      <c r="M410" t="n">
+        <v>1</v>
+      </c>
+      <c r="N410" t="n">
+        <v>2</v>
+      </c>
+      <c r="O410" t="inlineStr">
+        <is>
+          <t>['88']</t>
+        </is>
+      </c>
+      <c r="P410" t="inlineStr">
+        <is>
+          <t>['83']</t>
+        </is>
+      </c>
+      <c r="Q410" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R410" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S410" t="n">
+        <v>4</v>
+      </c>
+      <c r="T410" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U410" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V410" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="W410" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X410" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Y410" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z410" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA410" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB410" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AC410" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD410" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE410" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AF410" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="AG410" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH410" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AI410" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AJ410" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AK410" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL410" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM410" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AN410" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AO410" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AP410" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AQ410" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AR410" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AS410" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AT410" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AU410" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV410" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW410" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX410" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY410" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ410" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA410" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB410" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC410" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD410" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BE410" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF410" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BG410" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BH410" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BI410" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BJ410" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BK410" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BL410" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BM410" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BN410" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BO410" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BP410" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="1" t="n">
+        <v>410</v>
+      </c>
+      <c r="B411" t="n">
+        <v>8229816</v>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E411" s="2" t="n">
+        <v>45899.85416666666</v>
+      </c>
+      <c r="F411" t="n">
+        <v>0</v>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>New York RB</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>Columbus Crew</t>
+        </is>
+      </c>
+      <c r="I411" t="n">
+        <v>0</v>
+      </c>
+      <c r="J411" t="n">
+        <v>0</v>
+      </c>
+      <c r="K411" t="n">
+        <v>0</v>
+      </c>
+      <c r="L411" t="n">
+        <v>0</v>
+      </c>
+      <c r="M411" t="n">
+        <v>0</v>
+      </c>
+      <c r="N411" t="n">
+        <v>0</v>
+      </c>
+      <c r="O411" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P411" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q411" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R411" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S411" t="n">
+        <v>3</v>
+      </c>
+      <c r="T411" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="U411" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V411" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="W411" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X411" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="Y411" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z411" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA411" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB411" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AC411" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD411" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE411" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF411" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AG411" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH411" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AI411" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AJ411" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AK411" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL411" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM411" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN411" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AO411" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AP411" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AQ411" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR411" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AS411" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AT411" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU411" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV411" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW411" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX411" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY411" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ411" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA411" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB411" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC411" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD411" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BE411" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="BF411" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BG411" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BH411" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BI411" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BJ411" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BK411" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BL411" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BM411" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="BN411" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BO411" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BP411" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="1" t="n">
+        <v>411</v>
+      </c>
+      <c r="B412" t="n">
+        <v>8229821</v>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E412" s="2" t="n">
+        <v>45899.85416666666</v>
+      </c>
+      <c r="F412" t="n">
+        <v>0</v>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>FC Cincinnati</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>Philadelphia Union</t>
+        </is>
+      </c>
+      <c r="I412" t="n">
+        <v>0</v>
+      </c>
+      <c r="J412" t="n">
+        <v>0</v>
+      </c>
+      <c r="K412" t="n">
+        <v>0</v>
+      </c>
+      <c r="L412" t="n">
+        <v>0</v>
+      </c>
+      <c r="M412" t="n">
+        <v>1</v>
+      </c>
+      <c r="N412" t="n">
+        <v>1</v>
+      </c>
+      <c r="O412" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P412" t="inlineStr">
+        <is>
+          <t>['49']</t>
+        </is>
+      </c>
+      <c r="Q412" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R412" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="S412" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T412" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U412" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="V412" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="W412" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X412" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="Y412" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z412" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA412" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB412" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC412" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD412" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE412" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF412" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="AG412" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH412" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AI412" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AJ412" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AK412" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL412" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM412" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN412" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AO412" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AP412" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AQ412" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AR412" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS412" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AT412" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AU412" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV412" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW412" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX412" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY412" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ412" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA412" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB412" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC412" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD412" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BE412" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF412" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BG412" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BH412" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BI412" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BJ412" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BK412" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BL412" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BM412" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BN412" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BO412" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BP412" t="n">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="1" t="n">
+        <v>412</v>
+      </c>
+      <c r="B413" t="n">
+        <v>8229818</v>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E413" s="2" t="n">
+        <v>45899.85416666666</v>
+      </c>
+      <c r="F413" t="n">
+        <v>0</v>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>New England Revolution</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="I413" t="n">
+        <v>1</v>
+      </c>
+      <c r="J413" t="n">
+        <v>1</v>
+      </c>
+      <c r="K413" t="n">
+        <v>2</v>
+      </c>
+      <c r="L413" t="n">
+        <v>1</v>
+      </c>
+      <c r="M413" t="n">
+        <v>2</v>
+      </c>
+      <c r="N413" t="n">
+        <v>3</v>
+      </c>
+      <c r="O413" t="inlineStr">
+        <is>
+          <t>['24']</t>
+        </is>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>['12', '87']</t>
+        </is>
+      </c>
+      <c r="Q413" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="R413" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="S413" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="T413" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U413" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V413" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="W413" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X413" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y413" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z413" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AA413" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB413" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC413" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD413" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE413" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF413" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="AG413" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AH413" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AI413" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ413" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AK413" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL413" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM413" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AN413" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AO413" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AP413" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AQ413" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AR413" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AS413" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AT413" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AU413" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV413" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW413" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX413" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY413" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ413" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA413" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB413" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC413" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD413" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BE413" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF413" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BG413" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH413" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BI413" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BJ413" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BK413" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BL413" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BM413" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BN413" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BO413" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="BP413" t="n">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="1" t="n">
+        <v>413</v>
+      </c>
+      <c r="B414" t="n">
+        <v>8229819</v>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E414" s="2" t="n">
+        <v>45899.85416666666</v>
+      </c>
+      <c r="F414" t="n">
+        <v>0</v>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>DC United</t>
+        </is>
+      </c>
+      <c r="I414" t="n">
+        <v>1</v>
+      </c>
+      <c r="J414" t="n">
+        <v>1</v>
+      </c>
+      <c r="K414" t="n">
+        <v>2</v>
+      </c>
+      <c r="L414" t="n">
+        <v>1</v>
+      </c>
+      <c r="M414" t="n">
+        <v>2</v>
+      </c>
+      <c r="N414" t="n">
+        <v>3</v>
+      </c>
+      <c r="O414" t="inlineStr">
+        <is>
+          <t>['19']</t>
+        </is>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>['43', '77']</t>
+        </is>
+      </c>
+      <c r="Q414" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="R414" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="S414" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="T414" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U414" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V414" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W414" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X414" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y414" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z414" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA414" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AB414" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AC414" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD414" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE414" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF414" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AG414" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH414" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AI414" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AJ414" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AK414" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AL414" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM414" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AN414" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AO414" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AP414" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AQ414" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AR414" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AS414" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AT414" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AU414" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV414" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW414" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX414" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY414" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ414" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA414" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB414" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC414" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD414" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BE414" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF414" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BG414" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH414" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="BI414" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BJ414" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="BK414" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BL414" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM414" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BN414" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BO414" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BP414" t="n">
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP414"/>
+  <dimension ref="A1:BP419"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="AQ9" t="n">
         <v>1.43</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ12" t="n">
         <v>0.79</v>
@@ -4184,7 +4184,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.38</v>
+        <v>0.57</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
@@ -5489,7 +5489,7 @@
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ23" t="n">
         <v>0.87</v>
@@ -5925,10 +5925,10 @@
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR25" t="n">
         <v>0</v>
@@ -7454,7 +7454,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR32" t="n">
         <v>1.43</v>
@@ -9195,10 +9195,10 @@
         <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR40" t="n">
         <v>1.46</v>
@@ -9413,10 +9413,10 @@
         <v>1</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR41" t="n">
         <v>1.37</v>
@@ -12029,7 +12029,7 @@
         <v>1.5</v>
       </c>
       <c r="AP53" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ53" t="n">
         <v>1.86</v>
@@ -12683,7 +12683,7 @@
         <v>0</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ56" t="n">
         <v>1.14</v>
@@ -12904,7 +12904,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ57" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR57" t="n">
         <v>1.67</v>
@@ -13994,7 +13994,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ62" t="n">
-        <v>0.38</v>
+        <v>0.57</v>
       </c>
       <c r="AR62" t="n">
         <v>1.4</v>
@@ -14209,7 +14209,7 @@
         <v>0.5</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ63" t="n">
         <v>0.36</v>
@@ -15302,7 +15302,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ68" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR68" t="n">
         <v>1.55</v>
@@ -15517,7 +15517,7 @@
         <v>0.25</v>
       </c>
       <c r="AP69" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="AQ69" t="n">
         <v>0.87</v>
@@ -15735,7 +15735,7 @@
         <v>0</v>
       </c>
       <c r="AP70" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ70" t="n">
         <v>1.25</v>
@@ -16174,7 +16174,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ72" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR72" t="n">
         <v>1.81</v>
@@ -16392,7 +16392,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ73" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR73" t="n">
         <v>2.13</v>
@@ -16825,7 +16825,7 @@
         <v>3</v>
       </c>
       <c r="AP75" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ75" t="n">
         <v>2.08</v>
@@ -18787,7 +18787,7 @@
         <v>1.5</v>
       </c>
       <c r="AP84" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ84" t="n">
         <v>0.86</v>
@@ -19005,7 +19005,7 @@
         <v>0</v>
       </c>
       <c r="AP85" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="AQ85" t="n">
         <v>1.93</v>
@@ -19877,7 +19877,7 @@
         <v>1.5</v>
       </c>
       <c r="AP89" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ89" t="n">
         <v>1.23</v>
@@ -20098,7 +20098,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ90" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR90" t="n">
         <v>0.97</v>
@@ -21839,10 +21839,10 @@
         <v>1.5</v>
       </c>
       <c r="AP98" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR98" t="n">
         <v>1.51</v>
@@ -22057,7 +22057,7 @@
         <v>1.33</v>
       </c>
       <c r="AP99" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ99" t="n">
         <v>0.36</v>
@@ -22496,7 +22496,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ101" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR101" t="n">
         <v>1.59</v>
@@ -25327,7 +25327,7 @@
         <v>1</v>
       </c>
       <c r="AP114" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="AQ114" t="n">
         <v>0.86</v>
@@ -25766,7 +25766,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ116" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR116" t="n">
         <v>1.53</v>
@@ -25984,7 +25984,7 @@
         <v>2</v>
       </c>
       <c r="AQ117" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR117" t="n">
         <v>1.59</v>
@@ -26199,10 +26199,10 @@
         <v>1.33</v>
       </c>
       <c r="AP118" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ118" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR118" t="n">
         <v>1.59</v>
@@ -26635,7 +26635,7 @@
         <v>2.33</v>
       </c>
       <c r="AP120" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ120" t="n">
         <v>1.38</v>
@@ -26853,7 +26853,7 @@
         <v>0.5</v>
       </c>
       <c r="AP121" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ121" t="n">
         <v>0.36</v>
@@ -27510,7 +27510,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ124" t="n">
-        <v>0.38</v>
+        <v>0.57</v>
       </c>
       <c r="AR124" t="n">
         <v>1.85</v>
@@ -28597,7 +28597,7 @@
         <v>2.33</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ129" t="n">
         <v>1.57</v>
@@ -28815,7 +28815,7 @@
         <v>2</v>
       </c>
       <c r="AP130" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ130" t="n">
         <v>1.38</v>
@@ -29036,7 +29036,7 @@
         <v>1</v>
       </c>
       <c r="AQ131" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR131" t="n">
         <v>1.25</v>
@@ -30998,7 +30998,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ140" t="n">
-        <v>0.38</v>
+        <v>0.57</v>
       </c>
       <c r="AR140" t="n">
         <v>1.76</v>
@@ -31216,7 +31216,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ141" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR141" t="n">
         <v>1.62</v>
@@ -31867,7 +31867,7 @@
         <v>1.8</v>
       </c>
       <c r="AP144" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="AQ144" t="n">
         <v>1.57</v>
@@ -32521,7 +32521,7 @@
         <v>2</v>
       </c>
       <c r="AP147" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ147" t="n">
         <v>1.57</v>
@@ -33178,7 +33178,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ150" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR150" t="n">
         <v>1.33</v>
@@ -34268,7 +34268,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ155" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR155" t="n">
         <v>1.34</v>
@@ -34701,7 +34701,7 @@
         <v>1.6</v>
       </c>
       <c r="AP157" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ157" t="n">
         <v>1.86</v>
@@ -35576,7 +35576,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ161" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR161" t="n">
         <v>2.02</v>
@@ -35794,7 +35794,7 @@
         <v>2</v>
       </c>
       <c r="AQ162" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR162" t="n">
         <v>1.74</v>
@@ -36445,7 +36445,7 @@
         <v>0.4</v>
       </c>
       <c r="AP165" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ165" t="n">
         <v>0.36</v>
@@ -36666,7 +36666,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ166" t="n">
-        <v>0.38</v>
+        <v>0.57</v>
       </c>
       <c r="AR166" t="n">
         <v>1.48</v>
@@ -37099,7 +37099,7 @@
         <v>2.5</v>
       </c>
       <c r="AP168" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ168" t="n">
         <v>1.69</v>
@@ -38407,7 +38407,7 @@
         <v>0.8</v>
       </c>
       <c r="AP174" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="AQ174" t="n">
         <v>1.07</v>
@@ -38843,7 +38843,7 @@
         <v>1.2</v>
       </c>
       <c r="AP176" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ176" t="n">
         <v>2.08</v>
@@ -39282,7 +39282,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ178" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR178" t="n">
         <v>1.74</v>
@@ -41023,7 +41023,7 @@
         <v>0.4</v>
       </c>
       <c r="AP186" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="AQ186" t="n">
         <v>0.5</v>
@@ -41459,7 +41459,7 @@
         <v>0.5</v>
       </c>
       <c r="AP188" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ188" t="n">
         <v>0.79</v>
@@ -41677,10 +41677,10 @@
         <v>0.2</v>
       </c>
       <c r="AP189" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ189" t="n">
-        <v>0.38</v>
+        <v>0.57</v>
       </c>
       <c r="AR189" t="n">
         <v>1.48</v>
@@ -41898,7 +41898,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ190" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR190" t="n">
         <v>1.39</v>
@@ -42552,7 +42552,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ193" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR193" t="n">
         <v>1.66</v>
@@ -43642,7 +43642,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ198" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR198" t="n">
         <v>1.1</v>
@@ -44075,7 +44075,7 @@
         <v>0.83</v>
       </c>
       <c r="AP200" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ200" t="n">
         <v>0.36</v>
@@ -44293,7 +44293,7 @@
         <v>0.67</v>
       </c>
       <c r="AP201" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="AQ201" t="n">
         <v>0.8</v>
@@ -44511,7 +44511,7 @@
         <v>2.2</v>
       </c>
       <c r="AP202" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ202" t="n">
         <v>1.57</v>
@@ -44732,7 +44732,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ203" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR203" t="n">
         <v>0.97</v>
@@ -46912,7 +46912,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ213" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR213" t="n">
         <v>1.71</v>
@@ -47781,7 +47781,7 @@
         <v>1</v>
       </c>
       <c r="AP217" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ217" t="n">
         <v>1.23</v>
@@ -47999,7 +47999,7 @@
         <v>1.57</v>
       </c>
       <c r="AP218" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ218" t="n">
         <v>1.43</v>
@@ -48656,7 +48656,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ221" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR221" t="n">
         <v>1.94</v>
@@ -50400,7 +50400,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ229" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR229" t="n">
         <v>1.74</v>
@@ -51269,7 +51269,7 @@
         <v>0.88</v>
       </c>
       <c r="AP233" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ233" t="n">
         <v>0.86</v>
@@ -51490,7 +51490,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ234" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR234" t="n">
         <v>1.39</v>
@@ -51926,7 +51926,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ236" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR236" t="n">
         <v>1.1</v>
@@ -52141,10 +52141,10 @@
         <v>1.43</v>
       </c>
       <c r="AP237" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ237" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR237" t="n">
         <v>1.58</v>
@@ -52359,7 +52359,7 @@
         <v>0.86</v>
       </c>
       <c r="AP238" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="AQ238" t="n">
         <v>1.21</v>
@@ -53670,7 +53670,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ244" t="n">
-        <v>0.38</v>
+        <v>0.57</v>
       </c>
       <c r="AR244" t="n">
         <v>1.41</v>
@@ -56068,7 +56068,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ255" t="n">
-        <v>0.38</v>
+        <v>0.57</v>
       </c>
       <c r="AR255" t="n">
         <v>1.64</v>
@@ -56286,7 +56286,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ256" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR256" t="n">
         <v>1.29</v>
@@ -56501,7 +56501,7 @@
         <v>0.22</v>
       </c>
       <c r="AP257" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ257" t="n">
         <v>0.36</v>
@@ -57373,7 +57373,7 @@
         <v>1.44</v>
       </c>
       <c r="AP261" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ261" t="n">
         <v>1.38</v>
@@ -57591,7 +57591,7 @@
         <v>1.29</v>
       </c>
       <c r="AP262" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ262" t="n">
         <v>2.08</v>
@@ -57809,7 +57809,7 @@
         <v>0.63</v>
       </c>
       <c r="AP263" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ263" t="n">
         <v>0.5</v>
@@ -59338,7 +59338,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ270" t="n">
-        <v>0.38</v>
+        <v>0.57</v>
       </c>
       <c r="AR270" t="n">
         <v>1.64</v>
@@ -59771,10 +59771,10 @@
         <v>1.25</v>
       </c>
       <c r="AP272" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ272" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR272" t="n">
         <v>1.57</v>
@@ -59992,7 +59992,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ273" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR273" t="n">
         <v>0.97</v>
@@ -60207,7 +60207,7 @@
         <v>0.7</v>
       </c>
       <c r="AP274" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ274" t="n">
         <v>1.07</v>
@@ -60425,7 +60425,7 @@
         <v>1.44</v>
       </c>
       <c r="AP275" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ275" t="n">
         <v>1.64</v>
@@ -61736,7 +61736,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ281" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR281" t="n">
         <v>1.12</v>
@@ -62172,7 +62172,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ283" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR283" t="n">
         <v>0.98</v>
@@ -63259,7 +63259,7 @@
         <v>0.8</v>
       </c>
       <c r="AP288" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ288" t="n">
         <v>0.86</v>
@@ -65442,7 +65442,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ298" t="n">
-        <v>0.38</v>
+        <v>0.57</v>
       </c>
       <c r="AR298" t="n">
         <v>1.15</v>
@@ -66093,7 +66093,7 @@
         <v>1.9</v>
       </c>
       <c r="AP301" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="AQ301" t="n">
         <v>1.64</v>
@@ -66750,7 +66750,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ304" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR304" t="n">
         <v>1.7</v>
@@ -67622,7 +67622,7 @@
         <v>2</v>
       </c>
       <c r="AQ308" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR308" t="n">
         <v>1.85</v>
@@ -68058,7 +68058,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ310" t="n">
-        <v>0.38</v>
+        <v>0.57</v>
       </c>
       <c r="AR310" t="n">
         <v>1.17</v>
@@ -68927,7 +68927,7 @@
         <v>1.45</v>
       </c>
       <c r="AP314" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ314" t="n">
         <v>1.43</v>
@@ -69363,10 +69363,10 @@
         <v>1.4</v>
       </c>
       <c r="AP316" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ316" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR316" t="n">
         <v>1.53</v>
@@ -69581,7 +69581,7 @@
         <v>0.9</v>
       </c>
       <c r="AP317" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ317" t="n">
         <v>1.14</v>
@@ -70238,7 +70238,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ320" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR320" t="n">
         <v>1.45</v>
@@ -70889,10 +70889,10 @@
         <v>1.22</v>
       </c>
       <c r="AP323" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ323" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR323" t="n">
         <v>1.55</v>
@@ -72415,7 +72415,7 @@
         <v>1.6</v>
       </c>
       <c r="AP330" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="AQ330" t="n">
         <v>1.38</v>
@@ -72633,7 +72633,7 @@
         <v>0.88</v>
       </c>
       <c r="AP331" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ331" t="n">
         <v>1.25</v>
@@ -73072,7 +73072,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ333" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR333" t="n">
         <v>1.66</v>
@@ -75252,7 +75252,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ343" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR343" t="n">
         <v>1.66</v>
@@ -75467,7 +75467,7 @@
         <v>0.91</v>
       </c>
       <c r="AP344" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ344" t="n">
         <v>1.21</v>
@@ -76121,7 +76121,7 @@
         <v>1.22</v>
       </c>
       <c r="AP347" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="AQ347" t="n">
         <v>1</v>
@@ -78086,7 +78086,7 @@
         <v>2</v>
       </c>
       <c r="AQ356" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR356" t="n">
         <v>1.86</v>
@@ -78958,7 +78958,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ360" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR360" t="n">
         <v>1.71</v>
@@ -79391,7 +79391,7 @@
         <v>1.67</v>
       </c>
       <c r="AP362" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ362" t="n">
         <v>1.86</v>
@@ -79830,7 +79830,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ364" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR364" t="n">
         <v>1.51</v>
@@ -80702,7 +80702,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ368" t="n">
-        <v>0.38</v>
+        <v>0.57</v>
       </c>
       <c r="AR368" t="n">
         <v>1.3</v>
@@ -80917,10 +80917,10 @@
         <v>1.18</v>
       </c>
       <c r="AP369" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ369" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR369" t="n">
         <v>1.5</v>
@@ -81135,7 +81135,7 @@
         <v>1.42</v>
       </c>
       <c r="AP370" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ370" t="n">
         <v>1.21</v>
@@ -81356,7 +81356,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ371" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR371" t="n">
         <v>1.24</v>
@@ -81789,7 +81789,7 @@
         <v>1.91</v>
       </c>
       <c r="AP373" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ373" t="n">
         <v>2.08</v>
@@ -82661,10 +82661,10 @@
         <v>0.83</v>
       </c>
       <c r="AP377" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ377" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR377" t="n">
         <v>1.5</v>
@@ -84623,7 +84623,7 @@
         <v>1.23</v>
       </c>
       <c r="AP386" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ386" t="n">
         <v>1.14</v>
@@ -84841,7 +84841,7 @@
         <v>1.42</v>
       </c>
       <c r="AP387" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ387" t="n">
         <v>1.38</v>
@@ -85280,7 +85280,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ389" t="n">
-        <v>0.38</v>
+        <v>0.57</v>
       </c>
       <c r="AR389" t="n">
         <v>1.54</v>
@@ -86370,7 +86370,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ394" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR394" t="n">
         <v>1.83</v>
@@ -87893,7 +87893,7 @@
         <v>1.77</v>
       </c>
       <c r="AP401" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="AQ401" t="n">
         <v>1.64</v>
@@ -88114,7 +88114,7 @@
         <v>1</v>
       </c>
       <c r="AQ402" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR402" t="n">
         <v>1.52</v>
@@ -88768,7 +88768,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ405" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR405" t="n">
         <v>1.59</v>
@@ -88986,7 +88986,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ406" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR406" t="n">
         <v>1.4</v>
@@ -90806,6 +90806,1096 @@
       </c>
       <c r="BP414" t="n">
         <v>1.34</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="1" t="n">
+        <v>414</v>
+      </c>
+      <c r="B415" t="n">
+        <v>8229810</v>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E415" s="2" t="n">
+        <v>45899.89583333334</v>
+      </c>
+      <c r="F415" t="n">
+        <v>0</v>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>St. Louis City</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>Houston Dynamo</t>
+        </is>
+      </c>
+      <c r="I415" t="n">
+        <v>0</v>
+      </c>
+      <c r="J415" t="n">
+        <v>1</v>
+      </c>
+      <c r="K415" t="n">
+        <v>1</v>
+      </c>
+      <c r="L415" t="n">
+        <v>2</v>
+      </c>
+      <c r="M415" t="n">
+        <v>3</v>
+      </c>
+      <c r="N415" t="n">
+        <v>5</v>
+      </c>
+      <c r="O415" t="inlineStr">
+        <is>
+          <t>['86', '89']</t>
+        </is>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>['20', '50', '72']</t>
+        </is>
+      </c>
+      <c r="Q415" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R415" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S415" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="T415" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="U415" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V415" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W415" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="X415" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Y415" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z415" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA415" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB415" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AC415" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD415" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE415" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF415" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG415" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AH415" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AI415" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ415" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AK415" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL415" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM415" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AN415" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AO415" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AP415" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AQ415" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AR415" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AS415" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AT415" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AU415" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV415" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW415" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX415" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY415" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ415" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA415" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB415" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC415" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD415" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE415" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF415" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BG415" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BH415" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BI415" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ415" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BK415" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BL415" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BM415" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BN415" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BO415" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="BP415" t="n">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="1" t="n">
+        <v>415</v>
+      </c>
+      <c r="B416" t="n">
+        <v>8229808</v>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E416" s="2" t="n">
+        <v>45899.89583333334</v>
+      </c>
+      <c r="F416" t="n">
+        <v>0</v>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>Sporting KC</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>Colorado Rapids</t>
+        </is>
+      </c>
+      <c r="I416" t="n">
+        <v>1</v>
+      </c>
+      <c r="J416" t="n">
+        <v>2</v>
+      </c>
+      <c r="K416" t="n">
+        <v>3</v>
+      </c>
+      <c r="L416" t="n">
+        <v>4</v>
+      </c>
+      <c r="M416" t="n">
+        <v>2</v>
+      </c>
+      <c r="N416" t="n">
+        <v>6</v>
+      </c>
+      <c r="O416" t="inlineStr">
+        <is>
+          <t>['4', '73', '75', '81']</t>
+        </is>
+      </c>
+      <c r="P416" t="inlineStr">
+        <is>
+          <t>['22', '31']</t>
+        </is>
+      </c>
+      <c r="Q416" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R416" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S416" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T416" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="U416" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="V416" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="W416" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="X416" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y416" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z416" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AA416" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AB416" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AC416" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD416" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE416" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF416" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG416" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH416" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AI416" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AJ416" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AK416" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL416" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM416" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AN416" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO416" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AP416" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AQ416" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AR416" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AS416" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AT416" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AU416" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV416" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW416" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX416" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY416" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ416" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA416" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB416" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC416" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD416" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BE416" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF416" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BG416" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH416" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BI416" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BJ416" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BK416" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BL416" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BM416" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BN416" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BO416" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BP416" t="n">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="1" t="n">
+        <v>416</v>
+      </c>
+      <c r="B417" t="n">
+        <v>8229799</v>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E417" s="2" t="n">
+        <v>45899.89583333334</v>
+      </c>
+      <c r="F417" t="n">
+        <v>0</v>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>SJ Earthquakes</t>
+        </is>
+      </c>
+      <c r="I417" t="n">
+        <v>2</v>
+      </c>
+      <c r="J417" t="n">
+        <v>0</v>
+      </c>
+      <c r="K417" t="n">
+        <v>2</v>
+      </c>
+      <c r="L417" t="n">
+        <v>3</v>
+      </c>
+      <c r="M417" t="n">
+        <v>1</v>
+      </c>
+      <c r="N417" t="n">
+        <v>4</v>
+      </c>
+      <c r="O417" t="inlineStr">
+        <is>
+          <t>['12', '33', '77']</t>
+        </is>
+      </c>
+      <c r="P417" t="inlineStr">
+        <is>
+          <t>['53']</t>
+        </is>
+      </c>
+      <c r="Q417" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R417" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S417" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T417" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U417" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V417" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="W417" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X417" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y417" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z417" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AA417" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB417" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AC417" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD417" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE417" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF417" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="AG417" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AH417" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AI417" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AJ417" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AK417" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL417" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM417" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN417" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AO417" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AP417" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AQ417" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AR417" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AS417" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AT417" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AU417" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV417" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW417" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX417" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY417" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ417" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA417" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB417" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC417" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD417" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BE417" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="BF417" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BG417" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BH417" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BI417" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BJ417" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BK417" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BL417" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BM417" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BN417" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BO417" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BP417" t="n">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="1" t="n">
+        <v>417</v>
+      </c>
+      <c r="B418" t="n">
+        <v>8229817</v>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E418" s="2" t="n">
+        <v>45899.89583333334</v>
+      </c>
+      <c r="F418" t="n">
+        <v>0</v>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>Nashville SC</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>Atlanta United FC</t>
+        </is>
+      </c>
+      <c r="I418" t="n">
+        <v>0</v>
+      </c>
+      <c r="J418" t="n">
+        <v>1</v>
+      </c>
+      <c r="K418" t="n">
+        <v>1</v>
+      </c>
+      <c r="L418" t="n">
+        <v>0</v>
+      </c>
+      <c r="M418" t="n">
+        <v>1</v>
+      </c>
+      <c r="N418" t="n">
+        <v>1</v>
+      </c>
+      <c r="O418" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P418" t="inlineStr">
+        <is>
+          <t>['24']</t>
+        </is>
+      </c>
+      <c r="Q418" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="R418" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S418" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="T418" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U418" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V418" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W418" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="X418" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="Y418" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z418" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AA418" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AB418" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AC418" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD418" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE418" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF418" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="AG418" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AH418" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AI418" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ418" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK418" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL418" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM418" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AN418" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AO418" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AP418" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AQ418" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AR418" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AS418" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AT418" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AU418" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV418" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW418" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX418" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY418" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ418" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA418" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB418" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC418" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD418" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BE418" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF418" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BG418" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BH418" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BI418" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BJ418" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BK418" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BL418" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BM418" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BN418" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BO418" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="BP418" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="1" t="n">
+        <v>418</v>
+      </c>
+      <c r="B419" t="n">
+        <v>8229814</v>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E419" s="2" t="n">
+        <v>45899.89583333334</v>
+      </c>
+      <c r="F419" t="n">
+        <v>0</v>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>Minnesota United</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>Portland Timbers</t>
+        </is>
+      </c>
+      <c r="I419" t="n">
+        <v>0</v>
+      </c>
+      <c r="J419" t="n">
+        <v>0</v>
+      </c>
+      <c r="K419" t="n">
+        <v>0</v>
+      </c>
+      <c r="L419" t="n">
+        <v>1</v>
+      </c>
+      <c r="M419" t="n">
+        <v>1</v>
+      </c>
+      <c r="N419" t="n">
+        <v>2</v>
+      </c>
+      <c r="O419" t="inlineStr">
+        <is>
+          <t>['85']</t>
+        </is>
+      </c>
+      <c r="P419" t="inlineStr">
+        <is>
+          <t>['79']</t>
+        </is>
+      </c>
+      <c r="Q419" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R419" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S419" t="n">
+        <v>4</v>
+      </c>
+      <c r="T419" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="U419" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="V419" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="W419" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X419" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y419" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z419" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA419" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB419" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AC419" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD419" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE419" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF419" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="AG419" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH419" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AI419" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AJ419" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AK419" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL419" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM419" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN419" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AO419" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AP419" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ419" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AR419" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AS419" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AT419" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AU419" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV419" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW419" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX419" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY419" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ419" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA419" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB419" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC419" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD419" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BE419" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF419" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BG419" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH419" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BI419" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BJ419" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BK419" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BL419" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BM419" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BN419" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BO419" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BP419" t="n">
+        <v>1.32</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
@@ -91623,13 +91623,13 @@
         <v>13</v>
       </c>
       <c r="AX418" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY418" t="n">
         <v>19</v>
       </c>
       <c r="AZ418" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA418" t="n">
         <v>12</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
@@ -91187,13 +91187,13 @@
         <v>10</v>
       </c>
       <c r="AX416" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY416" t="n">
         <v>20</v>
       </c>
       <c r="AZ416" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA416" t="n">
         <v>8</v>
@@ -91614,13 +91614,13 @@
         <v>2.86</v>
       </c>
       <c r="AU418" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV418" t="n">
         <v>4</v>
       </c>
       <c r="AW418" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX418" t="n">
         <v>6</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP419"/>
+  <dimension ref="A1:BP420"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ2" t="n">
         <v>1.86</v>
@@ -3966,7 +3966,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ16" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -6797,7 +6797,7 @@
         <v>1</v>
       </c>
       <c r="AP29" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ29" t="n">
         <v>1.21</v>
@@ -9852,7 +9852,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ43" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR43" t="n">
         <v>1.28</v>
@@ -11157,7 +11157,7 @@
         <v>0</v>
       </c>
       <c r="AP49" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ49" t="n">
         <v>1.23</v>
@@ -16828,7 +16828,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ75" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR75" t="n">
         <v>1.68</v>
@@ -25548,7 +25548,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ115" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR115" t="n">
         <v>1.63</v>
@@ -25981,7 +25981,7 @@
         <v>1.5</v>
       </c>
       <c r="AP117" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ117" t="n">
         <v>1.13</v>
@@ -28382,7 +28382,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ128" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR128" t="n">
         <v>1.39</v>
@@ -32957,7 +32957,7 @@
         <v>1</v>
       </c>
       <c r="AP149" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ149" t="n">
         <v>0.36</v>
@@ -35791,7 +35791,7 @@
         <v>0.75</v>
       </c>
       <c r="AP162" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ162" t="n">
         <v>1.29</v>
@@ -38846,7 +38846,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ176" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR176" t="n">
         <v>1.49</v>
@@ -42331,7 +42331,7 @@
         <v>1.14</v>
       </c>
       <c r="AP192" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ192" t="n">
         <v>1.14</v>
@@ -51054,7 +51054,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ232" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR232" t="n">
         <v>1.93</v>
@@ -55847,7 +55847,7 @@
         <v>0.89</v>
       </c>
       <c r="AP254" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ254" t="n">
         <v>0.79</v>
@@ -57594,7 +57594,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ262" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR262" t="n">
         <v>1.6</v>
@@ -61082,7 +61082,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ278" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR278" t="n">
         <v>1.81</v>
@@ -62826,7 +62826,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ286" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR286" t="n">
         <v>1.03</v>
@@ -64131,7 +64131,7 @@
         <v>1.88</v>
       </c>
       <c r="AP292" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ292" t="n">
         <v>1.57</v>
@@ -67619,7 +67619,7 @@
         <v>1</v>
       </c>
       <c r="AP308" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ308" t="n">
         <v>0.87</v>
@@ -69148,7 +69148,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ315" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR315" t="n">
         <v>1.55</v>
@@ -70453,7 +70453,7 @@
         <v>1.6</v>
       </c>
       <c r="AP321" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ321" t="n">
         <v>1.38</v>
@@ -76775,7 +76775,7 @@
         <v>0.33</v>
       </c>
       <c r="AP350" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ350" t="n">
         <v>0.36</v>
@@ -78083,7 +78083,7 @@
         <v>1.1</v>
       </c>
       <c r="AP356" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ356" t="n">
         <v>1.14</v>
@@ -81792,7 +81792,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ373" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR373" t="n">
         <v>1.53</v>
@@ -86152,7 +86152,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ393" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR393" t="n">
         <v>1.78</v>
@@ -91896,6 +91896,224 @@
       </c>
       <c r="BP419" t="n">
         <v>1.32</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="1" t="n">
+        <v>419</v>
+      </c>
+      <c r="B420" t="n">
+        <v>8229792</v>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E420" s="2" t="n">
+        <v>45900.98958333334</v>
+      </c>
+      <c r="F420" t="n">
+        <v>0</v>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>Los Angeles FC</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="I420" t="n">
+        <v>1</v>
+      </c>
+      <c r="J420" t="n">
+        <v>1</v>
+      </c>
+      <c r="K420" t="n">
+        <v>2</v>
+      </c>
+      <c r="L420" t="n">
+        <v>1</v>
+      </c>
+      <c r="M420" t="n">
+        <v>2</v>
+      </c>
+      <c r="N420" t="n">
+        <v>3</v>
+      </c>
+      <c r="O420" t="inlineStr">
+        <is>
+          <t>['15']</t>
+        </is>
+      </c>
+      <c r="P420" t="inlineStr">
+        <is>
+          <t>['33', '66']</t>
+        </is>
+      </c>
+      <c r="Q420" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R420" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="S420" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T420" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U420" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V420" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="W420" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X420" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Y420" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z420" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AA420" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AB420" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC420" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD420" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE420" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF420" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="AG420" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH420" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AI420" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ420" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AK420" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AL420" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM420" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AN420" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO420" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AP420" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AQ420" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AR420" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AS420" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AT420" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AU420" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV420" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW420" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX420" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY420" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ420" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA420" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB420" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC420" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD420" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BE420" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF420" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BG420" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH420" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI420" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BJ420" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BK420" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BL420" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BM420" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BN420" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BO420" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BP420" t="n">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
@@ -90312,13 +90312,13 @@
         <v>4</v>
       </c>
       <c r="AW412" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX412" t="n">
         <v>10</v>
       </c>
       <c r="AY412" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ412" t="n">
         <v>14</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP420"/>
+  <dimension ref="A1:BP423"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2440,7 +2440,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -2658,7 +2658,7 @@
         <v>1</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ11" t="n">
         <v>0.87</v>
@@ -5707,7 +5707,7 @@
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ24" t="n">
         <v>0.8</v>
@@ -6146,7 +6146,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR26" t="n">
         <v>0</v>
@@ -7018,7 +7018,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="AR30" t="n">
         <v>0</v>
@@ -11596,7 +11596,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR51" t="n">
         <v>1.97</v>
@@ -12683,7 +12683,7 @@
         <v>0</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ56" t="n">
         <v>1.14</v>
@@ -13558,7 +13558,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ60" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="AR60" t="n">
         <v>0.78</v>
@@ -14212,7 +14212,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ63" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="AR63" t="n">
         <v>1.54</v>
@@ -15956,7 +15956,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ71" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR71" t="n">
         <v>1.35</v>
@@ -18351,7 +18351,7 @@
         <v>0.2</v>
       </c>
       <c r="AP82" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ82" t="n">
         <v>0.87</v>
@@ -19877,7 +19877,7 @@
         <v>1.5</v>
       </c>
       <c r="AP89" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ89" t="n">
         <v>1.23</v>
@@ -20534,7 +20534,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ92" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="AR92" t="n">
         <v>1.27</v>
@@ -20970,7 +20970,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ94" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR94" t="n">
         <v>1.49</v>
@@ -21624,7 +21624,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ97" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR97" t="n">
         <v>1.49</v>
@@ -23804,7 +23804,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ107" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR107" t="n">
         <v>1.45</v>
@@ -26417,7 +26417,7 @@
         <v>3</v>
       </c>
       <c r="AP119" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ119" t="n">
         <v>1.69</v>
@@ -26635,7 +26635,7 @@
         <v>2.33</v>
       </c>
       <c r="AP120" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ120" t="n">
         <v>1.38</v>
@@ -26856,7 +26856,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ121" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="AR121" t="n">
         <v>1.4</v>
@@ -28597,7 +28597,7 @@
         <v>2.33</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ129" t="n">
         <v>1.57</v>
@@ -28818,7 +28818,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ130" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR130" t="n">
         <v>1.79</v>
@@ -29251,7 +29251,7 @@
         <v>1.5</v>
       </c>
       <c r="AP132" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ132" t="n">
         <v>1.93</v>
@@ -31434,7 +31434,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ142" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR142" t="n">
         <v>1.48</v>
@@ -32742,7 +32742,7 @@
         <v>2</v>
       </c>
       <c r="AQ148" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR148" t="n">
         <v>1.4</v>
@@ -33614,7 +33614,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ152" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR152" t="n">
         <v>1.04</v>
@@ -34919,7 +34919,7 @@
         <v>1.2</v>
       </c>
       <c r="AP158" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ158" t="n">
         <v>1.64</v>
@@ -35140,7 +35140,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ159" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR159" t="n">
         <v>1.66</v>
@@ -36448,7 +36448,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ165" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="AR165" t="n">
         <v>1.55</v>
@@ -36663,7 +36663,7 @@
         <v>0.25</v>
       </c>
       <c r="AP166" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ166" t="n">
         <v>0.57</v>
@@ -37320,7 +37320,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ169" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR169" t="n">
         <v>1.77</v>
@@ -37538,7 +37538,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ170" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="AR170" t="n">
         <v>1.36</v>
@@ -38843,7 +38843,7 @@
         <v>1.2</v>
       </c>
       <c r="AP176" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ176" t="n">
         <v>2.14</v>
@@ -40590,7 +40590,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ184" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="AR184" t="n">
         <v>1.64</v>
@@ -41459,7 +41459,7 @@
         <v>0.5</v>
       </c>
       <c r="AP188" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ188" t="n">
         <v>0.79</v>
@@ -46040,7 +46040,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ209" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR209" t="n">
         <v>1.98</v>
@@ -46258,7 +46258,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ210" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="AR210" t="n">
         <v>1.75</v>
@@ -48002,7 +48002,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ218" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR218" t="n">
         <v>1.31</v>
@@ -49310,7 +49310,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ224" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR224" t="n">
         <v>1.6</v>
@@ -49964,7 +49964,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ227" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR227" t="n">
         <v>1.12</v>
@@ -52141,7 +52141,7 @@
         <v>1.43</v>
       </c>
       <c r="AP237" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ237" t="n">
         <v>1.13</v>
@@ -52798,7 +52798,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ240" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR240" t="n">
         <v>1.23</v>
@@ -56501,10 +56501,10 @@
         <v>0.22</v>
       </c>
       <c r="AP257" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ257" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="AR257" t="n">
         <v>1.54</v>
@@ -57809,7 +57809,7 @@
         <v>1.14</v>
       </c>
       <c r="AP263" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ263" t="n">
         <v>1.21</v>
@@ -58248,7 +58248,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ265" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR265" t="n">
         <v>1.36</v>
@@ -59989,7 +59989,7 @@
         <v>2</v>
       </c>
       <c r="AP273" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ273" t="n">
         <v>1.64</v>
@@ -60207,7 +60207,7 @@
         <v>1.44</v>
       </c>
       <c r="AP274" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ274" t="n">
         <v>1.64</v>
@@ -60864,7 +60864,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ277" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="AR277" t="n">
         <v>1.53</v>
@@ -63259,7 +63259,7 @@
         <v>0.64</v>
       </c>
       <c r="AP288" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ288" t="n">
         <v>1.07</v>
@@ -63480,7 +63480,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ289" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="AR289" t="n">
         <v>1.92</v>
@@ -66968,7 +66968,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ305" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR305" t="n">
         <v>1.32</v>
@@ -69363,7 +69363,7 @@
         <v>1.8</v>
       </c>
       <c r="AP316" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ316" t="n">
         <v>2.14</v>
@@ -69584,7 +69584,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ317" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR317" t="n">
         <v>1.46</v>
@@ -70674,7 +70674,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ322" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR322" t="n">
         <v>1.9</v>
@@ -70889,7 +70889,7 @@
         <v>1.22</v>
       </c>
       <c r="AP323" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ323" t="n">
         <v>1.14</v>
@@ -71982,7 +71982,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ328" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR328" t="n">
         <v>1.38</v>
@@ -73508,7 +73508,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ335" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR335" t="n">
         <v>1.84</v>
@@ -76560,7 +76560,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ349" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="AR349" t="n">
         <v>1.94</v>
@@ -79391,7 +79391,7 @@
         <v>1.67</v>
       </c>
       <c r="AP362" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ362" t="n">
         <v>1.86</v>
@@ -79609,7 +79609,7 @@
         <v>0.58</v>
       </c>
       <c r="AP363" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ363" t="n">
         <v>0.5</v>
@@ -81353,7 +81353,7 @@
         <v>1.11</v>
       </c>
       <c r="AP371" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ371" t="n">
         <v>1.25</v>
@@ -81571,7 +81571,7 @@
         <v>1.42</v>
       </c>
       <c r="AP372" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ372" t="n">
         <v>1.21</v>
@@ -84190,7 +84190,7 @@
         <v>2</v>
       </c>
       <c r="AQ384" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="AR384" t="n">
         <v>1.37</v>
@@ -84623,7 +84623,7 @@
         <v>0.42</v>
       </c>
       <c r="AP386" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ386" t="n">
         <v>0.36</v>
@@ -84844,7 +84844,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ387" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR387" t="n">
         <v>1.48</v>
@@ -87024,7 +87024,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ397" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR397" t="n">
         <v>1.69</v>
@@ -91599,7 +91599,7 @@
         <v>1.15</v>
       </c>
       <c r="AP418" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ418" t="n">
         <v>1.29</v>
@@ -92114,6 +92114,660 @@
       </c>
       <c r="BP420" t="n">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="1" t="n">
+        <v>420</v>
+      </c>
+      <c r="B421" t="n">
+        <v>8229404</v>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E421" s="2" t="n">
+        <v>45906.89583333334</v>
+      </c>
+      <c r="F421" t="n">
+        <v>0</v>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>Houston Dynamo</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>LA Galaxy</t>
+        </is>
+      </c>
+      <c r="I421" t="n">
+        <v>1</v>
+      </c>
+      <c r="J421" t="n">
+        <v>0</v>
+      </c>
+      <c r="K421" t="n">
+        <v>1</v>
+      </c>
+      <c r="L421" t="n">
+        <v>1</v>
+      </c>
+      <c r="M421" t="n">
+        <v>1</v>
+      </c>
+      <c r="N421" t="n">
+        <v>2</v>
+      </c>
+      <c r="O421" t="inlineStr">
+        <is>
+          <t>['35']</t>
+        </is>
+      </c>
+      <c r="P421" t="inlineStr">
+        <is>
+          <t>['90+9']</t>
+        </is>
+      </c>
+      <c r="Q421" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R421" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="S421" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="T421" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U421" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V421" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="W421" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X421" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y421" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z421" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AA421" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AB421" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="AC421" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD421" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE421" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF421" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="AG421" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH421" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AI421" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ421" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AK421" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL421" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM421" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AN421" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO421" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AP421" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ421" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AR421" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AS421" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AT421" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU421" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV421" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW421" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX421" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY421" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ421" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA421" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB421" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC421" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD421" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BE421" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BF421" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG421" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BH421" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BI421" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BJ421" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BK421" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BL421" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BM421" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BN421" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BO421" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BP421" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="1" t="n">
+        <v>421</v>
+      </c>
+      <c r="B422" t="n">
+        <v>8229558</v>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E422" s="2" t="n">
+        <v>45906.89583333334</v>
+      </c>
+      <c r="F422" t="n">
+        <v>0</v>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>Chicago Fire</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>New England Revolution</t>
+        </is>
+      </c>
+      <c r="I422" t="n">
+        <v>2</v>
+      </c>
+      <c r="J422" t="n">
+        <v>0</v>
+      </c>
+      <c r="K422" t="n">
+        <v>2</v>
+      </c>
+      <c r="L422" t="n">
+        <v>3</v>
+      </c>
+      <c r="M422" t="n">
+        <v>2</v>
+      </c>
+      <c r="N422" t="n">
+        <v>5</v>
+      </c>
+      <c r="O422" t="inlineStr">
+        <is>
+          <t>['2', '10', '68']</t>
+        </is>
+      </c>
+      <c r="P422" t="inlineStr">
+        <is>
+          <t>['78', '90+4']</t>
+        </is>
+      </c>
+      <c r="Q422" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="R422" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="S422" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T422" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U422" t="n">
+        <v>4</v>
+      </c>
+      <c r="V422" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="W422" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="X422" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y422" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z422" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AA422" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB422" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AC422" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD422" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE422" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF422" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="AG422" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AH422" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AI422" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ422" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AK422" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL422" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM422" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AN422" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AO422" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AP422" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AQ422" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR422" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AS422" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AT422" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AU422" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV422" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW422" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX422" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY422" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ422" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA422" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB422" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC422" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD422" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BE422" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF422" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BG422" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH422" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BI422" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BJ422" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BK422" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BL422" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BM422" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BN422" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO422" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BP422" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="1" t="n">
+        <v>422</v>
+      </c>
+      <c r="B423" t="n">
+        <v>8229545</v>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E423" s="2" t="n">
+        <v>45906.89583333334</v>
+      </c>
+      <c r="F423" t="n">
+        <v>0</v>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>St. Louis City</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>FC Dallas</t>
+        </is>
+      </c>
+      <c r="I423" t="n">
+        <v>1</v>
+      </c>
+      <c r="J423" t="n">
+        <v>1</v>
+      </c>
+      <c r="K423" t="n">
+        <v>2</v>
+      </c>
+      <c r="L423" t="n">
+        <v>1</v>
+      </c>
+      <c r="M423" t="n">
+        <v>1</v>
+      </c>
+      <c r="N423" t="n">
+        <v>2</v>
+      </c>
+      <c r="O423" t="inlineStr">
+        <is>
+          <t>['32']</t>
+        </is>
+      </c>
+      <c r="P423" t="inlineStr">
+        <is>
+          <t>['34']</t>
+        </is>
+      </c>
+      <c r="Q423" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R423" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S423" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T423" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="U423" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="V423" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="W423" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X423" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y423" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z423" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA423" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AB423" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC423" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD423" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE423" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF423" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AG423" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH423" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AI423" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ423" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AK423" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL423" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM423" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN423" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AO423" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AP423" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AQ423" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR423" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AS423" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AT423" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AU423" t="n">
+        <v>15</v>
+      </c>
+      <c r="AV423" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW423" t="n">
+        <v>28</v>
+      </c>
+      <c r="AX423" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY423" t="n">
+        <v>43</v>
+      </c>
+      <c r="AZ423" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA423" t="n">
+        <v>16</v>
+      </c>
+      <c r="BB423" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC423" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD423" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BE423" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="BF423" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BG423" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH423" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BI423" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BJ423" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BK423" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BL423" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM423" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BN423" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BO423" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BP423" t="n">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP423"/>
+  <dimension ref="A1:BP424"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5925,7 +5925,7 @@
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ25" t="n">
         <v>1.13</v>
@@ -6582,7 +6582,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR28" t="n">
         <v>0.65</v>
@@ -11160,7 +11160,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR49" t="n">
         <v>1.44</v>
@@ -12029,7 +12029,7 @@
         <v>1.5</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ53" t="n">
         <v>1.86</v>
@@ -15735,7 +15735,7 @@
         <v>0</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ70" t="n">
         <v>1.25</v>
@@ -19880,7 +19880,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ89" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR89" t="n">
         <v>1.66</v>
@@ -22057,7 +22057,7 @@
         <v>1.33</v>
       </c>
       <c r="AP99" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ99" t="n">
         <v>0.36</v>
@@ -24676,7 +24676,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ111" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR111" t="n">
         <v>1.64</v>
@@ -26199,7 +26199,7 @@
         <v>1.33</v>
       </c>
       <c r="AP118" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ118" t="n">
         <v>1.14</v>
@@ -32088,7 +32088,7 @@
         <v>1</v>
       </c>
       <c r="AQ145" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR145" t="n">
         <v>1.35</v>
@@ -36445,7 +36445,7 @@
         <v>0.4</v>
       </c>
       <c r="AP165" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ165" t="n">
         <v>0.4</v>
@@ -37974,7 +37974,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ172" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR172" t="n">
         <v>1.59</v>
@@ -47784,7 +47784,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ217" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR217" t="n">
         <v>1.59</v>
@@ -47999,7 +47999,7 @@
         <v>1.57</v>
       </c>
       <c r="AP218" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ218" t="n">
         <v>1.33</v>
@@ -54542,7 +54542,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ248" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR248" t="n">
         <v>1.74</v>
@@ -55196,7 +55196,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ251" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR251" t="n">
         <v>1.55</v>
@@ -58245,7 +58245,7 @@
         <v>1.44</v>
       </c>
       <c r="AP265" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ265" t="n">
         <v>1.36</v>
@@ -59771,7 +59771,7 @@
         <v>0.7</v>
       </c>
       <c r="AP272" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ272" t="n">
         <v>1.07</v>
@@ -62823,7 +62823,7 @@
         <v>0.8</v>
       </c>
       <c r="AP286" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ286" t="n">
         <v>0.86</v>
@@ -63698,7 +63698,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ290" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR290" t="n">
         <v>1.76</v>
@@ -68927,7 +68927,7 @@
         <v>0.9</v>
       </c>
       <c r="AP314" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ314" t="n">
         <v>1.14</v>
@@ -73726,7 +73726,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ336" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR336" t="n">
         <v>1.44</v>
@@ -76121,7 +76121,7 @@
         <v>0.91</v>
       </c>
       <c r="AP347" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ347" t="n">
         <v>1.21</v>
@@ -78958,7 +78958,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ360" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR360" t="n">
         <v>1.15</v>
@@ -81789,7 +81789,7 @@
         <v>1.91</v>
       </c>
       <c r="AP373" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ373" t="n">
         <v>2.14</v>
@@ -87242,7 +87242,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ398" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR398" t="n">
         <v>1.25</v>
@@ -91817,7 +91817,7 @@
         <v>0.93</v>
       </c>
       <c r="AP419" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ419" t="n">
         <v>0.87</v>
@@ -92768,6 +92768,224 @@
       </c>
       <c r="BP423" t="n">
         <v>1.4</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="1" t="n">
+        <v>423</v>
+      </c>
+      <c r="B424" t="n">
+        <v>8229562</v>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E424" s="2" t="n">
+        <v>45907.83333333334</v>
+      </c>
+      <c r="F424" t="n">
+        <v>0</v>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>Sporting KC</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="I424" t="n">
+        <v>1</v>
+      </c>
+      <c r="J424" t="n">
+        <v>1</v>
+      </c>
+      <c r="K424" t="n">
+        <v>2</v>
+      </c>
+      <c r="L424" t="n">
+        <v>1</v>
+      </c>
+      <c r="M424" t="n">
+        <v>2</v>
+      </c>
+      <c r="N424" t="n">
+        <v>3</v>
+      </c>
+      <c r="O424" t="inlineStr">
+        <is>
+          <t>['16']</t>
+        </is>
+      </c>
+      <c r="P424" t="inlineStr">
+        <is>
+          <t>['37', '82']</t>
+        </is>
+      </c>
+      <c r="Q424" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R424" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S424" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T424" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="U424" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="V424" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W424" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X424" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y424" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z424" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AA424" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AB424" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AC424" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD424" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE424" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF424" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG424" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH424" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AI424" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ424" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AK424" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL424" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM424" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AN424" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AO424" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AP424" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AQ424" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR424" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AS424" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AT424" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AU424" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV424" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW424" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX424" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY424" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ424" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA424" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB424" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC424" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD424" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BE424" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF424" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BG424" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH424" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BI424" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ424" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="BK424" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BL424" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BM424" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BN424" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BO424" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BP424" t="n">
+        <v>1.42</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
@@ -92704,7 +92704,7 @@
         <v>2.85</v>
       </c>
       <c r="AU423" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AV423" t="n">
         <v>2</v>
@@ -92716,7 +92716,7 @@
         <v>2</v>
       </c>
       <c r="AY423" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AZ423" t="n">
         <v>4</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP439"/>
+  <dimension ref="A1:BP440"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ4" t="n">
         <v>1.33</v>
@@ -4402,7 +4402,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR18" t="n">
         <v>0</v>
@@ -10285,7 +10285,7 @@
         <v>1</v>
       </c>
       <c r="AP45" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ45" t="n">
         <v>1.07</v>
@@ -12686,7 +12686,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR56" t="n">
         <v>1.81</v>
@@ -17697,7 +17697,7 @@
         <v>3</v>
       </c>
       <c r="AP79" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ79" t="n">
         <v>1.53</v>
@@ -19226,7 +19226,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ86" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR86" t="n">
         <v>2.15</v>
@@ -22714,7 +22714,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ102" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR102" t="n">
         <v>1.8</v>
@@ -23365,7 +23365,7 @@
         <v>0.25</v>
       </c>
       <c r="AP105" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ105" t="n">
         <v>1</v>
@@ -25112,7 +25112,7 @@
         <v>1</v>
       </c>
       <c r="AQ113" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR113" t="n">
         <v>1.02</v>
@@ -32306,7 +32306,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ146" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR146" t="n">
         <v>1.76</v>
@@ -32739,7 +32739,7 @@
         <v>1.8</v>
       </c>
       <c r="AP148" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ148" t="n">
         <v>1.36</v>
@@ -34483,7 +34483,7 @@
         <v>0.5</v>
       </c>
       <c r="AP156" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ156" t="n">
         <v>0.47</v>
@@ -38628,7 +38628,7 @@
         <v>1</v>
       </c>
       <c r="AQ175" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR175" t="n">
         <v>1.36</v>
@@ -42334,7 +42334,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ192" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR192" t="n">
         <v>1.83</v>
@@ -44950,7 +44950,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ204" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR204" t="n">
         <v>1.18</v>
@@ -45601,7 +45601,7 @@
         <v>1.17</v>
       </c>
       <c r="AP207" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ207" t="n">
         <v>1.6</v>
@@ -50397,7 +50397,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP229" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ229" t="n">
         <v>0.87</v>
@@ -52577,7 +52577,7 @@
         <v>1.71</v>
       </c>
       <c r="AP239" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ239" t="n">
         <v>1.5</v>
@@ -55632,7 +55632,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ253" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR253" t="n">
         <v>1.85</v>
@@ -68709,7 +68709,7 @@
         <v>1.7</v>
       </c>
       <c r="AP313" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ313" t="n">
         <v>1.13</v>
@@ -69148,7 +69148,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ315" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR315" t="n">
         <v>1.44</v>
@@ -78301,7 +78301,7 @@
         <v>1.92</v>
       </c>
       <c r="AP357" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ357" t="n">
         <v>1.93</v>
@@ -78522,7 +78522,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ358" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR358" t="n">
         <v>1.41</v>
@@ -83100,7 +83100,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ379" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR379" t="n">
         <v>1.43</v>
@@ -83315,7 +83315,7 @@
         <v>0.38</v>
       </c>
       <c r="AP380" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ380" t="n">
         <v>0.44</v>
@@ -85062,7 +85062,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ388" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR388" t="n">
         <v>1.58</v>
@@ -96256,6 +96256,224 @@
       </c>
       <c r="BP439" t="n">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="1" t="n">
+        <v>439</v>
+      </c>
+      <c r="B440" t="n">
+        <v>8229525</v>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E440" s="2" t="n">
+        <v>45916.85416666666</v>
+      </c>
+      <c r="F440" t="n">
+        <v>0</v>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>Inter Miami</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>Seattle Sounders</t>
+        </is>
+      </c>
+      <c r="I440" t="n">
+        <v>2</v>
+      </c>
+      <c r="J440" t="n">
+        <v>0</v>
+      </c>
+      <c r="K440" t="n">
+        <v>2</v>
+      </c>
+      <c r="L440" t="n">
+        <v>3</v>
+      </c>
+      <c r="M440" t="n">
+        <v>1</v>
+      </c>
+      <c r="N440" t="n">
+        <v>4</v>
+      </c>
+      <c r="O440" t="inlineStr">
+        <is>
+          <t>['12', '41', '52']</t>
+        </is>
+      </c>
+      <c r="P440" t="inlineStr">
+        <is>
+          <t>['69']</t>
+        </is>
+      </c>
+      <c r="Q440" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="R440" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S440" t="n">
+        <v>4</v>
+      </c>
+      <c r="T440" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="U440" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="V440" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W440" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X440" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y440" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z440" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA440" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB440" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AC440" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD440" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE440" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF440" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG440" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AH440" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AI440" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AJ440" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AK440" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AL440" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM440" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AN440" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO440" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AP440" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AQ440" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AR440" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AS440" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AT440" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AU440" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV440" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW440" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX440" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY440" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ440" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA440" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB440" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC440" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD440" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BE440" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF440" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BG440" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH440" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="BI440" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BJ440" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BK440" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BL440" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BM440" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BN440" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BO440" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BP440" t="n">
+        <v>1.32</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP440"/>
+  <dimension ref="A1:BP442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4399,7 +4399,7 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ18" t="n">
         <v>1.07</v>
@@ -4838,7 +4838,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR20" t="n">
         <v>0</v>
@@ -7672,7 +7672,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR33" t="n">
         <v>2.2</v>
@@ -7887,7 +7887,7 @@
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ34" t="n">
         <v>1.6</v>
@@ -9849,7 +9849,7 @@
         <v>3</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ43" t="n">
         <v>2.14</v>
@@ -11593,7 +11593,7 @@
         <v>1</v>
       </c>
       <c r="AP51" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ51" t="n">
         <v>1.33</v>
@@ -13122,7 +13122,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ58" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR58" t="n">
         <v>1.41</v>
@@ -15738,7 +15738,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ70" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR70" t="n">
         <v>1.65</v>
@@ -15953,7 +15953,7 @@
         <v>2</v>
       </c>
       <c r="AP71" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ71" t="n">
         <v>1.36</v>
@@ -18136,7 +18136,7 @@
         <v>0.87</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR81" t="n">
         <v>1.35</v>
@@ -19662,7 +19662,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ88" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR88" t="n">
         <v>1.82</v>
@@ -20531,7 +20531,7 @@
         <v>0.67</v>
       </c>
       <c r="AP92" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ92" t="n">
         <v>0.44</v>
@@ -22278,7 +22278,7 @@
         <v>1</v>
       </c>
       <c r="AQ100" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR100" t="n">
         <v>1.23</v>
@@ -22929,7 +22929,7 @@
         <v>1.33</v>
       </c>
       <c r="AP103" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ103" t="n">
         <v>1.93</v>
@@ -24237,7 +24237,7 @@
         <v>2</v>
       </c>
       <c r="AP109" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ109" t="n">
         <v>1.53</v>
@@ -26638,7 +26638,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ120" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR120" t="n">
         <v>1.69</v>
@@ -29469,7 +29469,7 @@
         <v>0.4</v>
       </c>
       <c r="AP133" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ133" t="n">
         <v>1</v>
@@ -29690,7 +29690,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ134" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR134" t="n">
         <v>1.22</v>
@@ -36227,7 +36227,7 @@
         <v>1.8</v>
       </c>
       <c r="AP164" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ164" t="n">
         <v>1.93</v>
@@ -37753,7 +37753,7 @@
         <v>0.25</v>
       </c>
       <c r="AP171" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ171" t="n">
         <v>0.87</v>
@@ -38192,7 +38192,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ173" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR173" t="n">
         <v>1.67</v>
@@ -39718,7 +39718,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ180" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR180" t="n">
         <v>1.94</v>
@@ -40154,7 +40154,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ182" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR182" t="n">
         <v>1.41</v>
@@ -41895,7 +41895,7 @@
         <v>1.67</v>
       </c>
       <c r="AP190" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ190" t="n">
         <v>1.14</v>
@@ -42985,7 +42985,7 @@
         <v>0.33</v>
       </c>
       <c r="AP195" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ195" t="n">
         <v>0.47</v>
@@ -45822,7 +45822,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ208" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR208" t="n">
         <v>1.44</v>
@@ -46476,7 +46476,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ211" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR211" t="n">
         <v>1.48</v>
@@ -47130,7 +47130,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ214" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR214" t="n">
         <v>1.2</v>
@@ -48435,7 +48435,7 @@
         <v>2</v>
       </c>
       <c r="AP220" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ220" t="n">
         <v>1.57</v>
@@ -48871,7 +48871,7 @@
         <v>1.71</v>
       </c>
       <c r="AP222" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ222" t="n">
         <v>1.57</v>
@@ -50615,7 +50615,7 @@
         <v>1</v>
       </c>
       <c r="AP230" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ230" t="n">
         <v>1.2</v>
@@ -52580,7 +52580,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ239" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR239" t="n">
         <v>1.41</v>
@@ -56065,7 +56065,7 @@
         <v>0.29</v>
       </c>
       <c r="AP255" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ255" t="n">
         <v>0.57</v>
@@ -58463,7 +58463,7 @@
         <v>1</v>
       </c>
       <c r="AP266" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ266" t="n">
         <v>0.8</v>
@@ -64349,7 +64349,7 @@
         <v>1.14</v>
       </c>
       <c r="AP293" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ293" t="n">
         <v>1</v>
@@ -66311,7 +66311,7 @@
         <v>0.5</v>
       </c>
       <c r="AP302" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ302" t="n">
         <v>0.53</v>
@@ -67186,7 +67186,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ306" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR306" t="n">
         <v>1.74</v>
@@ -69802,7 +69802,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ318" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR318" t="n">
         <v>1.51</v>
@@ -70017,7 +70017,7 @@
         <v>1.3</v>
       </c>
       <c r="AP319" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ319" t="n">
         <v>1.2</v>
@@ -72636,7 +72636,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ331" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR331" t="n">
         <v>1.52</v>
@@ -72854,7 +72854,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ332" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR332" t="n">
         <v>1.82</v>
@@ -76339,7 +76339,7 @@
         <v>1.83</v>
       </c>
       <c r="AP348" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ348" t="n">
         <v>1.93</v>
@@ -79827,7 +79827,7 @@
         <v>1.17</v>
       </c>
       <c r="AP364" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ364" t="n">
         <v>1.13</v>
@@ -81138,7 +81138,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ370" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR370" t="n">
         <v>1.57</v>
@@ -83972,7 +83972,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ383" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR383" t="n">
         <v>1.27</v>
@@ -84408,7 +84408,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ385" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR385" t="n">
         <v>1.17</v>
@@ -85931,7 +85931,7 @@
         <v>1.31</v>
       </c>
       <c r="AP392" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ392" t="n">
         <v>1.13</v>
@@ -88114,7 +88114,7 @@
         <v>1</v>
       </c>
       <c r="AQ402" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR402" t="n">
         <v>1.22</v>
@@ -88547,7 +88547,7 @@
         <v>1.77</v>
       </c>
       <c r="AP404" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ404" t="n">
         <v>1.93</v>
@@ -90294,7 +90294,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ412" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR412" t="n">
         <v>1.39</v>
@@ -90727,7 +90727,7 @@
         <v>0.64</v>
       </c>
       <c r="AP414" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ414" t="n">
         <v>0.8</v>
@@ -94218,7 +94218,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ430" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR430" t="n">
         <v>1.36</v>
@@ -94872,7 +94872,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ433" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR433" t="n">
         <v>1.75</v>
@@ -95305,7 +95305,7 @@
         <v>0.79</v>
       </c>
       <c r="AP435" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ435" t="n">
         <v>0.73</v>
@@ -96474,6 +96474,442 @@
       </c>
       <c r="BP440" t="n">
         <v>1.32</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="1" t="n">
+        <v>440</v>
+      </c>
+      <c r="B441" t="n">
+        <v>8229798</v>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E441" s="2" t="n">
+        <v>45917.85416666666</v>
+      </c>
+      <c r="F441" t="n">
+        <v>0</v>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>Columbus Crew</t>
+        </is>
+      </c>
+      <c r="I441" t="n">
+        <v>1</v>
+      </c>
+      <c r="J441" t="n">
+        <v>1</v>
+      </c>
+      <c r="K441" t="n">
+        <v>2</v>
+      </c>
+      <c r="L441" t="n">
+        <v>3</v>
+      </c>
+      <c r="M441" t="n">
+        <v>2</v>
+      </c>
+      <c r="N441" t="n">
+        <v>5</v>
+      </c>
+      <c r="O441" t="inlineStr">
+        <is>
+          <t>['45+3', '73', '90+4']</t>
+        </is>
+      </c>
+      <c r="P441" t="inlineStr">
+        <is>
+          <t>['40', '60']</t>
+        </is>
+      </c>
+      <c r="Q441" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R441" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S441" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T441" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="U441" t="n">
+        <v>3</v>
+      </c>
+      <c r="V441" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="W441" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X441" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y441" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z441" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AA441" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AB441" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AC441" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD441" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE441" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF441" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AG441" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AH441" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AI441" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ441" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AK441" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL441" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM441" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AN441" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AO441" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP441" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AQ441" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR441" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AS441" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AT441" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AU441" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV441" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW441" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX441" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY441" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ441" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA441" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB441" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC441" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD441" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BE441" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF441" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BG441" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BH441" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI441" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BJ441" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BK441" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BL441" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BM441" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BN441" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BO441" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BP441" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="1" t="n">
+        <v>441</v>
+      </c>
+      <c r="B442" t="n">
+        <v>8229557</v>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E442" s="2" t="n">
+        <v>45917.9375</v>
+      </c>
+      <c r="F442" t="n">
+        <v>0</v>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>Los Angeles FC</t>
+        </is>
+      </c>
+      <c r="I442" t="n">
+        <v>0</v>
+      </c>
+      <c r="J442" t="n">
+        <v>2</v>
+      </c>
+      <c r="K442" t="n">
+        <v>2</v>
+      </c>
+      <c r="L442" t="n">
+        <v>1</v>
+      </c>
+      <c r="M442" t="n">
+        <v>4</v>
+      </c>
+      <c r="N442" t="n">
+        <v>5</v>
+      </c>
+      <c r="O442" t="inlineStr">
+        <is>
+          <t>['76']</t>
+        </is>
+      </c>
+      <c r="P442" t="inlineStr">
+        <is>
+          <t>['3', '16', '82', '88']</t>
+        </is>
+      </c>
+      <c r="Q442" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="R442" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="S442" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T442" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U442" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="V442" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W442" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X442" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Y442" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z442" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA442" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB442" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AC442" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD442" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE442" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF442" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AG442" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH442" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI442" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AJ442" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AK442" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AL442" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM442" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AN442" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AO442" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AP442" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AQ442" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR442" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AS442" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AT442" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU442" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV442" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW442" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX442" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY442" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ442" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA442" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB442" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC442" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD442" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BE442" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="BF442" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BG442" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH442" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="BI442" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BJ442" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BK442" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BL442" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BM442" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BN442" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BO442" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP442" t="n">
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
@@ -96846,13 +96846,13 @@
         <v>3</v>
       </c>
       <c r="AU442" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV442" t="n">
         <v>6</v>
       </c>
       <c r="AW442" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX442" t="n">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP442"/>
+  <dimension ref="A1:BP444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2440,7 +2440,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -4617,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="AQ19" t="n">
         <v>1.93</v>
@@ -7887,7 +7887,7 @@
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ34" t="n">
         <v>1.6</v>
@@ -10288,7 +10288,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR45" t="n">
         <v>1.61</v>
@@ -11593,10 +11593,10 @@
         <v>1</v>
       </c>
       <c r="AP51" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR51" t="n">
         <v>1.97</v>
@@ -13337,7 +13337,7 @@
         <v>0</v>
       </c>
       <c r="AP59" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="AQ59" t="n">
         <v>1.13</v>
@@ -14645,7 +14645,7 @@
         <v>2</v>
       </c>
       <c r="AP65" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="AQ65" t="n">
         <v>0.53</v>
@@ -17482,7 +17482,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ78" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR78" t="n">
         <v>1.39</v>
@@ -20970,7 +20970,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ94" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR94" t="n">
         <v>1.49</v>
@@ -21403,7 +21403,7 @@
         <v>1.33</v>
       </c>
       <c r="AP96" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="AQ96" t="n">
         <v>1.6</v>
@@ -22929,7 +22929,7 @@
         <v>1.33</v>
       </c>
       <c r="AP103" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ103" t="n">
         <v>1.93</v>
@@ -23804,7 +23804,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ107" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR107" t="n">
         <v>1.45</v>
@@ -24237,7 +24237,7 @@
         <v>2</v>
       </c>
       <c r="AP109" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ109" t="n">
         <v>1.53</v>
@@ -24458,7 +24458,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ110" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR110" t="n">
         <v>0</v>
@@ -27507,7 +27507,7 @@
         <v>0.5</v>
       </c>
       <c r="AP124" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="AQ124" t="n">
         <v>0.57</v>
@@ -30777,7 +30777,7 @@
         <v>1</v>
       </c>
       <c r="AP139" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="AQ139" t="n">
         <v>0.8</v>
@@ -31434,7 +31434,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ142" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR142" t="n">
         <v>1.48</v>
@@ -33614,7 +33614,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ152" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR152" t="n">
         <v>1.04</v>
@@ -34050,7 +34050,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ154" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR154" t="n">
         <v>1.63</v>
@@ -36227,7 +36227,7 @@
         <v>1.8</v>
       </c>
       <c r="AP164" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ164" t="n">
         <v>1.93</v>
@@ -37320,7 +37320,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ169" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR169" t="n">
         <v>1.77</v>
@@ -37753,7 +37753,7 @@
         <v>0.25</v>
       </c>
       <c r="AP171" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ171" t="n">
         <v>0.87</v>
@@ -38189,7 +38189,7 @@
         <v>2.5</v>
       </c>
       <c r="AP173" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="AQ173" t="n">
         <v>1.4</v>
@@ -38410,7 +38410,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ174" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR174" t="n">
         <v>2.08</v>
@@ -40372,7 +40372,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ183" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR183" t="n">
         <v>1.81</v>
@@ -40587,7 +40587,7 @@
         <v>0.29</v>
       </c>
       <c r="AP184" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="AQ184" t="n">
         <v>0.44</v>
@@ -42985,7 +42985,7 @@
         <v>0.33</v>
       </c>
       <c r="AP195" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ195" t="n">
         <v>0.47</v>
@@ -46691,7 +46691,7 @@
         <v>1.83</v>
       </c>
       <c r="AP212" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="AQ212" t="n">
         <v>1.57</v>
@@ -48002,7 +48002,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ218" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR218" t="n">
         <v>1.31</v>
@@ -48871,7 +48871,7 @@
         <v>1.71</v>
       </c>
       <c r="AP222" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ222" t="n">
         <v>1.57</v>
@@ -49964,7 +49964,7 @@
         <v>0.87</v>
       </c>
       <c r="AQ227" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR227" t="n">
         <v>1.12</v>
@@ -50182,7 +50182,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ228" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR228" t="n">
         <v>1.45</v>
@@ -50615,7 +50615,7 @@
         <v>1</v>
       </c>
       <c r="AP230" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ230" t="n">
         <v>1.2</v>
@@ -52798,7 +52798,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ240" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR240" t="n">
         <v>1.23</v>
@@ -53452,7 +53452,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ243" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR243" t="n">
         <v>1.21</v>
@@ -56065,7 +56065,7 @@
         <v>0.29</v>
       </c>
       <c r="AP255" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ255" t="n">
         <v>0.57</v>
@@ -57155,10 +57155,10 @@
         <v>0.78</v>
       </c>
       <c r="AP260" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="AQ260" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR260" t="n">
         <v>1.7</v>
@@ -59774,7 +59774,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ272" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR272" t="n">
         <v>1.38</v>
@@ -63262,7 +63262,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ288" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR288" t="n">
         <v>1.56</v>
@@ -64349,7 +64349,7 @@
         <v>1.14</v>
       </c>
       <c r="AP293" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ293" t="n">
         <v>1</v>
@@ -66968,7 +66968,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ305" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR305" t="n">
         <v>1.32</v>
@@ -68491,7 +68491,7 @@
         <v>0.64</v>
       </c>
       <c r="AP312" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="AQ312" t="n">
         <v>0.47</v>
@@ -69584,7 +69584,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ317" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR317" t="n">
         <v>1.46</v>
@@ -71761,7 +71761,7 @@
         <v>0.75</v>
       </c>
       <c r="AP327" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="AQ327" t="n">
         <v>0.87</v>
@@ -71982,7 +71982,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ328" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR328" t="n">
         <v>1.38</v>
@@ -74162,7 +74162,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ338" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR338" t="n">
         <v>1.35</v>
@@ -78955,7 +78955,7 @@
         <v>0.91</v>
       </c>
       <c r="AP360" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="AQ360" t="n">
         <v>0.87</v>
@@ -80699,7 +80699,7 @@
         <v>1</v>
       </c>
       <c r="AP368" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="AQ368" t="n">
         <v>1</v>
@@ -82446,7 +82446,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ376" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR376" t="n">
         <v>1.48</v>
@@ -85931,7 +85931,7 @@
         <v>1.31</v>
       </c>
       <c r="AP392" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ392" t="n">
         <v>1.13</v>
@@ -86585,7 +86585,7 @@
         <v>1.69</v>
       </c>
       <c r="AP395" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="AQ395" t="n">
         <v>1.57</v>
@@ -87242,7 +87242,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ398" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR398" t="n">
         <v>1.69</v>
@@ -90512,7 +90512,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ413" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR413" t="n">
         <v>1.28</v>
@@ -90727,7 +90727,7 @@
         <v>0.64</v>
       </c>
       <c r="AP414" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ414" t="n">
         <v>0.8</v>
@@ -92692,7 +92692,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ423" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR423" t="n">
         <v>1.56</v>
@@ -96613,7 +96613,7 @@
         <v>1.5</v>
       </c>
       <c r="AP441" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ441" t="n">
         <v>1.4</v>
@@ -96910,6 +96910,442 @@
       </c>
       <c r="BP442" t="n">
         <v>1.26</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="1" t="n">
+        <v>442</v>
+      </c>
+      <c r="B443" t="n">
+        <v>8229526</v>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E443" s="2" t="n">
+        <v>45920.54166666666</v>
+      </c>
+      <c r="F443" t="n">
+        <v>0</v>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="I443" t="n">
+        <v>1</v>
+      </c>
+      <c r="J443" t="n">
+        <v>0</v>
+      </c>
+      <c r="K443" t="n">
+        <v>1</v>
+      </c>
+      <c r="L443" t="n">
+        <v>2</v>
+      </c>
+      <c r="M443" t="n">
+        <v>0</v>
+      </c>
+      <c r="N443" t="n">
+        <v>2</v>
+      </c>
+      <c r="O443" t="inlineStr">
+        <is>
+          <t>['11', '58']</t>
+        </is>
+      </c>
+      <c r="P443" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q443" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R443" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S443" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T443" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U443" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V443" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W443" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X443" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y443" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z443" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA443" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB443" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AC443" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD443" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE443" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AF443" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AG443" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AH443" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AI443" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AJ443" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK443" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL443" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM443" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AN443" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AO443" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AP443" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AQ443" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR443" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AS443" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AT443" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU443" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV443" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW443" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX443" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY443" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ443" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA443" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB443" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC443" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD443" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BE443" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="BF443" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BG443" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH443" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="BI443" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BJ443" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BK443" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BL443" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BM443" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BN443" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BO443" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BP443" t="n">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="1" t="n">
+        <v>443</v>
+      </c>
+      <c r="B444" t="n">
+        <v>8229563</v>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E444" s="2" t="n">
+        <v>45920.64583333334</v>
+      </c>
+      <c r="F444" t="n">
+        <v>0</v>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>Philadelphia Union</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>New England Revolution</t>
+        </is>
+      </c>
+      <c r="I444" t="n">
+        <v>0</v>
+      </c>
+      <c r="J444" t="n">
+        <v>0</v>
+      </c>
+      <c r="K444" t="n">
+        <v>0</v>
+      </c>
+      <c r="L444" t="n">
+        <v>1</v>
+      </c>
+      <c r="M444" t="n">
+        <v>0</v>
+      </c>
+      <c r="N444" t="n">
+        <v>1</v>
+      </c>
+      <c r="O444" t="inlineStr">
+        <is>
+          <t>['70']</t>
+        </is>
+      </c>
+      <c r="P444" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q444" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="R444" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S444" t="n">
+        <v>5</v>
+      </c>
+      <c r="T444" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U444" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="V444" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="W444" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="X444" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y444" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z444" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AA444" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AB444" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AC444" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD444" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE444" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF444" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AG444" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH444" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI444" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AJ444" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AK444" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AL444" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AM444" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AN444" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AO444" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AP444" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AQ444" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR444" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AS444" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AT444" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="AU444" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV444" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW444" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX444" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY444" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ444" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA444" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB444" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC444" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD444" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BE444" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="BF444" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BG444" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BH444" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI444" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BJ444" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BK444" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BL444" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BM444" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BN444" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BO444" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BP444" t="n">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP444"/>
+  <dimension ref="A1:BP445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AQ7" t="n">
         <v>0.87</v>
@@ -3966,7 +3966,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ16" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -8323,7 +8323,7 @@
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AQ36" t="n">
         <v>0.47</v>
@@ -9852,7 +9852,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ43" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AR43" t="n">
         <v>1.28</v>
@@ -13773,7 +13773,7 @@
         <v>3</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AQ61" t="n">
         <v>1.57</v>
@@ -16828,7 +16828,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ75" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AR75" t="n">
         <v>1.68</v>
@@ -17915,7 +17915,7 @@
         <v>0.67</v>
       </c>
       <c r="AP80" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AQ80" t="n">
         <v>1.33</v>
@@ -21621,7 +21621,7 @@
         <v>2.33</v>
       </c>
       <c r="AP97" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AQ97" t="n">
         <v>1.36</v>
@@ -23801,7 +23801,7 @@
         <v>0.33</v>
       </c>
       <c r="AP107" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AQ107" t="n">
         <v>1.25</v>
@@ -25548,7 +25548,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ115" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AR115" t="n">
         <v>1.63</v>
@@ -28382,7 +28382,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ128" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AR128" t="n">
         <v>1.39</v>
@@ -33393,7 +33393,7 @@
         <v>0.75</v>
       </c>
       <c r="AP151" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AQ151" t="n">
         <v>1.13</v>
@@ -38846,7 +38846,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ176" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AR176" t="n">
         <v>1.49</v>
@@ -43857,7 +43857,7 @@
         <v>1.8</v>
       </c>
       <c r="AP199" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AQ199" t="n">
         <v>1.53</v>
@@ -49089,7 +49089,7 @@
         <v>1.63</v>
       </c>
       <c r="AP223" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AQ223" t="n">
         <v>1.93</v>
@@ -49525,7 +49525,7 @@
         <v>1.43</v>
       </c>
       <c r="AP225" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AQ225" t="n">
         <v>1.6</v>
@@ -51054,7 +51054,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ232" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AR232" t="n">
         <v>1.93</v>
@@ -58030,7 +58030,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ264" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AR264" t="n">
         <v>1.6</v>
@@ -61082,7 +61082,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ278" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AR278" t="n">
         <v>1.81</v>
@@ -63044,7 +63044,7 @@
         <v>1</v>
       </c>
       <c r="AQ287" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AR287" t="n">
         <v>1.03</v>
@@ -68930,7 +68930,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ314" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AR314" t="n">
         <v>1.55</v>
@@ -71543,7 +71543,7 @@
         <v>1.64</v>
       </c>
       <c r="AP326" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AQ326" t="n">
         <v>1.57</v>
@@ -74159,7 +74159,7 @@
         <v>0.58</v>
       </c>
       <c r="AP338" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AQ338" t="n">
         <v>1</v>
@@ -78519,7 +78519,7 @@
         <v>1.09</v>
       </c>
       <c r="AP358" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AQ358" t="n">
         <v>1.07</v>
@@ -81792,7 +81792,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ373" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AR373" t="n">
         <v>1.53</v>
@@ -86152,7 +86152,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ393" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AR393" t="n">
         <v>1.78</v>
@@ -89201,7 +89201,7 @@
         <v>1</v>
       </c>
       <c r="AP407" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AQ407" t="n">
         <v>1</v>
@@ -92038,7 +92038,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ420" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AR420" t="n">
         <v>1.82</v>
@@ -94215,7 +94215,7 @@
         <v>1.38</v>
       </c>
       <c r="AP430" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AQ430" t="n">
         <v>1.4</v>
@@ -95827,7 +95827,7 @@
         <v>437</v>
       </c>
       <c r="B438" t="n">
-        <v>8229510</v>
+        <v>8229578</v>
       </c>
       <c r="C438" t="inlineStr">
         <is>
@@ -95847,197 +95847,197 @@
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="I438" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J438" t="n">
         <v>0</v>
       </c>
       <c r="K438" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L438" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M438" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N438" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O438" t="inlineStr">
         <is>
-          <t>['28', '73']</t>
+          <t>['90+5']</t>
         </is>
       </c>
       <c r="P438" t="inlineStr">
         <is>
-          <t>['70']</t>
+          <t>['74', '77', '90+2']</t>
         </is>
       </c>
       <c r="Q438" t="n">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="R438" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S438" t="n">
-        <v>3.99</v>
+        <v>4.4</v>
       </c>
       <c r="T438" t="n">
         <v>1.31</v>
       </c>
       <c r="U438" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="V438" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="W438" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="X438" t="n">
-        <v>5.6</v>
+        <v>5.25</v>
       </c>
       <c r="Y438" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z438" t="n">
-        <v>1.99</v>
+        <v>1.84</v>
       </c>
       <c r="AA438" t="n">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="AB438" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="AC438" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AD438" t="n">
         <v>10</v>
       </c>
       <c r="AE438" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AF438" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AG438" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AH438" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AI438" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AJ438" t="n">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="AK438" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AL438" t="n">
         <v>1.26</v>
       </c>
-      <c r="AL438" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AM438" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AN438" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AO438" t="n">
-        <v>0.5</v>
+        <v>1.86</v>
       </c>
       <c r="AP438" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AQ438" t="n">
-        <v>0.47</v>
+        <v>1.93</v>
       </c>
       <c r="AR438" t="n">
-        <v>1.41</v>
+        <v>1.56</v>
       </c>
       <c r="AS438" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AT438" t="n">
-        <v>2.52</v>
+        <v>2.81</v>
       </c>
       <c r="AU438" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="AV438" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW438" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX438" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY438" t="n">
+        <v>28</v>
+      </c>
+      <c r="AZ438" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA438" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB438" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC438" t="n">
         <v>10</v>
       </c>
-      <c r="AX438" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY438" t="n">
-        <v>14</v>
-      </c>
-      <c r="AZ438" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA438" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB438" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC438" t="n">
-        <v>8</v>
-      </c>
       <c r="BD438" t="n">
-        <v>1.87</v>
+        <v>1.35</v>
       </c>
       <c r="BE438" t="n">
-        <v>6.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF438" t="n">
-        <v>2.39</v>
+        <v>3.54</v>
       </c>
       <c r="BG438" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BH438" t="n">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="BI438" t="n">
         <v>1.47</v>
       </c>
       <c r="BJ438" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="BK438" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="BL438" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="BM438" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="BN438" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="BO438" t="n">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="BP438" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="439">
@@ -96045,7 +96045,7 @@
         <v>438</v>
       </c>
       <c r="B439" t="n">
-        <v>8229578</v>
+        <v>8229510</v>
       </c>
       <c r="C439" t="inlineStr">
         <is>
@@ -96065,197 +96065,197 @@
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="I439" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J439" t="n">
         <v>0</v>
       </c>
       <c r="K439" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L439" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M439" t="n">
+        <v>1</v>
+      </c>
+      <c r="N439" t="n">
         <v>3</v>
       </c>
-      <c r="N439" t="n">
-        <v>4</v>
-      </c>
       <c r="O439" t="inlineStr">
         <is>
-          <t>['90+5']</t>
+          <t>['28', '73']</t>
         </is>
       </c>
       <c r="P439" t="inlineStr">
         <is>
-          <t>['74', '77', '90+2']</t>
+          <t>['70']</t>
         </is>
       </c>
       <c r="Q439" t="n">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="R439" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S439" t="n">
-        <v>4.4</v>
+        <v>3.99</v>
       </c>
       <c r="T439" t="n">
         <v>1.31</v>
       </c>
       <c r="U439" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="V439" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="W439" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="X439" t="n">
-        <v>5.25</v>
+        <v>5.6</v>
       </c>
       <c r="Y439" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z439" t="n">
-        <v>1.84</v>
+        <v>1.99</v>
       </c>
       <c r="AA439" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="AB439" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="AC439" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AD439" t="n">
         <v>10</v>
       </c>
       <c r="AE439" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="AF439" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AG439" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AH439" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AI439" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ439" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AK439" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AL439" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM439" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN439" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AO439" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP439" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AQ439" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="AR439" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AS439" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AT439" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AU439" t="n">
         <v>4</v>
       </c>
-      <c r="AG439" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AH439" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AI439" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AJ439" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AK439" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AL439" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AM439" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AN439" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AO439" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AP439" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AQ439" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AR439" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AS439" t="n">
+      <c r="AV439" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW439" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX439" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY439" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ439" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA439" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB439" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC439" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD439" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BE439" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="BF439" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="BG439" t="n">
         <v>1.25</v>
       </c>
-      <c r="AT439" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AU439" t="n">
-        <v>14</v>
-      </c>
-      <c r="AV439" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW439" t="n">
-        <v>14</v>
-      </c>
-      <c r="AX439" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY439" t="n">
-        <v>28</v>
-      </c>
-      <c r="AZ439" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA439" t="n">
-        <v>9</v>
-      </c>
-      <c r="BB439" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC439" t="n">
-        <v>10</v>
-      </c>
-      <c r="BD439" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BE439" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF439" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="BG439" t="n">
-        <v>1.24</v>
-      </c>
       <c r="BH439" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="BI439" t="n">
         <v>1.47</v>
       </c>
       <c r="BJ439" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="BK439" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="BL439" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="BM439" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="BN439" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="BO439" t="n">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="BP439" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="440">
@@ -97346,6 +97346,224 @@
       </c>
       <c r="BP444" t="n">
         <v>1.5</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="1" t="n">
+        <v>444</v>
+      </c>
+      <c r="B445" t="n">
+        <v>8229588</v>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E445" s="2" t="n">
+        <v>45920.72916666666</v>
+      </c>
+      <c r="F445" t="n">
+        <v>0</v>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>Atlanta United FC</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="I445" t="n">
+        <v>0</v>
+      </c>
+      <c r="J445" t="n">
+        <v>1</v>
+      </c>
+      <c r="K445" t="n">
+        <v>1</v>
+      </c>
+      <c r="L445" t="n">
+        <v>1</v>
+      </c>
+      <c r="M445" t="n">
+        <v>1</v>
+      </c>
+      <c r="N445" t="n">
+        <v>2</v>
+      </c>
+      <c r="O445" t="inlineStr">
+        <is>
+          <t>['61']</t>
+        </is>
+      </c>
+      <c r="P445" t="inlineStr">
+        <is>
+          <t>['32']</t>
+        </is>
+      </c>
+      <c r="Q445" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R445" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S445" t="n">
+        <v>3</v>
+      </c>
+      <c r="T445" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="U445" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="V445" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W445" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X445" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Y445" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z445" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AA445" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB445" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AC445" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD445" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE445" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF445" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AG445" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH445" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AI445" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ445" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AK445" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AL445" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM445" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN445" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO445" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AP445" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ445" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AR445" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AS445" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AT445" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AU445" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV445" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW445" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX445" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY445" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ445" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA445" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB445" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC445" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD445" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BE445" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF445" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BG445" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BH445" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI445" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BJ445" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BK445" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BL445" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BM445" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="BN445" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BO445" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP445" t="n">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
@@ -97506,13 +97506,13 @@
         <v>4</v>
       </c>
       <c r="AW445" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX445" t="n">
         <v>2</v>
       </c>
       <c r="AY445" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ445" t="n">
         <v>6</v>
@@ -98826,13 +98826,13 @@
         <v>8</v>
       </c>
       <c r="BA451" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BB451" t="n">
         <v>10</v>
       </c>
       <c r="BC451" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD451" t="n">
         <v>1.93</v>
@@ -99026,7 +99026,7 @@
         <v>2.92</v>
       </c>
       <c r="AU452" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV452" t="n">
         <v>9</v>
@@ -99038,7 +99038,7 @@
         <v>9</v>
       </c>
       <c r="AY452" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ452" t="n">
         <v>18</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP455"/>
+  <dimension ref="A1:BP457"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ2" t="n">
         <v>1.93</v>
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ12" t="n">
         <v>0.73</v>
@@ -3312,7 +3312,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -4402,7 +4402,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR18" t="n">
         <v>0</v>
@@ -6797,7 +6797,7 @@
         <v>1</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ29" t="n">
         <v>1.33</v>
@@ -9413,7 +9413,7 @@
         <v>1</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ41" t="n">
         <v>0.8100000000000001</v>
@@ -11157,7 +11157,7 @@
         <v>0</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ49" t="n">
         <v>1.27</v>
@@ -12468,7 +12468,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ55" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR55" t="n">
         <v>1.02</v>
@@ -12686,7 +12686,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR56" t="n">
         <v>1.81</v>
@@ -16825,7 +16825,7 @@
         <v>3</v>
       </c>
       <c r="AP75" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ75" t="n">
         <v>2.07</v>
@@ -18790,7 +18790,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ84" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR84" t="n">
         <v>1.85</v>
@@ -19226,7 +19226,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ86" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR86" t="n">
         <v>2.15</v>
@@ -21839,7 +21839,7 @@
         <v>1.5</v>
       </c>
       <c r="AP98" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ98" t="n">
         <v>1.07</v>
@@ -22714,7 +22714,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ102" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR102" t="n">
         <v>1.8</v>
@@ -25112,7 +25112,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ113" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR113" t="n">
         <v>1.02</v>
@@ -25330,7 +25330,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ114" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR114" t="n">
         <v>1.89</v>
@@ -25981,7 +25981,7 @@
         <v>1.5</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ117" t="n">
         <v>1.13</v>
@@ -26853,7 +26853,7 @@
         <v>0.5</v>
       </c>
       <c r="AP121" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ121" t="n">
         <v>0.44</v>
@@ -31652,7 +31652,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ143" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR143" t="n">
         <v>1.63</v>
@@ -32306,7 +32306,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ146" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR146" t="n">
         <v>1.76</v>
@@ -32957,7 +32957,7 @@
         <v>1</v>
       </c>
       <c r="AP149" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ149" t="n">
         <v>0.6899999999999999</v>
@@ -34701,7 +34701,7 @@
         <v>1.6</v>
       </c>
       <c r="AP157" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ157" t="n">
         <v>1.93</v>
@@ -35358,7 +35358,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ160" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR160" t="n">
         <v>1.88</v>
@@ -35791,7 +35791,7 @@
         <v>0.75</v>
       </c>
       <c r="AP162" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ162" t="n">
         <v>1.2</v>
@@ -38628,7 +38628,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ175" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR175" t="n">
         <v>1.36</v>
@@ -39064,7 +39064,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ177" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR177" t="n">
         <v>0.99</v>
@@ -41677,7 +41677,7 @@
         <v>0.2</v>
       </c>
       <c r="AP189" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ189" t="n">
         <v>0.57</v>
@@ -42331,10 +42331,10 @@
         <v>1.14</v>
       </c>
       <c r="AP192" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ192" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR192" t="n">
         <v>1.83</v>
@@ -44511,7 +44511,7 @@
         <v>2.2</v>
       </c>
       <c r="AP202" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ202" t="n">
         <v>1.67</v>
@@ -44950,7 +44950,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ204" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR204" t="n">
         <v>1.18</v>
@@ -45168,7 +45168,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ205" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR205" t="n">
         <v>1.69</v>
@@ -51269,10 +51269,10 @@
         <v>0.88</v>
       </c>
       <c r="AP233" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ233" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR233" t="n">
         <v>1.54</v>
@@ -54324,7 +54324,7 @@
         <v>1</v>
       </c>
       <c r="AQ247" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR247" t="n">
         <v>1.43</v>
@@ -55632,7 +55632,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ253" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR253" t="n">
         <v>1.85</v>
@@ -55847,7 +55847,7 @@
         <v>0.89</v>
       </c>
       <c r="AP254" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ254" t="n">
         <v>0.73</v>
@@ -57591,7 +57591,7 @@
         <v>0.63</v>
       </c>
       <c r="AP262" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ262" t="n">
         <v>0.63</v>
@@ -62826,7 +62826,7 @@
         <v>1</v>
       </c>
       <c r="AQ286" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR286" t="n">
         <v>1.43</v>
@@ -64131,7 +64131,7 @@
         <v>1.88</v>
       </c>
       <c r="AP292" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ292" t="n">
         <v>1.67</v>
@@ -67619,7 +67619,7 @@
         <v>1</v>
       </c>
       <c r="AP308" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ308" t="n">
         <v>0.8100000000000001</v>
@@ -69148,7 +69148,7 @@
         <v>1</v>
       </c>
       <c r="AQ315" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR315" t="n">
         <v>1.44</v>
@@ -69581,7 +69581,7 @@
         <v>1.45</v>
       </c>
       <c r="AP317" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ317" t="n">
         <v>1.25</v>
@@ -70453,7 +70453,7 @@
         <v>1.6</v>
       </c>
       <c r="AP321" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ321" t="n">
         <v>1.36</v>
@@ -73944,7 +73944,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ337" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR337" t="n">
         <v>1.36</v>
@@ -76993,7 +76993,7 @@
         <v>0.33</v>
       </c>
       <c r="AP351" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ351" t="n">
         <v>0.44</v>
@@ -77865,7 +77865,7 @@
         <v>1.1</v>
       </c>
       <c r="AP355" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ355" t="n">
         <v>1.07</v>
@@ -78522,7 +78522,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ358" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR358" t="n">
         <v>1.41</v>
@@ -81353,7 +81353,7 @@
         <v>1.18</v>
       </c>
       <c r="AP371" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ371" t="n">
         <v>1.2</v>
@@ -82664,7 +82664,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ377" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR377" t="n">
         <v>1.37</v>
@@ -83100,7 +83100,7 @@
         <v>1</v>
       </c>
       <c r="AQ379" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR379" t="n">
         <v>1.43</v>
@@ -83754,7 +83754,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ382" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR382" t="n">
         <v>1.43</v>
@@ -84623,7 +84623,7 @@
         <v>1.42</v>
       </c>
       <c r="AP386" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ386" t="n">
         <v>1.36</v>
@@ -85062,7 +85062,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ388" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR388" t="n">
         <v>1.58</v>
@@ -91381,7 +91381,7 @@
         <v>1.21</v>
       </c>
       <c r="AP417" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ417" t="n">
         <v>1.13</v>
@@ -92035,7 +92035,7 @@
         <v>2.08</v>
       </c>
       <c r="AP420" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ420" t="n">
         <v>2.07</v>
@@ -95827,7 +95827,7 @@
         <v>437</v>
       </c>
       <c r="B438" t="n">
-        <v>8229578</v>
+        <v>8229510</v>
       </c>
       <c r="C438" t="inlineStr">
         <is>
@@ -95847,197 +95847,197 @@
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="I438" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J438" t="n">
         <v>0</v>
       </c>
       <c r="K438" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L438" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M438" t="n">
+        <v>1</v>
+      </c>
+      <c r="N438" t="n">
         <v>3</v>
       </c>
-      <c r="N438" t="n">
-        <v>4</v>
-      </c>
       <c r="O438" t="inlineStr">
         <is>
-          <t>['90+5']</t>
+          <t>['28', '73']</t>
         </is>
       </c>
       <c r="P438" t="inlineStr">
         <is>
-          <t>['74', '77', '90+2']</t>
+          <t>['70']</t>
         </is>
       </c>
       <c r="Q438" t="n">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="R438" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S438" t="n">
-        <v>4.4</v>
+        <v>3.99</v>
       </c>
       <c r="T438" t="n">
         <v>1.31</v>
       </c>
       <c r="U438" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="V438" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="W438" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="X438" t="n">
-        <v>5.25</v>
+        <v>5.6</v>
       </c>
       <c r="Y438" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z438" t="n">
-        <v>1.84</v>
+        <v>1.99</v>
       </c>
       <c r="AA438" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="AB438" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="AC438" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AD438" t="n">
         <v>10</v>
       </c>
       <c r="AE438" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="AF438" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AG438" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AH438" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AI438" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ438" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AK438" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AL438" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM438" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN438" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AO438" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP438" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AQ438" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AR438" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AS438" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AT438" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AU438" t="n">
         <v>4</v>
       </c>
-      <c r="AG438" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AH438" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AI438" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AJ438" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AK438" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AL438" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AM438" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AN438" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AO438" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AP438" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AQ438" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AR438" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AS438" t="n">
+      <c r="AV438" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW438" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX438" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY438" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ438" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA438" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB438" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC438" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD438" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BE438" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="BF438" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="BG438" t="n">
         <v>1.25</v>
       </c>
-      <c r="AT438" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AU438" t="n">
-        <v>14</v>
-      </c>
-      <c r="AV438" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW438" t="n">
-        <v>14</v>
-      </c>
-      <c r="AX438" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY438" t="n">
-        <v>28</v>
-      </c>
-      <c r="AZ438" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA438" t="n">
-        <v>9</v>
-      </c>
-      <c r="BB438" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC438" t="n">
-        <v>10</v>
-      </c>
-      <c r="BD438" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BE438" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF438" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="BG438" t="n">
-        <v>1.24</v>
-      </c>
       <c r="BH438" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="BI438" t="n">
         <v>1.47</v>
       </c>
       <c r="BJ438" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="BK438" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="BL438" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="BM438" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="BN438" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="BO438" t="n">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="BP438" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="439">
@@ -96045,7 +96045,7 @@
         <v>438</v>
       </c>
       <c r="B439" t="n">
-        <v>8229510</v>
+        <v>8229578</v>
       </c>
       <c r="C439" t="inlineStr">
         <is>
@@ -96065,197 +96065,197 @@
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="I439" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J439" t="n">
         <v>0</v>
       </c>
       <c r="K439" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L439" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M439" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N439" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O439" t="inlineStr">
         <is>
-          <t>['28', '73']</t>
+          <t>['90+5']</t>
         </is>
       </c>
       <c r="P439" t="inlineStr">
         <is>
-          <t>['70']</t>
+          <t>['74', '77', '90+2']</t>
         </is>
       </c>
       <c r="Q439" t="n">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="R439" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S439" t="n">
-        <v>3.99</v>
+        <v>4.4</v>
       </c>
       <c r="T439" t="n">
         <v>1.31</v>
       </c>
       <c r="U439" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="V439" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="W439" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="X439" t="n">
-        <v>5.6</v>
+        <v>5.25</v>
       </c>
       <c r="Y439" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z439" t="n">
-        <v>1.99</v>
+        <v>1.84</v>
       </c>
       <c r="AA439" t="n">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="AB439" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="AC439" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AD439" t="n">
         <v>10</v>
       </c>
       <c r="AE439" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AF439" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AG439" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AH439" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AI439" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AJ439" t="n">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="AK439" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AL439" t="n">
         <v>1.26</v>
       </c>
-      <c r="AL439" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AM439" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AN439" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AO439" t="n">
-        <v>0.5</v>
+        <v>1.86</v>
       </c>
       <c r="AP439" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AQ439" t="n">
-        <v>0.63</v>
+        <v>1.93</v>
       </c>
       <c r="AR439" t="n">
-        <v>1.41</v>
+        <v>1.56</v>
       </c>
       <c r="AS439" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AT439" t="n">
-        <v>2.52</v>
+        <v>2.81</v>
       </c>
       <c r="AU439" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="AV439" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW439" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX439" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY439" t="n">
+        <v>28</v>
+      </c>
+      <c r="AZ439" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA439" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB439" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC439" t="n">
         <v>10</v>
       </c>
-      <c r="AX439" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY439" t="n">
-        <v>14</v>
-      </c>
-      <c r="AZ439" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA439" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB439" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC439" t="n">
-        <v>8</v>
-      </c>
       <c r="BD439" t="n">
-        <v>1.87</v>
+        <v>1.35</v>
       </c>
       <c r="BE439" t="n">
-        <v>6.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF439" t="n">
-        <v>2.39</v>
+        <v>3.54</v>
       </c>
       <c r="BG439" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BH439" t="n">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="BI439" t="n">
         <v>1.47</v>
       </c>
       <c r="BJ439" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="BK439" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="BL439" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="BM439" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="BN439" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="BO439" t="n">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="BP439" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="440">
@@ -96398,7 +96398,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ440" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR440" t="n">
         <v>1.46</v>
@@ -97509,13 +97509,13 @@
         <v>11</v>
       </c>
       <c r="AX445" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY445" t="n">
         <v>17</v>
       </c>
       <c r="AZ445" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA445" t="n">
         <v>4</v>
@@ -97789,7 +97789,7 @@
         <v>446</v>
       </c>
       <c r="B447" t="n">
-        <v>8229565</v>
+        <v>8229515</v>
       </c>
       <c r="C447" t="inlineStr">
         <is>
@@ -97809,197 +97809,197 @@
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="I447" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J447" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K447" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L447" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M447" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N447" t="n">
         <v>2</v>
       </c>
       <c r="O447" t="inlineStr">
         <is>
-          <t>['16']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P447" t="inlineStr">
         <is>
-          <t>['51']</t>
+          <t>['23', '29']</t>
         </is>
       </c>
       <c r="Q447" t="n">
-        <v>1.95</v>
+        <v>3.4</v>
       </c>
       <c r="R447" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="S447" t="n">
-        <v>4.95</v>
+        <v>2.78</v>
       </c>
       <c r="T447" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U447" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="V447" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="W447" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X447" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y447" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z447" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AA447" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB447" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC447" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD447" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE447" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF447" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AG447" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH447" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI447" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ447" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AK447" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AL447" t="n">
         <v>1.25</v>
       </c>
-      <c r="U447" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="V447" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="W447" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="X447" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="Y447" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z447" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AA447" t="n">
-        <v>4.54</v>
-      </c>
-      <c r="AB447" t="n">
-        <v>5.57</v>
-      </c>
-      <c r="AC447" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AD447" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE447" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF447" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AG447" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH447" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AI447" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AJ447" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK447" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AL447" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AM447" t="n">
-        <v>2.5</v>
+        <v>1.31</v>
       </c>
       <c r="AN447" t="n">
-        <v>1.87</v>
+        <v>0.73</v>
       </c>
       <c r="AO447" t="n">
-        <v>1</v>
+        <v>0.47</v>
       </c>
       <c r="AP447" t="n">
-        <v>1.81</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ447" t="n">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="AR447" t="n">
-        <v>1.75</v>
+        <v>1.32</v>
       </c>
       <c r="AS447" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AT447" t="n">
-        <v>2.82</v>
+        <v>2.44</v>
       </c>
       <c r="AU447" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AV447" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AW447" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AX447" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AY447" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ447" t="n">
         <v>12</v>
       </c>
-      <c r="AZ447" t="n">
-        <v>4</v>
-      </c>
       <c r="BA447" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BB447" t="n">
         <v>3</v>
       </c>
       <c r="BC447" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BD447" t="n">
-        <v>1.29</v>
+        <v>2.18</v>
       </c>
       <c r="BE447" t="n">
-        <v>9.699999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="BF447" t="n">
-        <v>4</v>
+        <v>2.12</v>
       </c>
       <c r="BG447" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="BH447" t="n">
-        <v>2.6</v>
+        <v>2.49</v>
       </c>
       <c r="BI447" t="n">
-        <v>1.68</v>
+        <v>1.88</v>
       </c>
       <c r="BJ447" t="n">
-        <v>2.04</v>
+        <v>1.92</v>
       </c>
       <c r="BK447" t="n">
-        <v>2.63</v>
+        <v>2.52</v>
       </c>
       <c r="BL447" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="BM447" t="n">
-        <v>2.75</v>
+        <v>3.28</v>
       </c>
       <c r="BN447" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="BO447" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BP447" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="448">
@@ -98225,7 +98225,7 @@
         <v>448</v>
       </c>
       <c r="B449" t="n">
-        <v>8229515</v>
+        <v>8229565</v>
       </c>
       <c r="C449" t="inlineStr">
         <is>
@@ -98245,197 +98245,197 @@
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="I449" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J449" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K449" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L449" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M449" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N449" t="n">
         <v>2</v>
       </c>
       <c r="O449" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['16']</t>
         </is>
       </c>
       <c r="P449" t="inlineStr">
         <is>
-          <t>['23', '29']</t>
+          <t>['51']</t>
         </is>
       </c>
       <c r="Q449" t="n">
-        <v>3.4</v>
+        <v>1.95</v>
       </c>
       <c r="R449" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="S449" t="n">
-        <v>2.78</v>
+        <v>4.95</v>
       </c>
       <c r="T449" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="U449" t="n">
-        <v>3.38</v>
+        <v>3.55</v>
       </c>
       <c r="V449" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="W449" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="X449" t="n">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="Y449" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z449" t="n">
-        <v>3.15</v>
+        <v>1.56</v>
       </c>
       <c r="AA449" t="n">
-        <v>3.45</v>
+        <v>4.54</v>
       </c>
       <c r="AB449" t="n">
-        <v>2.05</v>
+        <v>5.57</v>
       </c>
       <c r="AC449" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AD449" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE449" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF449" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AG449" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH449" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AI449" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AJ449" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK449" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL449" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AM449" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AN449" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AO449" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP449" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AQ449" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR449" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS449" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AT449" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AU449" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV449" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW449" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX449" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY449" t="n">
         <v>12</v>
       </c>
-      <c r="AE449" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF449" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AG449" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AH449" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AI449" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AJ449" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AK449" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AL449" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AM449" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN449" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="AO449" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="AP449" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="AQ449" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="AR449" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AS449" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AT449" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AU449" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV449" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW449" t="n">
-        <v>13</v>
-      </c>
-      <c r="AX449" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY449" t="n">
-        <v>19</v>
-      </c>
       <c r="AZ449" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="BA449" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BB449" t="n">
         <v>3</v>
       </c>
       <c r="BC449" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BD449" t="n">
-        <v>2.18</v>
+        <v>1.29</v>
       </c>
       <c r="BE449" t="n">
-        <v>6.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="BF449" t="n">
-        <v>2.12</v>
+        <v>4</v>
       </c>
       <c r="BG449" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="BH449" t="n">
-        <v>2.49</v>
+        <v>2.6</v>
       </c>
       <c r="BI449" t="n">
-        <v>1.88</v>
+        <v>1.68</v>
       </c>
       <c r="BJ449" t="n">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="BK449" t="n">
-        <v>2.52</v>
+        <v>2.63</v>
       </c>
       <c r="BL449" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="BM449" t="n">
-        <v>3.28</v>
+        <v>2.75</v>
       </c>
       <c r="BN449" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="BO449" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="BP449" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="450">
@@ -98817,13 +98817,13 @@
         <v>10</v>
       </c>
       <c r="AX451" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY451" t="n">
         <v>17</v>
       </c>
       <c r="AZ451" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA451" t="n">
         <v>9</v>
@@ -98879,7 +98879,7 @@
         <v>451</v>
       </c>
       <c r="B452" t="n">
-        <v>8229567</v>
+        <v>8229523</v>
       </c>
       <c r="C452" t="inlineStr">
         <is>
@@ -98899,12 +98899,12 @@
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="I452" t="n">
@@ -98920,10 +98920,10 @@
         <v>0</v>
       </c>
       <c r="M452" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N452" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O452" t="inlineStr">
         <is>
@@ -98932,164 +98932,164 @@
       </c>
       <c r="P452" t="inlineStr">
         <is>
-          <t>['26', '41', '70']</t>
+          <t>['2', '42']</t>
         </is>
       </c>
       <c r="Q452" t="n">
-        <v>2.61</v>
+        <v>3.89</v>
       </c>
       <c r="R452" t="n">
         <v>2.5</v>
       </c>
       <c r="S452" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="T452" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="U452" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="V452" t="n">
-        <v>2.32</v>
+        <v>2.02</v>
       </c>
       <c r="W452" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="X452" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="Y452" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="Z452" t="n">
-        <v>2.15</v>
+        <v>2.94</v>
       </c>
       <c r="AA452" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AB452" t="n">
-        <v>2.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC452" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AD452" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="AE452" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AF452" t="n">
-        <v>5.16</v>
+        <v>5.25</v>
       </c>
       <c r="AG452" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="AH452" t="n">
-        <v>2.46</v>
+        <v>2.7</v>
       </c>
       <c r="AI452" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="AJ452" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="AK452" t="n">
-        <v>1.29</v>
+        <v>1.9</v>
       </c>
       <c r="AL452" t="n">
         <v>1.25</v>
       </c>
       <c r="AM452" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="AN452" t="n">
-        <v>1.67</v>
+        <v>1.07</v>
       </c>
       <c r="AO452" t="n">
         <v>1.57</v>
       </c>
       <c r="AP452" t="n">
-        <v>1.56</v>
+        <v>1</v>
       </c>
       <c r="AQ452" t="n">
         <v>1.67</v>
       </c>
       <c r="AR452" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AS452" t="n">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AT452" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="AU452" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV452" t="n">
         <v>4</v>
       </c>
-      <c r="AV452" t="n">
+      <c r="AW452" t="n">
         <v>9</v>
       </c>
-      <c r="AW452" t="n">
+      <c r="AX452" t="n">
         <v>8</v>
       </c>
-      <c r="AX452" t="n">
+      <c r="AY452" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ452" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA452" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB452" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC452" t="n">
         <v>9</v>
       </c>
-      <c r="AY452" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ452" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA452" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB452" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC452" t="n">
-        <v>11</v>
-      </c>
       <c r="BD452" t="n">
-        <v>1.74</v>
+        <v>2.2</v>
       </c>
       <c r="BE452" t="n">
         <v>7</v>
       </c>
       <c r="BF452" t="n">
-        <v>3.15</v>
+        <v>2.1</v>
       </c>
       <c r="BG452" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="BH452" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="BI452" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="BJ452" t="n">
-        <v>2.57</v>
+        <v>3</v>
       </c>
       <c r="BK452" t="n">
-        <v>2.02</v>
+        <v>1.56</v>
       </c>
       <c r="BL452" t="n">
-        <v>1.99</v>
+        <v>2.23</v>
       </c>
       <c r="BM452" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="BN452" t="n">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="BO452" t="n">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="BP452" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="453">
@@ -99097,7 +99097,7 @@
         <v>452</v>
       </c>
       <c r="B453" t="n">
-        <v>8229523</v>
+        <v>8229567</v>
       </c>
       <c r="C453" t="inlineStr">
         <is>
@@ -99117,12 +99117,12 @@
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="I453" t="n">
@@ -99138,10 +99138,10 @@
         <v>0</v>
       </c>
       <c r="M453" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N453" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O453" t="inlineStr">
         <is>
@@ -99150,164 +99150,164 @@
       </c>
       <c r="P453" t="inlineStr">
         <is>
-          <t>['2', '42']</t>
+          <t>['26', '41', '70']</t>
         </is>
       </c>
       <c r="Q453" t="n">
-        <v>3.89</v>
+        <v>2.61</v>
       </c>
       <c r="R453" t="n">
         <v>2.5</v>
       </c>
       <c r="S453" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="T453" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="U453" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="V453" t="n">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="W453" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="X453" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="Y453" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="Z453" t="n">
-        <v>2.94</v>
+        <v>2.15</v>
       </c>
       <c r="AA453" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AB453" t="n">
-        <v>1.85</v>
+        <v>2.8</v>
       </c>
       <c r="AC453" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AD453" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="AE453" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AF453" t="n">
-        <v>5.25</v>
+        <v>5.16</v>
       </c>
       <c r="AG453" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="AH453" t="n">
-        <v>2.7</v>
+        <v>2.46</v>
       </c>
       <c r="AI453" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="AJ453" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="AK453" t="n">
-        <v>1.9</v>
+        <v>1.29</v>
       </c>
       <c r="AL453" t="n">
         <v>1.25</v>
       </c>
       <c r="AM453" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="AN453" t="n">
-        <v>1.07</v>
+        <v>1.67</v>
       </c>
       <c r="AO453" t="n">
         <v>1.57</v>
       </c>
       <c r="AP453" t="n">
-        <v>1</v>
+        <v>1.56</v>
       </c>
       <c r="AQ453" t="n">
         <v>1.67</v>
       </c>
       <c r="AR453" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AS453" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AT453" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="AU453" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AV453" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AW453" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX453" t="n">
         <v>9</v>
       </c>
-      <c r="AX453" t="n">
-        <v>8</v>
-      </c>
       <c r="AY453" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AZ453" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="BA453" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BB453" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BC453" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BD453" t="n">
-        <v>2.2</v>
+        <v>1.74</v>
       </c>
       <c r="BE453" t="n">
         <v>7</v>
       </c>
       <c r="BF453" t="n">
-        <v>2.1</v>
+        <v>3.15</v>
       </c>
       <c r="BG453" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="BH453" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="BI453" t="n">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="BJ453" t="n">
-        <v>3</v>
+        <v>2.57</v>
       </c>
       <c r="BK453" t="n">
-        <v>1.56</v>
+        <v>2.02</v>
       </c>
       <c r="BL453" t="n">
-        <v>2.23</v>
+        <v>1.99</v>
       </c>
       <c r="BM453" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="BN453" t="n">
-        <v>1.78</v>
+        <v>1.66</v>
       </c>
       <c r="BO453" t="n">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="BP453" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="454">
@@ -99315,7 +99315,7 @@
         <v>453</v>
       </c>
       <c r="B454" t="n">
-        <v>8229543</v>
+        <v>8229531</v>
       </c>
       <c r="C454" t="inlineStr">
         <is>
@@ -99335,197 +99335,197 @@
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="I454" t="n">
         <v>1</v>
       </c>
       <c r="J454" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K454" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L454" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M454" t="n">
         <v>3</v>
       </c>
       <c r="N454" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O454" t="inlineStr">
         <is>
-          <t>['39', '90+1']</t>
+          <t>['31']</t>
         </is>
       </c>
       <c r="P454" t="inlineStr">
         <is>
-          <t>['10', '22', '88']</t>
+          <t>['10', '19', '45']</t>
         </is>
       </c>
       <c r="Q454" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="R454" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S454" t="n">
+        <v>4</v>
+      </c>
+      <c r="T454" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="U454" t="n">
+        <v>4</v>
+      </c>
+      <c r="V454" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="W454" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="X454" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Y454" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z454" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AA454" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="AB454" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AC454" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD454" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE454" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AF454" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG454" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH454" t="n">
         <v>3.1</v>
       </c>
-      <c r="R454" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="S454" t="n">
+      <c r="AI454" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AJ454" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AK454" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AL454" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AM454" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN454" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO454" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AP454" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AQ454" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AR454" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AS454" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AT454" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AU454" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV454" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW454" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX454" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY454" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ454" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA454" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB454" t="n">
         <v>3</v>
       </c>
-      <c r="T454" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="U454" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="V454" t="n">
+      <c r="BC454" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD454" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BE454" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BF454" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BG454" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BH454" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BI454" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BJ454" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BK454" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BL454" t="n">
         <v>2.35</v>
       </c>
-      <c r="W454" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="X454" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="Y454" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z454" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AA454" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AB454" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AC454" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AD454" t="n">
-        <v>10</v>
-      </c>
-      <c r="AE454" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF454" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AG454" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AH454" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AI454" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AJ454" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AK454" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AL454" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AM454" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AN454" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AO454" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AP454" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ454" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR454" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AS454" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AT454" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AU454" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV454" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW454" t="n">
-        <v>15</v>
-      </c>
-      <c r="AX454" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY454" t="n">
-        <v>23</v>
-      </c>
-      <c r="AZ454" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA454" t="n">
-        <v>9</v>
-      </c>
-      <c r="BB454" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC454" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD454" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BE454" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="BF454" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="BG454" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BH454" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="BI454" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="BJ454" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BK454" t="n">
+      <c r="BM454" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BN454" t="n">
         <v>1.85</v>
       </c>
-      <c r="BL454" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BM454" t="n">
+      <c r="BO454" t="n">
         <v>2.28</v>
       </c>
-      <c r="BN454" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="BO454" t="n">
-        <v>2.95</v>
-      </c>
       <c r="BP454" t="n">
-        <v>1.34</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="455">
@@ -99533,7 +99533,7 @@
         <v>454</v>
       </c>
       <c r="B455" t="n">
-        <v>8229531</v>
+        <v>8229543</v>
       </c>
       <c r="C455" t="inlineStr">
         <is>
@@ -99553,197 +99553,633 @@
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="I455" t="n">
         <v>1</v>
       </c>
       <c r="J455" t="n">
+        <v>2</v>
+      </c>
+      <c r="K455" t="n">
         <v>3</v>
       </c>
-      <c r="K455" t="n">
-        <v>4</v>
-      </c>
       <c r="L455" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M455" t="n">
         <v>3</v>
       </c>
       <c r="N455" t="n">
+        <v>5</v>
+      </c>
+      <c r="O455" t="inlineStr">
+        <is>
+          <t>['39', '90+1']</t>
+        </is>
+      </c>
+      <c r="P455" t="inlineStr">
+        <is>
+          <t>['10', '22', '88']</t>
+        </is>
+      </c>
+      <c r="Q455" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R455" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S455" t="n">
+        <v>3</v>
+      </c>
+      <c r="T455" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U455" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="V455" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="W455" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X455" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Y455" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z455" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA455" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB455" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AC455" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD455" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE455" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF455" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AG455" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH455" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AI455" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ455" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AK455" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AL455" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM455" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN455" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AO455" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AP455" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ455" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR455" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AS455" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AT455" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AU455" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV455" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW455" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX455" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY455" t="n">
+        <v>23</v>
+      </c>
+      <c r="AZ455" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA455" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB455" t="n">
         <v>4</v>
       </c>
-      <c r="O455" t="inlineStr">
-        <is>
-          <t>['31']</t>
-        </is>
-      </c>
-      <c r="P455" t="inlineStr">
-        <is>
-          <t>['10', '19', '45']</t>
-        </is>
-      </c>
-      <c r="Q455" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="R455" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S455" t="n">
+      <c r="BC455" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD455" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BE455" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="BF455" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BG455" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BH455" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BI455" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BJ455" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BK455" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BL455" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BM455" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BN455" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BO455" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BP455" t="n">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="1" t="n">
+        <v>455</v>
+      </c>
+      <c r="B456" t="n">
+        <v>8229507</v>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E456" s="2" t="n">
+        <v>45921.83333333334</v>
+      </c>
+      <c r="F456" t="n">
+        <v>0</v>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>Seattle Sounders</t>
+        </is>
+      </c>
+      <c r="I456" t="n">
+        <v>1</v>
+      </c>
+      <c r="J456" t="n">
+        <v>0</v>
+      </c>
+      <c r="K456" t="n">
+        <v>1</v>
+      </c>
+      <c r="L456" t="n">
+        <v>2</v>
+      </c>
+      <c r="M456" t="n">
+        <v>1</v>
+      </c>
+      <c r="N456" t="n">
+        <v>3</v>
+      </c>
+      <c r="O456" t="inlineStr">
+        <is>
+          <t>['42', '90+6']</t>
+        </is>
+      </c>
+      <c r="P456" t="inlineStr">
+        <is>
+          <t>['46']</t>
+        </is>
+      </c>
+      <c r="Q456" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R456" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="S456" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T456" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="U456" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V456" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="W456" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X456" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y456" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z456" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AA456" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AB456" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AC456" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD456" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE456" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AF456" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="AG456" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AH456" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AI456" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AJ456" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AK456" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AL456" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM456" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN456" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AO456" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AP456" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ456" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR456" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AS456" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AT456" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AU456" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV456" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW456" t="n">
         <v>4</v>
       </c>
-      <c r="T455" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="U455" t="n">
+      <c r="AX456" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY456" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ456" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA456" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB456" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC456" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD456" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BE456" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF456" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BG456" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH456" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI456" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BJ456" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BK456" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BL456" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BM456" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BN456" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BO456" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BP456" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="1" t="n">
+        <v>456</v>
+      </c>
+      <c r="B457" t="n">
+        <v>8229556</v>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E457" s="2" t="n">
+        <v>45921.91666666666</v>
+      </c>
+      <c r="F457" t="n">
+        <v>0</v>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>Los Angeles FC</t>
+        </is>
+      </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="I457" t="n">
+        <v>2</v>
+      </c>
+      <c r="J457" t="n">
+        <v>1</v>
+      </c>
+      <c r="K457" t="n">
+        <v>3</v>
+      </c>
+      <c r="L457" t="n">
         <v>4</v>
       </c>
-      <c r="V455" t="n">
+      <c r="M457" t="n">
+        <v>1</v>
+      </c>
+      <c r="N457" t="n">
+        <v>5</v>
+      </c>
+      <c r="O457" t="inlineStr">
+        <is>
+          <t>['45+1', '45+3', '73', '87']</t>
+        </is>
+      </c>
+      <c r="P457" t="inlineStr">
+        <is>
+          <t>['14']</t>
+        </is>
+      </c>
+      <c r="Q457" t="n">
         <v>1.85</v>
       </c>
-      <c r="W455" t="n">
+      <c r="R457" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S457" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="T457" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U457" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V457" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="W457" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X457" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Y457" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z457" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA457" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB457" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AC457" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD457" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE457" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AF457" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="AG457" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AH457" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AI457" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AJ457" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AK457" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL457" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AM457" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AN457" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AO457" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AP457" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AQ457" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AR457" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS457" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AT457" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU457" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV457" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW457" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX457" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY457" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ457" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA457" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB457" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC457" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD457" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BE457" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="BF457" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BG457" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BH457" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI457" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ457" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="BK457" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BL457" t="n">
         <v>1.9</v>
       </c>
-      <c r="X455" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="Y455" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z455" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AA455" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="AB455" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AC455" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AD455" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE455" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AF455" t="n">
-        <v>7</v>
-      </c>
-      <c r="AG455" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH455" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AI455" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AJ455" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AK455" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AL455" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AM455" t="n">
-        <v>2</v>
-      </c>
-      <c r="AN455" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AO455" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="AP455" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AQ455" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="AR455" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AS455" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AT455" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AU455" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV455" t="n">
-        <v>7</v>
-      </c>
-      <c r="AW455" t="n">
-        <v>11</v>
-      </c>
-      <c r="AX455" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY455" t="n">
-        <v>21</v>
-      </c>
-      <c r="AZ455" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA455" t="n">
-        <v>11</v>
-      </c>
-      <c r="BB455" t="n">
-        <v>3</v>
-      </c>
-      <c r="BC455" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD455" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="BE455" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="BF455" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BG455" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BH455" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BI455" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BJ455" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BK455" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="BL455" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="BM455" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BN455" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BO455" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BP455" t="n">
-        <v>1.55</v>
+      <c r="BM457" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BN457" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BO457" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BP457" t="n">
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP457"/>
+  <dimension ref="A1:BP459"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7015,7 +7015,7 @@
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AQ30" t="n">
         <v>0.44</v>
@@ -7236,7 +7236,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR31" t="n">
         <v>1.32</v>
@@ -7887,7 +7887,7 @@
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ34" t="n">
         <v>1.6</v>
@@ -9198,7 +9198,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR40" t="n">
         <v>1.46</v>
@@ -9631,7 +9631,7 @@
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AQ42" t="n">
         <v>0.87</v>
@@ -11593,7 +11593,7 @@
         <v>1</v>
       </c>
       <c r="AP51" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ51" t="n">
         <v>1.25</v>
@@ -13776,7 +13776,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ61" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR61" t="n">
         <v>1.51</v>
@@ -16174,7 +16174,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ72" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR72" t="n">
         <v>1.81</v>
@@ -16607,7 +16607,7 @@
         <v>2</v>
       </c>
       <c r="AP74" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AQ74" t="n">
         <v>1.67</v>
@@ -21842,7 +21842,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR98" t="n">
         <v>1.51</v>
@@ -22493,7 +22493,7 @@
         <v>2.33</v>
       </c>
       <c r="AP101" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AQ101" t="n">
         <v>0.8100000000000001</v>
@@ -22929,7 +22929,7 @@
         <v>1.33</v>
       </c>
       <c r="AP103" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ103" t="n">
         <v>1.93</v>
@@ -24237,7 +24237,7 @@
         <v>2</v>
       </c>
       <c r="AP109" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ109" t="n">
         <v>1.53</v>
@@ -24673,7 +24673,7 @@
         <v>2</v>
       </c>
       <c r="AP111" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AQ111" t="n">
         <v>1.27</v>
@@ -26202,7 +26202,7 @@
         <v>1</v>
       </c>
       <c r="AQ118" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR118" t="n">
         <v>1.59</v>
@@ -26420,7 +26420,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ119" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR119" t="n">
         <v>0.97</v>
@@ -27074,7 +27074,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ122" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR122" t="n">
         <v>1.7</v>
@@ -33178,7 +33178,7 @@
         <v>1</v>
       </c>
       <c r="AQ150" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR150" t="n">
         <v>1.33</v>
@@ -35355,7 +35355,7 @@
         <v>1.2</v>
       </c>
       <c r="AP160" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AQ160" t="n">
         <v>0.8</v>
@@ -35576,7 +35576,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ161" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR161" t="n">
         <v>2.02</v>
@@ -36227,7 +36227,7 @@
         <v>1.8</v>
       </c>
       <c r="AP164" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ164" t="n">
         <v>2</v>
@@ -37102,7 +37102,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ168" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR168" t="n">
         <v>1.61</v>
@@ -37753,7 +37753,7 @@
         <v>0.25</v>
       </c>
       <c r="AP171" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ171" t="n">
         <v>0.87</v>
@@ -39715,7 +39715,7 @@
         <v>0.8</v>
       </c>
       <c r="AP180" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AQ180" t="n">
         <v>1.5</v>
@@ -41898,7 +41898,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ190" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR190" t="n">
         <v>1.39</v>
@@ -42116,7 +42116,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ191" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR191" t="n">
         <v>1.99</v>
@@ -42985,7 +42985,7 @@
         <v>0.33</v>
       </c>
       <c r="AP195" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ195" t="n">
         <v>0.63</v>
@@ -46694,7 +46694,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ212" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR212" t="n">
         <v>1.7</v>
@@ -47348,7 +47348,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ215" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR215" t="n">
         <v>1.71</v>
@@ -48871,7 +48871,7 @@
         <v>1.71</v>
       </c>
       <c r="AP222" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ222" t="n">
         <v>1.67</v>
@@ -50615,7 +50615,7 @@
         <v>1</v>
       </c>
       <c r="AP230" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ230" t="n">
         <v>1.2</v>
@@ -51705,7 +51705,7 @@
         <v>1.57</v>
       </c>
       <c r="AP235" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AQ235" t="n">
         <v>1.93</v>
@@ -55629,7 +55629,7 @@
         <v>1</v>
       </c>
       <c r="AP253" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AQ253" t="n">
         <v>1</v>
@@ -56065,7 +56065,7 @@
         <v>0.29</v>
       </c>
       <c r="AP255" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ255" t="n">
         <v>0.57</v>
@@ -61079,7 +61079,7 @@
         <v>1.5</v>
       </c>
       <c r="AP278" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AQ278" t="n">
         <v>2.07</v>
@@ -62390,7 +62390,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ284" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR284" t="n">
         <v>1.12</v>
@@ -64349,7 +64349,7 @@
         <v>1.14</v>
       </c>
       <c r="AP293" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ293" t="n">
         <v>1</v>
@@ -65442,7 +65442,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ298" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR298" t="n">
         <v>1.22</v>
@@ -67404,7 +67404,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ307" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR307" t="n">
         <v>1.15</v>
@@ -70892,7 +70892,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ323" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR323" t="n">
         <v>1.55</v>
@@ -71110,7 +71110,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ324" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR324" t="n">
         <v>1.5</v>
@@ -75034,7 +75034,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ342" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR342" t="n">
         <v>1.43</v>
@@ -77868,7 +77868,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ355" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR355" t="n">
         <v>1.86</v>
@@ -80045,7 +80045,7 @@
         <v>1</v>
       </c>
       <c r="AP365" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AQ365" t="n">
         <v>0.73</v>
@@ -81574,7 +81574,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ372" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR372" t="n">
         <v>1.24</v>
@@ -82882,7 +82882,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ378" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR378" t="n">
         <v>1.71</v>
@@ -85931,7 +85931,7 @@
         <v>1.31</v>
       </c>
       <c r="AP392" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ392" t="n">
         <v>1.06</v>
@@ -86367,7 +86367,7 @@
         <v>1.17</v>
       </c>
       <c r="AP394" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AQ394" t="n">
         <v>1.2</v>
@@ -87460,7 +87460,7 @@
         <v>0.87</v>
       </c>
       <c r="AQ399" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR399" t="n">
         <v>1.18</v>
@@ -88329,7 +88329,7 @@
         <v>0.38</v>
       </c>
       <c r="AP403" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AQ403" t="n">
         <v>0.6899999999999999</v>
@@ -88768,7 +88768,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ405" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR405" t="n">
         <v>1.59</v>
@@ -90727,7 +90727,7 @@
         <v>0.64</v>
       </c>
       <c r="AP414" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ414" t="n">
         <v>0.75</v>
@@ -91820,7 +91820,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ419" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR419" t="n">
         <v>1.54</v>
@@ -93346,7 +93346,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ426" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR426" t="n">
         <v>1.35</v>
@@ -95741,7 +95741,7 @@
         <v>1.64</v>
       </c>
       <c r="AP437" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AQ437" t="n">
         <v>1.53</v>
@@ -96613,7 +96613,7 @@
         <v>1.5</v>
       </c>
       <c r="AP441" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ441" t="n">
         <v>1.4</v>
@@ -97049,7 +97049,7 @@
         <v>1.07</v>
       </c>
       <c r="AP443" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ443" t="n">
         <v>1</v>
@@ -98578,7 +98578,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ450" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR450" t="n">
         <v>1.48</v>
@@ -100180,6 +100180,442 @@
       </c>
       <c r="BP457" t="n">
         <v>1.34</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="1" t="n">
+        <v>457</v>
+      </c>
+      <c r="B458" t="n">
+        <v>8229518</v>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E458" s="2" t="n">
+        <v>45924.85416666666</v>
+      </c>
+      <c r="F458" t="n">
+        <v>0</v>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>Inter Miami</t>
+        </is>
+      </c>
+      <c r="I458" t="n">
+        <v>0</v>
+      </c>
+      <c r="J458" t="n">
+        <v>1</v>
+      </c>
+      <c r="K458" t="n">
+        <v>1</v>
+      </c>
+      <c r="L458" t="n">
+        <v>0</v>
+      </c>
+      <c r="M458" t="n">
+        <v>4</v>
+      </c>
+      <c r="N458" t="n">
+        <v>4</v>
+      </c>
+      <c r="O458" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P458" t="inlineStr">
+        <is>
+          <t>['43', '74', '83', '86']</t>
+        </is>
+      </c>
+      <c r="Q458" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R458" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S458" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T458" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U458" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="V458" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="W458" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="X458" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Y458" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z458" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AA458" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB458" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC458" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD458" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE458" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF458" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG458" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AH458" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AI458" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AJ458" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AK458" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL458" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AM458" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AN458" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AO458" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AP458" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AQ458" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AR458" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AS458" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AT458" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AU458" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV458" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW458" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX458" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY458" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ458" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA458" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB458" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC458" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD458" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BE458" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF458" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="BG458" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BH458" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI458" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ458" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BK458" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BL458" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BM458" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BN458" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BO458" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BP458" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="1" t="n">
+        <v>458</v>
+      </c>
+      <c r="B459" t="n">
+        <v>8229550</v>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E459" s="2" t="n">
+        <v>45924.97916666666</v>
+      </c>
+      <c r="F459" t="n">
+        <v>0</v>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>Portland Timbers</t>
+        </is>
+      </c>
+      <c r="I459" t="n">
+        <v>0</v>
+      </c>
+      <c r="J459" t="n">
+        <v>1</v>
+      </c>
+      <c r="K459" t="n">
+        <v>1</v>
+      </c>
+      <c r="L459" t="n">
+        <v>1</v>
+      </c>
+      <c r="M459" t="n">
+        <v>1</v>
+      </c>
+      <c r="N459" t="n">
+        <v>2</v>
+      </c>
+      <c r="O459" t="inlineStr">
+        <is>
+          <t>['88']</t>
+        </is>
+      </c>
+      <c r="P459" t="inlineStr">
+        <is>
+          <t>['39']</t>
+        </is>
+      </c>
+      <c r="Q459" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="R459" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="S459" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="T459" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U459" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="V459" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="W459" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X459" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y459" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z459" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA459" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB459" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AC459" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD459" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE459" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF459" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="AG459" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AH459" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AI459" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AJ459" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AK459" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AL459" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AM459" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AN459" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AO459" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AP459" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AQ459" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AR459" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AS459" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AT459" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AU459" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV459" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW459" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX459" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY459" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ459" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA459" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB459" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC459" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD459" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BE459" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF459" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BG459" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH459" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BI459" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ459" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BK459" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BL459" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BM459" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BN459" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BO459" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BP459" t="n">
+        <v>1.35</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP473"/>
+  <dimension ref="A1:BP474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AQ3" t="n">
         <v>0.63</v>
@@ -7890,7 +7890,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AR34" t="n">
         <v>0</v>
@@ -8105,7 +8105,7 @@
         <v>0.5</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AQ35" t="n">
         <v>1</v>
@@ -10942,7 +10942,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ48" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AR48" t="n">
         <v>1.31</v>
@@ -13991,7 +13991,7 @@
         <v>0</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AQ62" t="n">
         <v>0.53</v>
@@ -19444,7 +19444,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ87" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AR87" t="n">
         <v>1.67</v>
@@ -20967,7 +20967,7 @@
         <v>0.5</v>
       </c>
       <c r="AP94" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AQ94" t="n">
         <v>1.25</v>
@@ -21406,7 +21406,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ96" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AR96" t="n">
         <v>1.79</v>
@@ -27292,7 +27292,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ123" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AR123" t="n">
         <v>1.99</v>
@@ -30123,7 +30123,7 @@
         <v>0.75</v>
       </c>
       <c r="AP136" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AQ136" t="n">
         <v>0.6899999999999999</v>
@@ -34922,7 +34922,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ158" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AR158" t="n">
         <v>1.39</v>
@@ -37971,7 +37971,7 @@
         <v>1.2</v>
       </c>
       <c r="AP172" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AQ172" t="n">
         <v>1.19</v>
@@ -45604,7 +45604,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ207" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AR207" t="n">
         <v>1.38</v>
@@ -49307,7 +49307,7 @@
         <v>1.5</v>
       </c>
       <c r="AP224" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AQ224" t="n">
         <v>1.33</v>
@@ -49528,7 +49528,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ225" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AR225" t="n">
         <v>1.36</v>
@@ -53667,7 +53667,7 @@
         <v>0.71</v>
       </c>
       <c r="AP244" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AQ244" t="n">
         <v>0.75</v>
@@ -58684,7 +58684,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ267" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AR267" t="n">
         <v>1.55</v>
@@ -60210,7 +60210,7 @@
         <v>1.06</v>
       </c>
       <c r="AQ274" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AR274" t="n">
         <v>1.53</v>
@@ -65224,7 +65224,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ297" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AR297" t="n">
         <v>1.51</v>
@@ -65875,7 +65875,7 @@
         <v>1.8</v>
       </c>
       <c r="AP300" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AQ300" t="n">
         <v>1.67</v>
@@ -69799,7 +69799,7 @@
         <v>1.44</v>
       </c>
       <c r="AP318" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AQ318" t="n">
         <v>1.31</v>
@@ -71107,7 +71107,7 @@
         <v>2</v>
       </c>
       <c r="AP324" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AQ324" t="n">
         <v>1.63</v>
@@ -74816,7 +74816,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AQ341" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AR341" t="n">
         <v>1.18</v>
@@ -77432,7 +77432,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ353" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AR353" t="n">
         <v>1.64</v>
@@ -82443,7 +82443,7 @@
         <v>0.77</v>
       </c>
       <c r="AP376" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AQ376" t="n">
         <v>1</v>
@@ -87021,7 +87021,7 @@
         <v>1.08</v>
       </c>
       <c r="AP397" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AQ397" t="n">
         <v>1.44</v>
@@ -87678,7 +87678,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ400" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AR400" t="n">
         <v>1.73</v>
@@ -90073,7 +90073,7 @@
         <v>1.54</v>
       </c>
       <c r="AP411" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AQ411" t="n">
         <v>1.63</v>
@@ -93125,7 +93125,7 @@
         <v>1.21</v>
       </c>
       <c r="AP425" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AQ425" t="n">
         <v>1.06</v>
@@ -93564,7 +93564,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="AQ427" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AR427" t="n">
         <v>1.18</v>
@@ -102302,13 +102302,13 @@
         <v>1</v>
       </c>
       <c r="AW467" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX467" t="n">
         <v>6</v>
       </c>
       <c r="AY467" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ467" t="n">
         <v>7</v>
@@ -103667,6 +103667,224 @@
         <v>2.71</v>
       </c>
       <c r="BP473" t="n">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="1" t="n">
+        <v>473</v>
+      </c>
+      <c r="B474" t="n">
+        <v>8229547</v>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E474" s="2" t="n">
+        <v>45928.83333333334</v>
+      </c>
+      <c r="F474" t="n">
+        <v>0</v>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>FC Cincinnati</t>
+        </is>
+      </c>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>Orlando City</t>
+        </is>
+      </c>
+      <c r="I474" t="n">
+        <v>0</v>
+      </c>
+      <c r="J474" t="n">
+        <v>0</v>
+      </c>
+      <c r="K474" t="n">
+        <v>0</v>
+      </c>
+      <c r="L474" t="n">
+        <v>1</v>
+      </c>
+      <c r="M474" t="n">
+        <v>1</v>
+      </c>
+      <c r="N474" t="n">
+        <v>2</v>
+      </c>
+      <c r="O474" t="inlineStr">
+        <is>
+          <t>['73']</t>
+        </is>
+      </c>
+      <c r="P474" t="inlineStr">
+        <is>
+          <t>['90+5']</t>
+        </is>
+      </c>
+      <c r="Q474" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R474" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="S474" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="T474" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U474" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="V474" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W474" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="X474" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Y474" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z474" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA474" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB474" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC474" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD474" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE474" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF474" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="AG474" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AH474" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AI474" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AJ474" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AK474" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AL474" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM474" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AN474" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO474" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AP474" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AQ474" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AR474" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AS474" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AT474" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AU474" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV474" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW474" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX474" t="n">
+        <v>18</v>
+      </c>
+      <c r="AY474" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ474" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA474" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB474" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC474" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD474" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BE474" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF474" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BG474" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BH474" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="BI474" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BJ474" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BK474" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BL474" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BM474" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BN474" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BO474" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BP474" t="n">
         <v>1.37</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP474"/>
+  <dimension ref="A1:BP475"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ4" t="n">
         <v>1.44</v>
@@ -1568,7 +1568,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -8980,7 +8980,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR39" t="n">
         <v>0</v>
@@ -10285,7 +10285,7 @@
         <v>1</v>
       </c>
       <c r="AP45" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ45" t="n">
         <v>1</v>
@@ -10724,7 +10724,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR47" t="n">
         <v>0</v>
@@ -16610,7 +16610,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ74" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR74" t="n">
         <v>1.75</v>
@@ -17697,7 +17697,7 @@
         <v>3</v>
       </c>
       <c r="AP79" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ79" t="n">
         <v>1.63</v>
@@ -20752,7 +20752,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ93" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR93" t="n">
         <v>1.53</v>
@@ -23365,7 +23365,7 @@
         <v>0.25</v>
       </c>
       <c r="AP105" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ105" t="n">
         <v>1</v>
@@ -31870,7 +31870,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ144" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR144" t="n">
         <v>2.01</v>
@@ -32739,7 +32739,7 @@
         <v>1.8</v>
       </c>
       <c r="AP148" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ148" t="n">
         <v>1.33</v>
@@ -34483,7 +34483,7 @@
         <v>0.5</v>
       </c>
       <c r="AP156" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ156" t="n">
         <v>0.63</v>
@@ -43642,7 +43642,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ198" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR198" t="n">
         <v>1.54</v>
@@ -45601,7 +45601,7 @@
         <v>1.17</v>
       </c>
       <c r="AP207" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ207" t="n">
         <v>1.56</v>
@@ -48874,7 +48874,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ222" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR222" t="n">
         <v>1.62</v>
@@ -50397,7 +50397,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP229" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ229" t="n">
         <v>1</v>
@@ -52577,7 +52577,7 @@
         <v>1.71</v>
       </c>
       <c r="AP239" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ239" t="n">
         <v>1.31</v>
@@ -53234,7 +53234,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ242" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR242" t="n">
         <v>1.67</v>
@@ -54978,7 +54978,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="AQ250" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR250" t="n">
         <v>1.18</v>
@@ -65878,7 +65878,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ300" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR300" t="n">
         <v>1.53</v>
@@ -68709,7 +68709,7 @@
         <v>1.7</v>
       </c>
       <c r="AP313" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ313" t="n">
         <v>1.06</v>
@@ -71546,7 +71546,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ326" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR326" t="n">
         <v>1.36</v>
@@ -74380,7 +74380,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ339" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR339" t="n">
         <v>1.26</v>
@@ -78301,7 +78301,7 @@
         <v>1.92</v>
       </c>
       <c r="AP357" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ357" t="n">
         <v>2</v>
@@ -83315,7 +83315,7 @@
         <v>0.38</v>
       </c>
       <c r="AP380" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ380" t="n">
         <v>0.44</v>
@@ -86588,7 +86588,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ395" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR395" t="n">
         <v>1.76</v>
@@ -96395,7 +96395,7 @@
         <v>1.14</v>
       </c>
       <c r="AP440" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ440" t="n">
         <v>1</v>
@@ -97703,7 +97703,7 @@
         <v>0.8</v>
       </c>
       <c r="AP446" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ446" t="n">
         <v>0.75</v>
@@ -99232,7 +99232,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ453" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR453" t="n">
         <v>1.52</v>
@@ -103825,7 +103825,7 @@
         <v>10</v>
       </c>
       <c r="AV474" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW474" t="n">
         <v>8</v>
@@ -103837,7 +103837,7 @@
         <v>18</v>
       </c>
       <c r="AZ474" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA474" t="n">
         <v>2</v>
@@ -103886,6 +103886,224 @@
       </c>
       <c r="BP474" t="n">
         <v>1.37</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="1" t="n">
+        <v>474</v>
+      </c>
+      <c r="B475" t="n">
+        <v>8229813</v>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E475" s="2" t="n">
+        <v>45930.85416666666</v>
+      </c>
+      <c r="F475" t="n">
+        <v>0</v>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>Inter Miami</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>Chicago Fire</t>
+        </is>
+      </c>
+      <c r="I475" t="n">
+        <v>1</v>
+      </c>
+      <c r="J475" t="n">
+        <v>3</v>
+      </c>
+      <c r="K475" t="n">
+        <v>4</v>
+      </c>
+      <c r="L475" t="n">
+        <v>3</v>
+      </c>
+      <c r="M475" t="n">
+        <v>5</v>
+      </c>
+      <c r="N475" t="n">
+        <v>8</v>
+      </c>
+      <c r="O475" t="inlineStr">
+        <is>
+          <t>['39', '57', '74']</t>
+        </is>
+      </c>
+      <c r="P475" t="inlineStr">
+        <is>
+          <t>['11', '31', '43', '80', '83']</t>
+        </is>
+      </c>
+      <c r="Q475" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R475" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="S475" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="T475" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U475" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="V475" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="W475" t="n">
+        <v>2</v>
+      </c>
+      <c r="X475" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y475" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z475" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AA475" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AB475" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC475" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD475" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE475" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF475" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG475" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH475" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AI475" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AJ475" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK475" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AL475" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AM475" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AN475" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AO475" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AP475" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ475" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AR475" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AS475" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AT475" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AU475" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV475" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW475" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX475" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY475" t="n">
+        <v>24</v>
+      </c>
+      <c r="AZ475" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA475" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB475" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC475" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD475" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BE475" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF475" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BG475" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH475" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BI475" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BJ475" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BK475" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BL475" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BM475" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BN475" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BO475" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP475" t="n">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/USA MLS_2025.xlsx
@@ -104040,7 +104040,7 @@
         <v>2.96</v>
       </c>
       <c r="AU475" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV475" t="n">
         <v>6</v>
@@ -104052,7 +104052,7 @@
         <v>5</v>
       </c>
       <c r="AY475" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AZ475" t="n">
         <v>11</v>
